--- a/riftbound_collection.xlsx
+++ b/riftbound_collection.xlsx
@@ -24,6 +24,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deck - Miss Fortune" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deck - Draven" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sim - All Decks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deck - Lucian Purifier" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deck - Sett" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,7 +160,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="87">
+  <fills count="91">
     <fill>
       <patternFill/>
     </fill>
@@ -590,6 +592,26 @@
         <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A0080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A0DAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5E2E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -640,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="852">
+  <cellXfs count="901">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3185,6 +3207,153 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="82" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="88" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="88" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="67" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="68" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="61" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="61" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="90" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="90" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3998,7 +4167,11 @@
           <t>Other friendly units enter ready.</t>
         </is>
       </c>
-      <c r="K8" s="667" t="n"/>
+      <c r="K8" s="428" t="inlineStr">
+        <is>
+          <t>Sett(1)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="57" t="inlineStr">
@@ -4373,7 +4546,7 @@
       </c>
       <c r="K15" s="428" t="inlineStr">
         <is>
-          <t>Voli(2)</t>
+          <t>Voli(2) | Sett(1)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6530,7 @@
       </c>
       <c r="K54" s="428" t="inlineStr">
         <is>
-          <t>Voli SB(2)</t>
+          <t>Voli SB(2) | Sett(1)</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6691,11 @@
           <t>When you play me, ready another unit.</t>
         </is>
       </c>
-      <c r="K57" s="667" t="n"/>
+      <c r="K57" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(1)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="59" t="inlineStr">
@@ -6620,7 +6797,11 @@
           <t>HIDDEN (Hide now for 1 Rune to react with later for 0.)</t>
         </is>
       </c>
-      <c r="K59" s="667" t="n"/>
+      <c r="K59" s="428" t="inlineStr">
+        <is>
+          <t>Sett(2)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="59" t="inlineStr">
@@ -6727,7 +6908,11 @@
 When you play me, channel 1 rune exhausted.</t>
         </is>
       </c>
-      <c r="K61" s="667" t="n"/>
+      <c r="K61" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="59" t="inlineStr">
@@ -7028,7 +7213,11 @@
 As you play this, you may spend a buff as an additional cost. If you do, ignore this spell's cost. Ready a unit.</t>
         </is>
       </c>
-      <c r="K67" s="667" t="n"/>
+      <c r="K67" s="428" t="inlineStr">
+        <is>
+          <t>Sett(2)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="59" t="inlineStr">
@@ -7079,7 +7268,11 @@
           <t>When you play me, you may spend a buff to buff me and ready me. (If I don't have a buff, I get a +1 Might buff.)</t>
         </is>
       </c>
-      <c r="K68" s="667" t="n"/>
+      <c r="K68" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="59" t="inlineStr">
@@ -7185,7 +7378,11 @@
           <t>When you play me, choose an enemy unit at a battlefield. We deal damage equal to our Mights to each other.</t>
         </is>
       </c>
-      <c r="K70" s="667" t="n"/>
+      <c r="K70" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="59" t="inlineStr">
@@ -7236,7 +7433,11 @@
           <t>ACCELERATE (You may pay 1 body as an additional cost to have me enter ready.)Other buffed friendly units at my battlefield have +2 Might.</t>
         </is>
       </c>
-      <c r="K71" s="667" t="n"/>
+      <c r="K71" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="59" t="inlineStr">
@@ -7283,7 +7484,11 @@
           <t>When you buff a friendly unit, you may pay body and exhaust this to ready it.</t>
         </is>
       </c>
-      <c r="K72" s="667" t="n"/>
+      <c r="K72" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="59" t="inlineStr">
@@ -7331,7 +7536,11 @@
 For each friendly unit, you may spend its buff to ready it. Then buff all friendly units. (Each one that doesn't have a buff gets a +1 Might buff.)</t>
         </is>
       </c>
-      <c r="K73" s="667" t="n"/>
+      <c r="K73" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="59" t="inlineStr">
@@ -7379,7 +7588,11 @@
 Give a unit +7 Might this turn.</t>
         </is>
       </c>
-      <c r="K74" s="667" t="n"/>
+      <c r="K74" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="59" t="inlineStr">
@@ -7430,7 +7643,11 @@
           <t>Spend my buff: Choose one you've not chosen turn —•Deal 2 to a unit at a battlefield.•Stun a unit at a battlefield•Ready me.•Give me GANKING this turn.</t>
         </is>
       </c>
-      <c r="K75" s="667" t="n"/>
+      <c r="K75" s="428" t="inlineStr">
+        <is>
+          <t>Lucian SB(3)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="59" t="inlineStr">
@@ -7481,7 +7698,11 @@
           <t>SHIELD 3 (+3 Might while I'm a defender.)TANK (I must be assigned combat damage first.)When an opponent moves to a battlefield other than mine, draw 1. (Bases are not battlefields.)</t>
         </is>
       </c>
-      <c r="K76" s="667" t="n"/>
+      <c r="K76" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="55" t="inlineStr">
@@ -8442,7 +8663,11 @@
           <t>DEATHKNELL - Channel 1 rune exhausted. (When I die, get the effect.)</t>
         </is>
       </c>
-      <c r="K95" s="667" t="n"/>
+      <c r="K95" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="58" t="inlineStr">
@@ -8640,7 +8865,11 @@
           <t>When a buffed friendly unit dies, buff another friendly unit. (If it doesn't have a buff, it gets a +1 Might buff.)</t>
         </is>
       </c>
-      <c r="K99" s="667" t="n"/>
+      <c r="K99" s="428" t="inlineStr">
+        <is>
+          <t>Sett(2)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="58" t="inlineStr">
@@ -10297,7 +10526,11 @@
           <t>Kill a gear. Its controller draws 2.</t>
         </is>
       </c>
-      <c r="K133" s="667" t="n"/>
+      <c r="K133" s="428" t="inlineStr">
+        <is>
+          <t>Lucian SB(3)</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="57" t="inlineStr">
@@ -10403,7 +10636,11 @@
           <t>When you play me, give a unit [GANKING] this turn. (It can move from battlefield to battlefield)</t>
         </is>
       </c>
-      <c r="K135" s="667" t="n"/>
+      <c r="K135" s="428" t="inlineStr">
+        <is>
+          <t>Sett(2)</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="57" t="inlineStr">
@@ -10454,7 +10691,11 @@
           <t>[WEAPONMASTER] (When you play me, you may [Equip] one of your Equipment to me for 1 Rune less, even if it's already attached.)</t>
         </is>
       </c>
-      <c r="K136" s="667" t="n"/>
+      <c r="K136" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="57" t="inlineStr">
@@ -10505,7 +10746,7 @@
       </c>
       <c r="K137" s="428" t="inlineStr">
         <is>
-          <t>Draven SB(2)</t>
+          <t>Draven SB(2) | Lucian(1)</t>
         </is>
       </c>
     </row>
@@ -10915,7 +11156,11 @@
           <t>1, Fury, Recycle a unit from your trash, Exhaust: Play a 3 Might Mech unit token to your base.</t>
         </is>
       </c>
-      <c r="K145" s="667" t="n"/>
+      <c r="K145" s="428" t="inlineStr">
+        <is>
+          <t>Lucian SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="57" t="inlineStr">
@@ -11074,7 +11319,11 @@
 Might +2</t>
         </is>
       </c>
-      <c r="K148" s="667" t="n"/>
+      <c r="K148" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(2)</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="57" t="inlineStr">
@@ -11272,7 +11521,11 @@
           <t>[EQUIP 1, Fury] (1, Fury: Attach this to a unit you control.) My hold effects are also conquer effects, and vice verse. Might +2</t>
         </is>
       </c>
-      <c r="K152" s="667" t="n"/>
+      <c r="K152" s="428" t="inlineStr">
+        <is>
+          <t>Lucian SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="49" t="inlineStr">
@@ -13290,7 +13543,11 @@
           <t>When you play me, you may draw 1 or buff me. (To buff a unit, give it a +1 Might buff if it doesn't already have one.)</t>
         </is>
       </c>
-      <c r="K192" s="667" t="n"/>
+      <c r="K192" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="A193" s="59" t="inlineStr">
@@ -13341,7 +13598,11 @@
           <t>[WEAPONMASTER] (When you play me, you may [EQUIP] One of your Equipment to me for Rune less, even if it's already attached.)</t>
         </is>
       </c>
-      <c r="K193" s="667" t="n"/>
+      <c r="K193" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" s="59" t="inlineStr">
@@ -13505,7 +13766,7 @@
       </c>
       <c r="K196" s="428" t="inlineStr">
         <is>
-          <t>MF(2)</t>
+          <t>MF(2) | Lucian(1)</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13819,11 @@
           <t>[GANKING] (I can move from battlefield to battlefield.)</t>
         </is>
       </c>
-      <c r="K197" s="667" t="n"/>
+      <c r="K197" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="59" t="inlineStr">
@@ -13606,7 +13871,11 @@
 Give a unit +5 Might this turn.</t>
         </is>
       </c>
-      <c r="K198" s="667" t="n"/>
+      <c r="K198" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="A199" s="59" t="inlineStr">
@@ -13658,7 +13927,11 @@
 When you play me, if you paid the additional cost, buff me. (Give me a +1 Might Buff if I don't already have one.)</t>
         </is>
       </c>
-      <c r="K199" s="667" t="n"/>
+      <c r="K199" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="59" t="inlineStr">
@@ -13709,7 +13982,11 @@
           <t>[WEAPONMASTER] (When you play me, you may [EQUIP] one of your Equipment to me for Rune less, even if it's already attached.)</t>
         </is>
       </c>
-      <c r="K200" s="667" t="n"/>
+      <c r="K200" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="A201" s="59" t="inlineStr">
@@ -13760,7 +14037,11 @@
           <t>When you play a card with Power cost 2 Runes or more, draw 1.</t>
         </is>
       </c>
-      <c r="K201" s="667" t="n"/>
+      <c r="K201" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="59" t="inlineStr">
@@ -13812,7 +14093,11 @@
 When you spend a buff, play a Gold gear token exhausted.</t>
         </is>
       </c>
-      <c r="K202" s="667" t="n"/>
+      <c r="K202" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="59" t="inlineStr">
@@ -13860,7 +14145,11 @@
 [DEFLECT] (Opponents must pay Rune to choose me with a spell or ability.) +1 Might</t>
         </is>
       </c>
-      <c r="K203" s="667" t="n"/>
+      <c r="K203" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15" customHeight="1">
       <c r="A204" s="59" t="inlineStr">
@@ -13912,7 +14201,11 @@
 I cost 2 less for each of your [MIGHTY] units. A unit is Mighty while it has 5+ Might.)</t>
         </is>
       </c>
-      <c r="K204" s="667" t="n"/>
+      <c r="K204" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="59" t="inlineStr">
@@ -14007,7 +14300,11 @@
           <t>I can't be chosen by enemy spells and abilities.</t>
         </is>
       </c>
-      <c r="K206" s="667" t="n"/>
+      <c r="K206" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="59" t="inlineStr">
@@ -14051,7 +14348,11 @@
 Draw 1 for each of your [MIGHTY] units. (A unit is Mighty while it has 5+ Might)</t>
         </is>
       </c>
-      <c r="K207" s="667" t="n"/>
+      <c r="K207" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="A208" s="59" t="inlineStr">
@@ -14094,7 +14395,11 @@
           <t>Choose an equipped friendly unit. It deals damage equal to its Might to an enemy unit. Then detach an Equipment from it.</t>
         </is>
       </c>
-      <c r="K208" s="667" t="n"/>
+      <c r="K208" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15" customHeight="1">
       <c r="A209" s="59" t="inlineStr">
@@ -14142,7 +14447,11 @@
 When I conquer, buff me. (If I don't have a buff, I get a +1 Might buff.)+1 Might</t>
         </is>
       </c>
-      <c r="K209" s="667" t="n"/>
+      <c r="K209" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="59" t="inlineStr">
@@ -14195,7 +14504,11 @@
 When you play me, if you paid the additional cost, move an enemy gear to your base. You control it until I leave the board. If it's an Equipment, attach it to me.</t>
         </is>
       </c>
-      <c r="K210" s="667" t="n"/>
+      <c r="K210" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="A211" s="59" t="inlineStr">
@@ -14246,7 +14559,11 @@
           <t>When I attack or defend one on one, double my Might this combat.</t>
         </is>
       </c>
-      <c r="K211" s="667" t="n"/>
+      <c r="K211" s="428" t="inlineStr">
+        <is>
+          <t>Sett(2)</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1">
       <c r="A212" s="59" t="inlineStr">
@@ -14347,7 +14664,11 @@
 When I move to a battlefield, give a friendly unit my keywords and +Might equal to my Might this turn.</t>
         </is>
       </c>
-      <c r="K213" s="667" t="n"/>
+      <c r="K213" s="428" t="inlineStr">
+        <is>
+          <t>Sett SB(1)</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15" customHeight="1">
       <c r="A214" s="59" t="inlineStr">
@@ -14398,7 +14719,11 @@
           <t>[WEAPONMASTER] (When you play me, you may [Equip] one of your Equipment to me for 1 Rune less, even if it's already attached.) The first time I conquer each turn, ready me.</t>
         </is>
       </c>
-      <c r="K214" s="667" t="n"/>
+      <c r="K214" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(2)</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="59" t="inlineStr">
@@ -14505,7 +14830,11 @@
 When I conquer an open battlefield, deal damage equal to my Might to an enemy unit in a base.</t>
         </is>
       </c>
-      <c r="K216" s="667" t="n"/>
+      <c r="K216" s="428" t="inlineStr">
+        <is>
+          <t>Lucian(3)</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1">
       <c r="A217" s="59" t="inlineStr">
@@ -16267,7 +16596,11 @@
           <t>[DEATHKNELL] — If I was [MIGHTY], draw 2. (When I die, get the effect. I'm Mighty while I have 5+ Might.)</t>
         </is>
       </c>
-      <c r="K251" s="667" t="n"/>
+      <c r="K251" s="428" t="inlineStr">
+        <is>
+          <t>Sett(3)</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15" customHeight="1">
       <c r="A252" s="58" t="inlineStr">
@@ -17891,7 +18224,7 @@
       <c r="K286" s="667" t="n"/>
     </row>
     <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="679" t="inlineStr">
+      <c r="A287" s="830" t="inlineStr">
         <is>
           <t>SFD-042</t>
         </is>
@@ -17950,17 +18283,17 @@
       <c r="B288" s="360" t="n">
         <v>1</v>
       </c>
-      <c r="C288" s="774" t="inlineStr">
+      <c r="C288" s="835" t="inlineStr">
         <is>
           <t>Back-Alley Bar</t>
         </is>
       </c>
-      <c r="D288" s="774" t="inlineStr">
+      <c r="D288" s="835" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E288" s="774" t="inlineStr">
+      <c r="E288" s="835" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
@@ -17975,12 +18308,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H288" s="774" t="inlineStr">
+      <c r="H288" s="835" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I288" s="774" t="inlineStr"/>
+      <c r="I288" s="835" t="inlineStr"/>
       <c r="J288" s="97" t="inlineStr">
         <is>
           <t>When a unit moves from here, give it +1 Might this turn.</t>
@@ -17997,17 +18330,17 @@
       <c r="B289" s="360" t="n">
         <v>1</v>
       </c>
-      <c r="C289" s="774" t="inlineStr">
+      <c r="C289" s="835" t="inlineStr">
         <is>
           <t>Power Nexus</t>
         </is>
       </c>
-      <c r="D289" s="774" t="inlineStr">
+      <c r="D289" s="835" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E289" s="774" t="inlineStr">
+      <c r="E289" s="835" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
@@ -18022,12 +18355,12 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H289" s="774" t="inlineStr">
+      <c r="H289" s="835" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I289" s="774" t="inlineStr"/>
+      <c r="I289" s="835" t="inlineStr"/>
       <c r="J289" s="97" t="inlineStr">
         <is>
           <t>When you hold here, you may pay Rune Rune Rune Rune to score 1 point.</t>
@@ -18177,46 +18510,46 @@
       </c>
     </row>
     <row r="293" ht="16" customHeight="1">
-      <c r="A293" s="774" t="inlineStr">
+      <c r="A293" s="835" t="inlineStr">
         <is>
           <t>OGN-297</t>
         </is>
       </c>
-      <c r="B293" s="774" t="n">
+      <c r="B293" s="835" t="n">
         <v>1</v>
       </c>
-      <c r="C293" s="774" t="inlineStr">
+      <c r="C293" s="835" t="inlineStr">
         <is>
           <t>Windswept Hillock</t>
         </is>
       </c>
-      <c r="D293" s="774" t="inlineStr">
+      <c r="D293" s="835" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E293" s="774" t="inlineStr">
+      <c r="E293" s="835" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
       </c>
-      <c r="F293" s="774" t="inlineStr">
+      <c r="F293" s="835" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G293" s="774" t="inlineStr">
+      <c r="G293" s="835" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H293" s="774" t="inlineStr">
+      <c r="H293" s="835" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I293" s="774" t="inlineStr"/>
-      <c r="J293" s="774" t="inlineStr"/>
+      <c r="I293" s="835" t="inlineStr"/>
+      <c r="J293" s="835" t="inlineStr"/>
       <c r="K293" s="710" t="n"/>
     </row>
   </sheetData>
@@ -18296,26 +18629,26 @@
       <c r="H4" s="669" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="811" t="inlineStr">
+      <c r="A5" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="B5" s="811" t="inlineStr">
+      <c r="B5" s="849" t="inlineStr">
         <is>
           <t>Win Rate G1</t>
         </is>
       </c>
-      <c r="C5" s="811" t="inlineStr">
+      <c r="C5" s="849" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D5" s="811" t="inlineStr"/>
-      <c r="E5" s="811" t="inlineStr"/>
-      <c r="F5" s="811" t="inlineStr"/>
-      <c r="G5" s="811" t="inlineStr"/>
-      <c r="H5" s="811" t="inlineStr">
+      <c r="D5" s="849" t="inlineStr"/>
+      <c r="E5" s="849" t="inlineStr"/>
+      <c r="F5" s="849" t="inlineStr"/>
+      <c r="G5" s="849" t="inlineStr"/>
+      <c r="H5" s="849" t="inlineStr">
         <is>
           <t>Card-Based Analysis</t>
         </is>
@@ -18327,12 +18660,12 @@
           <t>vs Draven (meta)</t>
         </is>
       </c>
-      <c r="B6" s="676" t="inlineStr">
+      <c r="B6" s="832" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="C6" s="676" t="inlineStr">
+      <c r="C6" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -18353,12 +18686,12 @@
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="679" t="inlineStr">
+      <c r="B7" s="830" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C7" s="679" t="inlineStr">
+      <c r="C7" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -18379,12 +18712,12 @@
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="679" t="inlineStr">
+      <c r="B8" s="830" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="C8" s="679" t="inlineStr">
+      <c r="C8" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -18405,12 +18738,12 @@
           <t>vs Draven (ours)</t>
         </is>
       </c>
-      <c r="B9" s="676" t="inlineStr">
+      <c r="B9" s="832" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="C9" s="676" t="inlineStr">
+      <c r="C9" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -18431,12 +18764,12 @@
           <t>vs Volibear (ours)</t>
         </is>
       </c>
-      <c r="B10" s="679" t="inlineStr">
+      <c r="B10" s="830" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="C10" s="679" t="inlineStr">
+      <c r="C10" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -18457,12 +18790,12 @@
           <t>vs Miss Fortune (ours)</t>
         </is>
       </c>
-      <c r="B11" s="676" t="inlineStr">
+      <c r="B11" s="832" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C11" s="676" t="inlineStr">
+      <c r="C11" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -18706,54 +19039,54 @@
       <c r="H23" s="669" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="811" t="inlineStr">
+      <c r="A24" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B24" s="811" t="inlineStr">
+      <c r="B24" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C24" s="811" t="inlineStr">
+      <c r="C24" s="849" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D24" s="811" t="inlineStr">
+      <c r="D24" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E24" s="811" t="inlineStr">
+      <c r="E24" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F24" s="811" t="inlineStr">
+      <c r="F24" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G24" s="811" t="inlineStr">
+      <c r="G24" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H24" s="811" t="inlineStr">
+      <c r="H24" s="849" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="679" t="inlineStr">
+      <c r="A25" s="830" t="inlineStr">
         <is>
           <t>SFD-197</t>
         </is>
       </c>
-      <c r="B25" s="679" t="inlineStr">
+      <c r="B25" s="830" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
@@ -18790,12 +19123,12 @@
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="802" t="inlineStr">
+      <c r="A26" s="831" t="inlineStr">
         <is>
           <t>SFD-177</t>
         </is>
       </c>
-      <c r="B26" s="802" t="inlineStr">
+      <c r="B26" s="831" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
@@ -18856,54 +19189,54 @@
       <c r="H28" s="669" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="811" t="inlineStr">
+      <c r="A29" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B29" s="811" t="inlineStr">
+      <c r="B29" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C29" s="811" t="inlineStr">
+      <c r="C29" s="849" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D29" s="811" t="inlineStr">
+      <c r="D29" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E29" s="811" t="inlineStr">
+      <c r="E29" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F29" s="811" t="inlineStr">
+      <c r="F29" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G29" s="811" t="inlineStr">
+      <c r="G29" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H29" s="811" t="inlineStr">
+      <c r="H29" s="849" t="inlineStr">
         <is>
           <t>Card Function</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="679" t="inlineStr">
+      <c r="A30" s="830" t="inlineStr">
         <is>
           <t>OGN-058</t>
         </is>
       </c>
-      <c r="B30" s="679" t="n">
+      <c r="B30" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C30" s="680" t="inlineStr">
@@ -18938,12 +19271,12 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="802" t="inlineStr">
+      <c r="A31" s="831" t="inlineStr">
         <is>
           <t>OGN-209</t>
         </is>
       </c>
-      <c r="B31" s="802" t="n">
+      <c r="B31" s="831" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="702" t="inlineStr">
@@ -18978,12 +19311,12 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="802" t="inlineStr">
+      <c r="A32" s="831" t="inlineStr">
         <is>
           <t>OGN-213</t>
         </is>
       </c>
-      <c r="B32" s="802" t="n">
+      <c r="B32" s="831" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="702" t="inlineStr">
@@ -19018,12 +19351,12 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="679" t="inlineStr">
+      <c r="A33" s="830" t="inlineStr">
         <is>
           <t>SFD-031</t>
         </is>
       </c>
-      <c r="B33" s="679" t="n">
+      <c r="B33" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="680" t="inlineStr">
@@ -19054,12 +19387,12 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="679" t="inlineStr">
+      <c r="A34" s="830" t="inlineStr">
         <is>
           <t>SFD-033</t>
         </is>
       </c>
-      <c r="B34" s="679" t="n">
+      <c r="B34" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="680" t="inlineStr">
@@ -19094,12 +19427,12 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="679" t="inlineStr">
+      <c r="A35" s="830" t="inlineStr">
         <is>
           <t>SFD-034</t>
         </is>
       </c>
-      <c r="B35" s="679" t="n">
+      <c r="B35" s="830" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="680" t="inlineStr">
@@ -19134,12 +19467,12 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="679" t="inlineStr">
+      <c r="A36" s="830" t="inlineStr">
         <is>
           <t>SFD-038</t>
         </is>
       </c>
-      <c r="B36" s="679" t="n">
+      <c r="B36" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="680" t="inlineStr">
@@ -19174,12 +19507,12 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="679" t="inlineStr">
+      <c r="A37" s="830" t="inlineStr">
         <is>
           <t>SFD-039</t>
         </is>
       </c>
-      <c r="B37" s="679" t="n">
+      <c r="B37" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="680" t="inlineStr">
@@ -19214,12 +19547,12 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="679" t="inlineStr">
+      <c r="A38" s="830" t="inlineStr">
         <is>
           <t>SFD-042</t>
         </is>
       </c>
-      <c r="B38" s="679" t="n">
+      <c r="B38" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="680" t="inlineStr">
@@ -19250,12 +19583,12 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="679" t="inlineStr">
+      <c r="A39" s="830" t="inlineStr">
         <is>
           <t>SFD-043</t>
         </is>
       </c>
-      <c r="B39" s="679" t="n">
+      <c r="B39" s="830" t="n">
         <v>3</v>
       </c>
       <c r="C39" s="680" t="inlineStr">
@@ -19286,12 +19619,12 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="679" t="inlineStr">
+      <c r="A40" s="830" t="inlineStr">
         <is>
           <t>SFD-051</t>
         </is>
       </c>
-      <c r="B40" s="679" t="n">
+      <c r="B40" s="830" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="680" t="inlineStr">
@@ -19326,12 +19659,12 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="802" t="inlineStr">
+      <c r="A41" s="831" t="inlineStr">
         <is>
           <t>SFD-153</t>
         </is>
       </c>
-      <c r="B41" s="802" t="n">
+      <c r="B41" s="831" t="n">
         <v>3</v>
       </c>
       <c r="C41" s="702" t="inlineStr">
@@ -19362,12 +19695,12 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="802" t="inlineStr">
+      <c r="A42" s="831" t="inlineStr">
         <is>
           <t>SFD-154</t>
         </is>
       </c>
-      <c r="B42" s="802" t="n">
+      <c r="B42" s="831" t="n">
         <v>3</v>
       </c>
       <c r="C42" s="702" t="inlineStr">
@@ -19398,12 +19731,12 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="802" t="inlineStr">
+      <c r="A43" s="831" t="inlineStr">
         <is>
           <t>SFD-161</t>
         </is>
       </c>
-      <c r="B43" s="802" t="n">
+      <c r="B43" s="831" t="n">
         <v>3</v>
       </c>
       <c r="C43" s="702" t="inlineStr">
@@ -19438,12 +19771,12 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="802" t="inlineStr">
+      <c r="A44" s="831" t="inlineStr">
         <is>
           <t>SFD-163</t>
         </is>
       </c>
-      <c r="B44" s="802" t="n">
+      <c r="B44" s="831" t="n">
         <v>2</v>
       </c>
       <c r="C44" s="702" t="inlineStr">
@@ -19474,12 +19807,12 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="802" t="inlineStr">
+      <c r="A45" s="831" t="inlineStr">
         <is>
           <t>SFD-172</t>
         </is>
       </c>
-      <c r="B45" s="802" t="n">
+      <c r="B45" s="831" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="702" t="inlineStr">
@@ -19510,12 +19843,12 @@
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="679" t="inlineStr">
+      <c r="A46" s="830" t="inlineStr">
         <is>
           <t>SFD-198</t>
         </is>
       </c>
-      <c r="B46" s="679" t="n">
+      <c r="B46" s="830" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="680" t="inlineStr">
@@ -19614,54 +19947,54 @@
       <c r="H51" s="669" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="811" t="inlineStr">
+      <c r="A52" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B52" s="811" t="inlineStr">
+      <c r="B52" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C52" s="811" t="inlineStr">
+      <c r="C52" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="D52" s="811" t="inlineStr">
+      <c r="D52" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E52" s="811" t="inlineStr">
+      <c r="E52" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F52" s="811" t="inlineStr">
+      <c r="F52" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G52" s="811" t="inlineStr">
+      <c r="G52" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H52" s="811" t="inlineStr">
+      <c r="H52" s="849" t="inlineStr">
         <is>
           <t>G2 Plan + Swap</t>
         </is>
       </c>
     </row>
     <row r="53" ht="50" customHeight="1">
-      <c r="A53" s="802" t="inlineStr">
+      <c r="A53" s="831" t="inlineStr">
         <is>
           <t>SFD-157</t>
         </is>
       </c>
-      <c r="B53" s="802" t="n">
+      <c r="B53" s="831" t="n">
         <v>3</v>
       </c>
       <c r="C53" s="799" t="inlineStr">
@@ -19696,12 +20029,12 @@
       </c>
     </row>
     <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="802" t="inlineStr">
+      <c r="A54" s="831" t="inlineStr">
         <is>
           <t>SFD-159</t>
         </is>
       </c>
-      <c r="B54" s="802" t="n">
+      <c r="B54" s="831" t="n">
         <v>3</v>
       </c>
       <c r="C54" s="799" t="inlineStr">
@@ -19736,12 +20069,12 @@
       </c>
     </row>
     <row r="55" ht="50" customHeight="1">
-      <c r="A55" s="802" t="inlineStr">
+      <c r="A55" s="831" t="inlineStr">
         <is>
           <t>SFD-158</t>
         </is>
       </c>
-      <c r="B55" s="802" t="n">
+      <c r="B55" s="831" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="799" t="inlineStr">
@@ -19776,12 +20109,12 @@
       </c>
     </row>
     <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="679" t="inlineStr">
+      <c r="A56" s="830" t="inlineStr">
         <is>
           <t>OGN-065</t>
         </is>
       </c>
-      <c r="B56" s="679" t="n">
+      <c r="B56" s="830" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="678" t="inlineStr">
@@ -19850,12 +20183,12 @@
           <t>Play equipment every turn to trigger Azir legend. Even cheap 1-cost equipment activates the free soldier. Never skip equipment.</t>
         </is>
       </c>
-      <c r="C59" s="774" t="inlineStr"/>
-      <c r="D59" s="774" t="inlineStr"/>
-      <c r="E59" s="774" t="inlineStr"/>
-      <c r="F59" s="774" t="inlineStr"/>
-      <c r="G59" s="774" t="inlineStr"/>
-      <c r="H59" s="774" t="inlineStr"/>
+      <c r="C59" s="835" t="inlineStr"/>
+      <c r="D59" s="835" t="inlineStr"/>
+      <c r="E59" s="835" t="inlineStr"/>
+      <c r="F59" s="835" t="inlineStr"/>
+      <c r="G59" s="835" t="inlineStr"/>
+      <c r="H59" s="835" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="709" t="inlineStr">
@@ -19886,12 +20219,12 @@
           <t>Arise! is your biggest turn. Wait until you have 3+ equipment in play. One card makes 3-4 soldiers instantly. Play it when opponent is tapped out.</t>
         </is>
       </c>
-      <c r="C61" s="774" t="inlineStr"/>
-      <c r="D61" s="774" t="inlineStr"/>
-      <c r="E61" s="774" t="inlineStr"/>
-      <c r="F61" s="774" t="inlineStr"/>
-      <c r="G61" s="774" t="inlineStr"/>
-      <c r="H61" s="774" t="inlineStr"/>
+      <c r="C61" s="835" t="inlineStr"/>
+      <c r="D61" s="835" t="inlineStr"/>
+      <c r="E61" s="835" t="inlineStr"/>
+      <c r="F61" s="835" t="inlineStr"/>
+      <c r="G61" s="835" t="inlineStr"/>
+      <c r="H61" s="835" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="709" t="inlineStr">
@@ -19922,12 +20255,12 @@
           <t>Azir Sovereign moves and swaps with another unit. Move him to a contested field mid-attack. Bring equipment with him. Surprise attacker.</t>
         </is>
       </c>
-      <c r="C63" s="774" t="inlineStr"/>
-      <c r="D63" s="774" t="inlineStr"/>
-      <c r="E63" s="774" t="inlineStr"/>
-      <c r="F63" s="774" t="inlineStr"/>
-      <c r="G63" s="774" t="inlineStr"/>
-      <c r="H63" s="774" t="inlineStr"/>
+      <c r="C63" s="835" t="inlineStr"/>
+      <c r="D63" s="835" t="inlineStr"/>
+      <c r="E63" s="835" t="inlineStr"/>
+      <c r="F63" s="835" t="inlineStr"/>
+      <c r="G63" s="835" t="inlineStr"/>
+      <c r="H63" s="835" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="709" t="inlineStr">
@@ -19958,12 +20291,12 @@
           <t>Unsung Hero: buff it first with Feral Strength or B.F. Sword. Then let it die in combat. Drawing 2 cards from a unit death is massive.</t>
         </is>
       </c>
-      <c r="C65" s="774" t="inlineStr"/>
-      <c r="D65" s="774" t="inlineStr"/>
-      <c r="E65" s="774" t="inlineStr"/>
-      <c r="F65" s="774" t="inlineStr"/>
-      <c r="G65" s="774" t="inlineStr"/>
-      <c r="H65" s="774" t="inlineStr"/>
+      <c r="C65" s="835" t="inlineStr"/>
+      <c r="D65" s="835" t="inlineStr"/>
+      <c r="E65" s="835" t="inlineStr"/>
+      <c r="F65" s="835" t="inlineStr"/>
+      <c r="G65" s="835" t="inlineStr"/>
+      <c r="H65" s="835" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="709" t="inlineStr">
@@ -20071,7 +20404,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="772" t="inlineStr">
+      <c r="A5" s="834" t="inlineStr">
         <is>
           <t>Draven - Vanquisher</t>
         </is>
@@ -20084,27 +20417,27 @@
       <c r="C5" s="707" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="676" t="inlineStr">
+      <c r="D5" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E5" s="676" t="inlineStr">
+      <c r="E5" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F5" s="676" t="inlineStr">
+      <c r="F5" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G5" s="676" t="inlineStr">
+      <c r="G5" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H5" s="676" t="inlineStr">
+      <c r="H5" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -20129,12 +20462,12 @@
       <c r="C6" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="676" t="inlineStr">
+      <c r="D6" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E6" s="676" t="inlineStr">
+      <c r="E6" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20161,7 +20494,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="772" t="inlineStr">
+      <c r="A7" s="834" t="inlineStr">
         <is>
           <t>Battering Ram</t>
         </is>
@@ -20174,12 +20507,12 @@
       <c r="C7" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="676" t="inlineStr">
+      <c r="D7" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E7" s="676" t="inlineStr">
+      <c r="E7" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20219,27 +20552,27 @@
       <c r="C8" s="709" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="676" t="inlineStr">
+      <c r="D8" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E8" s="676" t="inlineStr">
+      <c r="E8" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F8" s="676" t="inlineStr">
+      <c r="F8" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G8" s="676" t="inlineStr">
+      <c r="G8" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H8" s="676" t="inlineStr">
+      <c r="H8" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -20251,7 +20584,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="772" t="inlineStr">
+      <c r="A9" s="834" t="inlineStr">
         <is>
           <t>Irelia - Fervent</t>
         </is>
@@ -20264,27 +20597,27 @@
       <c r="C9" s="707" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="676" t="inlineStr">
+      <c r="D9" s="832" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E9" s="676" t="inlineStr">
+      <c r="E9" s="832" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" s="676" t="inlineStr">
+      <c r="F9" s="832" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G9" s="676" t="inlineStr">
+      <c r="G9" s="832" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H9" s="676" t="inlineStr">
+      <c r="H9" s="832" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -20309,27 +20642,27 @@
       <c r="C10" s="709" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="676" t="inlineStr">
+      <c r="D10" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E10" s="676" t="inlineStr">
+      <c r="E10" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F10" s="676" t="inlineStr">
+      <c r="F10" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G10" s="676" t="inlineStr">
+      <c r="G10" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H10" s="676" t="inlineStr">
+      <c r="H10" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -20341,7 +20674,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="772" t="inlineStr">
+      <c r="A11" s="834" t="inlineStr">
         <is>
           <t>Ravenbloom Student</t>
         </is>
@@ -20354,12 +20687,12 @@
       <c r="C11" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="676" t="inlineStr">
+      <c r="D11" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E11" s="676" t="inlineStr">
+      <c r="E11" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20399,27 +20732,27 @@
       <c r="C12" s="709" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="676" t="inlineStr">
+      <c r="D12" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E12" s="676" t="inlineStr">
+      <c r="E12" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F12" s="676" t="inlineStr">
+      <c r="F12" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G12" s="676" t="inlineStr">
+      <c r="G12" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H12" s="676" t="inlineStr">
+      <c r="H12" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -20431,7 +20764,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="772" t="inlineStr">
+      <c r="A13" s="834" t="inlineStr">
         <is>
           <t>Called Shot</t>
         </is>
@@ -20444,27 +20777,27 @@
       <c r="C13" s="707" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="676" t="inlineStr">
+      <c r="D13" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E13" s="676" t="inlineStr">
+      <c r="E13" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F13" s="676" t="inlineStr">
+      <c r="F13" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G13" s="676" t="inlineStr">
+      <c r="G13" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H13" s="676" t="inlineStr">
+      <c r="H13" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -20538,7 +20871,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="772" t="inlineStr">
+      <c r="A17" s="834" t="inlineStr">
         <is>
           <t>Minotaur Reckoner</t>
         </is>
@@ -20551,12 +20884,12 @@
       <c r="C17" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="676" t="inlineStr">
+      <c r="D17" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E17" s="676" t="inlineStr">
+      <c r="E17" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20596,12 +20929,12 @@
       <c r="C18" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="676" t="inlineStr">
+      <c r="D18" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E18" s="676" t="inlineStr">
+      <c r="E18" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20628,7 +20961,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="772" t="inlineStr">
+      <c r="A19" s="834" t="inlineStr">
         <is>
           <t>Cruel Patron</t>
         </is>
@@ -20641,12 +20974,12 @@
       <c r="C19" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="676" t="inlineStr">
+      <c r="D19" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E19" s="676" t="inlineStr">
+      <c r="E19" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20686,12 +21019,12 @@
       <c r="C20" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="676" t="inlineStr">
+      <c r="D20" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E20" s="676" t="inlineStr">
+      <c r="E20" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20718,7 +21051,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="772" t="inlineStr">
+      <c r="A21" s="834" t="inlineStr">
         <is>
           <t>Sandshifter</t>
         </is>
@@ -20731,12 +21064,12 @@
       <c r="C21" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="676" t="inlineStr">
+      <c r="D21" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E21" s="676" t="inlineStr">
+      <c r="E21" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20776,12 +21109,12 @@
       <c r="C22" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="676" t="inlineStr">
+      <c r="D22" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E22" s="676" t="inlineStr">
+      <c r="E22" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20808,7 +21141,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="772" t="inlineStr">
+      <c r="A23" s="834" t="inlineStr">
         <is>
           <t>Shakedown</t>
         </is>
@@ -20821,12 +21154,12 @@
       <c r="C23" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="676" t="inlineStr">
+      <c r="D23" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E23" s="676" t="inlineStr">
+      <c r="E23" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20866,12 +21199,12 @@
       <c r="C24" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="676" t="inlineStr">
+      <c r="D24" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E24" s="676" t="inlineStr">
+      <c r="E24" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20898,7 +21231,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="772" t="inlineStr">
+      <c r="A25" s="834" t="inlineStr">
         <is>
           <t>Fading Memories</t>
         </is>
@@ -20911,22 +21244,22 @@
       <c r="C25" s="707" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="676" t="inlineStr">
+      <c r="D25" s="832" t="inlineStr">
         <is>
           <t>23.7%</t>
         </is>
       </c>
-      <c r="E25" s="676" t="inlineStr">
+      <c r="E25" s="832" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="F25" s="676" t="inlineStr">
+      <c r="F25" s="832" t="inlineStr">
         <is>
           <t>32.3%</t>
         </is>
       </c>
-      <c r="G25" s="676" t="inlineStr">
+      <c r="G25" s="832" t="inlineStr">
         <is>
           <t>36.4%</t>
         </is>
@@ -20956,12 +21289,12 @@
       <c r="C26" s="709" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="676" t="inlineStr">
+      <c r="D26" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E26" s="676" t="inlineStr">
+      <c r="E26" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -20988,7 +21321,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="772" t="inlineStr">
+      <c r="A27" s="834" t="inlineStr">
         <is>
           <t>Soaring Scout</t>
         </is>
@@ -21001,12 +21334,12 @@
       <c r="C27" s="707" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="676" t="inlineStr">
+      <c r="D27" s="832" t="inlineStr">
         <is>
           <t>33.8%</t>
         </is>
       </c>
-      <c r="E27" s="676" t="inlineStr">
+      <c r="E27" s="832" t="inlineStr">
         <is>
           <t>39.4%</t>
         </is>
@@ -21046,27 +21379,27 @@
       <c r="C28" s="709" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="676" t="inlineStr">
+      <c r="D28" s="832" t="inlineStr">
         <is>
           <t>12.5%</t>
         </is>
       </c>
-      <c r="E28" s="676" t="inlineStr">
+      <c r="E28" s="832" t="inlineStr">
         <is>
           <t>15.0%</t>
         </is>
       </c>
-      <c r="F28" s="676" t="inlineStr">
+      <c r="F28" s="832" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
-      <c r="G28" s="676" t="inlineStr">
+      <c r="G28" s="832" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H28" s="676" t="inlineStr">
+      <c r="H28" s="832" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
@@ -21154,26 +21487,26 @@
       <c r="H4" s="712" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="811" t="inlineStr">
+      <c r="A5" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="B5" s="811" t="inlineStr">
+      <c r="B5" s="849" t="inlineStr">
         <is>
           <t>Win Rate G1</t>
         </is>
       </c>
-      <c r="C5" s="811" t="inlineStr">
+      <c r="C5" s="849" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D5" s="811" t="inlineStr"/>
-      <c r="E5" s="811" t="inlineStr"/>
-      <c r="F5" s="811" t="inlineStr"/>
-      <c r="G5" s="811" t="inlineStr"/>
-      <c r="H5" s="811" t="inlineStr">
+      <c r="D5" s="849" t="inlineStr"/>
+      <c r="E5" s="849" t="inlineStr"/>
+      <c r="F5" s="849" t="inlineStr"/>
+      <c r="G5" s="849" t="inlineStr"/>
+      <c r="H5" s="849" t="inlineStr">
         <is>
           <t>Card-Based Analysis</t>
         </is>
@@ -21185,12 +21518,12 @@
           <t>vs Draven (meta)</t>
         </is>
       </c>
-      <c r="B6" s="676" t="inlineStr">
+      <c r="B6" s="832" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="C6" s="676" t="inlineStr">
+      <c r="C6" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -21211,12 +21544,12 @@
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="802" t="inlineStr">
+      <c r="B7" s="831" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C7" s="802" t="inlineStr">
+      <c r="C7" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -21237,12 +21570,12 @@
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="802" t="inlineStr">
+      <c r="B8" s="831" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="C8" s="802" t="inlineStr">
+      <c r="C8" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -21263,12 +21596,12 @@
           <t>vs Draven (ours)</t>
         </is>
       </c>
-      <c r="B9" s="676" t="inlineStr">
+      <c r="B9" s="832" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="C9" s="676" t="inlineStr">
+      <c r="C9" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -21289,12 +21622,12 @@
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B10" s="802" t="inlineStr">
+      <c r="B10" s="831" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C10" s="802" t="inlineStr">
+      <c r="C10" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -21315,12 +21648,12 @@
           <t>vs Miss Fortune (ours)</t>
         </is>
       </c>
-      <c r="B11" s="676" t="inlineStr">
+      <c r="B11" s="832" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="C11" s="676" t="inlineStr">
+      <c r="C11" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -21341,12 +21674,12 @@
           <t>META AVG G1</t>
         </is>
       </c>
-      <c r="B12" s="815" t="inlineStr">
+      <c r="B12" s="840" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="C12" s="815" t="inlineStr">
+      <c r="C12" s="840" t="inlineStr">
         <is>
           <t>NEEDS SB</t>
         </is>
@@ -21564,42 +21897,42 @@
       <c r="H23" s="712" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="811" t="inlineStr">
+      <c r="A24" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B24" s="811" t="inlineStr">
+      <c r="B24" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C24" s="811" t="inlineStr">
+      <c r="C24" s="849" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D24" s="811" t="inlineStr">
+      <c r="D24" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E24" s="811" t="inlineStr">
+      <c r="E24" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F24" s="811" t="inlineStr">
+      <c r="F24" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G24" s="811" t="inlineStr">
+      <c r="G24" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H24" s="811" t="inlineStr">
+      <c r="H24" s="849" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -21714,42 +22047,42 @@
       <c r="H28" s="712" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="811" t="inlineStr">
+      <c r="A29" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B29" s="811" t="inlineStr">
+      <c r="B29" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C29" s="811" t="inlineStr">
+      <c r="C29" s="849" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D29" s="811" t="inlineStr">
+      <c r="D29" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E29" s="811" t="inlineStr">
+      <c r="E29" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F29" s="811" t="inlineStr">
+      <c r="F29" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G29" s="811" t="inlineStr">
+      <c r="G29" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H29" s="811" t="inlineStr">
+      <c r="H29" s="849" t="inlineStr">
         <is>
           <t>Card Function</t>
         </is>
@@ -22316,12 +22649,12 @@
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="815" t="inlineStr">
+      <c r="A44" s="840" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="815" t="n">
+      <c r="B44" s="840" t="n">
         <v>40</v>
       </c>
       <c r="C44" s="712" t="inlineStr"/>
@@ -22384,42 +22717,42 @@
       <c r="H48" s="712" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="811" t="inlineStr">
+      <c r="A49" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B49" s="811" t="inlineStr">
+      <c r="B49" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C49" s="811" t="inlineStr">
+      <c r="C49" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="D49" s="811" t="inlineStr">
+      <c r="D49" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E49" s="811" t="inlineStr">
+      <c r="E49" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F49" s="811" t="inlineStr">
+      <c r="F49" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G49" s="811" t="inlineStr">
+      <c r="G49" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H49" s="811" t="inlineStr">
+      <c r="H49" s="849" t="inlineStr">
         <is>
           <t>G2 Plan + Swap</t>
         </is>
@@ -22580,12 +22913,12 @@
           <t>Ramp turns 1-4. Never play Kadregrin before turn 5 — you won't have enough runes. Build up. Be patient. The payoff is coming.</t>
         </is>
       </c>
-      <c r="C55" s="774" t="inlineStr"/>
-      <c r="D55" s="774" t="inlineStr"/>
-      <c r="E55" s="774" t="inlineStr"/>
-      <c r="F55" s="774" t="inlineStr"/>
-      <c r="G55" s="774" t="inlineStr"/>
-      <c r="H55" s="774" t="inlineStr"/>
+      <c r="C55" s="835" t="inlineStr"/>
+      <c r="D55" s="835" t="inlineStr"/>
+      <c r="E55" s="835" t="inlineStr"/>
+      <c r="F55" s="835" t="inlineStr"/>
+      <c r="G55" s="835" t="inlineStr"/>
+      <c r="H55" s="835" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="709" t="inlineStr">
@@ -22616,12 +22949,12 @@
           <t>Volibear Furious has DEFLECT 2. Opponent must spend 2 runes to choose him with a spell. Most decks can't afford to. He's effectively removal-proof.</t>
         </is>
       </c>
-      <c r="C57" s="774" t="inlineStr"/>
-      <c r="D57" s="774" t="inlineStr"/>
-      <c r="E57" s="774" t="inlineStr"/>
-      <c r="F57" s="774" t="inlineStr"/>
-      <c r="G57" s="774" t="inlineStr"/>
-      <c r="H57" s="774" t="inlineStr"/>
+      <c r="C57" s="835" t="inlineStr"/>
+      <c r="D57" s="835" t="inlineStr"/>
+      <c r="E57" s="835" t="inlineStr"/>
+      <c r="F57" s="835" t="inlineStr"/>
+      <c r="G57" s="835" t="inlineStr"/>
+      <c r="H57" s="835" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="709" t="inlineStr">
@@ -22652,12 +22985,12 @@
           <t>Challenge in sideboard: pick Kadregrin or Volibear as your friendly unit. Pick their most dangerous threat as their unit. Forced fight. Your 9M wins every time.</t>
         </is>
       </c>
-      <c r="C59" s="774" t="inlineStr"/>
-      <c r="D59" s="774" t="inlineStr"/>
-      <c r="E59" s="774" t="inlineStr"/>
-      <c r="F59" s="774" t="inlineStr"/>
-      <c r="G59" s="774" t="inlineStr"/>
-      <c r="H59" s="774" t="inlineStr"/>
+      <c r="C59" s="835" t="inlineStr"/>
+      <c r="D59" s="835" t="inlineStr"/>
+      <c r="E59" s="835" t="inlineStr"/>
+      <c r="F59" s="835" t="inlineStr"/>
+      <c r="G59" s="835" t="inlineStr"/>
+      <c r="H59" s="835" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="709" t="inlineStr">
@@ -22688,12 +23021,12 @@
           <t>Mountain Drake (9/10) is your backup dragon. If Kadregrin gets answered, Drake is waiting. You can have two 9M+ bodies at different fields simultaneously.</t>
         </is>
       </c>
-      <c r="C61" s="774" t="inlineStr"/>
-      <c r="D61" s="774" t="inlineStr"/>
-      <c r="E61" s="774" t="inlineStr"/>
-      <c r="F61" s="774" t="inlineStr"/>
-      <c r="G61" s="774" t="inlineStr"/>
-      <c r="H61" s="774" t="inlineStr"/>
+      <c r="C61" s="835" t="inlineStr"/>
+      <c r="D61" s="835" t="inlineStr"/>
+      <c r="E61" s="835" t="inlineStr"/>
+      <c r="F61" s="835" t="inlineStr"/>
+      <c r="G61" s="835" t="inlineStr"/>
+      <c r="H61" s="835" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="709" t="inlineStr">
@@ -23037,10 +23370,10 @@
           <t>Full combo: 3x Ram + Rhasa</t>
         </is>
       </c>
-      <c r="B12" s="676" t="n">
+      <c r="B12" s="832" t="n">
         <v>21</v>
       </c>
-      <c r="C12" s="676" t="inlineStr">
+      <c r="C12" s="832" t="inlineStr">
         <is>
           <t>Not beatable in combat</t>
         </is>
@@ -23104,7 +23437,7 @@
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="772" t="inlineStr">
+      <c r="A15" s="834" t="inlineStr">
         <is>
           <t>vs Draven Midrange</t>
         </is>
@@ -23178,7 +23511,7 @@
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="772" t="inlineStr">
+      <c r="A17" s="834" t="inlineStr">
         <is>
           <t>vs Irelia Voltron</t>
         </is>
@@ -23188,7 +23521,7 @@
           <t>Turn 4</t>
         </is>
       </c>
-      <c r="C17" s="676" t="inlineStr">
+      <c r="C17" s="832" t="inlineStr">
         <is>
           <t>36% Fading Memories (only 2x!)</t>
         </is>
@@ -23314,16 +23647,16 @@
           <t>BUY LIST &amp; GAP ANALYSIS — The 80% Standard</t>
         </is>
       </c>
-      <c r="B2" s="810" t="inlineStr"/>
-      <c r="C2" s="810" t="inlineStr"/>
-      <c r="D2" s="810" t="inlineStr"/>
-      <c r="E2" s="810" t="inlineStr"/>
-      <c r="F2" s="810" t="inlineStr"/>
-      <c r="G2" s="810" t="inlineStr"/>
-      <c r="H2" s="810" t="inlineStr"/>
-      <c r="I2" s="810" t="inlineStr"/>
-      <c r="J2" s="810" t="inlineStr"/>
-      <c r="K2" s="810" t="inlineStr"/>
+      <c r="B2" s="826" t="inlineStr"/>
+      <c r="C2" s="826" t="inlineStr"/>
+      <c r="D2" s="826" t="inlineStr"/>
+      <c r="E2" s="826" t="inlineStr"/>
+      <c r="F2" s="826" t="inlineStr"/>
+      <c r="G2" s="826" t="inlineStr"/>
+      <c r="H2" s="826" t="inlineStr"/>
+      <c r="I2" s="826" t="inlineStr"/>
+      <c r="J2" s="826" t="inlineStr"/>
+      <c r="K2" s="826" t="inlineStr"/>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="119" t="inlineStr">
@@ -23408,7 +23741,7 @@
           <t>OGN-180</t>
         </is>
       </c>
-      <c r="C5" s="772" t="inlineStr">
+      <c r="C5" s="834" t="inlineStr">
         <is>
           <t>Fading Memories</t>
         </is>
@@ -23428,12 +23761,12 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="G5" s="676" t="inlineStr">
+      <c r="G5" s="832" t="inlineStr">
         <is>
           <t>36.4%</t>
         </is>
       </c>
-      <c r="H5" s="676" t="inlineStr">
+      <c r="H5" s="832" t="inlineStr">
         <is>
           <t>69.4%</t>
         </is>
@@ -23443,7 +23776,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="J5" s="676" t="inlineStr">
+      <c r="J5" s="832" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
@@ -23463,7 +23796,7 @@
           <t>SFD-???</t>
         </is>
       </c>
-      <c r="C6" s="772" t="inlineStr">
+      <c r="C6" s="834" t="inlineStr">
         <is>
           <t>Rebuke</t>
         </is>
@@ -23488,7 +23821,7 @@
           <t>83.2%</t>
         </is>
       </c>
-      <c r="H6" s="679" t="inlineStr">
+      <c r="H6" s="830" t="inlineStr">
         <is>
           <t>90.7%</t>
         </is>
@@ -23498,7 +23831,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="J6" s="679" t="inlineStr">
+      <c r="J6" s="830" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -23518,7 +23851,7 @@
           <t>OGN-???</t>
         </is>
       </c>
-      <c r="C7" s="772" t="inlineStr">
+      <c r="C7" s="834" t="inlineStr">
         <is>
           <t>Ride the Wind</t>
         </is>
@@ -23538,7 +23871,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G7" s="676" t="inlineStr">
+      <c r="G7" s="832" t="inlineStr">
         <is>
           <t>63.3%</t>
         </is>
@@ -23573,7 +23906,7 @@
           <t>OGN-???</t>
         </is>
       </c>
-      <c r="C8" s="772" t="inlineStr">
+      <c r="C8" s="834" t="inlineStr">
         <is>
           <t>En Garde</t>
         </is>
@@ -23593,12 +23926,12 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="G8" s="676" t="inlineStr">
+      <c r="G8" s="832" t="inlineStr">
         <is>
           <t>69.5%</t>
         </is>
       </c>
-      <c r="H8" s="679" t="inlineStr">
+      <c r="H8" s="830" t="inlineStr">
         <is>
           <t>83.2%</t>
         </is>
@@ -23608,7 +23941,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="J8" s="679" t="inlineStr">
+      <c r="J8" s="830" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -23628,7 +23961,7 @@
           <t>SFD-???</t>
         </is>
       </c>
-      <c r="C9" s="772" t="inlineStr">
+      <c r="C9" s="834" t="inlineStr">
         <is>
           <t>Switcheroo</t>
         </is>
@@ -23648,7 +23981,7 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="G9" s="676" t="inlineStr">
+      <c r="G9" s="832" t="inlineStr">
         <is>
           <t>62.6%</t>
         </is>
@@ -23828,26 +24161,26 @@
       <c r="H4" s="729" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="811" t="inlineStr">
+      <c r="A5" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="B5" s="811" t="inlineStr">
+      <c r="B5" s="849" t="inlineStr">
         <is>
           <t>Win Rate G1</t>
         </is>
       </c>
-      <c r="C5" s="811" t="inlineStr">
+      <c r="C5" s="849" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D5" s="811" t="inlineStr"/>
-      <c r="E5" s="811" t="inlineStr"/>
-      <c r="F5" s="811" t="inlineStr"/>
-      <c r="G5" s="811" t="inlineStr"/>
-      <c r="H5" s="811" t="inlineStr">
+      <c r="D5" s="849" t="inlineStr"/>
+      <c r="E5" s="849" t="inlineStr"/>
+      <c r="F5" s="849" t="inlineStr"/>
+      <c r="G5" s="849" t="inlineStr"/>
+      <c r="H5" s="849" t="inlineStr">
         <is>
           <t>Card-Based Analysis</t>
         </is>
@@ -23859,12 +24192,12 @@
           <t>vs Draven (meta)</t>
         </is>
       </c>
-      <c r="B6" s="676" t="inlineStr">
+      <c r="B6" s="832" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="C6" s="676" t="inlineStr">
+      <c r="C6" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -23885,12 +24218,12 @@
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="679" t="inlineStr">
+      <c r="B7" s="830" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C7" s="679" t="inlineStr">
+      <c r="C7" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -23911,12 +24244,12 @@
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="679" t="inlineStr">
+      <c r="B8" s="830" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="C8" s="679" t="inlineStr">
+      <c r="C8" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -23937,12 +24270,12 @@
           <t>vs Draven (ours)</t>
         </is>
       </c>
-      <c r="B9" s="676" t="inlineStr">
+      <c r="B9" s="832" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="C9" s="676" t="inlineStr">
+      <c r="C9" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -23963,12 +24296,12 @@
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B10" s="802" t="inlineStr">
+      <c r="B10" s="831" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C10" s="802" t="inlineStr">
+      <c r="C10" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -23989,12 +24322,12 @@
           <t>vs Volibear (ours)</t>
         </is>
       </c>
-      <c r="B11" s="802" t="inlineStr">
+      <c r="B11" s="831" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C11" s="802" t="inlineStr">
+      <c r="C11" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -24015,12 +24348,12 @@
           <t>META AVG G1</t>
         </is>
       </c>
-      <c r="B12" s="816" t="inlineStr">
+      <c r="B12" s="841" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
       </c>
-      <c r="C12" s="816" t="inlineStr">
+      <c r="C12" s="841" t="inlineStr">
         <is>
           <t>NEEDS SB</t>
         </is>
@@ -24238,42 +24571,42 @@
       <c r="H23" s="729" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="811" t="inlineStr">
+      <c r="A24" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B24" s="811" t="inlineStr">
+      <c r="B24" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C24" s="811" t="inlineStr">
+      <c r="C24" s="849" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D24" s="811" t="inlineStr">
+      <c r="D24" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E24" s="811" t="inlineStr">
+      <c r="E24" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F24" s="811" t="inlineStr">
+      <c r="F24" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G24" s="811" t="inlineStr">
+      <c r="G24" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H24" s="811" t="inlineStr">
+      <c r="H24" s="849" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -24388,42 +24721,42 @@
       <c r="H28" s="729" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="811" t="inlineStr">
+      <c r="A29" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B29" s="811" t="inlineStr">
+      <c r="B29" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C29" s="811" t="inlineStr">
+      <c r="C29" s="849" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D29" s="811" t="inlineStr">
+      <c r="D29" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E29" s="811" t="inlineStr">
+      <c r="E29" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F29" s="811" t="inlineStr">
+      <c r="F29" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G29" s="811" t="inlineStr">
+      <c r="G29" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H29" s="811" t="inlineStr">
+      <c r="H29" s="849" t="inlineStr">
         <is>
           <t>Card Function</t>
         </is>
@@ -25026,12 +25359,12 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="816" t="inlineStr">
+      <c r="A45" s="841" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="816" t="n">
+      <c r="B45" s="841" t="n">
         <v>40</v>
       </c>
       <c r="C45" s="729" t="inlineStr"/>
@@ -25094,42 +25427,42 @@
       <c r="H49" s="729" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="811" t="inlineStr">
+      <c r="A50" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B50" s="811" t="inlineStr">
+      <c r="B50" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C50" s="811" t="inlineStr">
+      <c r="C50" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="D50" s="811" t="inlineStr">
+      <c r="D50" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E50" s="811" t="inlineStr">
+      <c r="E50" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F50" s="811" t="inlineStr">
+      <c r="F50" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G50" s="811" t="inlineStr">
+      <c r="G50" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H50" s="811" t="inlineStr">
+      <c r="H50" s="849" t="inlineStr">
         <is>
           <t>G2 Plan + Swap</t>
         </is>
@@ -25330,12 +25663,12 @@
           <t>Trinity Force is your win condition. Equip it ASAP on your strongest unit. Hold a field with that unit every turn. Score 1 free point every turn just from existing.</t>
         </is>
       </c>
-      <c r="C57" s="774" t="inlineStr"/>
-      <c r="D57" s="774" t="inlineStr"/>
-      <c r="E57" s="774" t="inlineStr"/>
-      <c r="F57" s="774" t="inlineStr"/>
-      <c r="G57" s="774" t="inlineStr"/>
-      <c r="H57" s="774" t="inlineStr"/>
+      <c r="C57" s="835" t="inlineStr"/>
+      <c r="D57" s="835" t="inlineStr"/>
+      <c r="E57" s="835" t="inlineStr"/>
+      <c r="F57" s="835" t="inlineStr"/>
+      <c r="G57" s="835" t="inlineStr"/>
+      <c r="H57" s="835" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="709" t="inlineStr">
@@ -25366,12 +25699,12 @@
           <t>Ride the Wind combo: Trinity carrier conquers field 1. Ride the Wind readies it + gives GANKING. Conquer field 2 same turn. Score 2 conquest points + Trinity passive. 3 points one turn.</t>
         </is>
       </c>
-      <c r="C59" s="774" t="inlineStr"/>
-      <c r="D59" s="774" t="inlineStr"/>
-      <c r="E59" s="774" t="inlineStr"/>
-      <c r="F59" s="774" t="inlineStr"/>
-      <c r="G59" s="774" t="inlineStr"/>
-      <c r="H59" s="774" t="inlineStr"/>
+      <c r="C59" s="835" t="inlineStr"/>
+      <c r="D59" s="835" t="inlineStr"/>
+      <c r="E59" s="835" t="inlineStr"/>
+      <c r="F59" s="835" t="inlineStr"/>
+      <c r="G59" s="835" t="inlineStr"/>
+      <c r="H59" s="835" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="709" t="inlineStr">
@@ -25402,12 +25735,12 @@
           <t>Boots of Swiftness on Trinity carrier = permanent GANKING without spending legend exhaust. Free up your legend exhaust for another unit.</t>
         </is>
       </c>
-      <c r="C61" s="774" t="inlineStr"/>
-      <c r="D61" s="774" t="inlineStr"/>
-      <c r="E61" s="774" t="inlineStr"/>
-      <c r="F61" s="774" t="inlineStr"/>
-      <c r="G61" s="774" t="inlineStr"/>
-      <c r="H61" s="774" t="inlineStr"/>
+      <c r="C61" s="835" t="inlineStr"/>
+      <c r="D61" s="835" t="inlineStr"/>
+      <c r="E61" s="835" t="inlineStr"/>
+      <c r="F61" s="835" t="inlineStr"/>
+      <c r="G61" s="835" t="inlineStr"/>
+      <c r="H61" s="835" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="709" t="inlineStr">
@@ -25438,12 +25771,12 @@
           <t>Overt Op: spend all your unit buffs to ready all units here. After conquering a field, ready everything = attack again. Double conquest available every turn with buffs.</t>
         </is>
       </c>
-      <c r="C63" s="774" t="inlineStr"/>
-      <c r="D63" s="774" t="inlineStr"/>
-      <c r="E63" s="774" t="inlineStr"/>
-      <c r="F63" s="774" t="inlineStr"/>
-      <c r="G63" s="774" t="inlineStr"/>
-      <c r="H63" s="774" t="inlineStr"/>
+      <c r="C63" s="835" t="inlineStr"/>
+      <c r="D63" s="835" t="inlineStr"/>
+      <c r="E63" s="835" t="inlineStr"/>
+      <c r="F63" s="835" t="inlineStr"/>
+      <c r="G63" s="835" t="inlineStr"/>
+      <c r="H63" s="835" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="709" t="inlineStr">
@@ -25540,26 +25873,26 @@
       <c r="H4" s="743" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="811" t="inlineStr">
+      <c r="A5" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="B5" s="811" t="inlineStr">
+      <c r="B5" s="849" t="inlineStr">
         <is>
           <t>Win Rate G1</t>
         </is>
       </c>
-      <c r="C5" s="811" t="inlineStr">
+      <c r="C5" s="849" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D5" s="811" t="inlineStr"/>
-      <c r="E5" s="811" t="inlineStr"/>
-      <c r="F5" s="811" t="inlineStr"/>
-      <c r="G5" s="811" t="inlineStr"/>
-      <c r="H5" s="811" t="inlineStr">
+      <c r="D5" s="849" t="inlineStr"/>
+      <c r="E5" s="849" t="inlineStr"/>
+      <c r="F5" s="849" t="inlineStr"/>
+      <c r="G5" s="849" t="inlineStr"/>
+      <c r="H5" s="849" t="inlineStr">
         <is>
           <t>Card-Based Analysis</t>
         </is>
@@ -25571,12 +25904,12 @@
           <t>vs Draven (meta)</t>
         </is>
       </c>
-      <c r="B6" s="676" t="inlineStr">
+      <c r="B6" s="832" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="C6" s="676" t="inlineStr">
+      <c r="C6" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -25597,12 +25930,12 @@
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="679" t="inlineStr">
+      <c r="B7" s="830" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="C7" s="679" t="inlineStr">
+      <c r="C7" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -25623,12 +25956,12 @@
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="679" t="inlineStr">
+      <c r="B8" s="830" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C8" s="679" t="inlineStr">
+      <c r="C8" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -25649,12 +25982,12 @@
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B9" s="679" t="inlineStr">
+      <c r="B9" s="830" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C9" s="679" t="inlineStr">
+      <c r="C9" s="830" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
@@ -25675,12 +26008,12 @@
           <t>vs Volibear (ours)</t>
         </is>
       </c>
-      <c r="B10" s="676" t="inlineStr">
+      <c r="B10" s="832" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="C10" s="676" t="inlineStr">
+      <c r="C10" s="832" t="inlineStr">
         <is>
           <t>✗ SB NEEDED</t>
         </is>
@@ -25701,12 +26034,12 @@
           <t>vs Miss Fortune (ours)</t>
         </is>
       </c>
-      <c r="B11" s="802" t="inlineStr">
+      <c r="B11" s="831" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C11" s="802" t="inlineStr">
+      <c r="C11" s="831" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
@@ -25727,12 +26060,12 @@
           <t>META AVG G1</t>
         </is>
       </c>
-      <c r="B12" s="817" t="inlineStr">
+      <c r="B12" s="842" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="C12" s="817" t="inlineStr">
+      <c r="C12" s="842" t="inlineStr">
         <is>
           <t>PASS ✓</t>
         </is>
@@ -25950,42 +26283,42 @@
       <c r="H23" s="743" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="811" t="inlineStr">
+      <c r="A24" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B24" s="811" t="inlineStr">
+      <c r="B24" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C24" s="811" t="inlineStr">
+      <c r="C24" s="849" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D24" s="811" t="inlineStr">
+      <c r="D24" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E24" s="811" t="inlineStr">
+      <c r="E24" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F24" s="811" t="inlineStr">
+      <c r="F24" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G24" s="811" t="inlineStr">
+      <c r="G24" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H24" s="811" t="inlineStr">
+      <c r="H24" s="849" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -26100,42 +26433,42 @@
       <c r="H28" s="743" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="811" t="inlineStr">
+      <c r="A29" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B29" s="811" t="inlineStr">
+      <c r="B29" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C29" s="811" t="inlineStr">
+      <c r="C29" s="849" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D29" s="811" t="inlineStr">
+      <c r="D29" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E29" s="811" t="inlineStr">
+      <c r="E29" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F29" s="811" t="inlineStr">
+      <c r="F29" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G29" s="811" t="inlineStr">
+      <c r="G29" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H29" s="811" t="inlineStr">
+      <c r="H29" s="849" t="inlineStr">
         <is>
           <t>Card Function</t>
         </is>
@@ -26814,12 +27147,12 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="817" t="inlineStr">
+      <c r="A47" s="842" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B47" s="817" t="n">
+      <c r="B47" s="842" t="n">
         <v>40</v>
       </c>
       <c r="C47" s="743" t="inlineStr"/>
@@ -26882,42 +27215,42 @@
       <c r="H51" s="743" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="811" t="inlineStr">
+      <c r="A52" s="849" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B52" s="811" t="inlineStr">
+      <c r="B52" s="849" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C52" s="811" t="inlineStr">
+      <c r="C52" s="849" t="inlineStr">
         <is>
           <t>Matchup</t>
         </is>
       </c>
-      <c r="D52" s="811" t="inlineStr">
+      <c r="D52" s="849" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E52" s="811" t="inlineStr">
+      <c r="E52" s="849" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F52" s="811" t="inlineStr">
+      <c r="F52" s="849" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G52" s="811" t="inlineStr">
+      <c r="G52" s="849" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H52" s="811" t="inlineStr">
+      <c r="H52" s="849" t="inlineStr">
         <is>
           <t>G2 Plan + Swap</t>
         </is>
@@ -27154,12 +27487,12 @@
           <t>Chemtech Enforcer turn 2 every game. Attacks as 4M. Discards Flame Chompers = pay 1 Fury = Chompers plays free. Two bodies for 2+1 runes.</t>
         </is>
       </c>
-      <c r="C60" s="774" t="inlineStr"/>
-      <c r="D60" s="774" t="inlineStr"/>
-      <c r="E60" s="774" t="inlineStr"/>
-      <c r="F60" s="774" t="inlineStr"/>
-      <c r="G60" s="774" t="inlineStr"/>
-      <c r="H60" s="774" t="inlineStr"/>
+      <c r="C60" s="835" t="inlineStr"/>
+      <c r="D60" s="835" t="inlineStr"/>
+      <c r="E60" s="835" t="inlineStr"/>
+      <c r="F60" s="835" t="inlineStr"/>
+      <c r="G60" s="835" t="inlineStr"/>
+      <c r="H60" s="835" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="709" t="inlineStr">
@@ -27190,12 +27523,12 @@
           <t>Raging Soul only activates if discarded THIS turn. Chemtech discards it. NEVER play Raging Soul from hand — let Chemtech do it for free.</t>
         </is>
       </c>
-      <c r="C62" s="774" t="inlineStr"/>
-      <c r="D62" s="774" t="inlineStr"/>
-      <c r="E62" s="774" t="inlineStr"/>
-      <c r="F62" s="774" t="inlineStr"/>
-      <c r="G62" s="774" t="inlineStr"/>
-      <c r="H62" s="774" t="inlineStr"/>
+      <c r="C62" s="835" t="inlineStr"/>
+      <c r="D62" s="835" t="inlineStr"/>
+      <c r="E62" s="835" t="inlineStr"/>
+      <c r="F62" s="835" t="inlineStr"/>
+      <c r="G62" s="835" t="inlineStr"/>
+      <c r="H62" s="835" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="709" t="inlineStr">
@@ -27226,12 +27559,12 @@
           <t>Minotaur Reckoner: once on field, no unit can retreat to base. Play Reckoner then attack. Opponent's unit must fight. Your ASSAULT wins. They can never escape.</t>
         </is>
       </c>
-      <c r="C64" s="774" t="inlineStr"/>
-      <c r="D64" s="774" t="inlineStr"/>
-      <c r="E64" s="774" t="inlineStr"/>
-      <c r="F64" s="774" t="inlineStr"/>
-      <c r="G64" s="774" t="inlineStr"/>
-      <c r="H64" s="774" t="inlineStr"/>
+      <c r="C64" s="835" t="inlineStr"/>
+      <c r="D64" s="835" t="inlineStr"/>
+      <c r="E64" s="835" t="inlineStr"/>
+      <c r="F64" s="835" t="inlineStr"/>
+      <c r="G64" s="835" t="inlineStr"/>
+      <c r="H64" s="835" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="709" t="inlineStr">
@@ -27262,12 +27595,12 @@
           <t>G2 vs Volibear: Sky Splitter costs 2 when Armed Assailant (6M) is on field. Deals 5 to the 9M dragon. Dragon dies. OR play Fading Memories. Dragon dies next turn without combat.</t>
         </is>
       </c>
-      <c r="C66" s="774" t="inlineStr"/>
-      <c r="D66" s="774" t="inlineStr"/>
-      <c r="E66" s="774" t="inlineStr"/>
-      <c r="F66" s="774" t="inlineStr"/>
-      <c r="G66" s="774" t="inlineStr"/>
-      <c r="H66" s="774" t="inlineStr"/>
+      <c r="C66" s="835" t="inlineStr"/>
+      <c r="D66" s="835" t="inlineStr"/>
+      <c r="E66" s="835" t="inlineStr"/>
+      <c r="F66" s="835" t="inlineStr"/>
+      <c r="G66" s="835" t="inlineStr"/>
+      <c r="H66" s="835" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="709" t="inlineStr">
@@ -27319,15 +27652,15 @@
           <t>RIFTBOUND SIMULATION ENGINE — Deck Performance Matrix</t>
         </is>
       </c>
-      <c r="B1" s="810" t="inlineStr"/>
-      <c r="C1" s="810" t="inlineStr"/>
-      <c r="D1" s="810" t="inlineStr"/>
-      <c r="E1" s="810" t="inlineStr"/>
-      <c r="F1" s="810" t="inlineStr"/>
-      <c r="G1" s="810" t="inlineStr"/>
-      <c r="H1" s="810" t="inlineStr"/>
-      <c r="I1" s="810" t="inlineStr"/>
-      <c r="J1" s="810" t="inlineStr"/>
+      <c r="B1" s="826" t="inlineStr"/>
+      <c r="C1" s="826" t="inlineStr"/>
+      <c r="D1" s="826" t="inlineStr"/>
+      <c r="E1" s="826" t="inlineStr"/>
+      <c r="F1" s="826" t="inlineStr"/>
+      <c r="G1" s="826" t="inlineStr"/>
+      <c r="H1" s="826" t="inlineStr"/>
+      <c r="I1" s="826" t="inlineStr"/>
+      <c r="J1" s="826" t="inlineStr"/>
     </row>
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="751" t="inlineStr">
@@ -27335,30 +27668,30 @@
           <t>HOW THIS WORKS: Each matchup win rate is calculated from three inputs per deck: (1) SPEED — how many turns before your win condition is online, (2) PEAK POWER — maximum effective Might when your deck peaks, (3) CONSISTENCY — what % of games you hit your key cards by turn 5. The formula: Win Rate = 50% + Speed_Advantage×15 + Power_Advantage×20 + Consistency_Bonus×10 + Special_Mechanic_Modifier. Clipped to 5%-95%. To recalculate: change any INPUT cell (yellow background). Formulas auto-update. To test a new deck: replace a deck's inputs in its column. G2 win rates = G1 rate adjusted by sideboard effectiveness (also adjustable).</t>
         </is>
       </c>
-      <c r="B2" s="752" t="inlineStr"/>
-      <c r="C2" s="752" t="inlineStr"/>
-      <c r="D2" s="752" t="inlineStr"/>
-      <c r="E2" s="752" t="inlineStr"/>
-      <c r="F2" s="752" t="inlineStr"/>
-      <c r="G2" s="752" t="inlineStr"/>
-      <c r="H2" s="752" t="inlineStr"/>
-      <c r="I2" s="752" t="inlineStr"/>
-      <c r="J2" s="752" t="inlineStr"/>
+      <c r="B2" s="828" t="inlineStr"/>
+      <c r="C2" s="828" t="inlineStr"/>
+      <c r="D2" s="828" t="inlineStr"/>
+      <c r="E2" s="828" t="inlineStr"/>
+      <c r="F2" s="828" t="inlineStr"/>
+      <c r="G2" s="828" t="inlineStr"/>
+      <c r="H2" s="828" t="inlineStr"/>
+      <c r="I2" s="828" t="inlineStr"/>
+      <c r="J2" s="828" t="inlineStr"/>
     </row>
     <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="794" t="inlineStr"/>
-      <c r="B3" s="794" t="inlineStr"/>
-      <c r="C3" s="794" t="inlineStr"/>
-      <c r="D3" s="794" t="inlineStr"/>
-      <c r="E3" s="794" t="inlineStr"/>
-      <c r="F3" s="794" t="inlineStr"/>
-      <c r="G3" s="794" t="inlineStr"/>
-      <c r="H3" s="794" t="inlineStr"/>
-      <c r="I3" s="794" t="inlineStr"/>
-      <c r="J3" s="794" t="inlineStr"/>
+      <c r="A3" s="837" t="inlineStr"/>
+      <c r="B3" s="837" t="inlineStr"/>
+      <c r="C3" s="837" t="inlineStr"/>
+      <c r="D3" s="837" t="inlineStr"/>
+      <c r="E3" s="837" t="inlineStr"/>
+      <c r="F3" s="837" t="inlineStr"/>
+      <c r="G3" s="837" t="inlineStr"/>
+      <c r="H3" s="837" t="inlineStr"/>
+      <c r="I3" s="837" t="inlineStr"/>
+      <c r="J3" s="837" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="793" t="inlineStr">
+      <c r="A4" s="836" t="inlineStr">
         <is>
           <t>DECK INPUT PARAMETERS</t>
         </is>
@@ -27398,7 +27731,7 @@
           <t>Meta Ezreal</t>
         </is>
       </c>
-      <c r="I4" s="794" t="inlineStr"/>
+      <c r="I4" s="837" t="inlineStr"/>
       <c r="J4" s="760" t="inlineStr">
         <is>
           <t>Parameter Description</t>
@@ -27672,32 +28005,32 @@
       </c>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="A12" s="794" t="inlineStr"/>
-      <c r="B12" s="794" t="inlineStr"/>
-      <c r="C12" s="794" t="inlineStr"/>
-      <c r="D12" s="794" t="inlineStr"/>
-      <c r="E12" s="794" t="inlineStr"/>
-      <c r="F12" s="794" t="inlineStr"/>
-      <c r="G12" s="794" t="inlineStr"/>
-      <c r="H12" s="794" t="inlineStr"/>
-      <c r="I12" s="794" t="inlineStr"/>
-      <c r="J12" s="794" t="inlineStr"/>
+      <c r="A12" s="837" t="inlineStr"/>
+      <c r="B12" s="837" t="inlineStr"/>
+      <c r="C12" s="837" t="inlineStr"/>
+      <c r="D12" s="837" t="inlineStr"/>
+      <c r="E12" s="837" t="inlineStr"/>
+      <c r="F12" s="837" t="inlineStr"/>
+      <c r="G12" s="837" t="inlineStr"/>
+      <c r="H12" s="837" t="inlineStr"/>
+      <c r="I12" s="837" t="inlineStr"/>
+      <c r="J12" s="837" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="793" t="inlineStr">
+      <c r="A13" s="836" t="inlineStr">
         <is>
           <t>WIN RATE FORMULA</t>
         </is>
       </c>
-      <c r="B13" s="794" t="inlineStr"/>
-      <c r="C13" s="794" t="inlineStr"/>
-      <c r="D13" s="794" t="inlineStr"/>
-      <c r="E13" s="794" t="inlineStr"/>
-      <c r="F13" s="794" t="inlineStr"/>
-      <c r="G13" s="794" t="inlineStr"/>
-      <c r="H13" s="794" t="inlineStr"/>
-      <c r="I13" s="794" t="inlineStr"/>
-      <c r="J13" s="794" t="inlineStr"/>
+      <c r="B13" s="837" t="inlineStr"/>
+      <c r="C13" s="837" t="inlineStr"/>
+      <c r="D13" s="837" t="inlineStr"/>
+      <c r="E13" s="837" t="inlineStr"/>
+      <c r="F13" s="837" t="inlineStr"/>
+      <c r="G13" s="837" t="inlineStr"/>
+      <c r="H13" s="837" t="inlineStr"/>
+      <c r="I13" s="837" t="inlineStr"/>
+      <c r="J13" s="837" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="764" t="inlineStr">
@@ -27748,68 +28081,68 @@
       <c r="J16" s="765" t="inlineStr"/>
     </row>
     <row r="17" ht="6" customHeight="1">
-      <c r="A17" s="794" t="inlineStr"/>
-      <c r="B17" s="794" t="inlineStr"/>
-      <c r="C17" s="794" t="inlineStr"/>
-      <c r="D17" s="794" t="inlineStr"/>
-      <c r="E17" s="794" t="inlineStr"/>
-      <c r="F17" s="794" t="inlineStr"/>
-      <c r="G17" s="794" t="inlineStr"/>
-      <c r="H17" s="794" t="inlineStr"/>
-      <c r="I17" s="794" t="inlineStr"/>
-      <c r="J17" s="794" t="inlineStr"/>
+      <c r="A17" s="837" t="inlineStr"/>
+      <c r="B17" s="837" t="inlineStr"/>
+      <c r="C17" s="837" t="inlineStr"/>
+      <c r="D17" s="837" t="inlineStr"/>
+      <c r="E17" s="837" t="inlineStr"/>
+      <c r="F17" s="837" t="inlineStr"/>
+      <c r="G17" s="837" t="inlineStr"/>
+      <c r="H17" s="837" t="inlineStr"/>
+      <c r="I17" s="837" t="inlineStr"/>
+      <c r="J17" s="837" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="793" t="inlineStr">
+      <c r="A18" s="836" t="inlineStr">
         <is>
           <t>WIN RATE MATRIX — G1 (live formulas, updates when inputs change)</t>
         </is>
       </c>
-      <c r="B18" s="794" t="inlineStr"/>
-      <c r="C18" s="794" t="inlineStr"/>
-      <c r="D18" s="794" t="inlineStr"/>
-      <c r="E18" s="794" t="inlineStr"/>
-      <c r="F18" s="794" t="inlineStr"/>
-      <c r="G18" s="794" t="inlineStr"/>
-      <c r="H18" s="794" t="inlineStr"/>
-      <c r="I18" s="794" t="inlineStr"/>
-      <c r="J18" s="794" t="inlineStr"/>
+      <c r="B18" s="837" t="inlineStr"/>
+      <c r="C18" s="837" t="inlineStr"/>
+      <c r="D18" s="837" t="inlineStr"/>
+      <c r="E18" s="837" t="inlineStr"/>
+      <c r="F18" s="837" t="inlineStr"/>
+      <c r="G18" s="837" t="inlineStr"/>
+      <c r="H18" s="837" t="inlineStr"/>
+      <c r="I18" s="837" t="inlineStr"/>
+      <c r="J18" s="837" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="766" t="inlineStr">
+      <c r="A19" s="829" t="inlineStr">
         <is>
           <t>My Deck → vs Opponent ↓</t>
         </is>
       </c>
-      <c r="B19" s="814" t="inlineStr">
+      <c r="B19" s="839" t="inlineStr">
         <is>
           <t>Azir</t>
         </is>
       </c>
-      <c r="C19" s="815" t="inlineStr">
+      <c r="C19" s="840" t="inlineStr">
         <is>
           <t>Voli</t>
         </is>
       </c>
-      <c r="D19" s="816" t="inlineStr">
+      <c r="D19" s="841" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="E19" s="817" t="inlineStr">
+      <c r="E19" s="842" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="I19" s="771" t="inlineStr"/>
-      <c r="J19" s="766" t="inlineStr">
+      <c r="I19" s="833" t="inlineStr"/>
+      <c r="J19" s="829" t="inlineStr">
         <is>
           <t>Matchup Notes</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="772" t="inlineStr">
+      <c r="A20" s="834" t="inlineStr">
         <is>
           <t>vs Draven (meta)</t>
         </is>
@@ -27830,7 +28163,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((F5-E5)/10)*15+((E6-F6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-F9)/2)*8+(E8*8)+((E10-F10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I20" s="774" t="inlineStr"/>
+      <c r="I20" s="835" t="inlineStr"/>
       <c r="J20" s="97" t="inlineStr">
         <is>
           <t>Draven meta: ASSAULT flood, draws on wins. Whoever runs hotter on combat pump reactions.</t>
@@ -27838,7 +28171,7 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="772" t="inlineStr">
+      <c r="A21" s="834" t="inlineStr">
         <is>
           <t>vs Irelia (meta)</t>
         </is>
@@ -27859,7 +28192,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((G5-E5)/10)*15+((E6-G6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-G9)/2)*8+(E8*8)+((E10-G10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I21" s="774" t="inlineStr"/>
+      <c r="I21" s="835" t="inlineStr"/>
       <c r="J21" s="97" t="inlineStr">
         <is>
           <t>Irelia meta: one protected big unit, double-conquer. Flood decks win by going around her.</t>
@@ -27867,7 +28200,7 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="772" t="inlineStr">
+      <c r="A22" s="834" t="inlineStr">
         <is>
           <t>vs Ezreal (meta)</t>
         </is>
@@ -27888,7 +28221,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((H5-E5)/10)*15+((E6-H6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-H9)/2)*8+(E8*8)+((E10-H10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I22" s="774" t="inlineStr"/>
+      <c r="I22" s="835" t="inlineStr"/>
       <c r="J22" s="97" t="inlineStr">
         <is>
           <t>Ezreal meta: reactive draw engine. Passive scorers and fast decks win before he sets up.</t>
@@ -27896,7 +28229,7 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="772" t="inlineStr">
+      <c r="A23" s="834" t="inlineStr">
         <is>
           <t>vs Draven (ours)</t>
         </is>
@@ -27913,12 +28246,12 @@
         <f>MIN(0.95,MAX(0.05,0.5+((E5-D5)/10)*15+((D6-E6)/MAX(D6,0.01))*20+((D7-0.70))*10+((D9-E9)/2)*8+(D8*8)+((D10-E10)/10)*5))</f>
         <v/>
       </c>
-      <c r="E23" s="775" t="inlineStr">
+      <c r="E23" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I23" s="774" t="inlineStr"/>
+      <c r="I23" s="835" t="inlineStr"/>
       <c r="J23" s="97" t="inlineStr">
         <is>
           <t>Our Draven: ASSAULT + resource domination. Tryndamere bonus scoring. Reckoner traps.</t>
@@ -27926,12 +28259,12 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="772" t="inlineStr">
+      <c r="A24" s="834" t="inlineStr">
         <is>
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B24" s="775" t="inlineStr">
+      <c r="B24" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -27948,7 +28281,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((B5-E5)/10)*15+((E6-B6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-B9)/2)*8+(E8*8)+((E10-B10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I24" s="774" t="inlineStr"/>
+      <c r="I24" s="835" t="inlineStr"/>
       <c r="J24" s="97" t="inlineStr">
         <is>
           <t>Our Azir: token flood + soldier generation. Overwhelms control, loses to ASSAULT speed.</t>
@@ -27956,7 +28289,7 @@
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="772" t="inlineStr">
+      <c r="A25" s="834" t="inlineStr">
         <is>
           <t>vs Voli (ours)</t>
         </is>
@@ -27965,7 +28298,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((C5-B5)/10)*15+((B6-C6)/MAX(B6,0.01))*20+((B7-0.70))*10+((B9-C9)/2)*8+(B8*8)+((B10-C10)/10)*5))</f>
         <v/>
       </c>
-      <c r="C25" s="775" t="inlineStr">
+      <c r="C25" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -27978,7 +28311,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((C5-E5)/10)*15+((E6-C6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-C9)/2)*8+(E8*8)+((E10-C10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I25" s="774" t="inlineStr"/>
+      <c r="I25" s="835" t="inlineStr"/>
       <c r="J25" s="97" t="inlineStr">
         <is>
           <t>Our Voli: slow ramp, 9M dragon turn 5-6. Fast decks score before dragon lands.</t>
@@ -27986,7 +28319,7 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="772" t="inlineStr">
+      <c r="A26" s="834" t="inlineStr">
         <is>
           <t>vs MF (ours)</t>
         </is>
@@ -27999,7 +28332,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((D5-C5)/10)*15+((C6-D6)/MAX(C6,0.01))*20+((C7-0.70))*10+((C9-D9)/2)*8+(C8*8)+((C10-D10)/10)*5))</f>
         <v/>
       </c>
-      <c r="D26" s="775" t="inlineStr">
+      <c r="D26" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -28008,7 +28341,7 @@
         <f>MIN(0.95,MAX(0.05,0.5+((D5-E5)/10)*15+((E6-D6)/MAX(E6,0.01))*20+((E7-0.70))*10+((E9-D9)/2)*8+(E8*8)+((E10-D10)/10)*5))</f>
         <v/>
       </c>
-      <c r="I26" s="774" t="inlineStr"/>
+      <c r="I26" s="835" t="inlineStr"/>
       <c r="J26" s="97" t="inlineStr">
         <is>
           <t>Our MF: Trinity passive + GANKING. Consistent mid-range scorer. Hard to pin down.</t>
@@ -28016,7 +28349,7 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="821" t="inlineStr">
+      <c r="A27" s="838" t="inlineStr">
         <is>
           <t>META AVG G1 (vs Draven/Irelia/Ezreal)</t>
         </is>
@@ -28037,14 +28370,14 @@
         <f>AVERAGE(E20:E22)</f>
         <v/>
       </c>
-      <c r="F27" s="822" t="inlineStr"/>
-      <c r="G27" s="822" t="inlineStr"/>
-      <c r="H27" s="822" t="inlineStr"/>
-      <c r="I27" s="822" t="inlineStr"/>
-      <c r="J27" s="822" t="inlineStr"/>
+      <c r="F27" s="844" t="inlineStr"/>
+      <c r="G27" s="844" t="inlineStr"/>
+      <c r="H27" s="844" t="inlineStr"/>
+      <c r="I27" s="844" t="inlineStr"/>
+      <c r="J27" s="844" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="766" t="inlineStr">
+      <c r="A28" s="829" t="inlineStr">
         <is>
           <t>OVERALL AVG G1 (all matchups)</t>
         </is>
@@ -28065,68 +28398,68 @@
         <f>AVERAGE(E20:E26)</f>
         <v/>
       </c>
-      <c r="F28" s="771" t="inlineStr"/>
-      <c r="G28" s="771" t="inlineStr"/>
-      <c r="H28" s="771" t="inlineStr"/>
-      <c r="I28" s="771" t="inlineStr"/>
-      <c r="J28" s="771" t="inlineStr"/>
+      <c r="F28" s="833" t="inlineStr"/>
+      <c r="G28" s="833" t="inlineStr"/>
+      <c r="H28" s="833" t="inlineStr"/>
+      <c r="I28" s="833" t="inlineStr"/>
+      <c r="J28" s="833" t="inlineStr"/>
     </row>
     <row r="29" ht="6" customHeight="1">
-      <c r="A29" s="794" t="inlineStr"/>
-      <c r="B29" s="794" t="inlineStr"/>
-      <c r="C29" s="794" t="inlineStr"/>
-      <c r="D29" s="794" t="inlineStr"/>
-      <c r="E29" s="794" t="inlineStr"/>
-      <c r="F29" s="794" t="inlineStr"/>
-      <c r="G29" s="794" t="inlineStr"/>
-      <c r="H29" s="794" t="inlineStr"/>
-      <c r="I29" s="794" t="inlineStr"/>
-      <c r="J29" s="794" t="inlineStr"/>
+      <c r="A29" s="837" t="inlineStr"/>
+      <c r="B29" s="837" t="inlineStr"/>
+      <c r="C29" s="837" t="inlineStr"/>
+      <c r="D29" s="837" t="inlineStr"/>
+      <c r="E29" s="837" t="inlineStr"/>
+      <c r="F29" s="837" t="inlineStr"/>
+      <c r="G29" s="837" t="inlineStr"/>
+      <c r="H29" s="837" t="inlineStr"/>
+      <c r="I29" s="837" t="inlineStr"/>
+      <c r="J29" s="837" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="793" t="inlineStr">
+      <c r="A30" s="836" t="inlineStr">
         <is>
           <t>G2 WIN RATES — After Sideboard (formulas auto-adjust from G1 + SB input)</t>
         </is>
       </c>
-      <c r="B30" s="794" t="inlineStr"/>
-      <c r="C30" s="794" t="inlineStr"/>
-      <c r="D30" s="794" t="inlineStr"/>
-      <c r="E30" s="794" t="inlineStr"/>
-      <c r="F30" s="794" t="inlineStr"/>
-      <c r="G30" s="794" t="inlineStr"/>
-      <c r="H30" s="794" t="inlineStr"/>
-      <c r="I30" s="794" t="inlineStr"/>
-      <c r="J30" s="794" t="inlineStr"/>
+      <c r="B30" s="837" t="inlineStr"/>
+      <c r="C30" s="837" t="inlineStr"/>
+      <c r="D30" s="837" t="inlineStr"/>
+      <c r="E30" s="837" t="inlineStr"/>
+      <c r="F30" s="837" t="inlineStr"/>
+      <c r="G30" s="837" t="inlineStr"/>
+      <c r="H30" s="837" t="inlineStr"/>
+      <c r="I30" s="837" t="inlineStr"/>
+      <c r="J30" s="837" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="766" t="inlineStr">
+      <c r="A31" s="829" t="inlineStr">
         <is>
           <t>My Deck → vs Opponent ↓</t>
         </is>
       </c>
-      <c r="B31" s="814" t="inlineStr">
+      <c r="B31" s="839" t="inlineStr">
         <is>
           <t>Azir</t>
         </is>
       </c>
-      <c r="C31" s="815" t="inlineStr">
+      <c r="C31" s="840" t="inlineStr">
         <is>
           <t>Voli</t>
         </is>
       </c>
-      <c r="D31" s="816" t="inlineStr">
+      <c r="D31" s="841" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="E31" s="817" t="inlineStr">
+      <c r="E31" s="842" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="I31" s="771" t="inlineStr"/>
-      <c r="J31" s="766" t="inlineStr">
+      <c r="I31" s="833" t="inlineStr"/>
+      <c r="J31" s="829" t="inlineStr">
         <is>
           <t>G2 Notes</t>
         </is>
@@ -28237,7 +28570,7 @@
         <f>IF(D23&lt;0.5,MIN(0.95,D23+(D11-D23)*0.7),MIN(0.95,D23+0.05))</f>
         <v/>
       </c>
-      <c r="E35" s="775" t="inlineStr">
+      <c r="E35" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -28255,7 +28588,7 @@
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B36" s="775" t="inlineStr">
+      <c r="B36" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -28289,7 +28622,7 @@
         <f>IF(B25&lt;0.5,MIN(0.95,B25+(B11-B25)*0.7),MIN(0.95,B25+0.05))</f>
         <v/>
       </c>
-      <c r="C37" s="775" t="inlineStr">
+      <c r="C37" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -28323,7 +28656,7 @@
         <f>IF(C26&lt;0.5,MIN(0.95,C26+(C11-C26)*0.7),MIN(0.95,C26+0.05))</f>
         <v/>
       </c>
-      <c r="D38" s="775" t="inlineStr">
+      <c r="D38" s="845" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -28368,59 +28701,59 @@
       <c r="J39" s="786" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="793" t="inlineStr">
+      <c r="A41" s="836" t="inlineStr">
         <is>
           <t>DECK STAT COMPARISON (auto-calculated from input parameters)</t>
         </is>
       </c>
-      <c r="B41" s="794" t="inlineStr"/>
-      <c r="C41" s="794" t="inlineStr"/>
-      <c r="D41" s="794" t="inlineStr"/>
-      <c r="E41" s="794" t="inlineStr"/>
-      <c r="F41" s="794" t="inlineStr"/>
-      <c r="G41" s="794" t="inlineStr"/>
-      <c r="H41" s="794" t="inlineStr"/>
-      <c r="I41" s="794" t="inlineStr"/>
-      <c r="J41" s="794" t="inlineStr"/>
+      <c r="B41" s="837" t="inlineStr"/>
+      <c r="C41" s="837" t="inlineStr"/>
+      <c r="D41" s="837" t="inlineStr"/>
+      <c r="E41" s="837" t="inlineStr"/>
+      <c r="F41" s="837" t="inlineStr"/>
+      <c r="G41" s="837" t="inlineStr"/>
+      <c r="H41" s="837" t="inlineStr"/>
+      <c r="I41" s="837" t="inlineStr"/>
+      <c r="J41" s="837" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="811" t="inlineStr">
+      <c r="A42" s="849" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B42" s="814" t="inlineStr">
+      <c r="B42" s="839" t="inlineStr">
         <is>
           <t>Azir</t>
         </is>
       </c>
-      <c r="C42" s="815" t="inlineStr">
+      <c r="C42" s="840" t="inlineStr">
         <is>
           <t>Volibear</t>
         </is>
       </c>
-      <c r="D42" s="816" t="inlineStr">
+      <c r="D42" s="841" t="inlineStr">
         <is>
           <t>Miss Fortune</t>
         </is>
       </c>
-      <c r="E42" s="817" t="inlineStr">
+      <c r="E42" s="842" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="F42" s="811" t="inlineStr"/>
-      <c r="G42" s="811" t="inlineStr"/>
-      <c r="H42" s="811" t="inlineStr"/>
-      <c r="I42" s="811" t="inlineStr"/>
-      <c r="J42" s="811" t="inlineStr">
+      <c r="F42" s="849" t="inlineStr"/>
+      <c r="G42" s="849" t="inlineStr"/>
+      <c r="H42" s="849" t="inlineStr"/>
+      <c r="I42" s="849" t="inlineStr"/>
+      <c r="J42" s="849" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="772" t="inlineStr">
+      <c r="A43" s="834" t="inlineStr">
         <is>
           <t>Turns to Win Con</t>
         </is>
@@ -28441,10 +28774,10 @@
         <f>E5</f>
         <v/>
       </c>
-      <c r="F43" s="774" t="inlineStr"/>
-      <c r="G43" s="774" t="inlineStr"/>
-      <c r="H43" s="774" t="inlineStr"/>
-      <c r="I43" s="774" t="inlineStr"/>
+      <c r="F43" s="835" t="inlineStr"/>
+      <c r="G43" s="835" t="inlineStr"/>
+      <c r="H43" s="835" t="inlineStr"/>
+      <c r="I43" s="835" t="inlineStr"/>
       <c r="J43" s="97" t="inlineStr">
         <is>
           <t>Lower is better. Draven=4 turns, Voli=7 turns.</t>
@@ -28452,7 +28785,7 @@
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="772" t="inlineStr">
+      <c r="A44" s="834" t="inlineStr">
         <is>
           <t>Peak Might/Field</t>
         </is>
@@ -28473,10 +28806,10 @@
         <f>E6</f>
         <v/>
       </c>
-      <c r="F44" s="774" t="inlineStr"/>
-      <c r="G44" s="774" t="inlineStr"/>
-      <c r="H44" s="774" t="inlineStr"/>
-      <c r="I44" s="774" t="inlineStr"/>
+      <c r="F44" s="835" t="inlineStr"/>
+      <c r="G44" s="835" t="inlineStr"/>
+      <c r="H44" s="835" t="inlineStr"/>
+      <c r="I44" s="835" t="inlineStr"/>
       <c r="J44" s="97" t="inlineStr">
         <is>
           <t>Higher = harder to beat in combat. Voli dragon = 9M.</t>
@@ -28484,7 +28817,7 @@
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="772" t="inlineStr">
+      <c r="A45" s="834" t="inlineStr">
         <is>
           <t>Consistency (T5)</t>
         </is>
@@ -28505,10 +28838,10 @@
         <f>TEXT(E7,"0%")</f>
         <v/>
       </c>
-      <c r="F45" s="774" t="inlineStr"/>
-      <c r="G45" s="774" t="inlineStr"/>
-      <c r="H45" s="774" t="inlineStr"/>
-      <c r="I45" s="774" t="inlineStr"/>
+      <c r="F45" s="835" t="inlineStr"/>
+      <c r="G45" s="835" t="inlineStr"/>
+      <c r="H45" s="835" t="inlineStr"/>
+      <c r="I45" s="835" t="inlineStr"/>
       <c r="J45" s="97" t="inlineStr">
         <is>
           <t>Chance of hitting key cards by turn 5. Draven highest.</t>
@@ -28516,7 +28849,7 @@
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="772" t="inlineStr">
+      <c r="A46" s="834" t="inlineStr">
         <is>
           <t>Passive Score/Turn</t>
         </is>
@@ -28537,10 +28870,10 @@
         <f>E8</f>
         <v/>
       </c>
-      <c r="F46" s="774" t="inlineStr"/>
-      <c r="G46" s="774" t="inlineStr"/>
-      <c r="H46" s="774" t="inlineStr"/>
-      <c r="I46" s="774" t="inlineStr"/>
+      <c r="F46" s="835" t="inlineStr"/>
+      <c r="G46" s="835" t="inlineStr"/>
+      <c r="H46" s="835" t="inlineStr"/>
+      <c r="I46" s="835" t="inlineStr"/>
       <c r="J46" s="97" t="inlineStr">
         <is>
           <t>Free points per turn from passive effects. MF highest (Trinity).</t>
@@ -28548,7 +28881,7 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="772" t="inlineStr">
+      <c r="A47" s="834" t="inlineStr">
         <is>
           <t>Field Coverage</t>
         </is>
@@ -28569,10 +28902,10 @@
         <f>E9</f>
         <v/>
       </c>
-      <c r="F47" s="774" t="inlineStr"/>
-      <c r="G47" s="774" t="inlineStr"/>
-      <c r="H47" s="774" t="inlineStr"/>
-      <c r="I47" s="774" t="inlineStr"/>
+      <c r="F47" s="835" t="inlineStr"/>
+      <c r="G47" s="835" t="inlineStr"/>
+      <c r="H47" s="835" t="inlineStr"/>
+      <c r="I47" s="835" t="inlineStr"/>
       <c r="J47" s="97" t="inlineStr">
         <is>
           <t>Fields contested simultaneously. Max 2. Voli = 1.</t>
@@ -28580,7 +28913,7 @@
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="772" t="inlineStr">
+      <c r="A48" s="834" t="inlineStr">
         <is>
           <t>Removal Count</t>
         </is>
@@ -28601,10 +28934,10 @@
         <f>E10</f>
         <v/>
       </c>
-      <c r="F48" s="774" t="inlineStr"/>
-      <c r="G48" s="774" t="inlineStr"/>
-      <c r="H48" s="774" t="inlineStr"/>
-      <c r="I48" s="774" t="inlineStr"/>
+      <c r="F48" s="835" t="inlineStr"/>
+      <c r="G48" s="835" t="inlineStr"/>
+      <c r="H48" s="835" t="inlineStr"/>
+      <c r="I48" s="835" t="inlineStr"/>
       <c r="J48" s="97" t="inlineStr">
         <is>
           <t>Spells that kill/bounce enemy units. Voli highest.</t>
@@ -28612,7 +28945,7 @@
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="772" t="inlineStr">
+      <c r="A49" s="834" t="inlineStr">
         <is>
           <t>Speed Rank</t>
         </is>
@@ -28633,10 +28966,10 @@
         <f>RANK(E5,B5:E5,1)</f>
         <v/>
       </c>
-      <c r="F49" s="774" t="inlineStr"/>
-      <c r="G49" s="774" t="inlineStr"/>
-      <c r="H49" s="774" t="inlineStr"/>
-      <c r="I49" s="774" t="inlineStr"/>
+      <c r="F49" s="835" t="inlineStr"/>
+      <c r="G49" s="835" t="inlineStr"/>
+      <c r="H49" s="835" t="inlineStr"/>
+      <c r="I49" s="835" t="inlineStr"/>
       <c r="J49" s="97" t="inlineStr">
         <is>
           <t>1=Fastest. Lower speed = higher rank.</t>
@@ -28644,7 +28977,7 @@
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="772" t="inlineStr">
+      <c r="A50" s="834" t="inlineStr">
         <is>
           <t>Power Rank</t>
         </is>
@@ -28665,10 +28998,10 @@
         <f>RANK(E6,B6:E6,0)</f>
         <v/>
       </c>
-      <c r="F50" s="774" t="inlineStr"/>
-      <c r="G50" s="774" t="inlineStr"/>
-      <c r="H50" s="774" t="inlineStr"/>
-      <c r="I50" s="774" t="inlineStr"/>
+      <c r="F50" s="835" t="inlineStr"/>
+      <c r="G50" s="835" t="inlineStr"/>
+      <c r="H50" s="835" t="inlineStr"/>
+      <c r="I50" s="835" t="inlineStr"/>
       <c r="J50" s="97" t="inlineStr">
         <is>
           <t>1=Highest Might. Lower = more powerful.</t>
@@ -28676,23 +29009,23 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="793" t="inlineStr">
+      <c r="A52" s="836" t="inlineStr">
         <is>
           <t>HOW TO UPDATE THIS MODEL</t>
         </is>
       </c>
-      <c r="B52" s="794" t="inlineStr"/>
-      <c r="C52" s="794" t="inlineStr"/>
-      <c r="D52" s="794" t="inlineStr"/>
-      <c r="E52" s="794" t="inlineStr"/>
-      <c r="F52" s="794" t="inlineStr"/>
-      <c r="G52" s="794" t="inlineStr"/>
-      <c r="H52" s="794" t="inlineStr"/>
-      <c r="I52" s="794" t="inlineStr"/>
-      <c r="J52" s="794" t="inlineStr"/>
+      <c r="B52" s="837" t="inlineStr"/>
+      <c r="C52" s="837" t="inlineStr"/>
+      <c r="D52" s="837" t="inlineStr"/>
+      <c r="E52" s="837" t="inlineStr"/>
+      <c r="F52" s="837" t="inlineStr"/>
+      <c r="G52" s="837" t="inlineStr"/>
+      <c r="H52" s="837" t="inlineStr"/>
+      <c r="I52" s="837" t="inlineStr"/>
+      <c r="J52" s="837" t="inlineStr"/>
     </row>
     <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="823" t="inlineStr">
+      <c r="A53" s="850" t="inlineStr">
         <is>
           <t>Update after a session:</t>
         </is>
@@ -28702,14 +29035,14 @@
           <t>Change the INPUT cells (yellow background) in the parameter table above. All win rates auto-recalculate instantly. No code needed.</t>
         </is>
       </c>
-      <c r="C53" s="824" t="inlineStr"/>
-      <c r="D53" s="824" t="inlineStr"/>
-      <c r="E53" s="824" t="inlineStr"/>
-      <c r="F53" s="824" t="inlineStr"/>
-      <c r="G53" s="824" t="inlineStr"/>
-      <c r="H53" s="824" t="inlineStr"/>
-      <c r="I53" s="824" t="inlineStr"/>
-      <c r="J53" s="824" t="inlineStr"/>
+      <c r="C53" s="851" t="inlineStr"/>
+      <c r="D53" s="851" t="inlineStr"/>
+      <c r="E53" s="851" t="inlineStr"/>
+      <c r="F53" s="851" t="inlineStr"/>
+      <c r="G53" s="851" t="inlineStr"/>
+      <c r="H53" s="851" t="inlineStr"/>
+      <c r="I53" s="851" t="inlineStr"/>
+      <c r="J53" s="851" t="inlineStr"/>
     </row>
     <row r="54" ht="4" customHeight="1">
       <c r="A54" s="820" t="inlineStr"/>
@@ -28724,7 +29057,7 @@
       <c r="J54" s="820" t="inlineStr"/>
     </row>
     <row r="55" ht="40" customHeight="1">
-      <c r="A55" s="823" t="inlineStr">
+      <c r="A55" s="850" t="inlineStr">
         <is>
           <t>To test a new card swap:</t>
         </is>
@@ -28734,14 +29067,14 @@
           <t>If you swap a card in a deck that affects Speed or Peak Might, update those inputs. Example: replacing Noxus Hopeful with Tryndamere in Draven slightly lowers Speed but adds passive scoring — adjust Speed from 4 to 4.2 and add 0.1 to Passive Score.</t>
         </is>
       </c>
-      <c r="C55" s="824" t="inlineStr"/>
-      <c r="D55" s="824" t="inlineStr"/>
-      <c r="E55" s="824" t="inlineStr"/>
-      <c r="F55" s="824" t="inlineStr"/>
-      <c r="G55" s="824" t="inlineStr"/>
-      <c r="H55" s="824" t="inlineStr"/>
-      <c r="I55" s="824" t="inlineStr"/>
-      <c r="J55" s="824" t="inlineStr"/>
+      <c r="C55" s="851" t="inlineStr"/>
+      <c r="D55" s="851" t="inlineStr"/>
+      <c r="E55" s="851" t="inlineStr"/>
+      <c r="F55" s="851" t="inlineStr"/>
+      <c r="G55" s="851" t="inlineStr"/>
+      <c r="H55" s="851" t="inlineStr"/>
+      <c r="I55" s="851" t="inlineStr"/>
+      <c r="J55" s="851" t="inlineStr"/>
     </row>
     <row r="56" ht="4" customHeight="1">
       <c r="A56" s="820" t="inlineStr"/>
@@ -28756,7 +29089,7 @@
       <c r="J56" s="820" t="inlineStr"/>
     </row>
     <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="823" t="inlineStr">
+      <c r="A57" s="850" t="inlineStr">
         <is>
           <t>To test a new deck (deck 5):</t>
         </is>
@@ -28766,14 +29099,14 @@
           <t>Add a new column (I). Fill in all 7 parameter rows with yellow background. Add matchup rows using the formula pattern: =MIN(0.95,MAX(0.05,0.5+(opp_speed-my_speed)/10*15+...))</t>
         </is>
       </c>
-      <c r="C57" s="824" t="inlineStr"/>
-      <c r="D57" s="824" t="inlineStr"/>
-      <c r="E57" s="824" t="inlineStr"/>
-      <c r="F57" s="824" t="inlineStr"/>
-      <c r="G57" s="824" t="inlineStr"/>
-      <c r="H57" s="824" t="inlineStr"/>
-      <c r="I57" s="824" t="inlineStr"/>
-      <c r="J57" s="824" t="inlineStr"/>
+      <c r="C57" s="851" t="inlineStr"/>
+      <c r="D57" s="851" t="inlineStr"/>
+      <c r="E57" s="851" t="inlineStr"/>
+      <c r="F57" s="851" t="inlineStr"/>
+      <c r="G57" s="851" t="inlineStr"/>
+      <c r="H57" s="851" t="inlineStr"/>
+      <c r="I57" s="851" t="inlineStr"/>
+      <c r="J57" s="851" t="inlineStr"/>
     </row>
     <row r="58" ht="4" customHeight="1">
       <c r="A58" s="820" t="inlineStr"/>
@@ -28788,7 +29121,7 @@
       <c r="J58" s="820" t="inlineStr"/>
     </row>
     <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="823" t="inlineStr">
+      <c r="A59" s="850" t="inlineStr">
         <is>
           <t>To calibrate after real games:</t>
         </is>
@@ -28798,14 +29131,14 @@
           <t>After playing 10+ games in a matchup, update the input parameters to match what you observed. If Draven is actually winning 70% vs Azir instead of the calculated rate, increase Draven's Peak Might by 0.5 or decrease Azir's Field Coverage.</t>
         </is>
       </c>
-      <c r="C59" s="824" t="inlineStr"/>
-      <c r="D59" s="824" t="inlineStr"/>
-      <c r="E59" s="824" t="inlineStr"/>
-      <c r="F59" s="824" t="inlineStr"/>
-      <c r="G59" s="824" t="inlineStr"/>
-      <c r="H59" s="824" t="inlineStr"/>
-      <c r="I59" s="824" t="inlineStr"/>
-      <c r="J59" s="824" t="inlineStr"/>
+      <c r="C59" s="851" t="inlineStr"/>
+      <c r="D59" s="851" t="inlineStr"/>
+      <c r="E59" s="851" t="inlineStr"/>
+      <c r="F59" s="851" t="inlineStr"/>
+      <c r="G59" s="851" t="inlineStr"/>
+      <c r="H59" s="851" t="inlineStr"/>
+      <c r="I59" s="851" t="inlineStr"/>
+      <c r="J59" s="851" t="inlineStr"/>
     </row>
     <row r="60" ht="4" customHeight="1">
       <c r="A60" s="820" t="inlineStr"/>
@@ -28820,7 +29153,7 @@
       <c r="J60" s="820" t="inlineStr"/>
     </row>
     <row r="61" ht="40" customHeight="1">
-      <c r="A61" s="823" t="inlineStr">
+      <c r="A61" s="850" t="inlineStr">
         <is>
           <t>SB effectiveness input (row 11):</t>
         </is>
@@ -28830,14 +29163,14 @@
           <t>Set to the expected G2 win rate for your hardest matchup. Draven vs Voli: with Sky Splitter G2 = 0.65. If Sky Splitter consistently kills the dragon, increase to 0.72.</t>
         </is>
       </c>
-      <c r="C61" s="824" t="inlineStr"/>
-      <c r="D61" s="824" t="inlineStr"/>
-      <c r="E61" s="824" t="inlineStr"/>
-      <c r="F61" s="824" t="inlineStr"/>
-      <c r="G61" s="824" t="inlineStr"/>
-      <c r="H61" s="824" t="inlineStr"/>
-      <c r="I61" s="824" t="inlineStr"/>
-      <c r="J61" s="824" t="inlineStr"/>
+      <c r="C61" s="851" t="inlineStr"/>
+      <c r="D61" s="851" t="inlineStr"/>
+      <c r="E61" s="851" t="inlineStr"/>
+      <c r="F61" s="851" t="inlineStr"/>
+      <c r="G61" s="851" t="inlineStr"/>
+      <c r="H61" s="851" t="inlineStr"/>
+      <c r="I61" s="851" t="inlineStr"/>
+      <c r="J61" s="851" t="inlineStr"/>
     </row>
     <row r="62" ht="4" customHeight="1">
       <c r="A62" s="820" t="inlineStr"/>
@@ -28852,18 +29185,18 @@
       <c r="J62" s="820" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="793" t="inlineStr">
+      <c r="A64" s="836" t="inlineStr">
         <is>
           <t>REAL TOURNAMENT META — Spiritforged (updated March 2026)</t>
         </is>
       </c>
-      <c r="B64" s="794" t="inlineStr"/>
-      <c r="C64" s="794" t="inlineStr"/>
-      <c r="D64" s="794" t="inlineStr"/>
-      <c r="E64" s="794" t="inlineStr"/>
-      <c r="F64" s="794" t="inlineStr"/>
-      <c r="G64" s="794" t="inlineStr"/>
-      <c r="H64" s="794" t="inlineStr"/>
+      <c r="B64" s="837" t="inlineStr"/>
+      <c r="C64" s="837" t="inlineStr"/>
+      <c r="D64" s="837" t="inlineStr"/>
+      <c r="E64" s="837" t="inlineStr"/>
+      <c r="F64" s="837" t="inlineStr"/>
+      <c r="G64" s="837" t="inlineStr"/>
+      <c r="H64" s="837" t="inlineStr"/>
       <c r="I64" s="795" t="inlineStr">
         <is>
           <t>Source</t>
@@ -28959,12 +29292,12 @@
           <t>Fury+Chaos</t>
         </is>
       </c>
-      <c r="D67" s="802" t="inlineStr">
+      <c r="D67" s="831" t="inlineStr">
         <is>
           <t>64.3%</t>
         </is>
       </c>
-      <c r="E67" s="802" t="inlineStr">
+      <c r="E67" s="831" t="inlineStr">
         <is>
           <t>37.0%</t>
         </is>
@@ -29011,12 +29344,12 @@
           <t>Calm+Chaos</t>
         </is>
       </c>
-      <c r="D68" s="802" t="inlineStr">
+      <c r="D68" s="831" t="inlineStr">
         <is>
           <t>58.0%</t>
         </is>
       </c>
-      <c r="E68" s="802" t="inlineStr">
+      <c r="E68" s="831" t="inlineStr">
         <is>
           <t>16.4%</t>
         </is>
@@ -29063,12 +29396,12 @@
           <t>Mind+Chaos</t>
         </is>
       </c>
-      <c r="D69" s="802" t="inlineStr">
+      <c r="D69" s="831" t="inlineStr">
         <is>
           <t>61.0%</t>
         </is>
       </c>
-      <c r="E69" s="802" t="inlineStr">
+      <c r="E69" s="831" t="inlineStr">
         <is>
           <t>22.0%</t>
         </is>
@@ -29360,20 +29693,20 @@
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="793" t="inlineStr">
+      <c r="A76" s="836" t="inlineStr">
         <is>
           <t>EXPANDED MATCHUP MATRIX — Our 4 Decks vs Top 8 Meta Decks (live formulas)</t>
         </is>
       </c>
-      <c r="B76" s="794" t="inlineStr"/>
-      <c r="C76" s="794" t="inlineStr"/>
-      <c r="D76" s="794" t="inlineStr"/>
-      <c r="E76" s="794" t="inlineStr"/>
-      <c r="F76" s="794" t="inlineStr"/>
-      <c r="G76" s="794" t="inlineStr"/>
-      <c r="H76" s="794" t="inlineStr"/>
-      <c r="I76" s="794" t="inlineStr"/>
-      <c r="J76" s="794" t="inlineStr"/>
+      <c r="B76" s="837" t="inlineStr"/>
+      <c r="C76" s="837" t="inlineStr"/>
+      <c r="D76" s="837" t="inlineStr"/>
+      <c r="E76" s="837" t="inlineStr"/>
+      <c r="F76" s="837" t="inlineStr"/>
+      <c r="G76" s="837" t="inlineStr"/>
+      <c r="H76" s="837" t="inlineStr"/>
+      <c r="I76" s="837" t="inlineStr"/>
+      <c r="J76" s="837" t="inlineStr"/>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="796" t="inlineStr">
@@ -29397,63 +29730,63 @@
           <t>META DECK PARAMETERS (fill in yellow — use tournament win rates to calibrate)</t>
         </is>
       </c>
-      <c r="B78" s="810" t="inlineStr"/>
-      <c r="C78" s="810" t="inlineStr"/>
-      <c r="D78" s="810" t="inlineStr"/>
-      <c r="E78" s="810" t="inlineStr"/>
-      <c r="F78" s="810" t="inlineStr"/>
-      <c r="G78" s="810" t="inlineStr"/>
-      <c r="H78" s="810" t="inlineStr"/>
-      <c r="I78" s="810" t="inlineStr"/>
-      <c r="J78" s="810" t="inlineStr"/>
+      <c r="B78" s="826" t="inlineStr"/>
+      <c r="C78" s="826" t="inlineStr"/>
+      <c r="D78" s="826" t="inlineStr"/>
+      <c r="E78" s="826" t="inlineStr"/>
+      <c r="F78" s="826" t="inlineStr"/>
+      <c r="G78" s="826" t="inlineStr"/>
+      <c r="H78" s="826" t="inlineStr"/>
+      <c r="I78" s="826" t="inlineStr"/>
+      <c r="J78" s="826" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="811" t="inlineStr">
+      <c r="A79" s="849" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B79" s="811" t="inlineStr">
+      <c r="B79" s="849" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="C79" s="811" t="inlineStr">
+      <c r="C79" s="849" t="inlineStr">
         <is>
           <t>Irelia</t>
         </is>
       </c>
-      <c r="D79" s="811" t="inlineStr">
+      <c r="D79" s="849" t="inlineStr">
         <is>
           <t>Ezreal</t>
         </is>
       </c>
-      <c r="E79" s="811" t="inlineStr">
+      <c r="E79" s="849" t="inlineStr">
         <is>
           <t>Kai'Sa</t>
         </is>
       </c>
-      <c r="F79" s="811" t="inlineStr">
+      <c r="F79" s="849" t="inlineStr">
         <is>
           <t>Master Yi</t>
         </is>
       </c>
-      <c r="G79" s="811" t="inlineStr">
+      <c r="G79" s="849" t="inlineStr">
         <is>
           <t>Viktor</t>
         </is>
       </c>
-      <c r="H79" s="811" t="inlineStr">
+      <c r="H79" s="849" t="inlineStr">
         <is>
           <t>Sivir</t>
         </is>
       </c>
-      <c r="I79" s="811" t="inlineStr">
+      <c r="I79" s="849" t="inlineStr">
         <is>
           <t>Annie</t>
         </is>
       </c>
-      <c r="J79" s="811" t="inlineStr"/>
+      <c r="J79" s="849" t="inlineStr"/>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="812" t="inlineStr">
@@ -29713,30 +30046,30 @@
           <t>My Deck → vs Meta ↓</t>
         </is>
       </c>
-      <c r="B88" s="814" t="inlineStr">
+      <c r="B88" s="839" t="inlineStr">
         <is>
           <t>Azir</t>
         </is>
       </c>
-      <c r="C88" s="815" t="inlineStr">
+      <c r="C88" s="840" t="inlineStr">
         <is>
           <t>Volibear</t>
         </is>
       </c>
-      <c r="D88" s="816" t="inlineStr">
+      <c r="D88" s="841" t="inlineStr">
         <is>
           <t>Miss Fortune</t>
         </is>
       </c>
-      <c r="E88" s="817" t="inlineStr">
+      <c r="E88" s="842" t="inlineStr">
         <is>
           <t>Draven</t>
         </is>
       </c>
-      <c r="F88" s="810" t="inlineStr"/>
-      <c r="G88" s="810" t="inlineStr"/>
-      <c r="H88" s="810" t="inlineStr"/>
-      <c r="I88" s="810" t="inlineStr"/>
+      <c r="F88" s="826" t="inlineStr"/>
+      <c r="G88" s="826" t="inlineStr"/>
+      <c r="H88" s="826" t="inlineStr"/>
+      <c r="I88" s="826" t="inlineStr"/>
       <c r="J88" s="809" t="inlineStr">
         <is>
           <t>Tournament Context</t>
@@ -30000,7 +30333,7 @@
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="821" t="inlineStr">
+      <c r="A97" s="838" t="inlineStr">
         <is>
           <t>AVG vs Top 8 Meta (our 4 decks)</t>
         </is>
@@ -30021,30 +30354,30 @@
         <f>AVERAGE(E89:E96)</f>
         <v/>
       </c>
-      <c r="F97" s="822" t="inlineStr"/>
-      <c r="G97" s="822" t="inlineStr"/>
-      <c r="H97" s="822" t="inlineStr"/>
-      <c r="I97" s="822" t="inlineStr"/>
-      <c r="J97" s="822" t="inlineStr"/>
+      <c r="F97" s="844" t="inlineStr"/>
+      <c r="G97" s="844" t="inlineStr"/>
+      <c r="H97" s="844" t="inlineStr"/>
+      <c r="I97" s="844" t="inlineStr"/>
+      <c r="J97" s="844" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="793" t="inlineStr">
+      <c r="A99" s="836" t="inlineStr">
         <is>
           <t>HOW TO KEEP META DATA UPDATED</t>
         </is>
       </c>
-      <c r="B99" s="794" t="inlineStr"/>
-      <c r="C99" s="794" t="inlineStr"/>
-      <c r="D99" s="794" t="inlineStr"/>
-      <c r="E99" s="794" t="inlineStr"/>
-      <c r="F99" s="794" t="inlineStr"/>
-      <c r="G99" s="794" t="inlineStr"/>
-      <c r="H99" s="794" t="inlineStr"/>
-      <c r="I99" s="794" t="inlineStr"/>
-      <c r="J99" s="794" t="inlineStr"/>
+      <c r="B99" s="837" t="inlineStr"/>
+      <c r="C99" s="837" t="inlineStr"/>
+      <c r="D99" s="837" t="inlineStr"/>
+      <c r="E99" s="837" t="inlineStr"/>
+      <c r="F99" s="837" t="inlineStr"/>
+      <c r="G99" s="837" t="inlineStr"/>
+      <c r="H99" s="837" t="inlineStr"/>
+      <c r="I99" s="837" t="inlineStr"/>
+      <c r="J99" s="837" t="inlineStr"/>
     </row>
     <row r="100" ht="48" customHeight="1">
-      <c r="A100" s="823" t="inlineStr">
+      <c r="A100" s="850" t="inlineStr">
         <is>
           <t>After every major tournament:</t>
         </is>
@@ -30054,17 +30387,17 @@
           <t>Visit riftbound.gg/tier-list or riftdecks.com for updated win rates and conversion rates. Update the tournament win rate in column D of the meta table above. Update the META DECK PARAMETERS (yellow cells) to reflect any shifts — if Irelia gets a new card that makes her faster, lower her Speed input from 5 to 4.5.</t>
         </is>
       </c>
-      <c r="C100" s="824" t="inlineStr"/>
-      <c r="D100" s="824" t="inlineStr"/>
-      <c r="E100" s="824" t="inlineStr"/>
-      <c r="F100" s="824" t="inlineStr"/>
-      <c r="G100" s="824" t="inlineStr"/>
-      <c r="H100" s="824" t="inlineStr"/>
-      <c r="I100" s="824" t="inlineStr"/>
-      <c r="J100" s="824" t="inlineStr"/>
+      <c r="C100" s="851" t="inlineStr"/>
+      <c r="D100" s="851" t="inlineStr"/>
+      <c r="E100" s="851" t="inlineStr"/>
+      <c r="F100" s="851" t="inlineStr"/>
+      <c r="G100" s="851" t="inlineStr"/>
+      <c r="H100" s="851" t="inlineStr"/>
+      <c r="I100" s="851" t="inlineStr"/>
+      <c r="J100" s="851" t="inlineStr"/>
     </row>
     <row r="101" ht="48" customHeight="1">
-      <c r="A101" s="823" t="inlineStr">
+      <c r="A101" s="850" t="inlineStr">
         <is>
           <t>When a new set releases (next after Spiritforged):</t>
         </is>
@@ -30074,17 +30407,17 @@
           <t>New legends may enter the meta. Add them as new rows in the meta table. Add their parameters to the META DECK PARAMETERS columns. The formulas auto-extend — just copy a row formula pattern.</t>
         </is>
       </c>
-      <c r="C101" s="824" t="inlineStr"/>
-      <c r="D101" s="824" t="inlineStr"/>
-      <c r="E101" s="824" t="inlineStr"/>
-      <c r="F101" s="824" t="inlineStr"/>
-      <c r="G101" s="824" t="inlineStr"/>
-      <c r="H101" s="824" t="inlineStr"/>
-      <c r="I101" s="824" t="inlineStr"/>
-      <c r="J101" s="824" t="inlineStr"/>
+      <c r="C101" s="851" t="inlineStr"/>
+      <c r="D101" s="851" t="inlineStr"/>
+      <c r="E101" s="851" t="inlineStr"/>
+      <c r="F101" s="851" t="inlineStr"/>
+      <c r="G101" s="851" t="inlineStr"/>
+      <c r="H101" s="851" t="inlineStr"/>
+      <c r="I101" s="851" t="inlineStr"/>
+      <c r="J101" s="851" t="inlineStr"/>
     </row>
     <row r="102" ht="48" customHeight="1">
-      <c r="A102" s="823" t="inlineStr">
+      <c r="A102" s="850" t="inlineStr">
         <is>
           <t>If top 8 has duplicate legends:</t>
         </is>
@@ -30094,17 +30427,17 @@
           <t>Use unique builds as separate entries. Draven Midrange and Draven Miracle are different decks. Give each its own parameter column with slightly different Speed and Peak Might values. Example: Midrange Draven Speed=4, Miracle Draven Speed=5 (slower setup, explosive payoff).</t>
         </is>
       </c>
-      <c r="C102" s="824" t="inlineStr"/>
-      <c r="D102" s="824" t="inlineStr"/>
-      <c r="E102" s="824" t="inlineStr"/>
-      <c r="F102" s="824" t="inlineStr"/>
-      <c r="G102" s="824" t="inlineStr"/>
-      <c r="H102" s="824" t="inlineStr"/>
-      <c r="I102" s="824" t="inlineStr"/>
-      <c r="J102" s="824" t="inlineStr"/>
+      <c r="C102" s="851" t="inlineStr"/>
+      <c r="D102" s="851" t="inlineStr"/>
+      <c r="E102" s="851" t="inlineStr"/>
+      <c r="F102" s="851" t="inlineStr"/>
+      <c r="G102" s="851" t="inlineStr"/>
+      <c r="H102" s="851" t="inlineStr"/>
+      <c r="I102" s="851" t="inlineStr"/>
+      <c r="J102" s="851" t="inlineStr"/>
     </row>
     <row r="103" ht="48" customHeight="1">
-      <c r="A103" s="823" t="inlineStr">
+      <c r="A103" s="850" t="inlineStr">
         <is>
           <t>To add 8 unique decks when top 8 has duplicates:</t>
         </is>
@@ -30114,17 +30447,17 @@
           <t>Prioritize by archetype, not legend name. If Draven fills 4 spots, take the 2 builds plus the next 6 unique legends from the tier list. Goal: 8 mechanically distinct matchups so the simulation covers the full range of strategies you'll face.</t>
         </is>
       </c>
-      <c r="C103" s="824" t="inlineStr"/>
-      <c r="D103" s="824" t="inlineStr"/>
-      <c r="E103" s="824" t="inlineStr"/>
-      <c r="F103" s="824" t="inlineStr"/>
-      <c r="G103" s="824" t="inlineStr"/>
-      <c r="H103" s="824" t="inlineStr"/>
-      <c r="I103" s="824" t="inlineStr"/>
-      <c r="J103" s="824" t="inlineStr"/>
+      <c r="C103" s="851" t="inlineStr"/>
+      <c r="D103" s="851" t="inlineStr"/>
+      <c r="E103" s="851" t="inlineStr"/>
+      <c r="F103" s="851" t="inlineStr"/>
+      <c r="G103" s="851" t="inlineStr"/>
+      <c r="H103" s="851" t="inlineStr"/>
+      <c r="I103" s="851" t="inlineStr"/>
+      <c r="J103" s="851" t="inlineStr"/>
     </row>
     <row r="104" ht="48" customHeight="1">
-      <c r="A104" s="823" t="inlineStr">
+      <c r="A104" s="850" t="inlineStr">
         <is>
           <t>Calibrating after real games:</t>
         </is>
@@ -30134,14 +30467,3226 @@
           <t>Most important step. After 10+ games in a matchup, update the parameter that matters most. Lost to Kai'Sa more than expected? Increase her Peak Might from 5.0 to 5.5. Beating Irelia consistently? Raise your own Field Coverage input. The model is only as good as the inputs.</t>
         </is>
       </c>
-      <c r="C104" s="824" t="inlineStr"/>
-      <c r="D104" s="824" t="inlineStr"/>
-      <c r="E104" s="824" t="inlineStr"/>
-      <c r="F104" s="824" t="inlineStr"/>
-      <c r="G104" s="824" t="inlineStr"/>
-      <c r="H104" s="824" t="inlineStr"/>
-      <c r="I104" s="824" t="inlineStr"/>
-      <c r="J104" s="824" t="inlineStr"/>
+      <c r="C104" s="851" t="inlineStr"/>
+      <c r="D104" s="851" t="inlineStr"/>
+      <c r="E104" s="851" t="inlineStr"/>
+      <c r="F104" s="851" t="inlineStr"/>
+      <c r="G104" s="851" t="inlineStr"/>
+      <c r="H104" s="851" t="inlineStr"/>
+      <c r="I104" s="851" t="inlineStr"/>
+      <c r="J104" s="851" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="852" t="inlineStr">
+        <is>
+          <t>LUCIAN PURIFIER — THE ARMORY | Fury+Body | Gear Stack | 40 Cards</t>
+        </is>
+      </c>
+      <c r="B1" s="853" t="inlineStr"/>
+      <c r="C1" s="853" t="inlineStr"/>
+      <c r="D1" s="853" t="inlineStr"/>
+      <c r="E1" s="853" t="inlineStr"/>
+      <c r="F1" s="853" t="inlineStr"/>
+      <c r="G1" s="853" t="inlineStr"/>
+      <c r="H1" s="853" t="inlineStr"/>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="854" t="inlineStr">
+        <is>
+          <t>STRATEGY — GEAR STACKING: Lucian Purifier legend makes EVERY equipped piece of gear give ASSAULT. Stack Hexdrinker + Long Sword + Doran's Blade + Warmog's Armor + Serrated Dirk on one unit. That's +6M base + ASSAULT 7 while attacking. A 3M Sentinel Adept becomes a 16M attacker. WEAPONMASTER units equip gear on arrival at 1 rune less — so the whole stack goes on instantly. Strike Down then lets your 16M unit deal 16 damage directly to any enemy. Kills everything without combat. Yone conquers an open field, deals damage equal to his Might to a unit hiding in opponent's base. Lucian Merciless conquers, readies himself, conquers AGAIN. Two fields one unit one turn.</t>
+        </is>
+      </c>
+      <c r="B2" s="855" t="inlineStr"/>
+      <c r="C2" s="855" t="inlineStr"/>
+      <c r="D2" s="855" t="inlineStr"/>
+      <c r="E2" s="855" t="inlineStr"/>
+      <c r="F2" s="855" t="inlineStr"/>
+      <c r="G2" s="855" t="inlineStr"/>
+      <c r="H2" s="855" t="inlineStr"/>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="856" t="inlineStr"/>
+      <c r="B3" s="856" t="inlineStr"/>
+      <c r="C3" s="856" t="inlineStr"/>
+      <c r="D3" s="856" t="inlineStr"/>
+      <c r="E3" s="856" t="inlineStr"/>
+      <c r="F3" s="856" t="inlineStr"/>
+      <c r="G3" s="856" t="inlineStr"/>
+      <c r="H3" s="856" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="857" t="inlineStr">
+        <is>
+          <t>HOW TO PLAY — A B C D E F G</t>
+        </is>
+      </c>
+      <c r="B4" s="853" t="inlineStr"/>
+      <c r="C4" s="853" t="inlineStr"/>
+      <c r="D4" s="853" t="inlineStr"/>
+      <c r="E4" s="853" t="inlineStr"/>
+      <c r="F4" s="853" t="inlineStr"/>
+      <c r="G4" s="853" t="inlineStr"/>
+      <c r="H4" s="853" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="858" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="859" t="inlineStr">
+        <is>
+          <t>AWAKEN</t>
+        </is>
+      </c>
+      <c r="C5" s="685" t="inlineStr">
+        <is>
+          <t>Ready all units. Note which ones have gear equipped. That's your artillery for this turn.</t>
+        </is>
+      </c>
+      <c r="D5" s="860" t="inlineStr"/>
+      <c r="E5" s="860" t="inlineStr"/>
+      <c r="F5" s="860" t="inlineStr"/>
+      <c r="G5" s="860" t="inlineStr"/>
+      <c r="H5" s="860" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="861" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="862" t="inlineStr">
+        <is>
+          <t>BEGINNING</t>
+        </is>
+      </c>
+      <c r="C6" s="685" t="inlineStr">
+        <is>
+          <t>Score held fields. Equipped units with ASSAULT are about to win every combat.</t>
+        </is>
+      </c>
+      <c r="D6" s="860" t="inlineStr"/>
+      <c r="E6" s="860" t="inlineStr"/>
+      <c r="F6" s="860" t="inlineStr"/>
+      <c r="G6" s="860" t="inlineStr"/>
+      <c r="H6" s="860" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="863" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="864" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="C7" s="685" t="inlineStr">
+        <is>
+          <t>Draw Fury+Body runes. Plan: which unit gets which gear? Prioritize the biggest carrier.</t>
+        </is>
+      </c>
+      <c r="D7" s="860" t="inlineStr"/>
+      <c r="E7" s="860" t="inlineStr"/>
+      <c r="F7" s="860" t="inlineStr"/>
+      <c r="G7" s="860" t="inlineStr"/>
+      <c r="H7" s="860" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="865" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="866" t="inlineStr">
+        <is>
+          <t>DRAW</t>
+        </is>
+      </c>
+      <c r="C8" s="685" t="inlineStr">
+        <is>
+          <t>Draw 1. Yordle Explorer draws 1 extra whenever you play a card costing 2+ runes — gear triggers this.</t>
+        </is>
+      </c>
+      <c r="D8" s="860" t="inlineStr"/>
+      <c r="E8" s="860" t="inlineStr"/>
+      <c r="F8" s="860" t="inlineStr"/>
+      <c r="G8" s="860" t="inlineStr"/>
+      <c r="H8" s="860" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="867" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="868" t="inlineStr">
+        <is>
+          <t>EQUIP</t>
+        </is>
+      </c>
+      <c r="C9" s="685" t="inlineStr">
+        <is>
+          <t>Play a WEAPONMASTER unit (Yone/Lucian/Akshan/Sentinel) — equip gear at 1 rune less on entry. Stack as many gears as runes allow.</t>
+        </is>
+      </c>
+      <c r="D9" s="860" t="inlineStr"/>
+      <c r="E9" s="860" t="inlineStr"/>
+      <c r="F9" s="860" t="inlineStr"/>
+      <c r="G9" s="860" t="inlineStr"/>
+      <c r="H9" s="860" t="inlineStr"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="869" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B10" s="870" t="inlineStr">
+        <is>
+          <t>FIELD</t>
+        </is>
+      </c>
+      <c r="C10" s="685" t="inlineStr">
+        <is>
+          <t>Send fully-loaded carrier to a field. Play Strike Down: it deals damage equal to its Might to any enemy unit. Kills the 9M dragon. Kills anything.</t>
+        </is>
+      </c>
+      <c r="D10" s="860" t="inlineStr"/>
+      <c r="E10" s="860" t="inlineStr"/>
+      <c r="F10" s="860" t="inlineStr"/>
+      <c r="G10" s="860" t="inlineStr"/>
+      <c r="H10" s="860" t="inlineStr"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="871" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="872" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C11" s="685" t="inlineStr">
+        <is>
+          <t>Attack. Carrier has ASSAULT from every gear + legend. Punch First reaction for +6M more. Show of Strength +3M. Win. Yone deals bonus damage to their base unit on open conquests.</t>
+        </is>
+      </c>
+      <c r="D11" s="860" t="inlineStr"/>
+      <c r="E11" s="860" t="inlineStr"/>
+      <c r="F11" s="860" t="inlineStr"/>
+      <c r="G11" s="860" t="inlineStr"/>
+      <c r="H11" s="860" t="inlineStr"/>
+    </row>
+    <row r="12" ht="4" customHeight="1">
+      <c r="A12" s="856" t="inlineStr"/>
+      <c r="B12" s="856" t="inlineStr"/>
+      <c r="C12" s="856" t="inlineStr"/>
+      <c r="D12" s="856" t="inlineStr"/>
+      <c r="E12" s="856" t="inlineStr"/>
+      <c r="F12" s="856" t="inlineStr"/>
+      <c r="G12" s="856" t="inlineStr"/>
+      <c r="H12" s="856" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="857" t="inlineStr">
+        <is>
+          <t>LEGEND + CHAMPION ZONE</t>
+        </is>
+      </c>
+      <c r="B13" s="853" t="inlineStr"/>
+      <c r="C13" s="853" t="inlineStr"/>
+      <c r="D13" s="853" t="inlineStr"/>
+      <c r="E13" s="853" t="inlineStr"/>
+      <c r="F13" s="853" t="inlineStr"/>
+      <c r="G13" s="853" t="inlineStr"/>
+      <c r="H13" s="853" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B14" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C14" s="873" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="D14" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E14" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F14" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G14" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H14" s="873" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="874" t="inlineStr">
+        <is>
+          <t>SFD-183</t>
+        </is>
+      </c>
+      <c r="B15" s="874" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C15" s="875" t="inlineStr">
+        <is>
+          <t>Legend Zone</t>
+        </is>
+      </c>
+      <c r="D15" s="875" t="inlineStr">
+        <is>
+          <t>Lucian - Purifier</t>
+        </is>
+      </c>
+      <c r="E15" s="876" t="inlineStr">
+        <is>
+          <t>Fury;Body</t>
+        </is>
+      </c>
+      <c r="F15" s="877" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" s="877" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" s="222" t="inlineStr">
+        <is>
+          <t>Lucian - Purifier. Your Equipment EACH give ASSAULT (+1M while attacking). 5 gears = +5M on top of gear stats. Stack Hexdrinker x3 alone = +3M base + ASSAULT 3 while attacking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="878" t="inlineStr">
+        <is>
+          <t>SFD-116</t>
+        </is>
+      </c>
+      <c r="B16" s="878" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C16" s="879" t="inlineStr">
+        <is>
+          <t>Champion Zone</t>
+        </is>
+      </c>
+      <c r="D16" s="879" t="inlineStr">
+        <is>
+          <t>Yone - Blademaster</t>
+        </is>
+      </c>
+      <c r="E16" s="880" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F16" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="173" t="inlineStr">
+        <is>
+          <t>Yone - Blademaster. 5/5. WEAPONMASTER: equip one gear at 1 rune less on play. When I conquer an OPEN battlefield: deal damage equal to my Might to an enemy unit in a base. Bypass defense entirely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="4" customHeight="1">
+      <c r="A17" s="856" t="inlineStr"/>
+      <c r="B17" s="856" t="inlineStr"/>
+      <c r="C17" s="856" t="inlineStr"/>
+      <c r="D17" s="856" t="inlineStr"/>
+      <c r="E17" s="856" t="inlineStr"/>
+      <c r="F17" s="856" t="inlineStr"/>
+      <c r="G17" s="856" t="inlineStr"/>
+      <c r="H17" s="856" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="857" t="inlineStr">
+        <is>
+          <t>MAIN DECK — 40 Cards</t>
+        </is>
+      </c>
+      <c r="B18" s="853" t="inlineStr"/>
+      <c r="C18" s="853" t="inlineStr"/>
+      <c r="D18" s="853" t="inlineStr"/>
+      <c r="E18" s="853" t="inlineStr"/>
+      <c r="F18" s="853" t="inlineStr"/>
+      <c r="G18" s="853" t="inlineStr"/>
+      <c r="H18" s="853" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B19" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C19" s="873" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D19" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E19" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F19" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G19" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H19" s="873" t="inlineStr">
+        <is>
+          <t>What It Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="878" t="inlineStr">
+        <is>
+          <t>OGN-132</t>
+        </is>
+      </c>
+      <c r="B20" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="880" t="inlineStr">
+        <is>
+          <t>UTILITY</t>
+        </is>
+      </c>
+      <c r="D20" s="879" t="inlineStr">
+        <is>
+          <t>First Mate</t>
+        </is>
+      </c>
+      <c r="E20" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F20" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="173" t="inlineStr">
+        <is>
+          <t>First Mate. When you play me, ready another unit. Ready Yone after equipping him. He attacks immediately with full gear stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="874" t="inlineStr">
+        <is>
+          <t>SFD-008</t>
+        </is>
+      </c>
+      <c r="B21" s="874" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="876" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D21" s="875" t="inlineStr">
+        <is>
+          <t>Sentinel Adept</t>
+        </is>
+      </c>
+      <c r="E21" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F21" s="877" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G21" s="877" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" s="222" t="inlineStr">
+        <is>
+          <t>Sentinel Adept. 3/3. WEAPONMASTER. Standard gear carrier. Equips any gear at 1 rune less. Cheap and reliable. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="874" t="inlineStr">
+        <is>
+          <t>SFD-009</t>
+        </is>
+      </c>
+      <c r="B22" s="874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="876" t="inlineStr">
+        <is>
+          <t>GEAR</t>
+        </is>
+      </c>
+      <c r="D22" s="875" t="inlineStr">
+        <is>
+          <t>Serrated Dirk</t>
+        </is>
+      </c>
+      <c r="E22" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F22" s="877" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="877" t="inlineStr"/>
+      <c r="H22" s="222" t="inlineStr">
+        <is>
+          <t>Serrated Dirk. EQUIP Fury. ASSAULT 2. With Lucian legend = ASSAULT 3 while attacking. Cheapest damage spike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="874" t="inlineStr">
+        <is>
+          <t>SFD-022</t>
+        </is>
+      </c>
+      <c r="B23" s="874" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="876" t="inlineStr">
+        <is>
+          <t>GEAR</t>
+        </is>
+      </c>
+      <c r="D23" s="875" t="inlineStr">
+        <is>
+          <t>Long Sword</t>
+        </is>
+      </c>
+      <c r="E23" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F23" s="877" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" s="877" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="222" t="inlineStr">
+        <is>
+          <t>Long Sword. QUICK-DRAW = play as reaction, attaches instantly. EQUIP Fury +2M. With legend = +2M + ASSAULT 1. Surprise mid-combat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="878" t="inlineStr">
+        <is>
+          <t>SFD-092</t>
+        </is>
+      </c>
+      <c r="B24" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="880" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D24" s="879" t="inlineStr">
+        <is>
+          <t>Combat Chef</t>
+        </is>
+      </c>
+      <c r="E24" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F24" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G24" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" s="173" t="inlineStr">
+        <is>
+          <t>Combat Chef. 5/5. WEAPONMASTER. Big late carrier. 5M base + 5 gears = 10M base + ASSAULT 9 = 19M attacker. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="878" t="inlineStr">
+        <is>
+          <t>SFD-095</t>
+        </is>
+      </c>
+      <c r="B25" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="880" t="inlineStr">
+        <is>
+          <t>GEAR</t>
+        </is>
+      </c>
+      <c r="D25" s="879" t="inlineStr">
+        <is>
+          <t>Doran's Blade</t>
+        </is>
+      </c>
+      <c r="E25" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F25" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="173" t="inlineStr">
+        <is>
+          <t>Doran's Blade. EQUIP Body. +2M base. With legend = +2M + ASSAULT 1. Pure stat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="878" t="inlineStr">
+        <is>
+          <t>SFD-096</t>
+        </is>
+      </c>
+      <c r="B26" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="880" t="inlineStr">
+        <is>
+          <t>MOBILITY</t>
+        </is>
+      </c>
+      <c r="D26" s="879" t="inlineStr">
+        <is>
+          <t>Laurent Bladekeeper</t>
+        </is>
+      </c>
+      <c r="E26" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F26" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G26" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" s="173" t="inlineStr">
+        <is>
+          <t>Laurent Bladekeeper. 3/3 GANKING. Contests both fields. Can carry gear to either field. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="878" t="inlineStr">
+        <is>
+          <t>SFD-097</t>
+        </is>
+      </c>
+      <c r="B27" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="880" t="inlineStr">
+        <is>
+          <t>PUMP</t>
+        </is>
+      </c>
+      <c r="D27" s="879" t="inlineStr">
+        <is>
+          <t>Punch First</t>
+        </is>
+      </c>
+      <c r="E27" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F27" s="881" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" s="173" t="inlineStr">
+        <is>
+          <t>Punch First. +5M this turn. With Lucian legend = +6M (ASSAULT counts while attacking). On your 16M carrier = 22M one turn. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="878" t="inlineStr">
+        <is>
+          <t>SFD-099</t>
+        </is>
+      </c>
+      <c r="B28" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="880" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D28" s="879" t="inlineStr">
+        <is>
+          <t>Veteran Poro</t>
+        </is>
+      </c>
+      <c r="E28" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F28" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="173" t="inlineStr">
+        <is>
+          <t>Veteran Poro. 2/2. WEAPONMASTER. Cheapest carrier. Gets gear on turn 2. Even a 2/2 with Hexdrinker + Dirk = 2M base + ASSAULT 4 = 6M attacker turn 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="878" t="inlineStr">
+        <is>
+          <t>SFD-102</t>
+        </is>
+      </c>
+      <c r="B29" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="880" t="inlineStr">
+        <is>
+          <t>GEAR</t>
+        </is>
+      </c>
+      <c r="D29" s="879" t="inlineStr">
+        <is>
+          <t>Hexdrinker</t>
+        </is>
+      </c>
+      <c r="E29" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F29" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G29" s="881" t="inlineStr"/>
+      <c r="H29" s="173" t="inlineStr">
+        <is>
+          <t>Hexdrinker. EQUIP Body. +1M + DEFLECT. With legend = DEFLECT (opponent pays rune to target) + ASSAULT 1. Protection + attack. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="878" t="inlineStr">
+        <is>
+          <t>SFD-106</t>
+        </is>
+      </c>
+      <c r="B30" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="880" t="inlineStr">
+        <is>
+          <t>PUMP</t>
+        </is>
+      </c>
+      <c r="D30" s="879" t="inlineStr">
+        <is>
+          <t>Show of Strength</t>
+        </is>
+      </c>
+      <c r="E30" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F30" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" s="881" t="inlineStr"/>
+      <c r="H30" s="173" t="inlineStr">
+        <is>
+          <t>Show of Strength. REACTION +3M this turn to any unit. Surprise in combat. With legend = +4M. Wins trades opponent thought they were winning. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="878" t="inlineStr">
+        <is>
+          <t>SFD-107</t>
+        </is>
+      </c>
+      <c r="B31" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="880" t="inlineStr">
+        <is>
+          <t>REMOVAL</t>
+        </is>
+      </c>
+      <c r="D31" s="879" t="inlineStr">
+        <is>
+          <t>Strike Down</t>
+        </is>
+      </c>
+      <c r="E31" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F31" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G31" s="881" t="inlineStr"/>
+      <c r="H31" s="173" t="inlineStr">
+        <is>
+          <t>Strike Down. Choose equipped unit. It deals damage equal to its Might to an enemy unit. 16M unit = Strike Down deals 16. Kills anything. No combat needed. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="878" t="inlineStr">
+        <is>
+          <t>SFD-108</t>
+        </is>
+      </c>
+      <c r="B32" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="880" t="inlineStr">
+        <is>
+          <t>GEAR</t>
+        </is>
+      </c>
+      <c r="D32" s="879" t="inlineStr">
+        <is>
+          <t>Warmog's Armor</t>
+        </is>
+      </c>
+      <c r="E32" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F32" s="881" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" s="173" t="inlineStr">
+        <is>
+          <t>Warmog's Armor. EQUIP Body. When I conquer = buff me (+1M buff). With legend = buff + ASSAULT 1. Grows every conquest. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="878" t="inlineStr">
+        <is>
+          <t>SFD-109</t>
+        </is>
+      </c>
+      <c r="B33" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="880" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D33" s="879" t="inlineStr">
+        <is>
+          <t>Akshan - Mischievous</t>
+        </is>
+      </c>
+      <c r="E33" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F33" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G33" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H33" s="173" t="inlineStr">
+        <is>
+          <t>Akshan. 4/4. WEAPONMASTER. Pay Body+Body = steal an enemy gear and attach it to me. Take opponent's equipment, use it against them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="878" t="inlineStr">
+        <is>
+          <t>SFD-113</t>
+        </is>
+      </c>
+      <c r="B34" s="878" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="880" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D34" s="879" t="inlineStr">
+        <is>
+          <t>Lucian - Merciless</t>
+        </is>
+      </c>
+      <c r="E34" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F34" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G34" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" s="173" t="inlineStr">
+        <is>
+          <t>Lucian - Merciless. 3/3. WEAPONMASTER. First conquer this turn = ready me. He conquers twice. Two fields, one unit, one turn. Run x2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="878" t="inlineStr">
+        <is>
+          <t>SFD-116</t>
+        </is>
+      </c>
+      <c r="B35" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="880" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER</t>
+        </is>
+      </c>
+      <c r="D35" s="879" t="inlineStr">
+        <is>
+          <t>Yone - Blademaster</t>
+        </is>
+      </c>
+      <c r="E35" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F35" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G35" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H35" s="173" t="inlineStr">
+        <is>
+          <t>Yone - Blademaster. 5/5. WEAPONMASTER. Conquer open field = deal M damage to base unit. Champion zone. Kills hiding units. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="882" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B36" s="882" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" s="853" t="inlineStr"/>
+      <c r="D36" s="853" t="inlineStr"/>
+      <c r="E36" s="853" t="inlineStr"/>
+      <c r="F36" s="853" t="inlineStr"/>
+      <c r="G36" s="853" t="inlineStr"/>
+      <c r="H36" s="853" t="inlineStr"/>
+    </row>
+    <row r="37" ht="4" customHeight="1">
+      <c r="A37" s="856" t="inlineStr"/>
+      <c r="B37" s="856" t="inlineStr"/>
+      <c r="C37" s="856" t="inlineStr"/>
+      <c r="D37" s="856" t="inlineStr"/>
+      <c r="E37" s="856" t="inlineStr"/>
+      <c r="F37" s="856" t="inlineStr"/>
+      <c r="G37" s="856" t="inlineStr"/>
+      <c r="H37" s="856" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="883" t="inlineStr">
+        <is>
+          <t>RUNE DECK (12)</t>
+        </is>
+      </c>
+      <c r="B38" s="642" t="inlineStr">
+        <is>
+          <t>6x Fury (Red) + 6x Body (Orange) — Clean. No overlap with other decks.</t>
+        </is>
+      </c>
+      <c r="C38" s="884" t="inlineStr"/>
+      <c r="D38" s="884" t="inlineStr"/>
+      <c r="E38" s="884" t="inlineStr"/>
+      <c r="F38" s="884" t="inlineStr"/>
+      <c r="G38" s="884" t="inlineStr"/>
+      <c r="H38" s="884" t="inlineStr"/>
+    </row>
+    <row r="39" ht="4" customHeight="1">
+      <c r="A39" s="856" t="inlineStr"/>
+      <c r="B39" s="856" t="inlineStr"/>
+      <c r="C39" s="856" t="inlineStr"/>
+      <c r="D39" s="856" t="inlineStr"/>
+      <c r="E39" s="856" t="inlineStr"/>
+      <c r="F39" s="856" t="inlineStr"/>
+      <c r="G39" s="856" t="inlineStr"/>
+      <c r="H39" s="856" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="857" t="inlineStr">
+        <is>
+          <t>SIDEBOARD — 8 Cards</t>
+        </is>
+      </c>
+      <c r="B40" s="853" t="inlineStr"/>
+      <c r="C40" s="853" t="inlineStr"/>
+      <c r="D40" s="853" t="inlineStr"/>
+      <c r="E40" s="853" t="inlineStr"/>
+      <c r="F40" s="853" t="inlineStr"/>
+      <c r="G40" s="853" t="inlineStr"/>
+      <c r="H40" s="853" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B41" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C41" s="873" t="inlineStr">
+        <is>
+          <t>Matchup</t>
+        </is>
+      </c>
+      <c r="D41" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E41" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F41" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G41" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H41" s="873" t="inlineStr">
+        <is>
+          <t>G2 Plan + Swap</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="878" t="inlineStr">
+        <is>
+          <t>OGN-157</t>
+        </is>
+      </c>
+      <c r="B42" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="879" t="inlineStr">
+        <is>
+          <t>vs Control / Big Units</t>
+        </is>
+      </c>
+      <c r="D42" s="879" t="inlineStr">
+        <is>
+          <t>Udyr - Wildman</t>
+        </is>
+      </c>
+      <c r="E42" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F42" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G42" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H42" s="173" t="inlineStr">
+        <is>
+          <t>Udyr - Wildman. 6/6. Spend my buff: deal 2 to a unit, +2M, or ready me. Lee Sin legend buffs him every turn. Spend buff = clear a blocker AND ready Udyr to attack. || SWAP: OUT: SFD-099 Veteran Poro x2, SFD-009 Dirk x1 | IN: Udyr x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="874" t="inlineStr">
+        <is>
+          <t>SFD-005</t>
+        </is>
+      </c>
+      <c r="B43" s="874" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="875" t="inlineStr">
+        <is>
+          <t>vs Gear Decks / Azir</t>
+        </is>
+      </c>
+      <c r="D43" s="875" t="inlineStr">
+        <is>
+          <t>Detonate</t>
+        </is>
+      </c>
+      <c r="E43" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F43" s="877" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="877" t="inlineStr"/>
+      <c r="H43" s="222" t="inlineStr">
+        <is>
+          <t>Detonate. Kill a gear. Its controller draws 2. Strip opponent's equipment. Then they draw 2 — but their unit is now 3M smaller. Against Azir: kill their gear, troops shrink. || SWAP: OUT: OGN-132 x1, SFD-095 x1, SFD-022 x1 | IN: Detonate x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="874" t="inlineStr">
+        <is>
+          <t>SFD-030</t>
+        </is>
+      </c>
+      <c r="B44" s="874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="875" t="inlineStr">
+        <is>
+          <t>vs Control</t>
+        </is>
+      </c>
+      <c r="D44" s="875" t="inlineStr">
+        <is>
+          <t>Skyfall of Areion</t>
+        </is>
+      </c>
+      <c r="E44" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F44" s="877" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G44" s="877" t="inlineStr"/>
+      <c r="H44" s="222" t="inlineStr">
+        <is>
+          <t>Skyfall of Areion. EQUIP Fury. +2M. My HOLD effects are also CONQUER effects and vice versa. Hold a field = score like a conquest. Conquer = also gets hold bonuses. Stacks Warmog every turn. || SWAP: OUT: SFD-022 x1 | IN: Skyfall x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="874" t="inlineStr">
+        <is>
+          <t>SFD-019</t>
+        </is>
+      </c>
+      <c r="B45" s="874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="875" t="inlineStr">
+        <is>
+          <t>vs Attrition</t>
+        </is>
+      </c>
+      <c r="D45" s="875" t="inlineStr">
+        <is>
+          <t>Assembly Rig</t>
+        </is>
+      </c>
+      <c r="E45" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F45" s="877" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G45" s="877" t="inlineStr"/>
+      <c r="H45" s="222" t="inlineStr">
+        <is>
+          <t>Assembly Rig. Recycle a unit from trash, play 3M Mech token. Brings dead carriers back as Mechs. When your unit dies, Rig recycles it and spawns a replacement. || SWAP: OUT: OGN-132 x1 | IN: Assembly Rig x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="4" customHeight="1">
+      <c r="A46" s="856" t="inlineStr"/>
+      <c r="B46" s="856" t="inlineStr"/>
+      <c r="C46" s="856" t="inlineStr"/>
+      <c r="D46" s="856" t="inlineStr"/>
+      <c r="E46" s="856" t="inlineStr"/>
+      <c r="F46" s="856" t="inlineStr"/>
+      <c r="G46" s="856" t="inlineStr"/>
+      <c r="H46" s="856" t="inlineStr"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="857" t="inlineStr">
+        <is>
+          <t>GOLDEN RULES</t>
+        </is>
+      </c>
+      <c r="B47" s="853" t="inlineStr"/>
+      <c r="C47" s="853" t="inlineStr"/>
+      <c r="D47" s="853" t="inlineStr"/>
+      <c r="E47" s="853" t="inlineStr"/>
+      <c r="F47" s="853" t="inlineStr"/>
+      <c r="G47" s="853" t="inlineStr"/>
+      <c r="H47" s="853" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="885" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B48" s="97" t="inlineStr">
+        <is>
+          <t>WEAPONMASTER on arrival: when you play Yone/Lucian/Akshan/Sentinel/Poro, equip one gear at 1 rune less immediately. Play Veteran Poro turn 2, equip Hexdrinker for 1 rune. Turn 2 you have a 3M DEFLECT ASSAULT unit.</t>
+        </is>
+      </c>
+      <c r="C48" s="886" t="inlineStr"/>
+      <c r="D48" s="886" t="inlineStr"/>
+      <c r="E48" s="886" t="inlineStr"/>
+      <c r="F48" s="886" t="inlineStr"/>
+      <c r="G48" s="886" t="inlineStr"/>
+      <c r="H48" s="886" t="inlineStr"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="887" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B49" s="101" t="inlineStr">
+        <is>
+          <t>STACK gear on your best carrier. Three Hexdrinkers + Long Sword + Dirk = +4M base + ASSAULT 7 while attacking. Carrier attacks as 12M+. Nothing blocks that profitably.</t>
+        </is>
+      </c>
+      <c r="C49" s="888" t="inlineStr"/>
+      <c r="D49" s="888" t="inlineStr"/>
+      <c r="E49" s="888" t="inlineStr"/>
+      <c r="F49" s="888" t="inlineStr"/>
+      <c r="G49" s="888" t="inlineStr"/>
+      <c r="H49" s="888" t="inlineStr"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="885" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B50" s="97" t="inlineStr">
+        <is>
+          <t>Strike Down before attacking. Play it, your equipped unit deals its Might as damage to the strongest enemy. Kill their 9M dragon without combat. Then attack the open field.</t>
+        </is>
+      </c>
+      <c r="C50" s="886" t="inlineStr"/>
+      <c r="D50" s="886" t="inlineStr"/>
+      <c r="E50" s="886" t="inlineStr"/>
+      <c r="F50" s="886" t="inlineStr"/>
+      <c r="G50" s="886" t="inlineStr"/>
+      <c r="H50" s="886" t="inlineStr"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="887" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B51" s="101" t="inlineStr">
+        <is>
+          <t>Lucian Merciless conquers, READIES HIMSELF, conquers again. If both fields are open or lightly defended: Lucian takes both fields in one turn. Score 2 points from one unit.</t>
+        </is>
+      </c>
+      <c r="C51" s="888" t="inlineStr"/>
+      <c r="D51" s="888" t="inlineStr"/>
+      <c r="E51" s="888" t="inlineStr"/>
+      <c r="F51" s="888" t="inlineStr"/>
+      <c r="G51" s="888" t="inlineStr"/>
+      <c r="H51" s="888" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="885" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B52" s="97" t="inlineStr">
+        <is>
+          <t>Yone conquers an open field then deals damage to an enemy unit hiding in their base. Stack gear on Yone: his Might damage hits their best unit before it even attacks.</t>
+        </is>
+      </c>
+      <c r="C52" s="886" t="inlineStr"/>
+      <c r="D52" s="886" t="inlineStr"/>
+      <c r="E52" s="886" t="inlineStr"/>
+      <c r="F52" s="886" t="inlineStr"/>
+      <c r="G52" s="886" t="inlineStr"/>
+      <c r="H52" s="886" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="887" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B53" s="101" t="inlineStr">
+        <is>
+          <t>Long Sword is QUICK-DRAW = plays as a reaction. When your unit is in combat and opponent thinks they win — react with Long Sword. Unit gains +2M + ASSAULT 1 mid-combat. Surprise kill.</t>
+        </is>
+      </c>
+      <c r="C53" s="888" t="inlineStr"/>
+      <c r="D53" s="888" t="inlineStr"/>
+      <c r="E53" s="888" t="inlineStr"/>
+      <c r="F53" s="888" t="inlineStr"/>
+      <c r="G53" s="888" t="inlineStr"/>
+      <c r="H53" s="888" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="885" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" s="97" t="inlineStr">
+        <is>
+          <t>Akshan steals enemy gear. Pay Body+Body extra when playing Akshan, take an attached equipment from their unit and attach it to Akshan. Their unit shrinks. Akshan grows.</t>
+        </is>
+      </c>
+      <c r="C54" s="886" t="inlineStr"/>
+      <c r="D54" s="886" t="inlineStr"/>
+      <c r="E54" s="886" t="inlineStr"/>
+      <c r="F54" s="886" t="inlineStr"/>
+      <c r="G54" s="886" t="inlineStr"/>
+      <c r="H54" s="886" t="inlineStr"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="887" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B55" s="101" t="inlineStr">
+        <is>
+          <t>G2 vs control: bring Udyr x3. Lee Sin legend buffs him every turn. Spend buff = deal 2 to enemy unit = kill their key blocker = Udyr attacks freely. Control decks can't answer a unit that removes its own blockers.</t>
+        </is>
+      </c>
+      <c r="C55" s="888" t="inlineStr"/>
+      <c r="D55" s="888" t="inlineStr"/>
+      <c r="E55" s="888" t="inlineStr"/>
+      <c r="F55" s="888" t="inlineStr"/>
+      <c r="G55" s="888" t="inlineStr"/>
+      <c r="H55" s="888" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="889" t="inlineStr">
+        <is>
+          <t>SETT — THE BOSS | Body+Order | The Undying | 40 Cards</t>
+        </is>
+      </c>
+      <c r="B1" s="890" t="inlineStr"/>
+      <c r="C1" s="890" t="inlineStr"/>
+      <c r="D1" s="890" t="inlineStr"/>
+      <c r="E1" s="890" t="inlineStr"/>
+      <c r="F1" s="890" t="inlineStr"/>
+      <c r="G1" s="890" t="inlineStr"/>
+      <c r="H1" s="890" t="inlineStr"/>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="891" t="inlineStr">
+        <is>
+          <t>STRATEGY — UNITS NEVER DIE: Sett legend — when a BUFFED unit would die, pay 1 rune + exhaust Sett = it goes to your BASE instead. Not dead. Every conquest readies Sett instantly. Opponent plays removal on your unit. Sett sends it home. They spent their resources. You replay it next turn. They do it again. Sett again. After 2-3 cycles they have no removal left. Your units are all still alive. Attack with everything. Overt Operation spends ALL buffs = ALL units ready simultaneously. Every unit attacks at once. They have no blockers. You score everything. Buff engine: Fae Dragon buffs 4 units on play. Wildclaw Shaman spends a buff to buff itself AND enter ready — free attacker. Unsung Hero: once MIGHTY (5M+), let it die. Sett saves it OR it draws 2 cards from DEATHKNELL.</t>
+        </is>
+      </c>
+      <c r="B2" s="892" t="inlineStr"/>
+      <c r="C2" s="892" t="inlineStr"/>
+      <c r="D2" s="892" t="inlineStr"/>
+      <c r="E2" s="892" t="inlineStr"/>
+      <c r="F2" s="892" t="inlineStr"/>
+      <c r="G2" s="892" t="inlineStr"/>
+      <c r="H2" s="892" t="inlineStr"/>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="856" t="inlineStr"/>
+      <c r="B3" s="856" t="inlineStr"/>
+      <c r="C3" s="856" t="inlineStr"/>
+      <c r="D3" s="856" t="inlineStr"/>
+      <c r="E3" s="856" t="inlineStr"/>
+      <c r="F3" s="856" t="inlineStr"/>
+      <c r="G3" s="856" t="inlineStr"/>
+      <c r="H3" s="856" t="inlineStr"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="893" t="inlineStr">
+        <is>
+          <t>HOW TO PLAY — A B C D E F G</t>
+        </is>
+      </c>
+      <c r="B4" s="890" t="inlineStr"/>
+      <c r="C4" s="890" t="inlineStr"/>
+      <c r="D4" s="890" t="inlineStr"/>
+      <c r="E4" s="890" t="inlineStr"/>
+      <c r="F4" s="890" t="inlineStr"/>
+      <c r="G4" s="890" t="inlineStr"/>
+      <c r="H4" s="890" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="858" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="859" t="inlineStr">
+        <is>
+          <t>AWAKEN</t>
+        </is>
+      </c>
+      <c r="C5" s="685" t="inlineStr">
+        <is>
+          <t>Everything readies. Check: which units have buffs on them? Those are your Sett save targets.</t>
+        </is>
+      </c>
+      <c r="D5" s="860" t="inlineStr"/>
+      <c r="E5" s="860" t="inlineStr"/>
+      <c r="F5" s="860" t="inlineStr"/>
+      <c r="G5" s="860" t="inlineStr"/>
+      <c r="H5" s="860" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="861" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="862" t="inlineStr">
+        <is>
+          <t>BEGINNING</t>
+        </is>
+      </c>
+      <c r="C6" s="685" t="inlineStr">
+        <is>
+          <t>Score held fields. Fiora Peerless has DOUBLE MIGHT in 1v1 — she becomes MIGHTY instantly for Fiora legend trigger.</t>
+        </is>
+      </c>
+      <c r="D6" s="860" t="inlineStr"/>
+      <c r="E6" s="860" t="inlineStr"/>
+      <c r="F6" s="860" t="inlineStr"/>
+      <c r="G6" s="860" t="inlineStr"/>
+      <c r="H6" s="860" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="863" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="864" t="inlineStr">
+        <is>
+          <t>CHANNEL</t>
+        </is>
+      </c>
+      <c r="C7" s="685" t="inlineStr">
+        <is>
+          <t>Draw Body+Order runes. Soaring Scout DEATHKNELL channels 1 rune when it dies — death generates resources.</t>
+        </is>
+      </c>
+      <c r="D7" s="860" t="inlineStr"/>
+      <c r="E7" s="860" t="inlineStr"/>
+      <c r="F7" s="860" t="inlineStr"/>
+      <c r="G7" s="860" t="inlineStr"/>
+      <c r="H7" s="860" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="865" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="866" t="inlineStr">
+        <is>
+          <t>DRAW</t>
+        </is>
+      </c>
+      <c r="C8" s="685" t="inlineStr">
+        <is>
+          <t>Draw 1. Buhru Captain: draw 1 OR buff a unit on play. Yordle Explorer draws 1 whenever you play 2+ rune cards.</t>
+        </is>
+      </c>
+      <c r="D8" s="860" t="inlineStr"/>
+      <c r="E8" s="860" t="inlineStr"/>
+      <c r="F8" s="860" t="inlineStr"/>
+      <c r="G8" s="860" t="inlineStr"/>
+      <c r="H8" s="860" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="867" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="868" t="inlineStr">
+        <is>
+          <t>EXHAUST</t>
+        </is>
+      </c>
+      <c r="C9" s="685" t="inlineStr">
+        <is>
+          <t>Exhaust Sett REACTION when opponent's removal targets your buffed unit. Pay 1 rune. Unit recalled to base. Not dead. They wasted their card.</t>
+        </is>
+      </c>
+      <c r="D9" s="860" t="inlineStr"/>
+      <c r="E9" s="860" t="inlineStr"/>
+      <c r="F9" s="860" t="inlineStr"/>
+      <c r="G9" s="860" t="inlineStr"/>
+      <c r="H9" s="860" t="inlineStr"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="869" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B10" s="870" t="inlineStr">
+        <is>
+          <t>FLOOD</t>
+        </is>
+      </c>
+      <c r="C10" s="685" t="inlineStr">
+        <is>
+          <t>Play buff generators: Sea Monkey buffs a base unit, Pit Rookie buffs another, Fae Dragon buffs 4. Wildclaw Shaman spends buff = enters ready to attack same turn.</t>
+        </is>
+      </c>
+      <c r="D10" s="860" t="inlineStr"/>
+      <c r="E10" s="860" t="inlineStr"/>
+      <c r="F10" s="860" t="inlineStr"/>
+      <c r="G10" s="860" t="inlineStr"/>
+      <c r="H10" s="860" t="inlineStr"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="871" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="872" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C11" s="685" t="inlineStr">
+        <is>
+          <t>When they're out of removal: Overt Operation. Spend ALL buffs on ALL units = ALL units ready simultaneously. Attack with everything. Nothing to stop you. Score both fields.</t>
+        </is>
+      </c>
+      <c r="D11" s="860" t="inlineStr"/>
+      <c r="E11" s="860" t="inlineStr"/>
+      <c r="F11" s="860" t="inlineStr"/>
+      <c r="G11" s="860" t="inlineStr"/>
+      <c r="H11" s="860" t="inlineStr"/>
+    </row>
+    <row r="12" ht="4" customHeight="1">
+      <c r="A12" s="856" t="inlineStr"/>
+      <c r="B12" s="856" t="inlineStr"/>
+      <c r="C12" s="856" t="inlineStr"/>
+      <c r="D12" s="856" t="inlineStr"/>
+      <c r="E12" s="856" t="inlineStr"/>
+      <c r="F12" s="856" t="inlineStr"/>
+      <c r="G12" s="856" t="inlineStr"/>
+      <c r="H12" s="856" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="893" t="inlineStr">
+        <is>
+          <t>LEGEND + CHAMPION ZONE</t>
+        </is>
+      </c>
+      <c r="B13" s="890" t="inlineStr"/>
+      <c r="C13" s="890" t="inlineStr"/>
+      <c r="D13" s="890" t="inlineStr"/>
+      <c r="E13" s="890" t="inlineStr"/>
+      <c r="F13" s="890" t="inlineStr"/>
+      <c r="G13" s="890" t="inlineStr"/>
+      <c r="H13" s="890" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B14" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C14" s="873" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="D14" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E14" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F14" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G14" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H14" s="873" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="878" t="inlineStr">
+        <is>
+          <t>OGN-269</t>
+        </is>
+      </c>
+      <c r="B15" s="878" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C15" s="879" t="inlineStr">
+        <is>
+          <t>Legend Zone</t>
+        </is>
+      </c>
+      <c r="D15" s="879" t="inlineStr">
+        <is>
+          <t>Sett - The Boss</t>
+        </is>
+      </c>
+      <c r="E15" s="880" t="inlineStr">
+        <is>
+          <t>Body;Order</t>
+        </is>
+      </c>
+      <c r="F15" s="881" t="inlineStr"/>
+      <c r="G15" s="881" t="inlineStr"/>
+      <c r="H15" s="173" t="inlineStr">
+        <is>
+          <t>Sett - The Boss. When a BUFFED unit would die, pay 1 rune + exhaust me = RECALL it exhausted to base. When you conquer, ready me instantly. Conquering funds Sett saves. Save funds more attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="878" t="inlineStr">
+        <is>
+          <t>SFD-110</t>
+        </is>
+      </c>
+      <c r="B16" s="878" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C16" s="879" t="inlineStr">
+        <is>
+          <t>Champion Zone</t>
+        </is>
+      </c>
+      <c r="D16" s="879" t="inlineStr">
+        <is>
+          <t>Fiora - Peerless</t>
+        </is>
+      </c>
+      <c r="E16" s="880" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F16" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="173" t="inlineStr">
+        <is>
+          <t>Fiora - Peerless. 3/3. When I attack or defend one on one, DOUBLE my Might this combat. 3M becomes 6M instantly = MIGHTY. Fiora legend channels 1 rune when she becomes MIGHTY. She funds Sett saves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="4" customHeight="1">
+      <c r="A17" s="856" t="inlineStr"/>
+      <c r="B17" s="856" t="inlineStr"/>
+      <c r="C17" s="856" t="inlineStr"/>
+      <c r="D17" s="856" t="inlineStr"/>
+      <c r="E17" s="856" t="inlineStr"/>
+      <c r="F17" s="856" t="inlineStr"/>
+      <c r="G17" s="856" t="inlineStr"/>
+      <c r="H17" s="856" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="893" t="inlineStr">
+        <is>
+          <t>MAIN DECK — 40 Cards</t>
+        </is>
+      </c>
+      <c r="B18" s="890" t="inlineStr"/>
+      <c r="C18" s="890" t="inlineStr"/>
+      <c r="D18" s="890" t="inlineStr"/>
+      <c r="E18" s="890" t="inlineStr"/>
+      <c r="F18" s="890" t="inlineStr"/>
+      <c r="G18" s="890" t="inlineStr"/>
+      <c r="H18" s="890" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B19" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C19" s="873" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D19" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E19" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F19" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G19" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H19" s="873" t="inlineStr">
+        <is>
+          <t>What It Does</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="874" t="inlineStr">
+        <is>
+          <t>OGN-011</t>
+        </is>
+      </c>
+      <c r="B20" s="874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="876" t="inlineStr">
+        <is>
+          <t>FINISHER</t>
+        </is>
+      </c>
+      <c r="D20" s="875" t="inlineStr">
+        <is>
+          <t>Magma Wurm</t>
+        </is>
+      </c>
+      <c r="E20" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F20" s="877" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" s="877" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H20" s="222" t="inlineStr">
+        <is>
+          <t>Magma Wurm. 8/8. When I enter play, OTHER friendly units enter ready. Play Wurm + 3 units: all 4 attack same turn. Overt Op before = all buffed + all ready = overwhelming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="874" t="inlineStr">
+        <is>
+          <t>OGN-024</t>
+        </is>
+      </c>
+      <c r="B21" s="874" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="876" t="inlineStr">
+        <is>
+          <t>REMOVAL</t>
+        </is>
+      </c>
+      <c r="D21" s="875" t="inlineStr">
+        <is>
+          <t>Void Seeker</t>
+        </is>
+      </c>
+      <c r="E21" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F21" s="877" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G21" s="877" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="222" t="inlineStr">
+        <is>
+          <t>Void Seeker. Deal 4 to a unit. Draw 1 if you have fewer cards than opponent. Cheap spot removal. Clears low-M threats before they kill your key units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="878" t="inlineStr">
+        <is>
+          <t>OGN-128</t>
+        </is>
+      </c>
+      <c r="B22" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="880" t="inlineStr">
+        <is>
+          <t>REMOVAL</t>
+        </is>
+      </c>
+      <c r="D22" s="879" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="E22" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F22" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="173" t="inlineStr">
+        <is>
+          <t>Challenge. Choose friendly + enemy unit = they fight immediately. Force your 6M Fiora into their 5M unit. She doubles to 12M. She wins. Enemy dies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="878" t="inlineStr">
+        <is>
+          <t>OGN-135</t>
+        </is>
+      </c>
+      <c r="B23" s="878" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="880" t="inlineStr">
+        <is>
+          <t>HIDDEN</t>
+        </is>
+      </c>
+      <c r="D23" s="879" t="inlineStr">
+        <is>
+          <t>Pakaa Cub</t>
+        </is>
+      </c>
+      <c r="E23" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F23" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" s="173" t="inlineStr">
+        <is>
+          <t>Pakaa Cub. 3/3. HIDDEN (pay 1 rune to hide, play for free later). Surprise attacker nobody sees coming. Can't be reacted to on play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="878" t="inlineStr">
+        <is>
+          <t>OGN-146</t>
+        </is>
+      </c>
+      <c r="B24" s="878" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="880" t="inlineStr">
+        <is>
+          <t>REMOVAL</t>
+        </is>
+      </c>
+      <c r="D24" s="879" t="inlineStr">
+        <is>
+          <t>Wallop</t>
+        </is>
+      </c>
+      <c r="E24" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F24" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="173" t="inlineStr">
+        <is>
+          <t>Wallop. Buff a unit (gives it a +1M buff, makes it a Sett save target) then force it to fight an opponent's unit. Your buffed unit wins. Enemy dies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="878" t="inlineStr">
+        <is>
+          <t>OGN-147</t>
+        </is>
+      </c>
+      <c r="B25" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="880" t="inlineStr">
+        <is>
+          <t>BUFF</t>
+        </is>
+      </c>
+      <c r="D25" s="879" t="inlineStr">
+        <is>
+          <t>Wildclaw Shaman</t>
+        </is>
+      </c>
+      <c r="E25" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F25" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="173" t="inlineStr">
+        <is>
+          <t>Wildclaw Shaman. 4/3. Spend a buff on play = buff me AND ready me. Enters play already attacked. Lee Sin buffs someone, Shaman spends it = free attacker. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="878" t="inlineStr">
+        <is>
+          <t>OGN-153</t>
+        </is>
+      </c>
+      <c r="B26" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="880" t="inlineStr">
+        <is>
+          <t>NUKE</t>
+        </is>
+      </c>
+      <c r="D26" s="879" t="inlineStr">
+        <is>
+          <t>Overt Operation</t>
+        </is>
+      </c>
+      <c r="E26" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F26" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G26" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="173" t="inlineStr">
+        <is>
+          <t>Overt Operation. For each friendly BUFFED unit, spend their buff = ready ALL units here. 3 buffed units = all 3 ready simultaneously. Mass attack from nowhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="894" t="inlineStr">
+        <is>
+          <t>OGN-216</t>
+        </is>
+      </c>
+      <c r="B27" s="894" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="895" t="inlineStr">
+        <is>
+          <t>SAVE</t>
+        </is>
+      </c>
+      <c r="D27" s="896" t="inlineStr">
+        <is>
+          <t>Soaring Scout</t>
+        </is>
+      </c>
+      <c r="E27" s="897" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="F27" s="897" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G27" s="897" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="217" t="inlineStr">
+        <is>
+          <t>Soaring Scout. 2/1. DEATHKNELL = channel 1 rune exhausted. Cheapest Sett save target. If Sett saves it: replay next turn. If it dies: free rune. Cannot lose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="894" t="inlineStr">
+        <is>
+          <t>OGN-228</t>
+        </is>
+      </c>
+      <c r="B28" s="894" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="895" t="inlineStr">
+        <is>
+          <t>BACKUP</t>
+        </is>
+      </c>
+      <c r="D28" s="896" t="inlineStr">
+        <is>
+          <t>Vanguard Helm</t>
+        </is>
+      </c>
+      <c r="E28" s="897" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="F28" s="897" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="897" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="217" t="inlineStr">
+        <is>
+          <t>Vanguard Helm. When a BUFFED friendly unit dies, buff another. If Sett can't save (legend exhausted), the buff transfers. Nothing is wasted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="874" t="inlineStr">
+        <is>
+          <t>SFD-007</t>
+        </is>
+      </c>
+      <c r="B29" s="874" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="876" t="inlineStr">
+        <is>
+          <t>MOBILE</t>
+        </is>
+      </c>
+      <c r="D29" s="875" t="inlineStr">
+        <is>
+          <t>Gem Jammer</t>
+        </is>
+      </c>
+      <c r="E29" s="877" t="inlineStr">
+        <is>
+          <t>Fury</t>
+        </is>
+      </c>
+      <c r="F29" s="877" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G29" s="877" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" s="222" t="inlineStr">
+        <is>
+          <t>Gem Jammer. 2/2. When played: give a unit GANKING this turn. Gives your biggest unit access to both fields. Run x2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="878" t="inlineStr">
+        <is>
+          <t>SFD-091</t>
+        </is>
+      </c>
+      <c r="B30" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="880" t="inlineStr">
+        <is>
+          <t>DRAW</t>
+        </is>
+      </c>
+      <c r="D30" s="879" t="inlineStr">
+        <is>
+          <t>Buhru Captain</t>
+        </is>
+      </c>
+      <c r="E30" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F30" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G30" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" s="173" t="inlineStr">
+        <is>
+          <t>Buhru Captain. 3/3. Draw 1 OR buff me on play. Always useful. Drawing keeps your hand full when opponent keeps trying to kill your units. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="878" t="inlineStr">
+        <is>
+          <t>SFD-098</t>
+        </is>
+      </c>
+      <c r="B31" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="880" t="inlineStr">
+        <is>
+          <t>BUFF</t>
+        </is>
+      </c>
+      <c r="D31" s="879" t="inlineStr">
+        <is>
+          <t>Sea Monkey</t>
+        </is>
+      </c>
+      <c r="E31" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F31" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" s="881" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="173" t="inlineStr">
+        <is>
+          <t>Sea Monkey. 2/2. On play: buff a unit at your base. Cheap turn-1 play that immediately gives Sett a save target. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="878" t="inlineStr">
+        <is>
+          <t>SFD-100</t>
+        </is>
+      </c>
+      <c r="B32" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="880" t="inlineStr">
+        <is>
+          <t>DRAW</t>
+        </is>
+      </c>
+      <c r="D32" s="879" t="inlineStr">
+        <is>
+          <t>Yordle Explorer</t>
+        </is>
+      </c>
+      <c r="E32" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F32" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G32" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H32" s="173" t="inlineStr">
+        <is>
+          <t>Yordle Explorer. 4/4. Draw 1 whenever you play a card costing 2+ runes. Fae Dragon (7 cost) = draw. Overt Operation (5 cost) = draw. Hand stays full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="878" t="inlineStr">
+        <is>
+          <t>SFD-101</t>
+        </is>
+      </c>
+      <c r="B33" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="880" t="inlineStr">
+        <is>
+          <t>BUFF</t>
+        </is>
+      </c>
+      <c r="D33" s="879" t="inlineStr">
+        <is>
+          <t>Fae Dragon</t>
+        </is>
+      </c>
+      <c r="E33" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F33" s="881" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G33" s="881" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H33" s="173" t="inlineStr">
+        <is>
+          <t>Fae Dragon. 7/7. When played: buff up to 4 friendly units. One card gives 4 Sett save targets simultaneously. Massive turn. Run x3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="878" t="inlineStr">
+        <is>
+          <t>SFD-103</t>
+        </is>
+      </c>
+      <c r="B34" s="878" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="880" t="inlineStr">
+        <is>
+          <t>BODY</t>
+        </is>
+      </c>
+      <c r="D34" s="879" t="inlineStr">
+        <is>
+          <t>Jaull-Fish</t>
+        </is>
+      </c>
+      <c r="E34" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F34" s="881" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G34" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H34" s="173" t="inlineStr">
+        <is>
+          <t>Jaull-Fish. 7/6. ACCELERATE = pay 1 Body extra to enter ready. Big body that attacks immediately. Sett save target if it gets buffed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="878" t="inlineStr">
+        <is>
+          <t>SFD-110</t>
+        </is>
+      </c>
+      <c r="B35" s="878" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="880" t="inlineStr">
+        <is>
+          <t>CONQUER</t>
+        </is>
+      </c>
+      <c r="D35" s="879" t="inlineStr">
+        <is>
+          <t>Fiora - Peerless</t>
+        </is>
+      </c>
+      <c r="E35" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F35" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G35" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" s="173" t="inlineStr">
+        <is>
+          <t>Fiora Peerless. 3/3. DOUBLE Might in 1v1 = 6M. MIGHTY instantly. Fiora legend triggers = free rune. Small investment, big return. Champion zone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="894" t="inlineStr">
+        <is>
+          <t>SFD-167</t>
+        </is>
+      </c>
+      <c r="B36" s="894" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="895" t="inlineStr">
+        <is>
+          <t>SAVE</t>
+        </is>
+      </c>
+      <c r="D36" s="896" t="inlineStr">
+        <is>
+          <t>Unsung Hero</t>
+        </is>
+      </c>
+      <c r="E36" s="897" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="F36" s="897" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" s="897" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" s="217" t="inlineStr">
+        <is>
+          <t>Unsung Hero. 2/2. DEATHKNELL — if MIGHTY: draw 2. Buff it with Fae Dragon or Wildclaw = 3M = MIGHTY. Either Sett saves it (free body next turn) or it draws 2 on death.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="898" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B37" s="898" t="n">
+        <v>40</v>
+      </c>
+      <c r="C37" s="890" t="inlineStr"/>
+      <c r="D37" s="890" t="inlineStr"/>
+      <c r="E37" s="890" t="inlineStr"/>
+      <c r="F37" s="890" t="inlineStr"/>
+      <c r="G37" s="890" t="inlineStr"/>
+      <c r="H37" s="890" t="inlineStr"/>
+    </row>
+    <row r="38" ht="4" customHeight="1">
+      <c r="A38" s="856" t="inlineStr"/>
+      <c r="B38" s="856" t="inlineStr"/>
+      <c r="C38" s="856" t="inlineStr"/>
+      <c r="D38" s="856" t="inlineStr"/>
+      <c r="E38" s="856" t="inlineStr"/>
+      <c r="F38" s="856" t="inlineStr"/>
+      <c r="G38" s="856" t="inlineStr"/>
+      <c r="H38" s="856" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="899" t="inlineStr">
+        <is>
+          <t>RUNE DECK (12)</t>
+        </is>
+      </c>
+      <c r="B39" s="705" t="inlineStr">
+        <is>
+          <t>6x Body (Orange) + 6x Order (Yellow) — Clean. Zero overlap with other decks.</t>
+        </is>
+      </c>
+      <c r="C39" s="900" t="inlineStr"/>
+      <c r="D39" s="900" t="inlineStr"/>
+      <c r="E39" s="900" t="inlineStr"/>
+      <c r="F39" s="900" t="inlineStr"/>
+      <c r="G39" s="900" t="inlineStr"/>
+      <c r="H39" s="900" t="inlineStr"/>
+    </row>
+    <row r="40" ht="4" customHeight="1">
+      <c r="A40" s="856" t="inlineStr"/>
+      <c r="B40" s="856" t="inlineStr"/>
+      <c r="C40" s="856" t="inlineStr"/>
+      <c r="D40" s="856" t="inlineStr"/>
+      <c r="E40" s="856" t="inlineStr"/>
+      <c r="F40" s="856" t="inlineStr"/>
+      <c r="G40" s="856" t="inlineStr"/>
+      <c r="H40" s="856" t="inlineStr"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="893" t="inlineStr">
+        <is>
+          <t>SIDEBOARD — 8 Cards</t>
+        </is>
+      </c>
+      <c r="B41" s="890" t="inlineStr"/>
+      <c r="C41" s="890" t="inlineStr"/>
+      <c r="D41" s="890" t="inlineStr"/>
+      <c r="E41" s="890" t="inlineStr"/>
+      <c r="F41" s="890" t="inlineStr"/>
+      <c r="G41" s="890" t="inlineStr"/>
+      <c r="H41" s="890" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="873" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B42" s="873" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C42" s="873" t="inlineStr">
+        <is>
+          <t>Matchup</t>
+        </is>
+      </c>
+      <c r="D42" s="873" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E42" s="873" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="F42" s="873" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="G42" s="873" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="H42" s="873" t="inlineStr">
+        <is>
+          <t>G2 Plan + Swap</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="878" t="inlineStr">
+        <is>
+          <t>OGN-154</t>
+        </is>
+      </c>
+      <c r="B43" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="879" t="inlineStr">
+        <is>
+          <t>vs Azir Tokens</t>
+        </is>
+      </c>
+      <c r="D43" s="879" t="inlineStr">
+        <is>
+          <t>Primal Strength</t>
+        </is>
+      </c>
+      <c r="E43" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F43" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G43" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" s="173" t="inlineStr">
+        <is>
+          <t>Primal Strength. +7M to a unit this turn. On any unit = instant MIGHTY. Fiora legend triggers (channel rune). Sett save target. Against Azir's tokens this creates a unit they cannot block. || SWAP: OUT: OGN-135 x1 | IN: Primal Strength x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="878" t="inlineStr">
+        <is>
+          <t>OGN-149</t>
+        </is>
+      </c>
+      <c r="B44" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="879" t="inlineStr">
+        <is>
+          <t>vs Big Units</t>
+        </is>
+      </c>
+      <c r="D44" s="879" t="inlineStr">
+        <is>
+          <t>Carnivorous Snapvine</t>
+        </is>
+      </c>
+      <c r="E44" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F44" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G44" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H44" s="173" t="inlineStr">
+        <is>
+          <t>Carnivorous Snapvine. 5/6. On play: choose enemy unit. We deal damage equal to each other's Might. Your 7M Fae Dragon vs their 9M dragon = both die OR finish with Sett save. || SWAP: OUT: SFD-007 x1 | IN: Snapvine x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="878" t="inlineStr">
+        <is>
+          <t>OGN-151</t>
+        </is>
+      </c>
+      <c r="B45" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="879" t="inlineStr">
+        <is>
+          <t>vs Draven</t>
+        </is>
+      </c>
+      <c r="D45" s="879" t="inlineStr">
+        <is>
+          <t>Lee Sin - Centered</t>
+        </is>
+      </c>
+      <c r="E45" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F45" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G45" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H45" s="173" t="inlineStr">
+        <is>
+          <t>Lee Sin - Centered. 6/6 ACCELERATE. Enters ready, attacks immediately. 6M vs Draven's 4M ASSAULT units. They die. He draws nothing. Win combat. || SWAP: OUT: OGN-024 x1 | IN: Lee Sin x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="46" customHeight="1">
+      <c r="A46" s="878" t="inlineStr">
+        <is>
+          <t>SFD-105</t>
+        </is>
+      </c>
+      <c r="B46" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="879" t="inlineStr">
+        <is>
+          <t>vs Removal Heavy</t>
+        </is>
+      </c>
+      <c r="D46" s="879" t="inlineStr">
+        <is>
+          <t>Ruin Runner</t>
+        </is>
+      </c>
+      <c r="E46" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F46" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G46" s="881" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H46" s="173" t="inlineStr">
+        <is>
+          <t>Ruin Runner. 6/5. Cannot be chosen by enemy spells and abilities. Sett can still save it (Sett is not choosing it). Immune to Strike Down, Void Seeker, everything. || SWAP: OUT: OGN-128 x1 | IN: Ruin Runner x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="878" t="inlineStr">
+        <is>
+          <t>OGN-152</t>
+        </is>
+      </c>
+      <c r="B47" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="879" t="inlineStr">
+        <is>
+          <t>vs Fast Aggro</t>
+        </is>
+      </c>
+      <c r="D47" s="879" t="inlineStr">
+        <is>
+          <t>Mistfall</t>
+        </is>
+      </c>
+      <c r="E47" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F47" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G47" s="881" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" s="173" t="inlineStr">
+        <is>
+          <t>Mistfall Gear. When you buff a friendly unit, pay Body + exhaust this to ready it. Mass buff turn (Fae Dragon): each buff readies a unit. Overt Op + Mistfall = everything readies twice. || SWAP: OUT: OGN-146 x1 | IN: Mistfall x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="878" t="inlineStr">
+        <is>
+          <t>OGN-158</t>
+        </is>
+      </c>
+      <c r="B48" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="879" t="inlineStr">
+        <is>
+          <t>vs Everything</t>
+        </is>
+      </c>
+      <c r="D48" s="879" t="inlineStr">
+        <is>
+          <t>Volibear - Imposing</t>
+        </is>
+      </c>
+      <c r="E48" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F48" s="881" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G48" s="881" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H48" s="173" t="inlineStr">
+        <is>
+          <t>Volibear - Imposing. 12/10 SHIELD 3 TANK. Nuclear option. 12M attacker with SHIELD 3 (defends as 13M). Buff it once from Fae Dragon = 13M attacker. Sett saves it forever. || SWAP: OUT: SFD-100 x1 | IN: Volibear Imposing x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="878" t="inlineStr">
+        <is>
+          <t>SFD-112</t>
+        </is>
+      </c>
+      <c r="B49" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="879" t="inlineStr">
+        <is>
+          <t>vs Spell Control</t>
+        </is>
+      </c>
+      <c r="D49" s="879" t="inlineStr">
+        <is>
+          <t>Kato the Arm</t>
+        </is>
+      </c>
+      <c r="E49" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F49" s="881" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" s="881" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H49" s="173" t="inlineStr">
+        <is>
+          <t>Kato the Arm. 4/3. DEFLECT — opponents pay 1 rune to target with spells. Buff Kato repeatedly. He costs 1 extra rune to remove each time. Control decks run out of runes before they run out of your units. || SWAP: OUT: OGN-011 x1 | IN: Kato x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="878" t="inlineStr">
+        <is>
+          <t>OGN-137</t>
+        </is>
+      </c>
+      <c r="B50" s="878" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="879" t="inlineStr">
+        <is>
+          <t>vs Aggro</t>
+        </is>
+      </c>
+      <c r="D50" s="879" t="inlineStr">
+        <is>
+          <t>Stormclaw Ursine</t>
+        </is>
+      </c>
+      <c r="E50" s="881" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="F50" s="881" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G50" s="881" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H50" s="173" t="inlineStr">
+        <is>
+          <t>Stormclaw Ursine. 7/6 TANK. On play: channel 1 rune exhausted. Generates a rune AND is a 7M TANK that must be killed first. Funds Sett saves while absorbing damage. || SWAP: OUT: SFD-103 x1 | IN: Stormclaw Ursine x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="4" customHeight="1">
+      <c r="A51" s="856" t="inlineStr"/>
+      <c r="B51" s="856" t="inlineStr"/>
+      <c r="C51" s="856" t="inlineStr"/>
+      <c r="D51" s="856" t="inlineStr"/>
+      <c r="E51" s="856" t="inlineStr"/>
+      <c r="F51" s="856" t="inlineStr"/>
+      <c r="G51" s="856" t="inlineStr"/>
+      <c r="H51" s="856" t="inlineStr"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="893" t="inlineStr">
+        <is>
+          <t>GOLDEN RULES</t>
+        </is>
+      </c>
+      <c r="B52" s="890" t="inlineStr"/>
+      <c r="C52" s="890" t="inlineStr"/>
+      <c r="D52" s="890" t="inlineStr"/>
+      <c r="E52" s="890" t="inlineStr"/>
+      <c r="F52" s="890" t="inlineStr"/>
+      <c r="G52" s="890" t="inlineStr"/>
+      <c r="H52" s="890" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="885" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B53" s="97" t="inlineStr">
+        <is>
+          <t>Buff first, THEN Sett saves. Sett can only recall a BUFFED unit. Keep at least one buff on your most important unit at all times. Sea Monkey, Buhru Captain, Pit Rookie — all give buffs on entry.</t>
+        </is>
+      </c>
+      <c r="C53" s="886" t="inlineStr"/>
+      <c r="D53" s="886" t="inlineStr"/>
+      <c r="E53" s="886" t="inlineStr"/>
+      <c r="F53" s="886" t="inlineStr"/>
+      <c r="G53" s="886" t="inlineStr"/>
+      <c r="H53" s="886" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="887" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B54" s="101" t="inlineStr">
+        <is>
+          <t>Every conquest readies Sett. Attack with a unit, conquer a field, Sett readies immediately. Now when opponent plays removal — you have a ready Sett to save it. Conquer = insurance policy.</t>
+        </is>
+      </c>
+      <c r="C54" s="888" t="inlineStr"/>
+      <c r="D54" s="888" t="inlineStr"/>
+      <c r="E54" s="888" t="inlineStr"/>
+      <c r="F54" s="888" t="inlineStr"/>
+      <c r="G54" s="888" t="inlineStr"/>
+      <c r="H54" s="888" t="inlineStr"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="885" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B55" s="97" t="inlineStr">
+        <is>
+          <t>Overt Operation timing: wait until 3+ units all have buffs. Spend all buffs = all ready. Attack with everything at once. Opponent can only block one field. You score the other. Guaranteed.</t>
+        </is>
+      </c>
+      <c r="C55" s="886" t="inlineStr"/>
+      <c r="D55" s="886" t="inlineStr"/>
+      <c r="E55" s="886" t="inlineStr"/>
+      <c r="F55" s="886" t="inlineStr"/>
+      <c r="G55" s="886" t="inlineStr"/>
+      <c r="H55" s="886" t="inlineStr"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="887" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B56" s="101" t="inlineStr">
+        <is>
+          <t>Fiora Peerless in 1v1: her Might DOUBLES. 3M becomes 6M = MIGHTY immediately. Fiora legend channels 1 rune. Use that rune for Sett save on her. She conquers, Sett readies, she conquers again.</t>
+        </is>
+      </c>
+      <c r="C56" s="888" t="inlineStr"/>
+      <c r="D56" s="888" t="inlineStr"/>
+      <c r="E56" s="888" t="inlineStr"/>
+      <c r="F56" s="888" t="inlineStr"/>
+      <c r="G56" s="888" t="inlineStr"/>
+      <c r="H56" s="888" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="885" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B57" s="97" t="inlineStr">
+        <is>
+          <t>Soaring Scouts are bait. Play Scout, put 1 buff on it. Opponent kills it. Sett saves it (goes to base). OR opponent ignores it. Either way: Scout DEATHKNELL channels a rune if it dies. Always win.</t>
+        </is>
+      </c>
+      <c r="C57" s="886" t="inlineStr"/>
+      <c r="D57" s="886" t="inlineStr"/>
+      <c r="E57" s="886" t="inlineStr"/>
+      <c r="F57" s="886" t="inlineStr"/>
+      <c r="G57" s="886" t="inlineStr"/>
+      <c r="H57" s="886" t="inlineStr"/>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="887" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B58" s="101" t="inlineStr">
+        <is>
+          <t>Vanguard Helm is your fail-safe. If Sett is exhausted and can't save a buffed unit that dies — Helm transfers the buff to another unit. The buff never disappears. Nothing is ever truly wasted.</t>
+        </is>
+      </c>
+      <c r="C58" s="888" t="inlineStr"/>
+      <c r="D58" s="888" t="inlineStr"/>
+      <c r="E58" s="888" t="inlineStr"/>
+      <c r="F58" s="888" t="inlineStr"/>
+      <c r="G58" s="888" t="inlineStr"/>
+      <c r="H58" s="888" t="inlineStr"/>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="885" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B59" s="97" t="inlineStr">
+        <is>
+          <t>Wildclaw Shaman: SPEND A BUFF to buff itself AND ready itself. Lee Sin buffs a unit on field. Play Shaman. Spend that buff. Shaman becomes 5M and attacks same turn. Two effects from one Lee Sin activation.</t>
+        </is>
+      </c>
+      <c r="C59" s="886" t="inlineStr"/>
+      <c r="D59" s="886" t="inlineStr"/>
+      <c r="E59" s="886" t="inlineStr"/>
+      <c r="F59" s="886" t="inlineStr"/>
+      <c r="G59" s="886" t="inlineStr"/>
+      <c r="H59" s="886" t="inlineStr"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="887" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B60" s="101" t="inlineStr">
+        <is>
+          <t>Magma Wurm is your win button. All OTHER units enter ready when Wurm plays. Save him for when you have 3-4 units on board. Play Wurm + all others ready + Overt Op = everything attacks simultaneously.</t>
+        </is>
+      </c>
+      <c r="C60" s="888" t="inlineStr"/>
+      <c r="D60" s="888" t="inlineStr"/>
+      <c r="E60" s="888" t="inlineStr"/>
+      <c r="F60" s="888" t="inlineStr"/>
+      <c r="G60" s="888" t="inlineStr"/>
+      <c r="H60" s="888" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -68021,17 +71566,17 @@
           <t>71.2%</t>
         </is>
       </c>
-      <c r="C5" s="679" t="inlineStr">
+      <c r="C5" s="830" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="D5" s="679" t="inlineStr">
+      <c r="D5" s="830" t="inlineStr">
         <is>
           <t>+17.9%</t>
         </is>
       </c>
-      <c r="E5" s="679" t="inlineStr">
+      <c r="E5" s="830" t="inlineStr">
         <is>
           <t>T5.0</t>
         </is>
@@ -68064,17 +71609,17 @@
           <t>86.2%</t>
         </is>
       </c>
-      <c r="C6" s="679" t="inlineStr">
+      <c r="C6" s="830" t="inlineStr">
         <is>
           <t>98.3%</t>
         </is>
       </c>
-      <c r="D6" s="679" t="inlineStr">
+      <c r="D6" s="830" t="inlineStr">
         <is>
           <t>+12.1%</t>
         </is>
       </c>
-      <c r="E6" s="679" t="inlineStr">
+      <c r="E6" s="830" t="inlineStr">
         <is>
           <t>T4.1</t>
         </is>
@@ -68107,17 +71652,17 @@
           <t>85.0%</t>
         </is>
       </c>
-      <c r="C7" s="679" t="inlineStr">
+      <c r="C7" s="830" t="inlineStr">
         <is>
           <t>98.3%</t>
         </is>
       </c>
-      <c r="D7" s="679" t="inlineStr">
+      <c r="D7" s="830" t="inlineStr">
         <is>
           <t>+13.3%</t>
         </is>
       </c>
-      <c r="E7" s="679" t="inlineStr">
+      <c r="E7" s="830" t="inlineStr">
         <is>
           <t>T3.5</t>
         </is>
@@ -68192,7 +71737,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="B10" s="676" t="inlineStr">
+      <c r="B10" s="832" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -68202,7 +71747,7 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="D10" s="676" t="inlineStr">
+      <c r="D10" s="832" t="inlineStr">
         <is>
           <t>0.22</t>
         </is>
@@ -68212,7 +71757,7 @@
           <t>0.50</t>
         </is>
       </c>
-      <c r="F10" s="679" t="inlineStr">
+      <c r="F10" s="830" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
@@ -68222,7 +71767,7 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="H10" s="679" t="inlineStr">
+      <c r="H10" s="830" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
@@ -68249,7 +71794,7 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="D11" s="676" t="inlineStr">
+      <c r="D11" s="832" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
@@ -68259,7 +71804,7 @@
           <t>1.50</t>
         </is>
       </c>
-      <c r="F11" s="679" t="inlineStr">
+      <c r="F11" s="830" t="inlineStr">
         <is>
           <t>4.70</t>
         </is>
@@ -68269,7 +71814,7 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="H11" s="679" t="inlineStr">
+      <c r="H11" s="830" t="inlineStr">
         <is>
           <t>4.33</t>
         </is>
@@ -68286,7 +71831,7 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="B12" s="679" t="inlineStr">
+      <c r="B12" s="830" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -68296,7 +71841,7 @@
           <t>1.9</t>
         </is>
       </c>
-      <c r="D12" s="679" t="inlineStr">
+      <c r="D12" s="830" t="inlineStr">
         <is>
           <t>3.38</t>
         </is>
@@ -68306,7 +71851,7 @@
           <t>3.00</t>
         </is>
       </c>
-      <c r="F12" s="679" t="inlineStr">
+      <c r="F12" s="830" t="inlineStr">
         <is>
           <t>6.47</t>
         </is>
@@ -68316,7 +71861,7 @@
           <t>1.00</t>
         </is>
       </c>
-      <c r="H12" s="679" t="inlineStr">
+      <c r="H12" s="830" t="inlineStr">
         <is>
           <t>7.07</t>
         </is>
@@ -68333,7 +71878,7 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="B13" s="679" t="inlineStr">
+      <c r="B13" s="830" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
@@ -68343,7 +71888,7 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="D13" s="679" t="inlineStr">
+      <c r="D13" s="830" t="inlineStr">
         <is>
           <t>6.06</t>
         </is>
@@ -68353,7 +71898,7 @@
           <t>5.00</t>
         </is>
       </c>
-      <c r="F13" s="679" t="inlineStr">
+      <c r="F13" s="830" t="inlineStr">
         <is>
           <t>8.11</t>
         </is>
@@ -68363,7 +71908,7 @@
           <t>2.50</t>
         </is>
       </c>
-      <c r="H13" s="679" t="inlineStr">
+      <c r="H13" s="830" t="inlineStr">
         <is>
           <t>7.82</t>
         </is>
@@ -68380,17 +71925,17 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="B14" s="679" t="inlineStr">
+      <c r="B14" s="830" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="C14" s="679" t="inlineStr">
+      <c r="C14" s="830" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="D14" s="679" t="inlineStr">
+      <c r="D14" s="830" t="inlineStr">
         <is>
           <t>8.51</t>
         </is>
@@ -68400,7 +71945,7 @@
           <t>7.00</t>
         </is>
       </c>
-      <c r="F14" s="679" t="inlineStr">
+      <c r="F14" s="830" t="inlineStr">
         <is>
           <t>6.83</t>
         </is>
@@ -68410,7 +71955,7 @@
           <t>4.50</t>
         </is>
       </c>
-      <c r="H14" s="679" t="inlineStr">
+      <c r="H14" s="830" t="inlineStr">
         <is>
           <t>7.51</t>
         </is>
@@ -68427,17 +71972,17 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="B15" s="679" t="inlineStr">
+      <c r="B15" s="830" t="inlineStr">
         <is>
           <t>28.0</t>
         </is>
       </c>
-      <c r="C15" s="679" t="inlineStr">
+      <c r="C15" s="830" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="D15" s="676" t="inlineStr">
+      <c r="D15" s="832" t="inlineStr">
         <is>
           <t>8.52</t>
         </is>
@@ -68447,7 +71992,7 @@
           <t>9.50</t>
         </is>
       </c>
-      <c r="F15" s="679" t="inlineStr">
+      <c r="F15" s="830" t="inlineStr">
         <is>
           <t>8.06</t>
         </is>
@@ -68457,7 +72002,7 @@
           <t>7.00</t>
         </is>
       </c>
-      <c r="H15" s="679" t="inlineStr">
+      <c r="H15" s="830" t="inlineStr">
         <is>
           <t>6.54</t>
         </is>
@@ -68474,7 +72019,7 @@
           <t>T7</t>
         </is>
       </c>
-      <c r="B16" s="676" t="inlineStr">
+      <c r="B16" s="832" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -68484,7 +72029,7 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" s="676" t="inlineStr">
+      <c r="D16" s="832" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
@@ -68494,7 +72039,7 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="F16" s="676" t="inlineStr">
+      <c r="F16" s="832" t="inlineStr">
         <is>
           <t>8.30</t>
         </is>
@@ -68504,7 +72049,7 @@
           <t>10.00</t>
         </is>
       </c>
-      <c r="H16" s="676" t="inlineStr">
+      <c r="H16" s="832" t="inlineStr">
         <is>
           <t>7.01</t>
         </is>
@@ -69397,14 +72942,14 @@
           <t>Everything readies. Scout is back in your hand from the legend ability last turn.</t>
         </is>
       </c>
-      <c r="D12" s="774" t="inlineStr"/>
-      <c r="E12" s="774" t="inlineStr"/>
-      <c r="F12" s="774" t="inlineStr"/>
-      <c r="G12" s="774" t="inlineStr"/>
-      <c r="H12" s="774" t="inlineStr"/>
+      <c r="D12" s="835" t="inlineStr"/>
+      <c r="E12" s="835" t="inlineStr"/>
+      <c r="F12" s="835" t="inlineStr"/>
+      <c r="G12" s="835" t="inlineStr"/>
+      <c r="H12" s="835" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="814" t="inlineStr">
+      <c r="A13" s="839" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -69419,11 +72964,11 @@
           <t>Score points for fields held. Check if any hidden cards need to be revealed this turn.</t>
         </is>
       </c>
-      <c r="D13" s="774" t="inlineStr"/>
-      <c r="E13" s="774" t="inlineStr"/>
-      <c r="F13" s="774" t="inlineStr"/>
-      <c r="G13" s="774" t="inlineStr"/>
-      <c r="H13" s="774" t="inlineStr"/>
+      <c r="D13" s="835" t="inlineStr"/>
+      <c r="E13" s="835" t="inlineStr"/>
+      <c r="F13" s="835" t="inlineStr"/>
+      <c r="G13" s="835" t="inlineStr"/>
+      <c r="H13" s="835" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="593" t="inlineStr">
@@ -69441,11 +72986,11 @@
           <t>Draw 2 runes (Mind blue + Chaos purple). Plan which drain spells you'll hold as reactions.</t>
         </is>
       </c>
-      <c r="D14" s="774" t="inlineStr"/>
-      <c r="E14" s="774" t="inlineStr"/>
-      <c r="F14" s="774" t="inlineStr"/>
-      <c r="G14" s="774" t="inlineStr"/>
-      <c r="H14" s="774" t="inlineStr"/>
+      <c r="D14" s="835" t="inlineStr"/>
+      <c r="E14" s="835" t="inlineStr"/>
+      <c r="F14" s="835" t="inlineStr"/>
+      <c r="G14" s="835" t="inlineStr"/>
+      <c r="H14" s="835" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="595" t="inlineStr">
@@ -69463,11 +73008,11 @@
           <t>Draw 1 card. You likely drew extra cards from Mushroom Pouch and Stupefy already.</t>
         </is>
       </c>
-      <c r="D15" s="774" t="inlineStr"/>
-      <c r="E15" s="774" t="inlineStr"/>
-      <c r="F15" s="774" t="inlineStr"/>
-      <c r="G15" s="774" t="inlineStr"/>
-      <c r="H15" s="774" t="inlineStr"/>
+      <c r="D15" s="835" t="inlineStr"/>
+      <c r="E15" s="835" t="inlineStr"/>
+      <c r="F15" s="835" t="inlineStr"/>
+      <c r="G15" s="835" t="inlineStr"/>
+      <c r="H15" s="835" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="597" t="inlineStr">
@@ -69485,11 +73030,11 @@
           <t>Exhaust Smoke Screen on opponent's biggest threat if available. Every -1M counts.</t>
         </is>
       </c>
-      <c r="D16" s="774" t="inlineStr"/>
-      <c r="E16" s="774" t="inlineStr"/>
-      <c r="F16" s="774" t="inlineStr"/>
-      <c r="G16" s="774" t="inlineStr"/>
-      <c r="H16" s="774" t="inlineStr"/>
+      <c r="D16" s="835" t="inlineStr"/>
+      <c r="E16" s="835" t="inlineStr"/>
+      <c r="F16" s="835" t="inlineStr"/>
+      <c r="G16" s="835" t="inlineStr"/>
+      <c r="H16" s="835" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="599" t="inlineStr">
@@ -69507,11 +73052,11 @@
           <t>Pay 1 energy to hide Wages of Pain or Consult the Past at a contested field. Teemo legend makes this free — costs energy not runes.</t>
         </is>
       </c>
-      <c r="D17" s="774" t="inlineStr"/>
-      <c r="E17" s="774" t="inlineStr"/>
-      <c r="F17" s="774" t="inlineStr"/>
-      <c r="G17" s="774" t="inlineStr"/>
-      <c r="H17" s="774" t="inlineStr"/>
+      <c r="D17" s="835" t="inlineStr"/>
+      <c r="E17" s="835" t="inlineStr"/>
+      <c r="F17" s="835" t="inlineStr"/>
+      <c r="G17" s="835" t="inlineStr"/>
+      <c r="H17" s="835" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="601" t="inlineStr">
@@ -69529,11 +73074,11 @@
           <t>Play Teemo Scout to an open field — he enters as 4M. Conquer. Exhaust legend to put Scout back in hand. React to attacks with drain spells.</t>
         </is>
       </c>
-      <c r="D18" s="774" t="inlineStr"/>
-      <c r="E18" s="774" t="inlineStr"/>
-      <c r="F18" s="774" t="inlineStr"/>
-      <c r="G18" s="774" t="inlineStr"/>
-      <c r="H18" s="774" t="inlineStr"/>
+      <c r="D18" s="835" t="inlineStr"/>
+      <c r="E18" s="835" t="inlineStr"/>
+      <c r="F18" s="835" t="inlineStr"/>
+      <c r="G18" s="835" t="inlineStr"/>
+      <c r="H18" s="835" t="inlineStr"/>
     </row>
     <row r="19" ht="5" customHeight="1">
       <c r="A19" s="672" t="inlineStr"/>
@@ -69560,42 +73105,42 @@
       <c r="H20" s="669" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="603" t="inlineStr">
+      <c r="A21" s="843" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B21" s="603" t="inlineStr">
+      <c r="B21" s="843" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C21" s="603" t="inlineStr">
+      <c r="C21" s="843" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="D21" s="603" t="inlineStr">
+      <c r="D21" s="843" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E21" s="603" t="inlineStr">
+      <c r="E21" s="843" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F21" s="603" t="inlineStr">
+      <c r="F21" s="843" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G21" s="603" t="inlineStr">
+      <c r="G21" s="843" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H21" s="603" t="inlineStr">
+      <c r="H21" s="843" t="inlineStr">
         <is>
           <t>Ability / Notes</t>
         </is>
@@ -69710,42 +73255,42 @@
       <c r="H25" s="669" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="603" t="inlineStr">
+      <c r="A26" s="843" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B26" s="603" t="inlineStr">
+      <c r="B26" s="843" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C26" s="603" t="inlineStr">
+      <c r="C26" s="843" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D26" s="603" t="inlineStr">
+      <c r="D26" s="843" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E26" s="603" t="inlineStr">
+      <c r="E26" s="843" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="F26" s="603" t="inlineStr">
+      <c r="F26" s="843" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="G26" s="603" t="inlineStr">
+      <c r="G26" s="843" t="inlineStr">
         <is>
           <t>Might</t>
         </is>
       </c>
-      <c r="H26" s="603" t="inlineStr">
+      <c r="H26" s="843" t="inlineStr">
         <is>
           <t>How It Works</t>
         </is>
@@ -70410,7 +73955,7 @@
       <c r="H44" s="672" t="inlineStr"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="772" t="inlineStr">
+      <c r="A45" s="834" t="inlineStr">
         <is>
           <t>RUNE DECK (12)</t>
         </is>
@@ -70420,12 +73965,12 @@
           <t>6x Mind (Blue) + 6x Chaos (Purple) — Completely clean. Zero overlap with Azir/Voli/MF.</t>
         </is>
       </c>
-      <c r="C45" s="774" t="inlineStr"/>
-      <c r="D45" s="774" t="inlineStr"/>
-      <c r="E45" s="774" t="inlineStr"/>
-      <c r="F45" s="774" t="inlineStr"/>
-      <c r="G45" s="774" t="inlineStr"/>
-      <c r="H45" s="774" t="inlineStr"/>
+      <c r="C45" s="835" t="inlineStr"/>
+      <c r="D45" s="835" t="inlineStr"/>
+      <c r="E45" s="835" t="inlineStr"/>
+      <c r="F45" s="835" t="inlineStr"/>
+      <c r="G45" s="835" t="inlineStr"/>
+      <c r="H45" s="835" t="inlineStr"/>
     </row>
     <row r="46" ht="5" customHeight="1">
       <c r="A46" s="672" t="inlineStr"/>
@@ -70452,33 +73997,33 @@
       <c r="H47" s="669" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="603" t="inlineStr">
+      <c r="A48" s="843" t="inlineStr">
         <is>
           <t>Card ID</t>
         </is>
       </c>
-      <c r="B48" s="603" t="inlineStr">
+      <c r="B48" s="843" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C48" s="603" t="inlineStr">
+      <c r="C48" s="843" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D48" s="603" t="inlineStr"/>
-      <c r="E48" s="603" t="inlineStr"/>
-      <c r="F48" s="603" t="inlineStr"/>
-      <c r="G48" s="603" t="inlineStr"/>
-      <c r="H48" s="603" t="inlineStr">
+      <c r="D48" s="843" t="inlineStr"/>
+      <c r="E48" s="843" t="inlineStr"/>
+      <c r="F48" s="843" t="inlineStr"/>
+      <c r="G48" s="843" t="inlineStr"/>
+      <c r="H48" s="843" t="inlineStr">
         <is>
           <t>Why This Field</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="679" t="inlineStr">
+      <c r="A49" s="830" t="inlineStr">
         <is>
           <t>OGN-278</t>
         </is>
@@ -70504,7 +74049,7 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="679" t="inlineStr">
+      <c r="A50" s="830" t="inlineStr">
         <is>
           <t>OGN-298</t>
         </is>
@@ -70530,7 +74075,7 @@
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="679" t="inlineStr">
+      <c r="A51" s="830" t="inlineStr">
         <is>
           <t>OGN-282</t>
         </is>
@@ -71012,12 +74557,12 @@
           <t>Hide one card every turn using the legend ability. 1 energy not runes. Mushroom Pouch draws a card at your next Beginning Phase automatically.</t>
         </is>
       </c>
-      <c r="C70" s="774" t="inlineStr"/>
-      <c r="D70" s="774" t="inlineStr"/>
-      <c r="E70" s="774" t="inlineStr"/>
-      <c r="F70" s="774" t="inlineStr"/>
-      <c r="G70" s="774" t="inlineStr"/>
-      <c r="H70" s="774" t="inlineStr"/>
+      <c r="C70" s="835" t="inlineStr"/>
+      <c r="D70" s="835" t="inlineStr"/>
+      <c r="E70" s="835" t="inlineStr"/>
+      <c r="F70" s="835" t="inlineStr"/>
+      <c r="G70" s="835" t="inlineStr"/>
+      <c r="H70" s="835" t="inlineStr"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="709" t="inlineStr">
@@ -71048,12 +74593,12 @@
           <t>Eager Apprentice at a battlefield makes all spells cost 1 less. Frigid Touch becomes 1 rune. Stupefy becomes 0. Play Apprentice early and protect her.</t>
         </is>
       </c>
-      <c r="C72" s="774" t="inlineStr"/>
-      <c r="D72" s="774" t="inlineStr"/>
-      <c r="E72" s="774" t="inlineStr"/>
-      <c r="F72" s="774" t="inlineStr"/>
-      <c r="G72" s="774" t="inlineStr"/>
-      <c r="H72" s="774" t="inlineStr"/>
+      <c r="C72" s="835" t="inlineStr"/>
+      <c r="D72" s="835" t="inlineStr"/>
+      <c r="E72" s="835" t="inlineStr"/>
+      <c r="F72" s="835" t="inlineStr"/>
+      <c r="G72" s="835" t="inlineStr"/>
+      <c r="H72" s="835" t="inlineStr"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="709" t="inlineStr">
@@ -71084,12 +74629,12 @@
           <t>Rocket Barrage vs big units: pay the REPEAT 4 Mind = deal 4 twice to the same unit = 8 total damage. Kills Kadregrin. Kills Volibear Furious.</t>
         </is>
       </c>
-      <c r="C74" s="774" t="inlineStr"/>
-      <c r="D74" s="774" t="inlineStr"/>
-      <c r="E74" s="774" t="inlineStr"/>
-      <c r="F74" s="774" t="inlineStr"/>
-      <c r="G74" s="774" t="inlineStr"/>
-      <c r="H74" s="774" t="inlineStr"/>
+      <c r="C74" s="835" t="inlineStr"/>
+      <c r="D74" s="835" t="inlineStr"/>
+      <c r="E74" s="835" t="inlineStr"/>
+      <c r="F74" s="835" t="inlineStr"/>
+      <c r="G74" s="835" t="inlineStr"/>
+      <c r="H74" s="835" t="inlineStr"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="709" t="inlineStr">
@@ -71120,12 +74665,12 @@
           <t>Sideboard Thousand-Tailed Watcher vs Volibear. One play. All enemy units -3M. Dragon fights at 6M. Watcher is 7M. Dragon loses. Game changes immediately.</t>
         </is>
       </c>
-      <c r="C76" s="774" t="inlineStr"/>
-      <c r="D76" s="774" t="inlineStr"/>
-      <c r="E76" s="774" t="inlineStr"/>
-      <c r="F76" s="774" t="inlineStr"/>
-      <c r="G76" s="774" t="inlineStr"/>
-      <c r="H76" s="774" t="inlineStr"/>
+      <c r="C76" s="835" t="inlineStr"/>
+      <c r="D76" s="835" t="inlineStr"/>
+      <c r="E76" s="835" t="inlineStr"/>
+      <c r="F76" s="835" t="inlineStr"/>
+      <c r="G76" s="835" t="inlineStr"/>
+      <c r="H76" s="835" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -72238,18 +75783,18 @@
       <c r="H24" s="702" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="774" t="inlineStr"/>
-      <c r="B25" s="774" t="inlineStr">
+      <c r="A25" s="835" t="inlineStr"/>
+      <c r="B25" s="835" t="inlineStr">
         <is>
           <t>WHITE = LOW — future builds</t>
         </is>
       </c>
-      <c r="C25" s="774" t="inlineStr"/>
-      <c r="D25" s="774" t="inlineStr"/>
-      <c r="E25" s="774" t="inlineStr"/>
-      <c r="F25" s="774" t="inlineStr"/>
-      <c r="G25" s="774" t="inlineStr"/>
-      <c r="H25" s="774" t="inlineStr"/>
+      <c r="C25" s="835" t="inlineStr"/>
+      <c r="D25" s="835" t="inlineStr"/>
+      <c r="E25" s="835" t="inlineStr"/>
+      <c r="F25" s="835" t="inlineStr"/>
+      <c r="G25" s="835" t="inlineStr"/>
+      <c r="H25" s="835" t="inlineStr"/>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="680" t="inlineStr"/>
@@ -72331,7 +75876,7 @@
       <c r="B5" s="360" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="772" t="inlineStr">
+      <c r="C5" s="834" t="inlineStr">
         <is>
           <t>Traveling Merchant / Scrapheap</t>
         </is>
@@ -72377,7 +75922,7 @@
       <c r="B7" s="360" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="772" t="inlineStr">
+      <c r="C7" s="834" t="inlineStr">
         <is>
           <t>Draven Vanquisher attacking</t>
         </is>
@@ -72423,7 +75968,7 @@
       <c r="B9" s="360" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="772" t="inlineStr">
+      <c r="C9" s="834" t="inlineStr">
         <is>
           <t>Battering Ram (4 cards played)</t>
         </is>
@@ -72469,7 +76014,7 @@
       <c r="B11" s="360" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="772" t="inlineStr">
+      <c r="C11" s="834" t="inlineStr">
         <is>
           <t>COMBO: Ram x3 + Rhasa at 0-3</t>
         </is>
@@ -72530,7 +76075,7 @@
       <c r="B15" s="360" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="772" t="inlineStr">
+      <c r="C15" s="834" t="inlineStr">
         <is>
           <t>Guardian Angel (hidden/played)</t>
         </is>
@@ -72576,7 +76121,7 @@
       <c r="B17" s="360" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="772" t="inlineStr">
+      <c r="C17" s="834" t="inlineStr">
         <is>
           <t>Irelia - Fervent enters</t>
         </is>
@@ -72622,7 +76167,7 @@
       <c r="B19" s="360" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="772" t="inlineStr">
+      <c r="C19" s="834" t="inlineStr">
         <is>
           <t>Irelia + En Garde + Defiant</t>
         </is>
@@ -72668,7 +76213,7 @@
       <c r="B21" s="360" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="772" t="inlineStr">
+      <c r="C21" s="834" t="inlineStr">
         <is>
           <t>Draven Audacious enters</t>
         </is>
@@ -72729,7 +76274,7 @@
       <c r="B25" s="360" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="772" t="inlineStr">
+      <c r="C25" s="834" t="inlineStr">
         <is>
           <t>Scrapheap / Stacked Deck</t>
         </is>
@@ -72775,7 +76320,7 @@
       <c r="B27" s="360" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="772" t="inlineStr">
+      <c r="C27" s="834" t="inlineStr">
         <is>
           <t>Ezreal - Prodigy enters</t>
         </is>
@@ -72821,7 +76366,7 @@
       <c r="B29" s="360" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="772" t="inlineStr">
+      <c r="C29" s="834" t="inlineStr">
         <is>
           <t>Ravenbloom Student + spells</t>
         </is>
@@ -72867,7 +76412,7 @@
       <c r="B31" s="360" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="772" t="inlineStr">
+      <c r="C31" s="834" t="inlineStr">
         <is>
           <t>COMBO flood turn</t>
         </is>

--- a/riftbound_collection.xlsx
+++ b/riftbound_collection.xlsx
@@ -161,7 +161,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="95">
+  <fills count="102">
     <fill>
       <patternFill/>
     </fill>
@@ -633,6 +633,41 @@
         <fgColor rgb="00FFE0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B4D2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A1A00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D2B4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A0A0A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A0A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A0030"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A1A0A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -683,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1003">
+  <cellXfs count="1037">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3677,6 +3712,108 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="95" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="99" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="99" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="99" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="100" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="101" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10067,7 +10204,11 @@
           <t>Increase the points needed to win the game by 1</t>
         </is>
       </c>
-      <c r="K115" s="984" t="n"/>
+      <c r="K115" s="428" t="inlineStr">
+        <is>
+          <t>Sett BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="14" t="inlineStr">
@@ -10114,7 +10255,11 @@
           <t>You may hide an additional card here.</t>
         </is>
       </c>
-      <c r="K116" s="984" t="n"/>
+      <c r="K116" s="428" t="inlineStr">
+        <is>
+          <t>Teemo BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
@@ -10161,7 +10306,11 @@
           <t>When you defend here, choose a unit. It gains SHIELD 2 this combat. (+2 Might while It's a defender.)</t>
         </is>
       </c>
-      <c r="K117" s="984" t="n"/>
+      <c r="K117" s="428" t="inlineStr">
+        <is>
+          <t>Sett BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="14" t="inlineStr">
@@ -10208,7 +10357,11 @@
           <t>When you hold here, draw 1.</t>
         </is>
       </c>
-      <c r="K118" s="984" t="n"/>
+      <c r="K118" s="428" t="inlineStr">
+        <is>
+          <t>Ahri BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="14" t="inlineStr">
@@ -10255,7 +10408,11 @@
           <t>When you conquer here, you may spend a buff to draw 1.</t>
         </is>
       </c>
-      <c r="K119" s="984" t="n"/>
+      <c r="K119" s="428" t="inlineStr">
+        <is>
+          <t>Sett BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="14" t="inlineStr">
@@ -10302,7 +10459,11 @@
           <t>Players channel one additional rune during their first Runic Phase this game.</t>
         </is>
       </c>
-      <c r="K120" s="984" t="n"/>
+      <c r="K120" s="428" t="inlineStr">
+        <is>
+          <t>Teemo BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="14" t="inlineStr">
@@ -10396,7 +10557,11 @@
           <t>When you hold this, activate the conquer abilities of units here.</t>
         </is>
       </c>
-      <c r="K122" s="984" t="n"/>
+      <c r="K122" s="428" t="inlineStr">
+        <is>
+          <t>Mf BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="14" t="inlineStr">
@@ -10490,7 +10655,11 @@
           <t>When you conquer here, ready 2 runes at the end of this turn</t>
         </is>
       </c>
-      <c r="K124" s="984" t="n"/>
+      <c r="K124" s="428" t="inlineStr">
+        <is>
+          <t>Voli BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="14" t="inlineStr">
@@ -10537,7 +10706,11 @@
           <t>When you hold here, if you have 7+ units here, you win the game.</t>
         </is>
       </c>
-      <c r="K125" s="984" t="n"/>
+      <c r="K125" s="428" t="inlineStr">
+        <is>
+          <t>Azir BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
@@ -10584,7 +10757,11 @@
           <t>Units here have +1 Might. (This includes attackers.)</t>
         </is>
       </c>
-      <c r="K126" s="984" t="n"/>
+      <c r="K126" s="428" t="inlineStr">
+        <is>
+          <t>Voli BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
@@ -10631,7 +10808,11 @@
           <t>Units can't move from here to base.</t>
         </is>
       </c>
-      <c r="K127" s="984" t="n"/>
+      <c r="K127" s="428" t="inlineStr">
+        <is>
+          <t>Draven BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="14" t="inlineStr">
@@ -10678,7 +10859,11 @@
           <t>When you conquer here, discard 1, then draw 1.</t>
         </is>
       </c>
-      <c r="K128" s="984" t="n"/>
+      <c r="K128" s="428" t="inlineStr">
+        <is>
+          <t>Draven BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="57" t="inlineStr">
@@ -18208,7 +18393,11 @@
           <t>When you conquer here, you may pay 1 and return a unit you control here to its owner's hand. If you do, play a 2 Might Sand Soldier unit token here.</t>
         </is>
       </c>
-      <c r="K274" s="984" t="n"/>
+      <c r="K274" s="428" t="inlineStr">
+        <is>
+          <t>Azir BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c r="A275" s="14" t="inlineStr">
@@ -18247,7 +18436,11 @@
           <t>While you control this battlefield, friendly legends have "Exhaust: Attach an Equipment you control to a unit you control."</t>
         </is>
       </c>
-      <c r="K275" s="984" t="n"/>
+      <c r="K275" s="428" t="inlineStr">
+        <is>
+          <t>Lucian BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="15" customHeight="1">
       <c r="A276" s="14" t="inlineStr">
@@ -18286,7 +18479,11 @@
           <t>Players can't score here until their third turn.</t>
         </is>
       </c>
-      <c r="K276" s="984" t="n"/>
+      <c r="K276" s="428" t="inlineStr">
+        <is>
+          <t>Ahri BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="15" customHeight="1">
       <c r="A277" s="14" t="inlineStr">
@@ -18325,7 +18522,11 @@
           <t>When you conquer here, you may pay 1 to ready your legend.</t>
         </is>
       </c>
-      <c r="K277" s="984" t="n"/>
+      <c r="K277" s="428" t="inlineStr">
+        <is>
+          <t>Azir BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="15" customHeight="1">
       <c r="A278" s="14" t="inlineStr">
@@ -18364,7 +18565,11 @@
           <t>While you control this battlefield, friendly [REPEAT] costs cost 1 less.</t>
         </is>
       </c>
-      <c r="K278" s="984" t="n"/>
+      <c r="K278" s="428" t="inlineStr">
+        <is>
+          <t>Draven BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="15" customHeight="1">
       <c r="A279" s="14" t="inlineStr">
@@ -18442,7 +18647,11 @@
           <t>While you control this battlefield, the first friendly non-token gear played each turn costs 1 less.</t>
         </is>
       </c>
-      <c r="K280" s="984" t="n"/>
+      <c r="K280" s="428" t="inlineStr">
+        <is>
+          <t>Lucian BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="15" customHeight="1">
       <c r="A281" s="14" t="inlineStr">
@@ -18481,7 +18690,11 @@
           <t>When you defend here, reveal the top card of your Main Deck. If it's a spell, put it in your hand. Otherwise, recycle it.</t>
         </is>
       </c>
-      <c r="K281" s="984" t="n"/>
+      <c r="K281" s="428" t="inlineStr">
+        <is>
+          <t>Ahri BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="15" customHeight="1">
       <c r="A282" s="14" t="inlineStr">
@@ -18559,7 +18772,11 @@
           <t>When you conquer here with one or more [MIGHTY] units, you may pay 1 to draw 1. (A unit is Mighty while it has 5+ .)</t>
         </is>
       </c>
-      <c r="K283" s="984" t="n"/>
+      <c r="K283" s="428" t="inlineStr">
+        <is>
+          <t>Voli BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="15" customHeight="1">
       <c r="A284" s="14" t="inlineStr">
@@ -18637,7 +18854,11 @@
           <t>When you conquer here, you may pay 1 to play a Gold gear token exhausted.</t>
         </is>
       </c>
-      <c r="K285" s="984" t="n"/>
+      <c r="K285" s="428" t="inlineStr">
+        <is>
+          <t>Teemo BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="15" customHeight="1">
       <c r="A286" s="14" t="inlineStr">
@@ -18676,44 +18897,48 @@
           <t>When you conquer here, you may ready a friendly gear. If it's an Equipment, you may detach it.</t>
         </is>
       </c>
-      <c r="K286" s="984" t="n"/>
+      <c r="K286" s="428" t="inlineStr">
+        <is>
+          <t>Lucian BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="912" t="inlineStr">
+      <c r="A287" s="997" t="inlineStr">
         <is>
           <t>SFD-042</t>
         </is>
       </c>
-      <c r="B287" s="936" t="n">
+      <c r="B287" s="998" t="n">
         <v>3</v>
       </c>
-      <c r="C287" s="913" t="inlineStr">
+      <c r="C287" s="996" t="inlineStr">
         <is>
           <t>Brutalizer</t>
         </is>
       </c>
-      <c r="D287" s="913" t="inlineStr">
+      <c r="D287" s="996" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="E287" s="913" t="inlineStr">
+      <c r="E287" s="996" t="inlineStr">
         <is>
           <t>Gear</t>
         </is>
       </c>
-      <c r="F287" s="936" t="inlineStr">
+      <c r="F287" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G287" s="936" t="inlineStr"/>
-      <c r="H287" s="913" t="inlineStr">
+      <c r="G287" s="998" t="inlineStr"/>
+      <c r="H287" s="996" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I287" s="913" t="inlineStr">
+      <c r="I287" s="996" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
@@ -18730,92 +18955,96 @@
       </c>
     </row>
     <row r="288" ht="15" customHeight="1">
-      <c r="A288" s="980" t="inlineStr">
+      <c r="A288" s="1007" t="inlineStr">
         <is>
           <t>OGN-277</t>
         </is>
       </c>
-      <c r="B288" s="360" t="n">
+      <c r="B288" s="1009" t="n">
         <v>1</v>
       </c>
-      <c r="C288" s="981" t="inlineStr">
+      <c r="C288" s="1010" t="inlineStr">
         <is>
           <t>Back-Alley Bar</t>
         </is>
       </c>
-      <c r="D288" s="981" t="inlineStr">
+      <c r="D288" s="1010" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E288" s="981" t="inlineStr">
+      <c r="E288" s="1010" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
       </c>
-      <c r="F288" s="360" t="inlineStr">
+      <c r="F288" s="1009" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G288" s="360" t="inlineStr">
+      <c r="G288" s="1009" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H288" s="981" t="inlineStr">
+      <c r="H288" s="1010" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I288" s="981" t="inlineStr"/>
+      <c r="I288" s="1010" t="inlineStr"/>
       <c r="J288" s="97" t="inlineStr">
         <is>
           <t>When a unit moves from here, give it +1 Might this turn.</t>
         </is>
       </c>
-      <c r="K288" s="984" t="n"/>
+      <c r="K288" s="428" t="inlineStr">
+        <is>
+          <t>Mf BF(1)</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="15" customHeight="1">
-      <c r="A289" s="980" t="inlineStr">
+      <c r="A289" s="1007" t="inlineStr">
         <is>
           <t>SFD-214</t>
         </is>
       </c>
-      <c r="B289" s="360" t="n">
+      <c r="B289" s="1009" t="n">
         <v>1</v>
       </c>
-      <c r="C289" s="981" t="inlineStr">
+      <c r="C289" s="1010" t="inlineStr">
         <is>
           <t>Power Nexus</t>
         </is>
       </c>
-      <c r="D289" s="981" t="inlineStr">
+      <c r="D289" s="1010" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E289" s="981" t="inlineStr">
+      <c r="E289" s="1010" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
       </c>
-      <c r="F289" s="360" t="inlineStr">
+      <c r="F289" s="1009" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G289" s="360" t="inlineStr">
+      <c r="G289" s="1009" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H289" s="981" t="inlineStr">
+      <c r="H289" s="1010" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I289" s="981" t="inlineStr"/>
+      <c r="I289" s="1010" t="inlineStr"/>
       <c r="J289" s="97" t="inlineStr">
         <is>
           <t>When you hold here, you may pay Rune Rune Rune Rune to score 1 point.</t>
@@ -18965,47 +19194,51 @@
       </c>
     </row>
     <row r="293" ht="16" customHeight="1">
-      <c r="A293" s="981" t="inlineStr">
+      <c r="A293" s="1010" t="inlineStr">
         <is>
           <t>OGN-297</t>
         </is>
       </c>
-      <c r="B293" s="981" t="n">
+      <c r="B293" s="1010" t="n">
         <v>1</v>
       </c>
-      <c r="C293" s="981" t="inlineStr">
+      <c r="C293" s="1010" t="inlineStr">
         <is>
           <t>Windswept Hillock</t>
         </is>
       </c>
-      <c r="D293" s="981" t="inlineStr">
+      <c r="D293" s="1010" t="inlineStr">
         <is>
           <t>Colorless</t>
         </is>
       </c>
-      <c r="E293" s="981" t="inlineStr">
+      <c r="E293" s="1010" t="inlineStr">
         <is>
           <t>Battlefield</t>
         </is>
       </c>
-      <c r="F293" s="981" t="inlineStr">
+      <c r="F293" s="1010" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G293" s="981" t="inlineStr">
+      <c r="G293" s="1010" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H293" s="981" t="inlineStr">
+      <c r="H293" s="1010" t="inlineStr">
         <is>
           <t>Uncommon</t>
         </is>
       </c>
-      <c r="I293" s="981" t="inlineStr"/>
-      <c r="J293" s="981" t="inlineStr"/>
-      <c r="K293" s="946" t="n"/>
+      <c r="I293" s="1010" t="inlineStr"/>
+      <c r="J293" s="1010" t="inlineStr"/>
+      <c r="K293" s="428" t="inlineStr">
+        <is>
+          <t>Mf BF(1)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19095,17 +19328,17 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="834" t="inlineStr">
+      <c r="A5" s="1008" t="inlineStr">
         <is>
           <t>Draven - Vanquisher</t>
         </is>
       </c>
-      <c r="B5" s="360" t="inlineStr">
+      <c r="B5" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C5" s="980" t="n">
+      <c r="C5" s="1007" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="909" t="inlineStr">
@@ -19185,17 +19418,17 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="834" t="inlineStr">
+      <c r="A7" s="1008" t="inlineStr">
         <is>
           <t>Battering Ram</t>
         </is>
       </c>
-      <c r="B7" s="360" t="inlineStr">
+      <c r="B7" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C7" s="980" t="n">
+      <c r="C7" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="909" t="inlineStr">
@@ -19275,17 +19508,17 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="834" t="inlineStr">
+      <c r="A9" s="1008" t="inlineStr">
         <is>
           <t>Irelia - Fervent</t>
         </is>
       </c>
-      <c r="B9" s="360" t="inlineStr">
+      <c r="B9" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C9" s="980" t="n">
+      <c r="C9" s="1007" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="909" t="inlineStr">
@@ -19365,17 +19598,17 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="834" t="inlineStr">
+      <c r="A11" s="1008" t="inlineStr">
         <is>
           <t>Ravenbloom Student</t>
         </is>
       </c>
-      <c r="B11" s="360" t="inlineStr">
+      <c r="B11" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C11" s="980" t="n">
+      <c r="C11" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="909" t="inlineStr">
@@ -19455,17 +19688,17 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="834" t="inlineStr">
+      <c r="A13" s="1008" t="inlineStr">
         <is>
           <t>Called Shot</t>
         </is>
       </c>
-      <c r="B13" s="360" t="inlineStr">
+      <c r="B13" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C13" s="980" t="n">
+      <c r="C13" s="1007" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="909" t="inlineStr">
@@ -19562,17 +19795,17 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="834" t="inlineStr">
+      <c r="A17" s="1008" t="inlineStr">
         <is>
           <t>Minotaur Reckoner</t>
         </is>
       </c>
-      <c r="B17" s="360" t="inlineStr">
+      <c r="B17" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C17" s="980" t="n">
+      <c r="C17" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D17" s="909" t="inlineStr">
@@ -19652,17 +19885,17 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="834" t="inlineStr">
+      <c r="A19" s="1008" t="inlineStr">
         <is>
           <t>Cruel Patron</t>
         </is>
       </c>
-      <c r="B19" s="360" t="inlineStr">
+      <c r="B19" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C19" s="980" t="n">
+      <c r="C19" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="909" t="inlineStr">
@@ -19742,17 +19975,17 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="834" t="inlineStr">
+      <c r="A21" s="1008" t="inlineStr">
         <is>
           <t>Sandshifter</t>
         </is>
       </c>
-      <c r="B21" s="360" t="inlineStr">
+      <c r="B21" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C21" s="980" t="n">
+      <c r="C21" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D21" s="909" t="inlineStr">
@@ -19832,17 +20065,17 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="834" t="inlineStr">
+      <c r="A23" s="1008" t="inlineStr">
         <is>
           <t>Shakedown</t>
         </is>
       </c>
-      <c r="B23" s="360" t="inlineStr">
+      <c r="B23" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C23" s="980" t="n">
+      <c r="C23" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D23" s="909" t="inlineStr">
@@ -19922,17 +20155,17 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="834" t="inlineStr">
+      <c r="A25" s="1008" t="inlineStr">
         <is>
           <t>Fading Memories</t>
         </is>
       </c>
-      <c r="B25" s="360" t="inlineStr">
+      <c r="B25" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C25" s="980" t="n">
+      <c r="C25" s="1007" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="909" t="inlineStr">
@@ -20012,17 +20245,17 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="834" t="inlineStr">
+      <c r="A27" s="1008" t="inlineStr">
         <is>
           <t>Soaring Scout</t>
         </is>
       </c>
-      <c r="B27" s="360" t="inlineStr">
+      <c r="B27" s="1009" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C27" s="980" t="n">
+      <c r="C27" s="1007" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="909" t="inlineStr">
@@ -20112,7 +20345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20154,14 +20387,14 @@
       <c r="H2" s="714" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="715" t="inlineStr">
@@ -20230,25 +20463,25 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="914" t="inlineStr">
+      <c r="A7" s="986" t="inlineStr">
         <is>
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="915" t="inlineStr">
+      <c r="B7" s="988" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C7" s="915" t="inlineStr">
+      <c r="C7" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D7" s="916" t="inlineStr"/>
-      <c r="E7" s="916" t="inlineStr"/>
-      <c r="F7" s="916" t="inlineStr"/>
-      <c r="G7" s="916" t="inlineStr"/>
+      <c r="D7" s="987" t="inlineStr"/>
+      <c r="E7" s="987" t="inlineStr"/>
+      <c r="F7" s="987" t="inlineStr"/>
+      <c r="G7" s="987" t="inlineStr"/>
       <c r="H7" s="217" t="inlineStr">
         <is>
           <t>She protects one unit and double-conquers. Your deck floods 2+ units at fields she can only cover one of. She can't be everywhere.</t>
@@ -20256,25 +20489,25 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="914" t="inlineStr">
+      <c r="A8" s="986" t="inlineStr">
         <is>
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="915" t="inlineStr">
+      <c r="B8" s="988" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="C8" s="915" t="inlineStr">
+      <c r="C8" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D8" s="916" t="inlineStr"/>
-      <c r="E8" s="916" t="inlineStr"/>
-      <c r="F8" s="916" t="inlineStr"/>
-      <c r="G8" s="916" t="inlineStr"/>
+      <c r="D8" s="987" t="inlineStr"/>
+      <c r="E8" s="987" t="inlineStr"/>
+      <c r="F8" s="987" t="inlineStr"/>
+      <c r="G8" s="987" t="inlineStr"/>
       <c r="H8" s="217" t="inlineStr">
         <is>
           <t>Reactive draw engine. He needs to target your units twice per turn to draw. Play proactively, he can't keep up with your board pressure.</t>
@@ -20308,25 +20541,25 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="914" t="inlineStr">
+      <c r="A10" s="986" t="inlineStr">
         <is>
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B10" s="915" t="inlineStr">
+      <c r="B10" s="988" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C10" s="915" t="inlineStr">
+      <c r="C10" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D10" s="916" t="inlineStr"/>
-      <c r="E10" s="916" t="inlineStr"/>
-      <c r="F10" s="916" t="inlineStr"/>
-      <c r="G10" s="916" t="inlineStr"/>
+      <c r="D10" s="987" t="inlineStr"/>
+      <c r="E10" s="987" t="inlineStr"/>
+      <c r="F10" s="987" t="inlineStr"/>
+      <c r="G10" s="987" t="inlineStr"/>
       <c r="H10" s="217" t="inlineStr">
         <is>
           <t>Token flood hits both fields with 2M soldiers. ASSAULT units beat tokens. Token decks struggle vs single high-M units. Dependent on matchup speed.</t>
@@ -20386,14 +20619,14 @@
       </c>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="951" t="inlineStr"/>
-      <c r="B13" s="951" t="inlineStr"/>
-      <c r="C13" s="951" t="inlineStr"/>
-      <c r="D13" s="951" t="inlineStr"/>
-      <c r="E13" s="951" t="inlineStr"/>
-      <c r="F13" s="951" t="inlineStr"/>
-      <c r="G13" s="951" t="inlineStr"/>
-      <c r="H13" s="951" t="inlineStr"/>
+      <c r="A13" s="1017" t="inlineStr"/>
+      <c r="B13" s="1017" t="inlineStr"/>
+      <c r="C13" s="1017" t="inlineStr"/>
+      <c r="D13" s="1017" t="inlineStr"/>
+      <c r="E13" s="1017" t="inlineStr"/>
+      <c r="F13" s="1017" t="inlineStr"/>
+      <c r="G13" s="1017" t="inlineStr"/>
+      <c r="H13" s="1017" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="715" t="inlineStr">
@@ -20564,14 +20797,14 @@
       <c r="H21" s="957" t="inlineStr"/>
     </row>
     <row r="22" ht="4" customHeight="1">
-      <c r="A22" s="951" t="inlineStr"/>
-      <c r="B22" s="951" t="inlineStr"/>
-      <c r="C22" s="951" t="inlineStr"/>
-      <c r="D22" s="951" t="inlineStr"/>
-      <c r="E22" s="951" t="inlineStr"/>
-      <c r="F22" s="951" t="inlineStr"/>
-      <c r="G22" s="951" t="inlineStr"/>
-      <c r="H22" s="951" t="inlineStr"/>
+      <c r="A22" s="1017" t="inlineStr"/>
+      <c r="B22" s="1017" t="inlineStr"/>
+      <c r="C22" s="1017" t="inlineStr"/>
+      <c r="D22" s="1017" t="inlineStr"/>
+      <c r="E22" s="1017" t="inlineStr"/>
+      <c r="F22" s="1017" t="inlineStr"/>
+      <c r="G22" s="1017" t="inlineStr"/>
+      <c r="H22" s="1017" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="715" t="inlineStr">
@@ -20714,14 +20947,14 @@
       </c>
     </row>
     <row r="27" ht="4" customHeight="1">
-      <c r="A27" s="951" t="inlineStr"/>
-      <c r="B27" s="951" t="inlineStr"/>
-      <c r="C27" s="951" t="inlineStr"/>
-      <c r="D27" s="951" t="inlineStr"/>
-      <c r="E27" s="951" t="inlineStr"/>
-      <c r="F27" s="951" t="inlineStr"/>
-      <c r="G27" s="951" t="inlineStr"/>
-      <c r="H27" s="951" t="inlineStr"/>
+      <c r="A27" s="1017" t="inlineStr"/>
+      <c r="B27" s="1017" t="inlineStr"/>
+      <c r="C27" s="1017" t="inlineStr"/>
+      <c r="D27" s="1017" t="inlineStr"/>
+      <c r="E27" s="1017" t="inlineStr"/>
+      <c r="F27" s="1017" t="inlineStr"/>
+      <c r="G27" s="1017" t="inlineStr"/>
+      <c r="H27" s="1017" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="715" t="inlineStr">
@@ -21356,14 +21589,14 @@
       <c r="H44" s="712" t="inlineStr"/>
     </row>
     <row r="45" ht="4" customHeight="1">
-      <c r="A45" s="951" t="inlineStr"/>
-      <c r="B45" s="951" t="inlineStr"/>
-      <c r="C45" s="951" t="inlineStr"/>
-      <c r="D45" s="951" t="inlineStr"/>
-      <c r="E45" s="951" t="inlineStr"/>
-      <c r="F45" s="951" t="inlineStr"/>
-      <c r="G45" s="951" t="inlineStr"/>
-      <c r="H45" s="951" t="inlineStr"/>
+      <c r="A45" s="1017" t="inlineStr"/>
+      <c r="B45" s="1017" t="inlineStr"/>
+      <c r="C45" s="1017" t="inlineStr"/>
+      <c r="D45" s="1017" t="inlineStr"/>
+      <c r="E45" s="1017" t="inlineStr"/>
+      <c r="F45" s="1017" t="inlineStr"/>
+      <c r="G45" s="1017" t="inlineStr"/>
+      <c r="H45" s="1017" t="inlineStr"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="726" t="inlineStr">
@@ -21384,14 +21617,14 @@
       <c r="H46" s="727" t="inlineStr"/>
     </row>
     <row r="47" ht="4" customHeight="1">
-      <c r="A47" s="951" t="inlineStr"/>
-      <c r="B47" s="951" t="inlineStr"/>
-      <c r="C47" s="951" t="inlineStr"/>
-      <c r="D47" s="951" t="inlineStr"/>
-      <c r="E47" s="951" t="inlineStr"/>
-      <c r="F47" s="951" t="inlineStr"/>
-      <c r="G47" s="951" t="inlineStr"/>
-      <c r="H47" s="951" t="inlineStr"/>
+      <c r="A47" s="1017" t="inlineStr"/>
+      <c r="B47" s="1017" t="inlineStr"/>
+      <c r="C47" s="1017" t="inlineStr"/>
+      <c r="D47" s="1017" t="inlineStr"/>
+      <c r="E47" s="1017" t="inlineStr"/>
+      <c r="F47" s="1017" t="inlineStr"/>
+      <c r="G47" s="1017" t="inlineStr"/>
+      <c r="H47" s="1017" t="inlineStr"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="715" t="inlineStr">
@@ -21570,14 +21803,14 @@
       </c>
     </row>
     <row r="53" ht="4" customHeight="1">
-      <c r="A53" s="951" t="inlineStr"/>
-      <c r="B53" s="951" t="inlineStr"/>
-      <c r="C53" s="951" t="inlineStr"/>
-      <c r="D53" s="951" t="inlineStr"/>
-      <c r="E53" s="951" t="inlineStr"/>
-      <c r="F53" s="951" t="inlineStr"/>
-      <c r="G53" s="951" t="inlineStr"/>
-      <c r="H53" s="951" t="inlineStr"/>
+      <c r="A53" s="1017" t="inlineStr"/>
+      <c r="B53" s="1017" t="inlineStr"/>
+      <c r="C53" s="1017" t="inlineStr"/>
+      <c r="D53" s="1017" t="inlineStr"/>
+      <c r="E53" s="1017" t="inlineStr"/>
+      <c r="F53" s="1017" t="inlineStr"/>
+      <c r="G53" s="1017" t="inlineStr"/>
+      <c r="H53" s="1017" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="715" t="inlineStr">
@@ -21594,7 +21827,7 @@
       <c r="H54" s="712" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="980" t="inlineStr">
+      <c r="A55" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -21604,12 +21837,12 @@
           <t>Ramp turns 1-4. Never play Kadregrin before turn 5 — you won't have enough runes. Build up. Be patient. The payoff is coming.</t>
         </is>
       </c>
-      <c r="C55" s="981" t="inlineStr"/>
-      <c r="D55" s="981" t="inlineStr"/>
-      <c r="E55" s="981" t="inlineStr"/>
-      <c r="F55" s="981" t="inlineStr"/>
-      <c r="G55" s="981" t="inlineStr"/>
-      <c r="H55" s="981" t="inlineStr"/>
+      <c r="C55" s="1010" t="inlineStr"/>
+      <c r="D55" s="1010" t="inlineStr"/>
+      <c r="E55" s="1010" t="inlineStr"/>
+      <c r="F55" s="1010" t="inlineStr"/>
+      <c r="G55" s="1010" t="inlineStr"/>
+      <c r="H55" s="1010" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="982" t="inlineStr">
@@ -21630,7 +21863,7 @@
       <c r="H56" s="983" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="980" t="inlineStr">
+      <c r="A57" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -21640,12 +21873,12 @@
           <t>Volibear Furious has DEFLECT 2. Opponent must spend 2 runes to choose him with a spell. Most decks can't afford to. He's effectively removal-proof.</t>
         </is>
       </c>
-      <c r="C57" s="981" t="inlineStr"/>
-      <c r="D57" s="981" t="inlineStr"/>
-      <c r="E57" s="981" t="inlineStr"/>
-      <c r="F57" s="981" t="inlineStr"/>
-      <c r="G57" s="981" t="inlineStr"/>
-      <c r="H57" s="981" t="inlineStr"/>
+      <c r="C57" s="1010" t="inlineStr"/>
+      <c r="D57" s="1010" t="inlineStr"/>
+      <c r="E57" s="1010" t="inlineStr"/>
+      <c r="F57" s="1010" t="inlineStr"/>
+      <c r="G57" s="1010" t="inlineStr"/>
+      <c r="H57" s="1010" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="982" t="inlineStr">
@@ -21666,7 +21899,7 @@
       <c r="H58" s="983" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="980" t="inlineStr">
+      <c r="A59" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -21676,12 +21909,12 @@
           <t>Challenge in sideboard: pick Kadregrin or Volibear as your friendly unit. Pick their most dangerous threat as their unit. Forced fight. Your 9M wins every time.</t>
         </is>
       </c>
-      <c r="C59" s="981" t="inlineStr"/>
-      <c r="D59" s="981" t="inlineStr"/>
-      <c r="E59" s="981" t="inlineStr"/>
-      <c r="F59" s="981" t="inlineStr"/>
-      <c r="G59" s="981" t="inlineStr"/>
-      <c r="H59" s="981" t="inlineStr"/>
+      <c r="C59" s="1010" t="inlineStr"/>
+      <c r="D59" s="1010" t="inlineStr"/>
+      <c r="E59" s="1010" t="inlineStr"/>
+      <c r="F59" s="1010" t="inlineStr"/>
+      <c r="G59" s="1010" t="inlineStr"/>
+      <c r="H59" s="1010" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="982" t="inlineStr">
@@ -21702,7 +21935,7 @@
       <c r="H60" s="983" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="980" t="inlineStr">
+      <c r="A61" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -21712,12 +21945,12 @@
           <t>Mountain Drake (9/10) is your backup dragon. If Kadregrin gets answered, Drake is waiting. You can have two 9M+ bodies at different fields simultaneously.</t>
         </is>
       </c>
-      <c r="C61" s="981" t="inlineStr"/>
-      <c r="D61" s="981" t="inlineStr"/>
-      <c r="E61" s="981" t="inlineStr"/>
-      <c r="F61" s="981" t="inlineStr"/>
-      <c r="G61" s="981" t="inlineStr"/>
-      <c r="H61" s="981" t="inlineStr"/>
+      <c r="C61" s="1010" t="inlineStr"/>
+      <c r="D61" s="1010" t="inlineStr"/>
+      <c r="E61" s="1010" t="inlineStr"/>
+      <c r="F61" s="1010" t="inlineStr"/>
+      <c r="G61" s="1010" t="inlineStr"/>
+      <c r="H61" s="1010" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="982" t="inlineStr">
@@ -21736,6 +21969,124 @@
       <c r="F62" s="983" t="inlineStr"/>
       <c r="G62" s="983" t="inlineStr"/>
       <c r="H62" s="983" t="inlineStr"/>
+    </row>
+    <row r="63" ht="4" customHeight="1">
+      <c r="A63" s="1017" t="inlineStr"/>
+      <c r="B63" s="1017" t="inlineStr"/>
+      <c r="C63" s="1017" t="inlineStr"/>
+      <c r="D63" s="1017" t="inlineStr"/>
+      <c r="E63" s="1017" t="inlineStr"/>
+      <c r="F63" s="1017" t="inlineStr"/>
+      <c r="G63" s="1017" t="inlineStr"/>
+      <c r="H63" s="1017" t="inlineStr"/>
+      <c r="I63" s="1017" t="inlineStr"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="1018" t="inlineStr">
+        <is>
+          <t>BATTLEFIELDS — Choose 2 of These 3 Each Game</t>
+        </is>
+      </c>
+      <c r="B64" s="1019" t="inlineStr"/>
+      <c r="C64" s="1019" t="inlineStr"/>
+      <c r="D64" s="1019" t="inlineStr"/>
+      <c r="E64" s="1019" t="inlineStr"/>
+      <c r="F64" s="1019" t="inlineStr"/>
+      <c r="G64" s="1019" t="inlineStr"/>
+      <c r="H64" s="1019" t="inlineStr"/>
+      <c r="I64" s="1019" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="1020" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B65" s="1020" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C65" s="1020" t="inlineStr"/>
+      <c r="D65" s="1020" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="E65" s="1020" t="inlineStr"/>
+      <c r="F65" s="1020" t="inlineStr"/>
+      <c r="G65" s="1020" t="inlineStr"/>
+      <c r="H65" s="1020" t="inlineStr"/>
+      <c r="I65" s="1020" t="inlineStr"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="1021" t="inlineStr">
+        <is>
+          <t>SFD-218</t>
+        </is>
+      </c>
+      <c r="B66" s="1022" t="inlineStr">
+        <is>
+          <t>Sunken Temple</t>
+        </is>
+      </c>
+      <c r="C66" s="1023" t="inlineStr"/>
+      <c r="D66" s="1024" t="inlineStr">
+        <is>
+          <t>When you conquer here with one or more [MIGHTY] units, you may pay 1 to draw 1. (A unit is Mighty while it has 5+ .)</t>
+        </is>
+      </c>
+      <c r="E66" s="1023" t="inlineStr"/>
+      <c r="F66" s="1023" t="inlineStr"/>
+      <c r="G66" s="1023" t="inlineStr"/>
+      <c r="H66" s="1023" t="inlineStr"/>
+      <c r="I66" s="1023" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="1021" t="inlineStr">
+        <is>
+          <t>OGN-289</t>
+        </is>
+      </c>
+      <c r="B67" s="1022" t="inlineStr">
+        <is>
+          <t>Targon's Peak</t>
+        </is>
+      </c>
+      <c r="C67" s="1023" t="inlineStr"/>
+      <c r="D67" s="1024" t="inlineStr">
+        <is>
+          <t>When you conquer here, ready 2 runes at the end of this turn</t>
+        </is>
+      </c>
+      <c r="E67" s="1023" t="inlineStr"/>
+      <c r="F67" s="1023" t="inlineStr"/>
+      <c r="G67" s="1023" t="inlineStr"/>
+      <c r="H67" s="1023" t="inlineStr"/>
+      <c r="I67" s="1023" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="1021" t="inlineStr">
+        <is>
+          <t>OGN-294</t>
+        </is>
+      </c>
+      <c r="B68" s="1022" t="inlineStr">
+        <is>
+          <t>Trifarian War Camp</t>
+        </is>
+      </c>
+      <c r="C68" s="1023" t="inlineStr"/>
+      <c r="D68" s="1024" t="inlineStr">
+        <is>
+          <t>Units here have +1 Might. (This includes attackers.)</t>
+        </is>
+      </c>
+      <c r="E68" s="1023" t="inlineStr"/>
+      <c r="F68" s="1023" t="inlineStr"/>
+      <c r="G68" s="1023" t="inlineStr"/>
+      <c r="H68" s="1023" t="inlineStr"/>
+      <c r="I68" s="1023" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22128,12 +22479,12 @@
       </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="834" t="inlineStr">
+      <c r="A15" s="1008" t="inlineStr">
         <is>
           <t>vs Draven Midrange</t>
         </is>
       </c>
-      <c r="B15" s="980" t="inlineStr">
+      <c r="B15" s="1007" t="inlineStr">
         <is>
           <t>Turn 3</t>
         </is>
@@ -22202,12 +22553,12 @@
       </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="834" t="inlineStr">
+      <c r="A17" s="1008" t="inlineStr">
         <is>
           <t>vs Irelia Voltron</t>
         </is>
       </c>
-      <c r="B17" s="980" t="inlineStr">
+      <c r="B17" s="1007" t="inlineStr">
         <is>
           <t>Turn 4</t>
         </is>
@@ -22298,12 +22649,12 @@
 This card should appear in EVERY deck you build. It is the single hardest counter to the top 2 meta combos in the game right now.</t>
         </is>
       </c>
-      <c r="B20" s="916" t="inlineStr"/>
-      <c r="C20" s="916" t="inlineStr"/>
-      <c r="D20" s="916" t="inlineStr"/>
-      <c r="E20" s="916" t="inlineStr"/>
-      <c r="F20" s="916" t="inlineStr"/>
-      <c r="G20" s="916" t="inlineStr"/>
+      <c r="B20" s="987" t="inlineStr"/>
+      <c r="C20" s="987" t="inlineStr"/>
+      <c r="D20" s="987" t="inlineStr"/>
+      <c r="E20" s="987" t="inlineStr"/>
+      <c r="F20" s="987" t="inlineStr"/>
+      <c r="G20" s="987" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22427,12 +22778,12 @@
       <c r="A5" s="644" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="360" t="inlineStr">
+      <c r="B5" s="1009" t="inlineStr">
         <is>
           <t>OGN-180</t>
         </is>
       </c>
-      <c r="C5" s="834" t="inlineStr">
+      <c r="C5" s="1008" t="inlineStr">
         <is>
           <t>Fading Memories</t>
         </is>
@@ -22442,12 +22793,12 @@
           <t>$0.16</t>
         </is>
       </c>
-      <c r="E5" s="360" t="inlineStr">
+      <c r="E5" s="1009" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="F5" s="360" t="inlineStr">
+      <c r="F5" s="1009" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -22462,7 +22813,7 @@
           <t>69.4%</t>
         </is>
       </c>
-      <c r="I5" s="980" t="inlineStr">
+      <c r="I5" s="1007" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -22482,12 +22833,12 @@
       <c r="A6" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="360" t="inlineStr">
+      <c r="B6" s="1009" t="inlineStr">
         <is>
           <t>SFD-???</t>
         </is>
       </c>
-      <c r="C6" s="834" t="inlineStr">
+      <c r="C6" s="1008" t="inlineStr">
         <is>
           <t>Rebuke</t>
         </is>
@@ -22497,12 +22848,12 @@
           <t>$0.42</t>
         </is>
       </c>
-      <c r="E6" s="360" t="inlineStr">
+      <c r="E6" s="1009" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F6" s="360" t="inlineStr">
+      <c r="F6" s="1009" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -22512,17 +22863,17 @@
           <t>83.2%</t>
         </is>
       </c>
-      <c r="H6" s="912" t="inlineStr">
+      <c r="H6" s="997" t="inlineStr">
         <is>
           <t>90.7%</t>
         </is>
       </c>
-      <c r="I6" s="980" t="inlineStr">
+      <c r="I6" s="1007" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="J6" s="912" t="inlineStr">
+      <c r="J6" s="997" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22537,12 +22888,12 @@
       <c r="A7" s="263" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="360" t="inlineStr">
+      <c r="B7" s="1009" t="inlineStr">
         <is>
           <t>OGN-???</t>
         </is>
       </c>
-      <c r="C7" s="834" t="inlineStr">
+      <c r="C7" s="1008" t="inlineStr">
         <is>
           <t>Ride the Wind</t>
         </is>
@@ -22552,12 +22903,12 @@
           <t>$0.57</t>
         </is>
       </c>
-      <c r="E7" s="360" t="inlineStr">
+      <c r="E7" s="1009" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F7" s="360" t="inlineStr">
+      <c r="F7" s="1009" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -22572,7 +22923,7 @@
           <t>77.7%</t>
         </is>
       </c>
-      <c r="I7" s="980" t="inlineStr">
+      <c r="I7" s="1007" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -22592,12 +22943,12 @@
       <c r="A8" s="515" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="360" t="inlineStr">
+      <c r="B8" s="1009" t="inlineStr">
         <is>
           <t>OGN-???</t>
         </is>
       </c>
-      <c r="C8" s="834" t="inlineStr">
+      <c r="C8" s="1008" t="inlineStr">
         <is>
           <t>En Garde</t>
         </is>
@@ -22607,12 +22958,12 @@
           <t>$0.17</t>
         </is>
       </c>
-      <c r="E8" s="360" t="inlineStr">
+      <c r="E8" s="1009" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F8" s="360" t="inlineStr">
+      <c r="F8" s="1009" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -22622,17 +22973,17 @@
           <t>69.5%</t>
         </is>
       </c>
-      <c r="H8" s="912" t="inlineStr">
+      <c r="H8" s="997" t="inlineStr">
         <is>
           <t>83.2%</t>
         </is>
       </c>
-      <c r="I8" s="980" t="inlineStr">
+      <c r="I8" s="1007" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="J8" s="912" t="inlineStr">
+      <c r="J8" s="997" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -22647,12 +22998,12 @@
       <c r="A9" s="593" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="360" t="inlineStr">
+      <c r="B9" s="1009" t="inlineStr">
         <is>
           <t>SFD-???</t>
         </is>
       </c>
-      <c r="C9" s="834" t="inlineStr">
+      <c r="C9" s="1008" t="inlineStr">
         <is>
           <t>Switcheroo</t>
         </is>
@@ -22662,12 +23013,12 @@
           <t>$0.49</t>
         </is>
       </c>
-      <c r="E9" s="360" t="inlineStr">
+      <c r="E9" s="1009" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F9" s="360" t="inlineStr">
+      <c r="F9" s="1009" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -22682,7 +23033,7 @@
           <t>74.7%</t>
         </is>
       </c>
-      <c r="I9" s="980" t="inlineStr">
+      <c r="I9" s="1007" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -22786,7 +23137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22828,14 +23179,14 @@
       <c r="H2" s="731" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="732" t="inlineStr">
@@ -22904,25 +23255,25 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="911" t="inlineStr">
+      <c r="A7" s="995" t="inlineStr">
         <is>
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="912" t="inlineStr">
+      <c r="B7" s="997" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C7" s="912" t="inlineStr">
+      <c r="C7" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D7" s="913" t="inlineStr"/>
-      <c r="E7" s="913" t="inlineStr"/>
-      <c r="F7" s="913" t="inlineStr"/>
-      <c r="G7" s="913" t="inlineStr"/>
+      <c r="D7" s="996" t="inlineStr"/>
+      <c r="E7" s="996" t="inlineStr"/>
+      <c r="F7" s="996" t="inlineStr"/>
+      <c r="G7" s="996" t="inlineStr"/>
       <c r="H7" s="112" t="inlineStr">
         <is>
           <t>She protects one unit and double-conquers. Your deck floods 2+ units at fields she can only cover one of. She can't be everywhere.</t>
@@ -22930,25 +23281,25 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="911" t="inlineStr">
+      <c r="A8" s="995" t="inlineStr">
         <is>
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="912" t="inlineStr">
+      <c r="B8" s="997" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="C8" s="912" t="inlineStr">
+      <c r="C8" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D8" s="913" t="inlineStr"/>
-      <c r="E8" s="913" t="inlineStr"/>
-      <c r="F8" s="913" t="inlineStr"/>
-      <c r="G8" s="913" t="inlineStr"/>
+      <c r="D8" s="996" t="inlineStr"/>
+      <c r="E8" s="996" t="inlineStr"/>
+      <c r="F8" s="996" t="inlineStr"/>
+      <c r="G8" s="996" t="inlineStr"/>
       <c r="H8" s="112" t="inlineStr">
         <is>
           <t>Reactive draw engine. He needs to target your units twice per turn to draw. Play proactively, he can't keep up with your board pressure.</t>
@@ -22982,25 +23333,25 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="914" t="inlineStr">
+      <c r="A10" s="986" t="inlineStr">
         <is>
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B10" s="915" t="inlineStr">
+      <c r="B10" s="988" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C10" s="915" t="inlineStr">
+      <c r="C10" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D10" s="916" t="inlineStr"/>
-      <c r="E10" s="916" t="inlineStr"/>
-      <c r="F10" s="916" t="inlineStr"/>
-      <c r="G10" s="916" t="inlineStr"/>
+      <c r="D10" s="987" t="inlineStr"/>
+      <c r="E10" s="987" t="inlineStr"/>
+      <c r="F10" s="987" t="inlineStr"/>
+      <c r="G10" s="987" t="inlineStr"/>
       <c r="H10" s="217" t="inlineStr">
         <is>
           <t>Token flood hits both fields with 2M soldiers. ASSAULT units beat tokens. Token decks struggle vs single high-M units. Dependent on matchup speed.</t>
@@ -23008,25 +23359,25 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="914" t="inlineStr">
+      <c r="A11" s="986" t="inlineStr">
         <is>
           <t>vs Volibear (ours)</t>
         </is>
       </c>
-      <c r="B11" s="915" t="inlineStr">
+      <c r="B11" s="988" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C11" s="915" t="inlineStr">
+      <c r="C11" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D11" s="916" t="inlineStr"/>
-      <c r="E11" s="916" t="inlineStr"/>
-      <c r="F11" s="916" t="inlineStr"/>
-      <c r="G11" s="916" t="inlineStr"/>
+      <c r="D11" s="987" t="inlineStr"/>
+      <c r="E11" s="987" t="inlineStr"/>
+      <c r="F11" s="987" t="inlineStr"/>
+      <c r="G11" s="987" t="inlineStr"/>
       <c r="H11" s="217" t="inlineStr">
         <is>
           <t>Dragon is 9M. Arrives turn 6. Fast decks score 4-5pts before it lands. Slow decks fall behind waiting for ramp. G2 SB answers the dragon directly.</t>
@@ -23060,14 +23411,14 @@
       </c>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="951" t="inlineStr"/>
-      <c r="B13" s="951" t="inlineStr"/>
-      <c r="C13" s="951" t="inlineStr"/>
-      <c r="D13" s="951" t="inlineStr"/>
-      <c r="E13" s="951" t="inlineStr"/>
-      <c r="F13" s="951" t="inlineStr"/>
-      <c r="G13" s="951" t="inlineStr"/>
-      <c r="H13" s="951" t="inlineStr"/>
+      <c r="A13" s="1017" t="inlineStr"/>
+      <c r="B13" s="1017" t="inlineStr"/>
+      <c r="C13" s="1017" t="inlineStr"/>
+      <c r="D13" s="1017" t="inlineStr"/>
+      <c r="E13" s="1017" t="inlineStr"/>
+      <c r="F13" s="1017" t="inlineStr"/>
+      <c r="G13" s="1017" t="inlineStr"/>
+      <c r="H13" s="1017" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="732" t="inlineStr">
@@ -23174,20 +23525,24 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="964" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>OGN-297</t>
         </is>
       </c>
       <c r="B19" s="965" t="inlineStr">
         <is>
-          <t>EXHAUST</t>
+          <t>Windswept Hillock</t>
         </is>
       </c>
       <c r="C19" s="685" t="inlineStr">
         <is>
-          <t>Exhaust MF legend: give a unit GANKING this turn. It can now move field to field. Target your Trinity Force carrier.</t>
-        </is>
-      </c>
-      <c r="D19" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D19" s="957" t="inlineStr">
+        <is>
+          <t>Units here have GANKING. (They can move from battlefield to battlefield.)</t>
+        </is>
+      </c>
       <c r="E19" s="957" t="inlineStr"/>
       <c r="F19" s="957" t="inlineStr"/>
       <c r="G19" s="957" t="inlineStr"/>
@@ -23196,20 +23551,24 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="966" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>OGN-277</t>
         </is>
       </c>
       <c r="B20" s="967" t="inlineStr">
         <is>
-          <t>FIELD</t>
+          <t>Back-Alley Bar</t>
         </is>
       </c>
       <c r="C20" s="685" t="inlineStr">
         <is>
-          <t>Play MF Buccaneer to an open battlefield directly. Play units to open fields from hand. No base deployment needed.</t>
-        </is>
-      </c>
-      <c r="D20" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D20" s="957" t="inlineStr">
+        <is>
+          <t>When a unit moves from here, give it +1 Might this turn.</t>
+        </is>
+      </c>
       <c r="E20" s="957" t="inlineStr"/>
       <c r="F20" s="957" t="inlineStr"/>
       <c r="G20" s="957" t="inlineStr"/>
@@ -23218,34 +23577,38 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="968" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OGN-286</t>
         </is>
       </c>
       <c r="B21" s="969" t="inlineStr">
         <is>
-          <t>GANKING</t>
+          <t>Reckoner's Arena</t>
         </is>
       </c>
       <c r="C21" s="685" t="inlineStr">
         <is>
-          <t>Trinity carrier conquers field 1. Ride the Wind: ready it + give GANKING. Conquer field 2 same turn. Score 2 points + passive Trinity. Opponent has no answer.</t>
-        </is>
-      </c>
-      <c r="D21" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D21" s="957" t="inlineStr">
+        <is>
+          <t>When you hold this, activate the conquer abilities of units here.</t>
+        </is>
+      </c>
       <c r="E21" s="957" t="inlineStr"/>
       <c r="F21" s="957" t="inlineStr"/>
       <c r="G21" s="957" t="inlineStr"/>
       <c r="H21" s="957" t="inlineStr"/>
     </row>
     <row r="22" ht="4" customHeight="1">
-      <c r="A22" s="951" t="inlineStr"/>
-      <c r="B22" s="951" t="inlineStr"/>
-      <c r="C22" s="951" t="inlineStr"/>
-      <c r="D22" s="951" t="inlineStr"/>
-      <c r="E22" s="951" t="inlineStr"/>
-      <c r="F22" s="951" t="inlineStr"/>
-      <c r="G22" s="951" t="inlineStr"/>
-      <c r="H22" s="951" t="inlineStr"/>
+      <c r="A22" s="1017" t="inlineStr"/>
+      <c r="B22" s="1017" t="inlineStr"/>
+      <c r="C22" s="1017" t="inlineStr"/>
+      <c r="D22" s="1017" t="inlineStr"/>
+      <c r="E22" s="1017" t="inlineStr"/>
+      <c r="F22" s="1017" t="inlineStr"/>
+      <c r="G22" s="1017" t="inlineStr"/>
+      <c r="H22" s="1017" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="732" t="inlineStr">
@@ -23388,14 +23751,14 @@
       </c>
     </row>
     <row r="27" ht="4" customHeight="1">
-      <c r="A27" s="951" t="inlineStr"/>
-      <c r="B27" s="951" t="inlineStr"/>
-      <c r="C27" s="951" t="inlineStr"/>
-      <c r="D27" s="951" t="inlineStr"/>
-      <c r="E27" s="951" t="inlineStr"/>
-      <c r="F27" s="951" t="inlineStr"/>
-      <c r="G27" s="951" t="inlineStr"/>
-      <c r="H27" s="951" t="inlineStr"/>
+      <c r="A27" s="1017" t="inlineStr"/>
+      <c r="B27" s="1017" t="inlineStr"/>
+      <c r="C27" s="1017" t="inlineStr"/>
+      <c r="D27" s="1017" t="inlineStr"/>
+      <c r="E27" s="1017" t="inlineStr"/>
+      <c r="F27" s="1017" t="inlineStr"/>
+      <c r="G27" s="1017" t="inlineStr"/>
+      <c r="H27" s="1017" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="732" t="inlineStr">
@@ -24066,14 +24429,14 @@
       <c r="H45" s="729" t="inlineStr"/>
     </row>
     <row r="46" ht="4" customHeight="1">
-      <c r="A46" s="951" t="inlineStr"/>
-      <c r="B46" s="951" t="inlineStr"/>
-      <c r="C46" s="951" t="inlineStr"/>
-      <c r="D46" s="951" t="inlineStr"/>
-      <c r="E46" s="951" t="inlineStr"/>
-      <c r="F46" s="951" t="inlineStr"/>
-      <c r="G46" s="951" t="inlineStr"/>
-      <c r="H46" s="951" t="inlineStr"/>
+      <c r="A46" s="1017" t="inlineStr"/>
+      <c r="B46" s="1017" t="inlineStr"/>
+      <c r="C46" s="1017" t="inlineStr"/>
+      <c r="D46" s="1017" t="inlineStr"/>
+      <c r="E46" s="1017" t="inlineStr"/>
+      <c r="F46" s="1017" t="inlineStr"/>
+      <c r="G46" s="1017" t="inlineStr"/>
+      <c r="H46" s="1017" t="inlineStr"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="739" t="inlineStr">
@@ -24094,14 +24457,14 @@
       <c r="H47" s="741" t="inlineStr"/>
     </row>
     <row r="48" ht="4" customHeight="1">
-      <c r="A48" s="951" t="inlineStr"/>
-      <c r="B48" s="951" t="inlineStr"/>
-      <c r="C48" s="951" t="inlineStr"/>
-      <c r="D48" s="951" t="inlineStr"/>
-      <c r="E48" s="951" t="inlineStr"/>
-      <c r="F48" s="951" t="inlineStr"/>
-      <c r="G48" s="951" t="inlineStr"/>
-      <c r="H48" s="951" t="inlineStr"/>
+      <c r="A48" s="1017" t="inlineStr"/>
+      <c r="B48" s="1017" t="inlineStr"/>
+      <c r="C48" s="1017" t="inlineStr"/>
+      <c r="D48" s="1017" t="inlineStr"/>
+      <c r="E48" s="1017" t="inlineStr"/>
+      <c r="F48" s="1017" t="inlineStr"/>
+      <c r="G48" s="1017" t="inlineStr"/>
+      <c r="H48" s="1017" t="inlineStr"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="732" t="inlineStr">
@@ -24320,14 +24683,14 @@
       </c>
     </row>
     <row r="55" ht="4" customHeight="1">
-      <c r="A55" s="951" t="inlineStr"/>
-      <c r="B55" s="951" t="inlineStr"/>
-      <c r="C55" s="951" t="inlineStr"/>
-      <c r="D55" s="951" t="inlineStr"/>
-      <c r="E55" s="951" t="inlineStr"/>
-      <c r="F55" s="951" t="inlineStr"/>
-      <c r="G55" s="951" t="inlineStr"/>
-      <c r="H55" s="951" t="inlineStr"/>
+      <c r="A55" s="1017" t="inlineStr"/>
+      <c r="B55" s="1017" t="inlineStr"/>
+      <c r="C55" s="1017" t="inlineStr"/>
+      <c r="D55" s="1017" t="inlineStr"/>
+      <c r="E55" s="1017" t="inlineStr"/>
+      <c r="F55" s="1017" t="inlineStr"/>
+      <c r="G55" s="1017" t="inlineStr"/>
+      <c r="H55" s="1017" t="inlineStr"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="732" t="inlineStr">
@@ -24344,7 +24707,7 @@
       <c r="H56" s="729" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="980" t="inlineStr">
+      <c r="A57" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -24354,12 +24717,12 @@
           <t>Trinity Force is your win condition. Equip it ASAP on your strongest unit. Hold a field with that unit every turn. Score 1 free point every turn just from existing.</t>
         </is>
       </c>
-      <c r="C57" s="981" t="inlineStr"/>
-      <c r="D57" s="981" t="inlineStr"/>
-      <c r="E57" s="981" t="inlineStr"/>
-      <c r="F57" s="981" t="inlineStr"/>
-      <c r="G57" s="981" t="inlineStr"/>
-      <c r="H57" s="981" t="inlineStr"/>
+      <c r="C57" s="1010" t="inlineStr"/>
+      <c r="D57" s="1010" t="inlineStr"/>
+      <c r="E57" s="1010" t="inlineStr"/>
+      <c r="F57" s="1010" t="inlineStr"/>
+      <c r="G57" s="1010" t="inlineStr"/>
+      <c r="H57" s="1010" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="982" t="inlineStr">
@@ -24380,7 +24743,7 @@
       <c r="H58" s="983" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="980" t="inlineStr">
+      <c r="A59" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -24390,12 +24753,12 @@
           <t>Ride the Wind combo: Trinity carrier conquers field 1. Ride the Wind readies it + gives GANKING. Conquer field 2 same turn. Score 2 conquest points + Trinity passive. 3 points one turn.</t>
         </is>
       </c>
-      <c r="C59" s="981" t="inlineStr"/>
-      <c r="D59" s="981" t="inlineStr"/>
-      <c r="E59" s="981" t="inlineStr"/>
-      <c r="F59" s="981" t="inlineStr"/>
-      <c r="G59" s="981" t="inlineStr"/>
-      <c r="H59" s="981" t="inlineStr"/>
+      <c r="C59" s="1010" t="inlineStr"/>
+      <c r="D59" s="1010" t="inlineStr"/>
+      <c r="E59" s="1010" t="inlineStr"/>
+      <c r="F59" s="1010" t="inlineStr"/>
+      <c r="G59" s="1010" t="inlineStr"/>
+      <c r="H59" s="1010" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="982" t="inlineStr">
@@ -24416,7 +24779,7 @@
       <c r="H60" s="983" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="980" t="inlineStr">
+      <c r="A61" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -24426,12 +24789,12 @@
           <t>Boots of Swiftness on Trinity carrier = permanent GANKING without spending legend exhaust. Free up your legend exhaust for another unit.</t>
         </is>
       </c>
-      <c r="C61" s="981" t="inlineStr"/>
-      <c r="D61" s="981" t="inlineStr"/>
-      <c r="E61" s="981" t="inlineStr"/>
-      <c r="F61" s="981" t="inlineStr"/>
-      <c r="G61" s="981" t="inlineStr"/>
-      <c r="H61" s="981" t="inlineStr"/>
+      <c r="C61" s="1010" t="inlineStr"/>
+      <c r="D61" s="1010" t="inlineStr"/>
+      <c r="E61" s="1010" t="inlineStr"/>
+      <c r="F61" s="1010" t="inlineStr"/>
+      <c r="G61" s="1010" t="inlineStr"/>
+      <c r="H61" s="1010" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="982" t="inlineStr">
@@ -24452,7 +24815,7 @@
       <c r="H62" s="983" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="980" t="inlineStr">
+      <c r="A63" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -24462,12 +24825,12 @@
           <t>Overt Op: spend all your unit buffs to ready all units here. After conquering a field, ready everything = attack again. Double conquest available every turn with buffs.</t>
         </is>
       </c>
-      <c r="C63" s="981" t="inlineStr"/>
-      <c r="D63" s="981" t="inlineStr"/>
-      <c r="E63" s="981" t="inlineStr"/>
-      <c r="F63" s="981" t="inlineStr"/>
-      <c r="G63" s="981" t="inlineStr"/>
-      <c r="H63" s="981" t="inlineStr"/>
+      <c r="C63" s="1010" t="inlineStr"/>
+      <c r="D63" s="1010" t="inlineStr"/>
+      <c r="E63" s="1010" t="inlineStr"/>
+      <c r="F63" s="1010" t="inlineStr"/>
+      <c r="G63" s="1010" t="inlineStr"/>
+      <c r="H63" s="1010" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="982" t="inlineStr">
@@ -24487,6 +24850,22 @@
       <c r="G64" s="983" t="inlineStr"/>
       <c r="H64" s="983" t="inlineStr"/>
     </row>
+    <row r="65" ht="4" customHeight="1">
+      <c r="A65" s="1017" t="inlineStr"/>
+      <c r="B65" s="1017" t="inlineStr"/>
+      <c r="C65" s="1017" t="inlineStr"/>
+      <c r="D65" s="1017" t="inlineStr"/>
+      <c r="E65" s="1017" t="inlineStr"/>
+      <c r="F65" s="1017" t="inlineStr"/>
+      <c r="G65" s="1017" t="inlineStr"/>
+      <c r="H65" s="1017" t="inlineStr"/>
+      <c r="I65" s="1017" t="inlineStr"/>
+    </row>
+    <row r="66" ht="15" customHeight="1"/>
+    <row r="67" ht="18" customHeight="1"/>
+    <row r="68" ht="32" customHeight="1"/>
+    <row r="69" ht="32" customHeight="1"/>
+    <row r="70" ht="32" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24498,7 +24877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24540,14 +24919,14 @@
       <c r="H2" s="744" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="745" t="inlineStr">
@@ -24616,25 +24995,25 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="911" t="inlineStr">
+      <c r="A7" s="995" t="inlineStr">
         <is>
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="912" t="inlineStr">
+      <c r="B7" s="997" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="C7" s="912" t="inlineStr">
+      <c r="C7" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D7" s="913" t="inlineStr"/>
-      <c r="E7" s="913" t="inlineStr"/>
-      <c r="F7" s="913" t="inlineStr"/>
-      <c r="G7" s="913" t="inlineStr"/>
+      <c r="D7" s="996" t="inlineStr"/>
+      <c r="E7" s="996" t="inlineStr"/>
+      <c r="F7" s="996" t="inlineStr"/>
+      <c r="G7" s="996" t="inlineStr"/>
       <c r="H7" s="112" t="inlineStr">
         <is>
           <t>She protects one unit and double-conquers. Your deck floods 2+ units at fields she can only cover one of. She can't be everywhere.</t>
@@ -24642,25 +25021,25 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="911" t="inlineStr">
+      <c r="A8" s="995" t="inlineStr">
         <is>
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="912" t="inlineStr">
+      <c r="B8" s="997" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C8" s="912" t="inlineStr">
+      <c r="C8" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D8" s="913" t="inlineStr"/>
-      <c r="E8" s="913" t="inlineStr"/>
-      <c r="F8" s="913" t="inlineStr"/>
-      <c r="G8" s="913" t="inlineStr"/>
+      <c r="D8" s="996" t="inlineStr"/>
+      <c r="E8" s="996" t="inlineStr"/>
+      <c r="F8" s="996" t="inlineStr"/>
+      <c r="G8" s="996" t="inlineStr"/>
       <c r="H8" s="112" t="inlineStr">
         <is>
           <t>Reactive draw engine. He needs to target your units twice per turn to draw. Play proactively, he can't keep up with your board pressure.</t>
@@ -24668,25 +25047,25 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="911" t="inlineStr">
+      <c r="A9" s="995" t="inlineStr">
         <is>
           <t>vs Azir (ours)</t>
         </is>
       </c>
-      <c r="B9" s="912" t="inlineStr">
+      <c r="B9" s="997" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C9" s="912" t="inlineStr">
+      <c r="C9" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D9" s="913" t="inlineStr"/>
-      <c r="E9" s="913" t="inlineStr"/>
-      <c r="F9" s="913" t="inlineStr"/>
-      <c r="G9" s="913" t="inlineStr"/>
+      <c r="D9" s="996" t="inlineStr"/>
+      <c r="E9" s="996" t="inlineStr"/>
+      <c r="F9" s="996" t="inlineStr"/>
+      <c r="G9" s="996" t="inlineStr"/>
       <c r="H9" s="112" t="inlineStr">
         <is>
           <t>Token flood hits both fields with 2M soldiers. ASSAULT units beat tokens. Token decks struggle vs single high-M units. Dependent on matchup speed.</t>
@@ -24720,25 +25099,25 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="914" t="inlineStr">
+      <c r="A11" s="986" t="inlineStr">
         <is>
           <t>vs Miss Fortune (ours)</t>
         </is>
       </c>
-      <c r="B11" s="915" t="inlineStr">
+      <c r="B11" s="988" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
       </c>
-      <c r="C11" s="915" t="inlineStr">
+      <c r="C11" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D11" s="916" t="inlineStr"/>
-      <c r="E11" s="916" t="inlineStr"/>
-      <c r="F11" s="916" t="inlineStr"/>
-      <c r="G11" s="916" t="inlineStr"/>
+      <c r="D11" s="987" t="inlineStr"/>
+      <c r="E11" s="987" t="inlineStr"/>
+      <c r="F11" s="987" t="inlineStr"/>
+      <c r="G11" s="987" t="inlineStr"/>
       <c r="H11" s="217" t="inlineStr">
         <is>
           <t>Trinity Force passive scoring competes with your win condition. Mobile units hit both fields. Whoever scores faster wins. Always close.</t>
@@ -24772,14 +25151,14 @@
       </c>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="951" t="inlineStr"/>
-      <c r="B13" s="951" t="inlineStr"/>
-      <c r="C13" s="951" t="inlineStr"/>
-      <c r="D13" s="951" t="inlineStr"/>
-      <c r="E13" s="951" t="inlineStr"/>
-      <c r="F13" s="951" t="inlineStr"/>
-      <c r="G13" s="951" t="inlineStr"/>
-      <c r="H13" s="951" t="inlineStr"/>
+      <c r="A13" s="1017" t="inlineStr"/>
+      <c r="B13" s="1017" t="inlineStr"/>
+      <c r="C13" s="1017" t="inlineStr"/>
+      <c r="D13" s="1017" t="inlineStr"/>
+      <c r="E13" s="1017" t="inlineStr"/>
+      <c r="F13" s="1017" t="inlineStr"/>
+      <c r="G13" s="1017" t="inlineStr"/>
+      <c r="H13" s="1017" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="745" t="inlineStr">
@@ -24950,14 +25329,14 @@
       <c r="H21" s="957" t="inlineStr"/>
     </row>
     <row r="22" ht="4" customHeight="1">
-      <c r="A22" s="951" t="inlineStr"/>
-      <c r="B22" s="951" t="inlineStr"/>
-      <c r="C22" s="951" t="inlineStr"/>
-      <c r="D22" s="951" t="inlineStr"/>
-      <c r="E22" s="951" t="inlineStr"/>
-      <c r="F22" s="951" t="inlineStr"/>
-      <c r="G22" s="951" t="inlineStr"/>
-      <c r="H22" s="951" t="inlineStr"/>
+      <c r="A22" s="1017" t="inlineStr"/>
+      <c r="B22" s="1017" t="inlineStr"/>
+      <c r="C22" s="1017" t="inlineStr"/>
+      <c r="D22" s="1017" t="inlineStr"/>
+      <c r="E22" s="1017" t="inlineStr"/>
+      <c r="F22" s="1017" t="inlineStr"/>
+      <c r="G22" s="1017" t="inlineStr"/>
+      <c r="H22" s="1017" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="745" t="inlineStr">
@@ -25100,14 +25479,14 @@
       </c>
     </row>
     <row r="27" ht="4" customHeight="1">
-      <c r="A27" s="951" t="inlineStr"/>
-      <c r="B27" s="951" t="inlineStr"/>
-      <c r="C27" s="951" t="inlineStr"/>
-      <c r="D27" s="951" t="inlineStr"/>
-      <c r="E27" s="951" t="inlineStr"/>
-      <c r="F27" s="951" t="inlineStr"/>
-      <c r="G27" s="951" t="inlineStr"/>
-      <c r="H27" s="951" t="inlineStr"/>
+      <c r="A27" s="1017" t="inlineStr"/>
+      <c r="B27" s="1017" t="inlineStr"/>
+      <c r="C27" s="1017" t="inlineStr"/>
+      <c r="D27" s="1017" t="inlineStr"/>
+      <c r="E27" s="1017" t="inlineStr"/>
+      <c r="F27" s="1017" t="inlineStr"/>
+      <c r="G27" s="1017" t="inlineStr"/>
+      <c r="H27" s="1017" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="745" t="inlineStr">
@@ -25854,14 +26233,14 @@
       <c r="H47" s="743" t="inlineStr"/>
     </row>
     <row r="48" ht="4" customHeight="1">
-      <c r="A48" s="951" t="inlineStr"/>
-      <c r="B48" s="951" t="inlineStr"/>
-      <c r="C48" s="951" t="inlineStr"/>
-      <c r="D48" s="951" t="inlineStr"/>
-      <c r="E48" s="951" t="inlineStr"/>
-      <c r="F48" s="951" t="inlineStr"/>
-      <c r="G48" s="951" t="inlineStr"/>
-      <c r="H48" s="951" t="inlineStr"/>
+      <c r="A48" s="1017" t="inlineStr"/>
+      <c r="B48" s="1017" t="inlineStr"/>
+      <c r="C48" s="1017" t="inlineStr"/>
+      <c r="D48" s="1017" t="inlineStr"/>
+      <c r="E48" s="1017" t="inlineStr"/>
+      <c r="F48" s="1017" t="inlineStr"/>
+      <c r="G48" s="1017" t="inlineStr"/>
+      <c r="H48" s="1017" t="inlineStr"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="883" t="inlineStr">
@@ -25882,14 +26261,14 @@
       <c r="H49" s="884" t="inlineStr"/>
     </row>
     <row r="50" ht="4" customHeight="1">
-      <c r="A50" s="951" t="inlineStr"/>
-      <c r="B50" s="951" t="inlineStr"/>
-      <c r="C50" s="951" t="inlineStr"/>
-      <c r="D50" s="951" t="inlineStr"/>
-      <c r="E50" s="951" t="inlineStr"/>
-      <c r="F50" s="951" t="inlineStr"/>
-      <c r="G50" s="951" t="inlineStr"/>
-      <c r="H50" s="951" t="inlineStr"/>
+      <c r="A50" s="1017" t="inlineStr"/>
+      <c r="B50" s="1017" t="inlineStr"/>
+      <c r="C50" s="1017" t="inlineStr"/>
+      <c r="D50" s="1017" t="inlineStr"/>
+      <c r="E50" s="1017" t="inlineStr"/>
+      <c r="F50" s="1017" t="inlineStr"/>
+      <c r="G50" s="1017" t="inlineStr"/>
+      <c r="H50" s="1017" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="745" t="inlineStr">
@@ -26144,14 +26523,14 @@
       </c>
     </row>
     <row r="58" ht="4" customHeight="1">
-      <c r="A58" s="951" t="inlineStr"/>
-      <c r="B58" s="951" t="inlineStr"/>
-      <c r="C58" s="951" t="inlineStr"/>
-      <c r="D58" s="951" t="inlineStr"/>
-      <c r="E58" s="951" t="inlineStr"/>
-      <c r="F58" s="951" t="inlineStr"/>
-      <c r="G58" s="951" t="inlineStr"/>
-      <c r="H58" s="951" t="inlineStr"/>
+      <c r="A58" s="1017" t="inlineStr"/>
+      <c r="B58" s="1017" t="inlineStr"/>
+      <c r="C58" s="1017" t="inlineStr"/>
+      <c r="D58" s="1017" t="inlineStr"/>
+      <c r="E58" s="1017" t="inlineStr"/>
+      <c r="F58" s="1017" t="inlineStr"/>
+      <c r="G58" s="1017" t="inlineStr"/>
+      <c r="H58" s="1017" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="745" t="inlineStr">
@@ -26168,7 +26547,7 @@
       <c r="H59" s="743" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="980" t="inlineStr">
+      <c r="A60" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -26178,12 +26557,12 @@
           <t>Chemtech Enforcer turn 2 every game. Attacks as 4M. Discards Flame Chompers = pay 1 Fury = Chompers plays free. Two bodies for 2+1 runes.</t>
         </is>
       </c>
-      <c r="C60" s="981" t="inlineStr"/>
-      <c r="D60" s="981" t="inlineStr"/>
-      <c r="E60" s="981" t="inlineStr"/>
-      <c r="F60" s="981" t="inlineStr"/>
-      <c r="G60" s="981" t="inlineStr"/>
-      <c r="H60" s="981" t="inlineStr"/>
+      <c r="C60" s="1010" t="inlineStr"/>
+      <c r="D60" s="1010" t="inlineStr"/>
+      <c r="E60" s="1010" t="inlineStr"/>
+      <c r="F60" s="1010" t="inlineStr"/>
+      <c r="G60" s="1010" t="inlineStr"/>
+      <c r="H60" s="1010" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="982" t="inlineStr">
@@ -26204,7 +26583,7 @@
       <c r="H61" s="983" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="980" t="inlineStr">
+      <c r="A62" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -26214,12 +26593,12 @@
           <t>Raging Soul only activates if discarded THIS turn. Chemtech discards it. NEVER play Raging Soul from hand — let Chemtech do it for free.</t>
         </is>
       </c>
-      <c r="C62" s="981" t="inlineStr"/>
-      <c r="D62" s="981" t="inlineStr"/>
-      <c r="E62" s="981" t="inlineStr"/>
-      <c r="F62" s="981" t="inlineStr"/>
-      <c r="G62" s="981" t="inlineStr"/>
-      <c r="H62" s="981" t="inlineStr"/>
+      <c r="C62" s="1010" t="inlineStr"/>
+      <c r="D62" s="1010" t="inlineStr"/>
+      <c r="E62" s="1010" t="inlineStr"/>
+      <c r="F62" s="1010" t="inlineStr"/>
+      <c r="G62" s="1010" t="inlineStr"/>
+      <c r="H62" s="1010" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="982" t="inlineStr">
@@ -26240,7 +26619,7 @@
       <c r="H63" s="983" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="980" t="inlineStr">
+      <c r="A64" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -26250,12 +26629,12 @@
           <t>Minotaur Reckoner: once on field, no unit can retreat to base. Play Reckoner then attack. Opponent's unit must fight. Your ASSAULT wins. They can never escape.</t>
         </is>
       </c>
-      <c r="C64" s="981" t="inlineStr"/>
-      <c r="D64" s="981" t="inlineStr"/>
-      <c r="E64" s="981" t="inlineStr"/>
-      <c r="F64" s="981" t="inlineStr"/>
-      <c r="G64" s="981" t="inlineStr"/>
-      <c r="H64" s="981" t="inlineStr"/>
+      <c r="C64" s="1010" t="inlineStr"/>
+      <c r="D64" s="1010" t="inlineStr"/>
+      <c r="E64" s="1010" t="inlineStr"/>
+      <c r="F64" s="1010" t="inlineStr"/>
+      <c r="G64" s="1010" t="inlineStr"/>
+      <c r="H64" s="1010" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="982" t="inlineStr">
@@ -26276,7 +26655,7 @@
       <c r="H65" s="983" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="980" t="inlineStr">
+      <c r="A66" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -26286,12 +26665,12 @@
           <t>G2 vs Volibear: Sky Splitter costs 2 when Armed Assailant (6M) is on field. Deals 5 to the 9M dragon. Dragon dies. OR play Fading Memories. Dragon dies next turn without combat.</t>
         </is>
       </c>
-      <c r="C66" s="981" t="inlineStr"/>
-      <c r="D66" s="981" t="inlineStr"/>
-      <c r="E66" s="981" t="inlineStr"/>
-      <c r="F66" s="981" t="inlineStr"/>
-      <c r="G66" s="981" t="inlineStr"/>
-      <c r="H66" s="981" t="inlineStr"/>
+      <c r="C66" s="1010" t="inlineStr"/>
+      <c r="D66" s="1010" t="inlineStr"/>
+      <c r="E66" s="1010" t="inlineStr"/>
+      <c r="F66" s="1010" t="inlineStr"/>
+      <c r="G66" s="1010" t="inlineStr"/>
+      <c r="H66" s="1010" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="982" t="inlineStr">
@@ -26310,6 +26689,140 @@
       <c r="F67" s="983" t="inlineStr"/>
       <c r="G67" s="983" t="inlineStr"/>
       <c r="H67" s="983" t="inlineStr"/>
+    </row>
+    <row r="68" ht="4" customHeight="1">
+      <c r="A68" s="1017" t="inlineStr"/>
+      <c r="B68" s="1017" t="inlineStr"/>
+      <c r="C68" s="1017" t="inlineStr"/>
+      <c r="D68" s="1017" t="inlineStr"/>
+      <c r="E68" s="1017" t="inlineStr"/>
+      <c r="F68" s="1017" t="inlineStr"/>
+      <c r="G68" s="1017" t="inlineStr"/>
+      <c r="H68" s="1017" t="inlineStr"/>
+      <c r="I68" s="1017" t="inlineStr"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="1011" t="inlineStr">
+        <is>
+          <t>BATTLEFIELDS — Choose 2 of These 3 Each Game</t>
+        </is>
+      </c>
+      <c r="B69" s="1012" t="inlineStr"/>
+      <c r="C69" s="1012" t="inlineStr"/>
+      <c r="D69" s="1012" t="inlineStr"/>
+      <c r="E69" s="1012" t="inlineStr"/>
+      <c r="F69" s="1012" t="inlineStr"/>
+      <c r="G69" s="1012" t="inlineStr"/>
+      <c r="H69" s="1012" t="inlineStr"/>
+      <c r="I69" s="1012" t="inlineStr"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="1013" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B70" s="1013" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C70" s="1013" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D70" s="1013" t="inlineStr"/>
+      <c r="E70" s="1013" t="inlineStr"/>
+      <c r="F70" s="1013" t="inlineStr"/>
+      <c r="G70" s="1013" t="inlineStr"/>
+      <c r="H70" s="1013" t="inlineStr"/>
+      <c r="I70" s="1013" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-295</t>
+        </is>
+      </c>
+      <c r="B71" s="1008" t="inlineStr">
+        <is>
+          <t>Vilemaw's Lair</t>
+        </is>
+      </c>
+      <c r="C71" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D71" s="1010" t="inlineStr"/>
+      <c r="E71" s="1010" t="inlineStr"/>
+      <c r="F71" s="1010" t="inlineStr"/>
+      <c r="G71" s="1010" t="inlineStr"/>
+      <c r="H71" s="1010" t="inlineStr"/>
+      <c r="I71" s="97" t="inlineStr">
+        <is>
+          <t>Units can't move from here to base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-298</t>
+        </is>
+      </c>
+      <c r="B72" s="1008" t="inlineStr">
+        <is>
+          <t>Zaun Warrens</t>
+        </is>
+      </c>
+      <c r="C72" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D72" s="1010" t="inlineStr"/>
+      <c r="E72" s="1010" t="inlineStr"/>
+      <c r="F72" s="1010" t="inlineStr"/>
+      <c r="G72" s="1010" t="inlineStr"/>
+      <c r="H72" s="1010" t="inlineStr"/>
+      <c r="I72" s="97" t="inlineStr">
+        <is>
+          <t>When you conquer here, discard 1, then draw 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="1007" t="inlineStr">
+        <is>
+          <t>SFD-211</t>
+        </is>
+      </c>
+      <c r="B73" s="1008" t="inlineStr">
+        <is>
+          <t>Marai Spire</t>
+        </is>
+      </c>
+      <c r="C73" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D73" s="1010" t="inlineStr"/>
+      <c r="E73" s="1010" t="inlineStr"/>
+      <c r="F73" s="1010" t="inlineStr"/>
+      <c r="G73" s="1010" t="inlineStr"/>
+      <c r="H73" s="1010" t="inlineStr"/>
+      <c r="I73" s="97" t="inlineStr">
+        <is>
+          <t>While you control this battlefield, friendly [REPEAT] costs cost 1 less.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26322,7 +26835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26364,14 +26877,14 @@
       <c r="H2" s="855" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="857" t="inlineStr">
@@ -26542,14 +27055,14 @@
       <c r="H11" s="957" t="inlineStr"/>
     </row>
     <row r="12" ht="4" customHeight="1">
-      <c r="A12" s="951" t="inlineStr"/>
-      <c r="B12" s="951" t="inlineStr"/>
-      <c r="C12" s="951" t="inlineStr"/>
-      <c r="D12" s="951" t="inlineStr"/>
-      <c r="E12" s="951" t="inlineStr"/>
-      <c r="F12" s="951" t="inlineStr"/>
-      <c r="G12" s="951" t="inlineStr"/>
-      <c r="H12" s="951" t="inlineStr"/>
+      <c r="A12" s="1017" t="inlineStr"/>
+      <c r="B12" s="1017" t="inlineStr"/>
+      <c r="C12" s="1017" t="inlineStr"/>
+      <c r="D12" s="1017" t="inlineStr"/>
+      <c r="E12" s="1017" t="inlineStr"/>
+      <c r="F12" s="1017" t="inlineStr"/>
+      <c r="G12" s="1017" t="inlineStr"/>
+      <c r="H12" s="1017" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="857" t="inlineStr">
@@ -26692,24 +27205,52 @@
       </c>
     </row>
     <row r="17" ht="4" customHeight="1">
-      <c r="A17" s="951" t="inlineStr"/>
-      <c r="B17" s="951" t="inlineStr"/>
-      <c r="C17" s="951" t="inlineStr"/>
-      <c r="D17" s="951" t="inlineStr"/>
-      <c r="E17" s="951" t="inlineStr"/>
-      <c r="F17" s="951" t="inlineStr"/>
-      <c r="G17" s="951" t="inlineStr"/>
-      <c r="H17" s="951" t="inlineStr"/>
+      <c r="A17" s="1017" t="inlineStr">
+        <is>
+          <t>SFD-208</t>
+        </is>
+      </c>
+      <c r="B17" s="1017" t="inlineStr">
+        <is>
+          <t>Forge of the Fluft</t>
+        </is>
+      </c>
+      <c r="C17" s="1017" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D17" s="1017" t="inlineStr">
+        <is>
+          <t>While you control this battlefield, friendly legends have "Exhaust: Attach an Equipment you control to a unit you control."</t>
+        </is>
+      </c>
+      <c r="E17" s="1017" t="inlineStr"/>
+      <c r="F17" s="1017" t="inlineStr"/>
+      <c r="G17" s="1017" t="inlineStr"/>
+      <c r="H17" s="1017" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="857" t="inlineStr">
         <is>
-          <t>MAIN DECK — 40 Cards</t>
-        </is>
-      </c>
-      <c r="B18" s="853" t="inlineStr"/>
-      <c r="C18" s="853" t="inlineStr"/>
-      <c r="D18" s="853" t="inlineStr"/>
+          <t>SFD-213</t>
+        </is>
+      </c>
+      <c r="B18" s="853" t="inlineStr">
+        <is>
+          <t>Ornn's Forge</t>
+        </is>
+      </c>
+      <c r="C18" s="853" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D18" s="853" t="inlineStr">
+        <is>
+          <t>While you control this battlefield, the first friendly non-token gear played each turn costs 1 less.</t>
+        </is>
+      </c>
       <c r="E18" s="853" t="inlineStr"/>
       <c r="F18" s="853" t="inlineStr"/>
       <c r="G18" s="853" t="inlineStr"/>
@@ -26718,22 +27259,22 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="970" t="inlineStr">
         <is>
-          <t>Card ID</t>
+          <t>SFD-221</t>
         </is>
       </c>
       <c r="B19" s="970" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>Veiled Temple</t>
         </is>
       </c>
       <c r="C19" s="970" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Battlefield</t>
         </is>
       </c>
       <c r="D19" s="970" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>When you conquer here, you may ready a friendly gear. If it's an Equipment, you may detach it.</t>
         </is>
       </c>
       <c r="E19" s="970" t="inlineStr">
@@ -27398,14 +27939,14 @@
       <c r="H36" s="853" t="inlineStr"/>
     </row>
     <row r="37" ht="4" customHeight="1">
-      <c r="A37" s="951" t="inlineStr"/>
-      <c r="B37" s="951" t="inlineStr"/>
-      <c r="C37" s="951" t="inlineStr"/>
-      <c r="D37" s="951" t="inlineStr"/>
-      <c r="E37" s="951" t="inlineStr"/>
-      <c r="F37" s="951" t="inlineStr"/>
-      <c r="G37" s="951" t="inlineStr"/>
-      <c r="H37" s="951" t="inlineStr"/>
+      <c r="A37" s="1017" t="inlineStr"/>
+      <c r="B37" s="1017" t="inlineStr"/>
+      <c r="C37" s="1017" t="inlineStr"/>
+      <c r="D37" s="1017" t="inlineStr"/>
+      <c r="E37" s="1017" t="inlineStr"/>
+      <c r="F37" s="1017" t="inlineStr"/>
+      <c r="G37" s="1017" t="inlineStr"/>
+      <c r="H37" s="1017" t="inlineStr"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="883" t="inlineStr">
@@ -27426,14 +27967,14 @@
       <c r="H38" s="884" t="inlineStr"/>
     </row>
     <row r="39" ht="4" customHeight="1">
-      <c r="A39" s="951" t="inlineStr"/>
-      <c r="B39" s="951" t="inlineStr"/>
-      <c r="C39" s="951" t="inlineStr"/>
-      <c r="D39" s="951" t="inlineStr"/>
-      <c r="E39" s="951" t="inlineStr"/>
-      <c r="F39" s="951" t="inlineStr"/>
-      <c r="G39" s="951" t="inlineStr"/>
-      <c r="H39" s="951" t="inlineStr"/>
+      <c r="A39" s="1017" t="inlineStr"/>
+      <c r="B39" s="1017" t="inlineStr"/>
+      <c r="C39" s="1017" t="inlineStr"/>
+      <c r="D39" s="1017" t="inlineStr"/>
+      <c r="E39" s="1017" t="inlineStr"/>
+      <c r="F39" s="1017" t="inlineStr"/>
+      <c r="G39" s="1017" t="inlineStr"/>
+      <c r="H39" s="1017" t="inlineStr"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="857" t="inlineStr">
@@ -27640,14 +28181,14 @@
       </c>
     </row>
     <row r="46" ht="4" customHeight="1">
-      <c r="A46" s="951" t="inlineStr"/>
-      <c r="B46" s="951" t="inlineStr"/>
-      <c r="C46" s="951" t="inlineStr"/>
-      <c r="D46" s="951" t="inlineStr"/>
-      <c r="E46" s="951" t="inlineStr"/>
-      <c r="F46" s="951" t="inlineStr"/>
-      <c r="G46" s="951" t="inlineStr"/>
-      <c r="H46" s="951" t="inlineStr"/>
+      <c r="A46" s="1017" t="inlineStr"/>
+      <c r="B46" s="1017" t="inlineStr"/>
+      <c r="C46" s="1017" t="inlineStr"/>
+      <c r="D46" s="1017" t="inlineStr"/>
+      <c r="E46" s="1017" t="inlineStr"/>
+      <c r="F46" s="1017" t="inlineStr"/>
+      <c r="G46" s="1017" t="inlineStr"/>
+      <c r="H46" s="1017" t="inlineStr"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="857" t="inlineStr">
@@ -27664,7 +28205,7 @@
       <c r="H47" s="853" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="980" t="inlineStr">
+      <c r="A48" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -27674,12 +28215,12 @@
           <t>WEAPONMASTER on arrival: when you play Yone/Lucian/Akshan/Sentinel/Poro, equip one gear at 1 rune less immediately. Play Veteran Poro turn 2, equip Hexdrinker for 1 rune. Turn 2 you have a 3M DEFLECT ASSAULT unit.</t>
         </is>
       </c>
-      <c r="C48" s="981" t="inlineStr"/>
-      <c r="D48" s="981" t="inlineStr"/>
-      <c r="E48" s="981" t="inlineStr"/>
-      <c r="F48" s="981" t="inlineStr"/>
-      <c r="G48" s="981" t="inlineStr"/>
-      <c r="H48" s="981" t="inlineStr"/>
+      <c r="C48" s="1010" t="inlineStr"/>
+      <c r="D48" s="1010" t="inlineStr"/>
+      <c r="E48" s="1010" t="inlineStr"/>
+      <c r="F48" s="1010" t="inlineStr"/>
+      <c r="G48" s="1010" t="inlineStr"/>
+      <c r="H48" s="1010" t="inlineStr"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="982" t="inlineStr">
@@ -27700,7 +28241,7 @@
       <c r="H49" s="983" t="inlineStr"/>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="980" t="inlineStr">
+      <c r="A50" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -27710,12 +28251,12 @@
           <t>Strike Down before attacking. Play it, your equipped unit deals its Might as damage to the strongest enemy. Kill their 9M dragon without combat. Then attack the open field.</t>
         </is>
       </c>
-      <c r="C50" s="981" t="inlineStr"/>
-      <c r="D50" s="981" t="inlineStr"/>
-      <c r="E50" s="981" t="inlineStr"/>
-      <c r="F50" s="981" t="inlineStr"/>
-      <c r="G50" s="981" t="inlineStr"/>
-      <c r="H50" s="981" t="inlineStr"/>
+      <c r="C50" s="1010" t="inlineStr"/>
+      <c r="D50" s="1010" t="inlineStr"/>
+      <c r="E50" s="1010" t="inlineStr"/>
+      <c r="F50" s="1010" t="inlineStr"/>
+      <c r="G50" s="1010" t="inlineStr"/>
+      <c r="H50" s="1010" t="inlineStr"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="982" t="inlineStr">
@@ -27736,7 +28277,7 @@
       <c r="H51" s="983" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="980" t="inlineStr">
+      <c r="A52" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -27746,12 +28287,12 @@
           <t>Yone conquers an open field then deals damage to an enemy unit hiding in their base. Stack gear on Yone: his Might damage hits their best unit before it even attacks.</t>
         </is>
       </c>
-      <c r="C52" s="981" t="inlineStr"/>
-      <c r="D52" s="981" t="inlineStr"/>
-      <c r="E52" s="981" t="inlineStr"/>
-      <c r="F52" s="981" t="inlineStr"/>
-      <c r="G52" s="981" t="inlineStr"/>
-      <c r="H52" s="981" t="inlineStr"/>
+      <c r="C52" s="1010" t="inlineStr"/>
+      <c r="D52" s="1010" t="inlineStr"/>
+      <c r="E52" s="1010" t="inlineStr"/>
+      <c r="F52" s="1010" t="inlineStr"/>
+      <c r="G52" s="1010" t="inlineStr"/>
+      <c r="H52" s="1010" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="982" t="inlineStr">
@@ -27772,7 +28313,7 @@
       <c r="H53" s="983" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="980" t="inlineStr">
+      <c r="A54" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -27782,12 +28323,12 @@
           <t>Akshan steals enemy gear. Pay Body+Body extra when playing Akshan, take an attached equipment from their unit and attach it to Akshan. Their unit shrinks. Akshan grows.</t>
         </is>
       </c>
-      <c r="C54" s="981" t="inlineStr"/>
-      <c r="D54" s="981" t="inlineStr"/>
-      <c r="E54" s="981" t="inlineStr"/>
-      <c r="F54" s="981" t="inlineStr"/>
-      <c r="G54" s="981" t="inlineStr"/>
-      <c r="H54" s="981" t="inlineStr"/>
+      <c r="C54" s="1010" t="inlineStr"/>
+      <c r="D54" s="1010" t="inlineStr"/>
+      <c r="E54" s="1010" t="inlineStr"/>
+      <c r="F54" s="1010" t="inlineStr"/>
+      <c r="G54" s="1010" t="inlineStr"/>
+      <c r="H54" s="1010" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="982" t="inlineStr">
@@ -27807,6 +28348,22 @@
       <c r="G55" s="983" t="inlineStr"/>
       <c r="H55" s="983" t="inlineStr"/>
     </row>
+    <row r="56" ht="4" customHeight="1">
+      <c r="A56" s="1017" t="inlineStr"/>
+      <c r="B56" s="1017" t="inlineStr"/>
+      <c r="C56" s="1017" t="inlineStr"/>
+      <c r="D56" s="1017" t="inlineStr"/>
+      <c r="E56" s="1017" t="inlineStr"/>
+      <c r="F56" s="1017" t="inlineStr"/>
+      <c r="G56" s="1017" t="inlineStr"/>
+      <c r="H56" s="1017" t="inlineStr"/>
+      <c r="I56" s="1017" t="inlineStr"/>
+    </row>
+    <row r="57" ht="15" customHeight="1"/>
+    <row r="58" ht="18" customHeight="1"/>
+    <row r="59" ht="32" customHeight="1"/>
+    <row r="60" ht="32" customHeight="1"/>
+    <row r="61" ht="32" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27818,7 +28375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27837,13 +28394,13 @@
           <t>SETT — THE BOSS | Body+Order | The Undying | 40 Cards</t>
         </is>
       </c>
-      <c r="B1" s="890" t="inlineStr"/>
-      <c r="C1" s="890" t="inlineStr"/>
-      <c r="D1" s="890" t="inlineStr"/>
-      <c r="E1" s="890" t="inlineStr"/>
-      <c r="F1" s="890" t="inlineStr"/>
-      <c r="G1" s="890" t="inlineStr"/>
-      <c r="H1" s="890" t="inlineStr"/>
+      <c r="B1" s="1015" t="inlineStr"/>
+      <c r="C1" s="1015" t="inlineStr"/>
+      <c r="D1" s="1015" t="inlineStr"/>
+      <c r="E1" s="1015" t="inlineStr"/>
+      <c r="F1" s="1015" t="inlineStr"/>
+      <c r="G1" s="1015" t="inlineStr"/>
+      <c r="H1" s="1015" t="inlineStr"/>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="891" t="inlineStr">
@@ -27860,28 +28417,28 @@
       <c r="H2" s="892" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="893" t="inlineStr">
+      <c r="A4" s="1014" t="inlineStr">
         <is>
           <t>HOW TO PLAY — A B C D E F G</t>
         </is>
       </c>
-      <c r="B4" s="890" t="inlineStr"/>
-      <c r="C4" s="890" t="inlineStr"/>
-      <c r="D4" s="890" t="inlineStr"/>
-      <c r="E4" s="890" t="inlineStr"/>
-      <c r="F4" s="890" t="inlineStr"/>
-      <c r="G4" s="890" t="inlineStr"/>
-      <c r="H4" s="890" t="inlineStr"/>
+      <c r="B4" s="1015" t="inlineStr"/>
+      <c r="C4" s="1015" t="inlineStr"/>
+      <c r="D4" s="1015" t="inlineStr"/>
+      <c r="E4" s="1015" t="inlineStr"/>
+      <c r="F4" s="1015" t="inlineStr"/>
+      <c r="G4" s="1015" t="inlineStr"/>
+      <c r="H4" s="1015" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="955" t="inlineStr">
@@ -28038,28 +28595,28 @@
       <c r="H11" s="957" t="inlineStr"/>
     </row>
     <row r="12" ht="4" customHeight="1">
-      <c r="A12" s="951" t="inlineStr"/>
-      <c r="B12" s="951" t="inlineStr"/>
-      <c r="C12" s="951" t="inlineStr"/>
-      <c r="D12" s="951" t="inlineStr"/>
-      <c r="E12" s="951" t="inlineStr"/>
-      <c r="F12" s="951" t="inlineStr"/>
-      <c r="G12" s="951" t="inlineStr"/>
-      <c r="H12" s="951" t="inlineStr"/>
+      <c r="A12" s="1017" t="inlineStr"/>
+      <c r="B12" s="1017" t="inlineStr"/>
+      <c r="C12" s="1017" t="inlineStr"/>
+      <c r="D12" s="1017" t="inlineStr"/>
+      <c r="E12" s="1017" t="inlineStr"/>
+      <c r="F12" s="1017" t="inlineStr"/>
+      <c r="G12" s="1017" t="inlineStr"/>
+      <c r="H12" s="1017" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="893" t="inlineStr">
+      <c r="A13" s="1014" t="inlineStr">
         <is>
           <t>LEGEND + CHAMPION ZONE</t>
         </is>
       </c>
-      <c r="B13" s="890" t="inlineStr"/>
-      <c r="C13" s="890" t="inlineStr"/>
-      <c r="D13" s="890" t="inlineStr"/>
-      <c r="E13" s="890" t="inlineStr"/>
-      <c r="F13" s="890" t="inlineStr"/>
-      <c r="G13" s="890" t="inlineStr"/>
-      <c r="H13" s="890" t="inlineStr"/>
+      <c r="B13" s="1015" t="inlineStr"/>
+      <c r="C13" s="1015" t="inlineStr"/>
+      <c r="D13" s="1015" t="inlineStr"/>
+      <c r="E13" s="1015" t="inlineStr"/>
+      <c r="F13" s="1015" t="inlineStr"/>
+      <c r="G13" s="1015" t="inlineStr"/>
+      <c r="H13" s="1015" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="970" t="inlineStr">
@@ -28180,28 +28737,28 @@
       </c>
     </row>
     <row r="17" ht="4" customHeight="1">
-      <c r="A17" s="951" t="inlineStr"/>
-      <c r="B17" s="951" t="inlineStr"/>
-      <c r="C17" s="951" t="inlineStr"/>
-      <c r="D17" s="951" t="inlineStr"/>
-      <c r="E17" s="951" t="inlineStr"/>
-      <c r="F17" s="951" t="inlineStr"/>
-      <c r="G17" s="951" t="inlineStr"/>
-      <c r="H17" s="951" t="inlineStr"/>
+      <c r="A17" s="1017" t="inlineStr"/>
+      <c r="B17" s="1017" t="inlineStr"/>
+      <c r="C17" s="1017" t="inlineStr"/>
+      <c r="D17" s="1017" t="inlineStr"/>
+      <c r="E17" s="1017" t="inlineStr"/>
+      <c r="F17" s="1017" t="inlineStr"/>
+      <c r="G17" s="1017" t="inlineStr"/>
+      <c r="H17" s="1017" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="893" t="inlineStr">
+      <c r="A18" s="1014" t="inlineStr">
         <is>
           <t>MAIN DECK — 40 Cards</t>
         </is>
       </c>
-      <c r="B18" s="890" t="inlineStr"/>
-      <c r="C18" s="890" t="inlineStr"/>
-      <c r="D18" s="890" t="inlineStr"/>
-      <c r="E18" s="890" t="inlineStr"/>
-      <c r="F18" s="890" t="inlineStr"/>
-      <c r="G18" s="890" t="inlineStr"/>
-      <c r="H18" s="890" t="inlineStr"/>
+      <c r="B18" s="1015" t="inlineStr"/>
+      <c r="C18" s="1015" t="inlineStr"/>
+      <c r="D18" s="1015" t="inlineStr"/>
+      <c r="E18" s="1015" t="inlineStr"/>
+      <c r="F18" s="1015" t="inlineStr"/>
+      <c r="G18" s="1015" t="inlineStr"/>
+      <c r="H18" s="1015" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="970" t="inlineStr">
@@ -28526,35 +29083,35 @@
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="915" t="inlineStr">
+      <c r="A27" s="988" t="inlineStr">
         <is>
           <t>OGN-216</t>
         </is>
       </c>
-      <c r="B27" s="915" t="n">
+      <c r="B27" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="916" t="inlineStr">
+      <c r="C27" s="987" t="inlineStr">
         <is>
           <t>SAVE</t>
         </is>
       </c>
-      <c r="D27" s="914" t="inlineStr">
+      <c r="D27" s="986" t="inlineStr">
         <is>
           <t>Soaring Scout</t>
         </is>
       </c>
-      <c r="E27" s="897" t="inlineStr">
+      <c r="E27" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F27" s="897" t="inlineStr">
+      <c r="F27" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G27" s="897" t="inlineStr">
+      <c r="G27" s="989" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -28566,35 +29123,35 @@
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="915" t="inlineStr">
+      <c r="A28" s="988" t="inlineStr">
         <is>
           <t>OGN-228</t>
         </is>
       </c>
-      <c r="B28" s="915" t="n">
+      <c r="B28" s="988" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="916" t="inlineStr">
+      <c r="C28" s="987" t="inlineStr">
         <is>
           <t>BACKUP</t>
         </is>
       </c>
-      <c r="D28" s="914" t="inlineStr">
+      <c r="D28" s="986" t="inlineStr">
         <is>
           <t>Vanguard Helm</t>
         </is>
       </c>
-      <c r="E28" s="897" t="inlineStr">
+      <c r="E28" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F28" s="897" t="inlineStr">
+      <c r="F28" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G28" s="897" t="inlineStr">
+      <c r="G28" s="989" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -28886,35 +29443,35 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="915" t="inlineStr">
+      <c r="A36" s="988" t="inlineStr">
         <is>
           <t>SFD-167</t>
         </is>
       </c>
-      <c r="B36" s="915" t="n">
+      <c r="B36" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="916" t="inlineStr">
+      <c r="C36" s="987" t="inlineStr">
         <is>
           <t>SAVE</t>
         </is>
       </c>
-      <c r="D36" s="914" t="inlineStr">
+      <c r="D36" s="986" t="inlineStr">
         <is>
           <t>Unsung Hero</t>
         </is>
       </c>
-      <c r="E36" s="897" t="inlineStr">
+      <c r="E36" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F36" s="897" t="inlineStr">
+      <c r="F36" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G36" s="897" t="inlineStr">
+      <c r="G36" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -28926,30 +29483,30 @@
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="898" t="inlineStr">
+      <c r="A37" s="1016" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="898" t="n">
+      <c r="B37" s="1016" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="890" t="inlineStr"/>
-      <c r="D37" s="890" t="inlineStr"/>
-      <c r="E37" s="890" t="inlineStr"/>
-      <c r="F37" s="890" t="inlineStr"/>
-      <c r="G37" s="890" t="inlineStr"/>
-      <c r="H37" s="890" t="inlineStr"/>
+      <c r="C37" s="1015" t="inlineStr"/>
+      <c r="D37" s="1015" t="inlineStr"/>
+      <c r="E37" s="1015" t="inlineStr"/>
+      <c r="F37" s="1015" t="inlineStr"/>
+      <c r="G37" s="1015" t="inlineStr"/>
+      <c r="H37" s="1015" t="inlineStr"/>
     </row>
     <row r="38" ht="4" customHeight="1">
-      <c r="A38" s="951" t="inlineStr"/>
-      <c r="B38" s="951" t="inlineStr"/>
-      <c r="C38" s="951" t="inlineStr"/>
-      <c r="D38" s="951" t="inlineStr"/>
-      <c r="E38" s="951" t="inlineStr"/>
-      <c r="F38" s="951" t="inlineStr"/>
-      <c r="G38" s="951" t="inlineStr"/>
-      <c r="H38" s="951" t="inlineStr"/>
+      <c r="A38" s="1017" t="inlineStr"/>
+      <c r="B38" s="1017" t="inlineStr"/>
+      <c r="C38" s="1017" t="inlineStr"/>
+      <c r="D38" s="1017" t="inlineStr"/>
+      <c r="E38" s="1017" t="inlineStr"/>
+      <c r="F38" s="1017" t="inlineStr"/>
+      <c r="G38" s="1017" t="inlineStr"/>
+      <c r="H38" s="1017" t="inlineStr"/>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="899" t="inlineStr">
@@ -28970,28 +29527,28 @@
       <c r="H39" s="900" t="inlineStr"/>
     </row>
     <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="951" t="inlineStr"/>
-      <c r="B40" s="951" t="inlineStr"/>
-      <c r="C40" s="951" t="inlineStr"/>
-      <c r="D40" s="951" t="inlineStr"/>
-      <c r="E40" s="951" t="inlineStr"/>
-      <c r="F40" s="951" t="inlineStr"/>
-      <c r="G40" s="951" t="inlineStr"/>
-      <c r="H40" s="951" t="inlineStr"/>
+      <c r="A40" s="1017" t="inlineStr"/>
+      <c r="B40" s="1017" t="inlineStr"/>
+      <c r="C40" s="1017" t="inlineStr"/>
+      <c r="D40" s="1017" t="inlineStr"/>
+      <c r="E40" s="1017" t="inlineStr"/>
+      <c r="F40" s="1017" t="inlineStr"/>
+      <c r="G40" s="1017" t="inlineStr"/>
+      <c r="H40" s="1017" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="893" t="inlineStr">
+      <c r="A41" s="1014" t="inlineStr">
         <is>
           <t>SIDEBOARD — 8 Cards</t>
         </is>
       </c>
-      <c r="B41" s="890" t="inlineStr"/>
-      <c r="C41" s="890" t="inlineStr"/>
-      <c r="D41" s="890" t="inlineStr"/>
-      <c r="E41" s="890" t="inlineStr"/>
-      <c r="F41" s="890" t="inlineStr"/>
-      <c r="G41" s="890" t="inlineStr"/>
-      <c r="H41" s="890" t="inlineStr"/>
+      <c r="B41" s="1015" t="inlineStr"/>
+      <c r="C41" s="1015" t="inlineStr"/>
+      <c r="D41" s="1015" t="inlineStr"/>
+      <c r="E41" s="1015" t="inlineStr"/>
+      <c r="F41" s="1015" t="inlineStr"/>
+      <c r="G41" s="1015" t="inlineStr"/>
+      <c r="H41" s="1015" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="970" t="inlineStr">
@@ -29356,31 +29913,31 @@
       </c>
     </row>
     <row r="51" ht="4" customHeight="1">
-      <c r="A51" s="951" t="inlineStr"/>
-      <c r="B51" s="951" t="inlineStr"/>
-      <c r="C51" s="951" t="inlineStr"/>
-      <c r="D51" s="951" t="inlineStr"/>
-      <c r="E51" s="951" t="inlineStr"/>
-      <c r="F51" s="951" t="inlineStr"/>
-      <c r="G51" s="951" t="inlineStr"/>
-      <c r="H51" s="951" t="inlineStr"/>
+      <c r="A51" s="1017" t="inlineStr"/>
+      <c r="B51" s="1017" t="inlineStr"/>
+      <c r="C51" s="1017" t="inlineStr"/>
+      <c r="D51" s="1017" t="inlineStr"/>
+      <c r="E51" s="1017" t="inlineStr"/>
+      <c r="F51" s="1017" t="inlineStr"/>
+      <c r="G51" s="1017" t="inlineStr"/>
+      <c r="H51" s="1017" t="inlineStr"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="893" t="inlineStr">
+      <c r="A52" s="1014" t="inlineStr">
         <is>
           <t>GOLDEN RULES</t>
         </is>
       </c>
-      <c r="B52" s="890" t="inlineStr"/>
-      <c r="C52" s="890" t="inlineStr"/>
-      <c r="D52" s="890" t="inlineStr"/>
-      <c r="E52" s="890" t="inlineStr"/>
-      <c r="F52" s="890" t="inlineStr"/>
-      <c r="G52" s="890" t="inlineStr"/>
-      <c r="H52" s="890" t="inlineStr"/>
+      <c r="B52" s="1015" t="inlineStr"/>
+      <c r="C52" s="1015" t="inlineStr"/>
+      <c r="D52" s="1015" t="inlineStr"/>
+      <c r="E52" s="1015" t="inlineStr"/>
+      <c r="F52" s="1015" t="inlineStr"/>
+      <c r="G52" s="1015" t="inlineStr"/>
+      <c r="H52" s="1015" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="980" t="inlineStr">
+      <c r="A53" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -29390,12 +29947,12 @@
           <t>Buff first, THEN Sett saves. Sett can only recall a BUFFED unit. Keep at least one buff on your most important unit at all times. Sea Monkey, Buhru Captain, Pit Rookie — all give buffs on entry.</t>
         </is>
       </c>
-      <c r="C53" s="981" t="inlineStr"/>
-      <c r="D53" s="981" t="inlineStr"/>
-      <c r="E53" s="981" t="inlineStr"/>
-      <c r="F53" s="981" t="inlineStr"/>
-      <c r="G53" s="981" t="inlineStr"/>
-      <c r="H53" s="981" t="inlineStr"/>
+      <c r="C53" s="1010" t="inlineStr"/>
+      <c r="D53" s="1010" t="inlineStr"/>
+      <c r="E53" s="1010" t="inlineStr"/>
+      <c r="F53" s="1010" t="inlineStr"/>
+      <c r="G53" s="1010" t="inlineStr"/>
+      <c r="H53" s="1010" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="982" t="inlineStr">
@@ -29416,7 +29973,7 @@
       <c r="H54" s="983" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="980" t="inlineStr">
+      <c r="A55" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -29426,12 +29983,12 @@
           <t>Overt Operation timing: wait until 3+ units all have buffs. Spend all buffs = all ready. Attack with everything at once. Opponent can only block one field. You score the other. Guaranteed.</t>
         </is>
       </c>
-      <c r="C55" s="981" t="inlineStr"/>
-      <c r="D55" s="981" t="inlineStr"/>
-      <c r="E55" s="981" t="inlineStr"/>
-      <c r="F55" s="981" t="inlineStr"/>
-      <c r="G55" s="981" t="inlineStr"/>
-      <c r="H55" s="981" t="inlineStr"/>
+      <c r="C55" s="1010" t="inlineStr"/>
+      <c r="D55" s="1010" t="inlineStr"/>
+      <c r="E55" s="1010" t="inlineStr"/>
+      <c r="F55" s="1010" t="inlineStr"/>
+      <c r="G55" s="1010" t="inlineStr"/>
+      <c r="H55" s="1010" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="982" t="inlineStr">
@@ -29452,7 +30009,7 @@
       <c r="H56" s="983" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="980" t="inlineStr">
+      <c r="A57" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -29462,12 +30019,12 @@
           <t>Soaring Scouts are bait. Play Scout, put 1 buff on it. Opponent kills it. Sett saves it (goes to base). OR opponent ignores it. Either way: Scout DEATHKNELL channels a rune if it dies. Always win.</t>
         </is>
       </c>
-      <c r="C57" s="981" t="inlineStr"/>
-      <c r="D57" s="981" t="inlineStr"/>
-      <c r="E57" s="981" t="inlineStr"/>
-      <c r="F57" s="981" t="inlineStr"/>
-      <c r="G57" s="981" t="inlineStr"/>
-      <c r="H57" s="981" t="inlineStr"/>
+      <c r="C57" s="1010" t="inlineStr"/>
+      <c r="D57" s="1010" t="inlineStr"/>
+      <c r="E57" s="1010" t="inlineStr"/>
+      <c r="F57" s="1010" t="inlineStr"/>
+      <c r="G57" s="1010" t="inlineStr"/>
+      <c r="H57" s="1010" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="982" t="inlineStr">
@@ -29488,7 +30045,7 @@
       <c r="H58" s="983" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="980" t="inlineStr">
+      <c r="A59" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -29498,12 +30055,12 @@
           <t>Wildclaw Shaman: SPEND A BUFF to buff itself AND ready itself. Lee Sin buffs a unit on field. Play Shaman. Spend that buff. Shaman becomes 5M and attacks same turn. Two effects from one Lee Sin activation.</t>
         </is>
       </c>
-      <c r="C59" s="981" t="inlineStr"/>
-      <c r="D59" s="981" t="inlineStr"/>
-      <c r="E59" s="981" t="inlineStr"/>
-      <c r="F59" s="981" t="inlineStr"/>
-      <c r="G59" s="981" t="inlineStr"/>
-      <c r="H59" s="981" t="inlineStr"/>
+      <c r="C59" s="1010" t="inlineStr"/>
+      <c r="D59" s="1010" t="inlineStr"/>
+      <c r="E59" s="1010" t="inlineStr"/>
+      <c r="F59" s="1010" t="inlineStr"/>
+      <c r="G59" s="1010" t="inlineStr"/>
+      <c r="H59" s="1010" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="982" t="inlineStr">
@@ -29522,6 +30079,140 @@
       <c r="F60" s="983" t="inlineStr"/>
       <c r="G60" s="983" t="inlineStr"/>
       <c r="H60" s="983" t="inlineStr"/>
+    </row>
+    <row r="61" ht="4" customHeight="1">
+      <c r="A61" s="1017" t="inlineStr"/>
+      <c r="B61" s="1017" t="inlineStr"/>
+      <c r="C61" s="1017" t="inlineStr"/>
+      <c r="D61" s="1017" t="inlineStr"/>
+      <c r="E61" s="1017" t="inlineStr"/>
+      <c r="F61" s="1017" t="inlineStr"/>
+      <c r="G61" s="1017" t="inlineStr"/>
+      <c r="H61" s="1017" t="inlineStr"/>
+      <c r="I61" s="1017" t="inlineStr"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="1014" t="inlineStr">
+        <is>
+          <t>BATTLEFIELDS — Choose 2 of These 3 Each Game</t>
+        </is>
+      </c>
+      <c r="B62" s="1015" t="inlineStr"/>
+      <c r="C62" s="1015" t="inlineStr"/>
+      <c r="D62" s="1015" t="inlineStr"/>
+      <c r="E62" s="1015" t="inlineStr"/>
+      <c r="F62" s="1015" t="inlineStr"/>
+      <c r="G62" s="1015" t="inlineStr"/>
+      <c r="H62" s="1015" t="inlineStr"/>
+      <c r="I62" s="1015" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="1016" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B63" s="1016" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C63" s="1016" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D63" s="1016" t="inlineStr"/>
+      <c r="E63" s="1016" t="inlineStr"/>
+      <c r="F63" s="1016" t="inlineStr"/>
+      <c r="G63" s="1016" t="inlineStr"/>
+      <c r="H63" s="1016" t="inlineStr"/>
+      <c r="I63" s="1016" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-282</t>
+        </is>
+      </c>
+      <c r="B64" s="1008" t="inlineStr">
+        <is>
+          <t>Monastery of Hirana</t>
+        </is>
+      </c>
+      <c r="C64" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D64" s="1010" t="inlineStr"/>
+      <c r="E64" s="1010" t="inlineStr"/>
+      <c r="F64" s="1010" t="inlineStr"/>
+      <c r="G64" s="1010" t="inlineStr"/>
+      <c r="H64" s="1010" t="inlineStr"/>
+      <c r="I64" s="97" t="inlineStr">
+        <is>
+          <t>When you conquer here, you may spend a buff to draw 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-279</t>
+        </is>
+      </c>
+      <c r="B65" s="1008" t="inlineStr">
+        <is>
+          <t>Fortified Position</t>
+        </is>
+      </c>
+      <c r="C65" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D65" s="1010" t="inlineStr"/>
+      <c r="E65" s="1010" t="inlineStr"/>
+      <c r="F65" s="1010" t="inlineStr"/>
+      <c r="G65" s="1010" t="inlineStr"/>
+      <c r="H65" s="1010" t="inlineStr"/>
+      <c r="I65" s="97" t="inlineStr">
+        <is>
+          <t>When you defend here, choose a unit. It gains SHIELD 2 this combat. (+2 Might while It's a defender.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-276</t>
+        </is>
+      </c>
+      <c r="B66" s="1008" t="inlineStr">
+        <is>
+          <t>Aspirant's Climb</t>
+        </is>
+      </c>
+      <c r="C66" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D66" s="1010" t="inlineStr"/>
+      <c r="E66" s="1010" t="inlineStr"/>
+      <c r="F66" s="1010" t="inlineStr"/>
+      <c r="G66" s="1010" t="inlineStr"/>
+      <c r="H66" s="1010" t="inlineStr"/>
+      <c r="I66" s="97" t="inlineStr">
+        <is>
+          <t>Increase the points needed to win the game by 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29534,7 +30225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29579,15 +30270,15 @@
       <c r="I2" s="904" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
-      <c r="I3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
+      <c r="I3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="906" t="inlineStr">
@@ -29678,50 +30369,50 @@
       <c r="I7" s="910" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="911" t="inlineStr">
+      <c r="A8" s="995" t="inlineStr">
         <is>
           <t>vs Lucian</t>
         </is>
       </c>
-      <c r="B8" s="912" t="inlineStr">
+      <c r="B8" s="997" t="inlineStr">
         <is>
           <t>94.0%</t>
         </is>
       </c>
-      <c r="C8" s="912" t="inlineStr">
+      <c r="C8" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D8" s="913" t="inlineStr"/>
-      <c r="E8" s="913" t="inlineStr"/>
-      <c r="F8" s="913" t="inlineStr"/>
-      <c r="G8" s="913" t="inlineStr"/>
-      <c r="H8" s="913" t="inlineStr"/>
-      <c r="I8" s="913" t="inlineStr"/>
+      <c r="D8" s="996" t="inlineStr"/>
+      <c r="E8" s="996" t="inlineStr"/>
+      <c r="F8" s="996" t="inlineStr"/>
+      <c r="G8" s="996" t="inlineStr"/>
+      <c r="H8" s="996" t="inlineStr"/>
+      <c r="I8" s="996" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="911" t="inlineStr">
+      <c r="A9" s="995" t="inlineStr">
         <is>
           <t>vs MF</t>
         </is>
       </c>
-      <c r="B9" s="912" t="inlineStr">
+      <c r="B9" s="997" t="inlineStr">
         <is>
           <t>90.4%</t>
         </is>
       </c>
-      <c r="C9" s="912" t="inlineStr">
+      <c r="C9" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D9" s="913" t="inlineStr"/>
-      <c r="E9" s="913" t="inlineStr"/>
-      <c r="F9" s="913" t="inlineStr"/>
-      <c r="G9" s="913" t="inlineStr"/>
-      <c r="H9" s="913" t="inlineStr"/>
-      <c r="I9" s="913" t="inlineStr"/>
+      <c r="D9" s="996" t="inlineStr"/>
+      <c r="E9" s="996" t="inlineStr"/>
+      <c r="F9" s="996" t="inlineStr"/>
+      <c r="G9" s="996" t="inlineStr"/>
+      <c r="H9" s="996" t="inlineStr"/>
+      <c r="I9" s="996" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="908" t="inlineStr">
@@ -29770,73 +30461,73 @@
       <c r="I11" s="910" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="914" t="inlineStr">
+      <c r="A12" s="986" t="inlineStr">
         <is>
           <t>vs MetaIrelia</t>
         </is>
       </c>
-      <c r="B12" s="915" t="inlineStr">
+      <c r="B12" s="988" t="inlineStr">
         <is>
           <t>54.6%</t>
         </is>
       </c>
-      <c r="C12" s="915" t="inlineStr">
+      <c r="C12" s="988" t="inlineStr">
         <is>
           <t>~ CLOSE</t>
         </is>
       </c>
-      <c r="D12" s="916" t="inlineStr"/>
-      <c r="E12" s="916" t="inlineStr"/>
-      <c r="F12" s="916" t="inlineStr"/>
-      <c r="G12" s="916" t="inlineStr"/>
-      <c r="H12" s="916" t="inlineStr"/>
-      <c r="I12" s="916" t="inlineStr"/>
+      <c r="D12" s="987" t="inlineStr"/>
+      <c r="E12" s="987" t="inlineStr"/>
+      <c r="F12" s="987" t="inlineStr"/>
+      <c r="G12" s="987" t="inlineStr"/>
+      <c r="H12" s="987" t="inlineStr"/>
+      <c r="I12" s="987" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="911" t="inlineStr">
+      <c r="A13" s="995" t="inlineStr">
         <is>
           <t>vs Sett</t>
         </is>
       </c>
-      <c r="B13" s="912" t="inlineStr">
+      <c r="B13" s="997" t="inlineStr">
         <is>
           <t>69.0%</t>
         </is>
       </c>
-      <c r="C13" s="912" t="inlineStr">
+      <c r="C13" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D13" s="913" t="inlineStr"/>
-      <c r="E13" s="913" t="inlineStr"/>
-      <c r="F13" s="913" t="inlineStr"/>
-      <c r="G13" s="913" t="inlineStr"/>
-      <c r="H13" s="913" t="inlineStr"/>
-      <c r="I13" s="913" t="inlineStr"/>
+      <c r="D13" s="996" t="inlineStr"/>
+      <c r="E13" s="996" t="inlineStr"/>
+      <c r="F13" s="996" t="inlineStr"/>
+      <c r="G13" s="996" t="inlineStr"/>
+      <c r="H13" s="996" t="inlineStr"/>
+      <c r="I13" s="996" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="911" t="inlineStr">
+      <c r="A14" s="995" t="inlineStr">
         <is>
           <t>vs Voli</t>
         </is>
       </c>
-      <c r="B14" s="912" t="inlineStr">
+      <c r="B14" s="997" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C14" s="912" t="inlineStr">
+      <c r="C14" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D14" s="913" t="inlineStr"/>
-      <c r="E14" s="913" t="inlineStr"/>
-      <c r="F14" s="913" t="inlineStr"/>
-      <c r="G14" s="913" t="inlineStr"/>
-      <c r="H14" s="913" t="inlineStr"/>
-      <c r="I14" s="913" t="inlineStr"/>
+      <c r="D14" s="996" t="inlineStr"/>
+      <c r="E14" s="996" t="inlineStr"/>
+      <c r="F14" s="996" t="inlineStr"/>
+      <c r="G14" s="996" t="inlineStr"/>
+      <c r="H14" s="996" t="inlineStr"/>
+      <c r="I14" s="996" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="906" t="inlineStr">
@@ -29862,15 +30553,15 @@
       </c>
     </row>
     <row r="16" ht="4" customHeight="1">
-      <c r="A16" s="951" t="inlineStr"/>
-      <c r="B16" s="951" t="inlineStr"/>
-      <c r="C16" s="951" t="inlineStr"/>
-      <c r="D16" s="951" t="inlineStr"/>
-      <c r="E16" s="951" t="inlineStr"/>
-      <c r="F16" s="951" t="inlineStr"/>
-      <c r="G16" s="951" t="inlineStr"/>
-      <c r="H16" s="951" t="inlineStr"/>
-      <c r="I16" s="951" t="inlineStr"/>
+      <c r="A16" s="1017" t="inlineStr"/>
+      <c r="B16" s="1017" t="inlineStr"/>
+      <c r="C16" s="1017" t="inlineStr"/>
+      <c r="D16" s="1017" t="inlineStr"/>
+      <c r="E16" s="1017" t="inlineStr"/>
+      <c r="F16" s="1017" t="inlineStr"/>
+      <c r="G16" s="1017" t="inlineStr"/>
+      <c r="H16" s="1017" t="inlineStr"/>
+      <c r="I16" s="1017" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="952" t="inlineStr">
@@ -29900,15 +30591,15 @@
       <c r="I17" s="953" t="inlineStr"/>
     </row>
     <row r="18" ht="4" customHeight="1">
-      <c r="A18" s="951" t="inlineStr"/>
-      <c r="B18" s="951" t="inlineStr"/>
-      <c r="C18" s="951" t="inlineStr"/>
-      <c r="D18" s="951" t="inlineStr"/>
-      <c r="E18" s="951" t="inlineStr"/>
-      <c r="F18" s="951" t="inlineStr"/>
-      <c r="G18" s="951" t="inlineStr"/>
-      <c r="H18" s="951" t="inlineStr"/>
-      <c r="I18" s="951" t="inlineStr"/>
+      <c r="A18" s="1017" t="inlineStr"/>
+      <c r="B18" s="1017" t="inlineStr"/>
+      <c r="C18" s="1017" t="inlineStr"/>
+      <c r="D18" s="1017" t="inlineStr"/>
+      <c r="E18" s="1017" t="inlineStr"/>
+      <c r="F18" s="1017" t="inlineStr"/>
+      <c r="G18" s="1017" t="inlineStr"/>
+      <c r="H18" s="1017" t="inlineStr"/>
+      <c r="I18" s="1017" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="906" t="inlineStr">
@@ -30087,15 +30778,15 @@
       <c r="I26" s="957" t="inlineStr"/>
     </row>
     <row r="27" ht="4" customHeight="1">
-      <c r="A27" s="951" t="inlineStr"/>
-      <c r="B27" s="951" t="inlineStr"/>
-      <c r="C27" s="951" t="inlineStr"/>
-      <c r="D27" s="951" t="inlineStr"/>
-      <c r="E27" s="951" t="inlineStr"/>
-      <c r="F27" s="951" t="inlineStr"/>
-      <c r="G27" s="951" t="inlineStr"/>
-      <c r="H27" s="951" t="inlineStr"/>
-      <c r="I27" s="951" t="inlineStr"/>
+      <c r="A27" s="1017" t="inlineStr"/>
+      <c r="B27" s="1017" t="inlineStr"/>
+      <c r="C27" s="1017" t="inlineStr"/>
+      <c r="D27" s="1017" t="inlineStr"/>
+      <c r="E27" s="1017" t="inlineStr"/>
+      <c r="F27" s="1017" t="inlineStr"/>
+      <c r="G27" s="1017" t="inlineStr"/>
+      <c r="H27" s="1017" t="inlineStr"/>
+      <c r="I27" s="1017" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="906" t="inlineStr">
@@ -30160,42 +30851,42 @@
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="912" t="inlineStr">
+      <c r="A30" s="997" t="inlineStr">
         <is>
           <t>OGN-255</t>
         </is>
       </c>
-      <c r="B30" s="912" t="inlineStr">
+      <c r="B30" s="997" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="C30" s="911" t="inlineStr">
+      <c r="C30" s="995" t="inlineStr">
         <is>
           <t>Legend Zone</t>
         </is>
       </c>
-      <c r="D30" s="911" t="inlineStr">
+      <c r="D30" s="995" t="inlineStr">
         <is>
           <t>Ahri - Nine-Tailed Fox</t>
         </is>
       </c>
-      <c r="E30" s="913" t="inlineStr">
+      <c r="E30" s="996" t="inlineStr">
         <is>
           <t>Calm;Mind</t>
         </is>
       </c>
-      <c r="F30" s="936" t="inlineStr">
+      <c r="F30" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G30" s="936" t="inlineStr">
+      <c r="G30" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H30" s="936" t="inlineStr">
+      <c r="H30" s="998" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -30254,15 +30945,15 @@
       </c>
     </row>
     <row r="32" ht="4" customHeight="1">
-      <c r="A32" s="951" t="inlineStr"/>
-      <c r="B32" s="951" t="inlineStr"/>
-      <c r="C32" s="951" t="inlineStr"/>
-      <c r="D32" s="951" t="inlineStr"/>
-      <c r="E32" s="951" t="inlineStr"/>
-      <c r="F32" s="951" t="inlineStr"/>
-      <c r="G32" s="951" t="inlineStr"/>
-      <c r="H32" s="951" t="inlineStr"/>
-      <c r="I32" s="951" t="inlineStr"/>
+      <c r="A32" s="1017" t="inlineStr"/>
+      <c r="B32" s="1017" t="inlineStr"/>
+      <c r="C32" s="1017" t="inlineStr"/>
+      <c r="D32" s="1017" t="inlineStr"/>
+      <c r="E32" s="1017" t="inlineStr"/>
+      <c r="F32" s="1017" t="inlineStr"/>
+      <c r="G32" s="1017" t="inlineStr"/>
+      <c r="H32" s="1017" t="inlineStr"/>
+      <c r="I32" s="1017" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="906" t="inlineStr">
@@ -30327,40 +31018,40 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="912" t="inlineStr">
+      <c r="A35" s="997" t="inlineStr">
         <is>
           <t>OGN-052</t>
         </is>
       </c>
-      <c r="B35" s="912" t="n">
+      <c r="B35" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="913" t="inlineStr">
+      <c r="C35" s="996" t="inlineStr">
         <is>
           <t>DEFENSE</t>
         </is>
       </c>
-      <c r="D35" s="911" t="inlineStr">
+      <c r="D35" s="995" t="inlineStr">
         <is>
           <t>Stalwart Poro</t>
         </is>
       </c>
-      <c r="E35" s="936" t="inlineStr">
+      <c r="E35" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F35" s="936" t="inlineStr">
+      <c r="F35" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G35" s="936" t="inlineStr">
+      <c r="G35" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H35" s="936" t="inlineStr">
+      <c r="H35" s="998" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30372,40 +31063,40 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="912" t="inlineStr">
+      <c r="A36" s="997" t="inlineStr">
         <is>
           <t>OGN-055</t>
         </is>
       </c>
-      <c r="B36" s="912" t="n">
+      <c r="B36" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="913" t="inlineStr">
+      <c r="C36" s="996" t="inlineStr">
         <is>
           <t>DEFENSE</t>
         </is>
       </c>
-      <c r="D36" s="911" t="inlineStr">
+      <c r="D36" s="995" t="inlineStr">
         <is>
           <t>Wielder of Water</t>
         </is>
       </c>
-      <c r="E36" s="936" t="inlineStr">
+      <c r="E36" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F36" s="936" t="inlineStr">
+      <c r="F36" s="998" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G36" s="936" t="inlineStr">
+      <c r="G36" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H36" s="936" t="inlineStr">
+      <c r="H36" s="998" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30509,20 +31200,22 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="971" t="inlineStr">
         <is>
-          <t>OGN-090</t>
-        </is>
-      </c>
-      <c r="B39" s="971" t="n">
-        <v>1</v>
+          <t>SFD-215</t>
+        </is>
+      </c>
+      <c r="B39" s="971" t="inlineStr">
+        <is>
+          <t>Ravenbloom Conservatory</t>
+        </is>
       </c>
       <c r="C39" s="972" t="inlineStr">
         <is>
-          <t>DEBUFF</t>
+          <t>Battlefield</t>
         </is>
       </c>
       <c r="D39" s="973" t="inlineStr">
         <is>
-          <t>Orb of Regret</t>
+          <t>When you defend here, reveal the top card of your Main Deck. If it's a spell, put it in your hand. Otherwise, recycle it.</t>
         </is>
       </c>
       <c r="E39" s="974" t="inlineStr">
@@ -30554,20 +31247,22 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="971" t="inlineStr">
         <is>
-          <t>OGN-093</t>
-        </is>
-      </c>
-      <c r="B40" s="971" t="n">
-        <v>3</v>
+          <t>OGN-280</t>
+        </is>
+      </c>
+      <c r="B40" s="971" t="inlineStr">
+        <is>
+          <t>Grove of the God-Willow</t>
+        </is>
       </c>
       <c r="C40" s="972" t="inlineStr">
         <is>
-          <t>DEBUFF</t>
+          <t>Battlefield</t>
         </is>
       </c>
       <c r="D40" s="973" t="inlineStr">
         <is>
-          <t>Smoke Screen</t>
+          <t>When you hold here, draw 1.</t>
         </is>
       </c>
       <c r="E40" s="974" t="inlineStr">
@@ -30599,20 +31294,22 @@
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="971" t="inlineStr">
         <is>
-          <t>OGN-095</t>
-        </is>
-      </c>
-      <c r="B41" s="971" t="n">
-        <v>3</v>
+          <t>SFD-209</t>
+        </is>
+      </c>
+      <c r="B41" s="971" t="inlineStr">
+        <is>
+          <t>Forgotten Monument</t>
+        </is>
       </c>
       <c r="C41" s="972" t="inlineStr">
         <is>
-          <t>DEBUFF</t>
+          <t>Battlefield</t>
         </is>
       </c>
       <c r="D41" s="973" t="inlineStr">
         <is>
-          <t>Stupefy</t>
+          <t>Players can't score here until their third turn.</t>
         </is>
       </c>
       <c r="E41" s="974" t="inlineStr">
@@ -30687,36 +31384,36 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="912" t="inlineStr">
+      <c r="A43" s="997" t="inlineStr">
         <is>
           <t>SFD-040</t>
         </is>
       </c>
-      <c r="B43" s="912" t="n">
+      <c r="B43" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="913" t="inlineStr">
+      <c r="C43" s="996" t="inlineStr">
         <is>
           <t>STUN</t>
         </is>
       </c>
-      <c r="D43" s="911" t="inlineStr">
+      <c r="D43" s="995" t="inlineStr">
         <is>
           <t>Thwonk!</t>
         </is>
       </c>
-      <c r="E43" s="936" t="inlineStr">
+      <c r="E43" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F43" s="936" t="inlineStr">
+      <c r="F43" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G43" s="936" t="inlineStr"/>
-      <c r="H43" s="936" t="inlineStr">
+      <c r="G43" s="998" t="inlineStr"/>
+      <c r="H43" s="998" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30728,36 +31425,36 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="912" t="inlineStr">
+      <c r="A44" s="997" t="inlineStr">
         <is>
           <t>SFD-063</t>
         </is>
       </c>
-      <c r="B44" s="912" t="n">
+      <c r="B44" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="913" t="inlineStr">
+      <c r="C44" s="996" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="D44" s="911" t="inlineStr">
+      <c r="D44" s="995" t="inlineStr">
         <is>
           <t>Chemtech Cask</t>
         </is>
       </c>
-      <c r="E44" s="936" t="inlineStr">
+      <c r="E44" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F44" s="936" t="inlineStr">
+      <c r="F44" s="998" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G44" s="936" t="inlineStr"/>
-      <c r="H44" s="936" t="inlineStr">
+      <c r="G44" s="998" t="inlineStr"/>
+      <c r="H44" s="998" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30855,40 +31552,40 @@
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="912" t="inlineStr">
+      <c r="A47" s="997" t="inlineStr">
         <is>
           <t>SFD-071</t>
         </is>
       </c>
-      <c r="B47" s="912" t="n">
+      <c r="B47" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="913" t="inlineStr">
+      <c r="C47" s="996" t="inlineStr">
         <is>
           <t>FINISHER</t>
         </is>
       </c>
-      <c r="D47" s="911" t="inlineStr">
+      <c r="D47" s="995" t="inlineStr">
         <is>
           <t>Breakneck Mech</t>
         </is>
       </c>
-      <c r="E47" s="936" t="inlineStr">
+      <c r="E47" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F47" s="936" t="inlineStr">
+      <c r="F47" s="998" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G47" s="936" t="inlineStr">
+      <c r="G47" s="998" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H47" s="936" t="inlineStr">
+      <c r="H47" s="998" t="inlineStr">
         <is>
           <t>U</t>
         </is>
@@ -30962,15 +31659,15 @@
       <c r="I49" s="902" t="inlineStr"/>
     </row>
     <row r="50" ht="4" customHeight="1">
-      <c r="A50" s="951" t="inlineStr"/>
-      <c r="B50" s="951" t="inlineStr"/>
-      <c r="C50" s="951" t="inlineStr"/>
-      <c r="D50" s="951" t="inlineStr"/>
-      <c r="E50" s="951" t="inlineStr"/>
-      <c r="F50" s="951" t="inlineStr"/>
-      <c r="G50" s="951" t="inlineStr"/>
-      <c r="H50" s="951" t="inlineStr"/>
-      <c r="I50" s="951" t="inlineStr"/>
+      <c r="A50" s="1017" t="inlineStr"/>
+      <c r="B50" s="1017" t="inlineStr"/>
+      <c r="C50" s="1017" t="inlineStr"/>
+      <c r="D50" s="1017" t="inlineStr"/>
+      <c r="E50" s="1017" t="inlineStr"/>
+      <c r="F50" s="1017" t="inlineStr"/>
+      <c r="G50" s="1017" t="inlineStr"/>
+      <c r="H50" s="1017" t="inlineStr"/>
+      <c r="I50" s="1017" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="906" t="inlineStr">
@@ -31035,40 +31732,40 @@
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="912" t="inlineStr">
+      <c r="A53" s="997" t="inlineStr">
         <is>
           <t>SFD-045</t>
         </is>
       </c>
-      <c r="B53" s="912" t="n">
+      <c r="B53" s="997" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="911" t="inlineStr">
+      <c r="C53" s="995" t="inlineStr">
         <is>
           <t>vs Irelia / Removal</t>
         </is>
       </c>
-      <c r="D53" s="911" t="inlineStr">
+      <c r="D53" s="995" t="inlineStr">
         <is>
           <t>Not So Fast</t>
         </is>
       </c>
-      <c r="E53" s="936" t="inlineStr">
+      <c r="E53" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F53" s="936" t="inlineStr">
+      <c r="F53" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G53" s="936" t="inlineStr">
+      <c r="G53" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H53" s="936" t="inlineStr">
+      <c r="H53" s="998" t="inlineStr">
         <is>
           <t>U</t>
         </is>
@@ -31080,40 +31777,40 @@
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
-      <c r="A54" s="912" t="inlineStr">
+      <c r="A54" s="997" t="inlineStr">
         <is>
           <t>OGN-065</t>
         </is>
       </c>
-      <c r="B54" s="912" t="n">
+      <c r="B54" s="997" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="911" t="inlineStr">
+      <c r="C54" s="995" t="inlineStr">
         <is>
           <t>vs Attrition / Control</t>
         </is>
       </c>
-      <c r="D54" s="911" t="inlineStr">
+      <c r="D54" s="995" t="inlineStr">
         <is>
           <t>Wizened Elder</t>
         </is>
       </c>
-      <c r="E54" s="936" t="inlineStr">
+      <c r="E54" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F54" s="936" t="inlineStr">
+      <c r="F54" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G54" s="936" t="inlineStr">
+      <c r="G54" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H54" s="936" t="inlineStr">
+      <c r="H54" s="998" t="inlineStr">
         <is>
           <t>U</t>
         </is>
@@ -31125,40 +31822,40 @@
       </c>
     </row>
     <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="912" t="inlineStr">
+      <c r="A55" s="997" t="inlineStr">
         <is>
           <t>SFD-037</t>
         </is>
       </c>
-      <c r="B55" s="912" t="n">
+      <c r="B55" s="997" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="911" t="inlineStr">
+      <c r="C55" s="995" t="inlineStr">
         <is>
           <t>vs Removal Heavy</t>
         </is>
       </c>
-      <c r="D55" s="911" t="inlineStr">
+      <c r="D55" s="995" t="inlineStr">
         <is>
           <t>Navori Scout</t>
         </is>
       </c>
-      <c r="E55" s="936" t="inlineStr">
+      <c r="E55" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F55" s="936" t="inlineStr">
+      <c r="F55" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G55" s="936" t="inlineStr">
+      <c r="G55" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H55" s="936" t="inlineStr">
+      <c r="H55" s="998" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31260,15 +31957,15 @@
       </c>
     </row>
     <row r="58" ht="4" customHeight="1">
-      <c r="A58" s="951" t="inlineStr"/>
-      <c r="B58" s="951" t="inlineStr"/>
-      <c r="C58" s="951" t="inlineStr"/>
-      <c r="D58" s="951" t="inlineStr"/>
-      <c r="E58" s="951" t="inlineStr"/>
-      <c r="F58" s="951" t="inlineStr"/>
-      <c r="G58" s="951" t="inlineStr"/>
-      <c r="H58" s="951" t="inlineStr"/>
-      <c r="I58" s="951" t="inlineStr"/>
+      <c r="A58" s="1017" t="inlineStr"/>
+      <c r="B58" s="1017" t="inlineStr"/>
+      <c r="C58" s="1017" t="inlineStr"/>
+      <c r="D58" s="1017" t="inlineStr"/>
+      <c r="E58" s="1017" t="inlineStr"/>
+      <c r="F58" s="1017" t="inlineStr"/>
+      <c r="G58" s="1017" t="inlineStr"/>
+      <c r="H58" s="1017" t="inlineStr"/>
+      <c r="I58" s="1017" t="inlineStr"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="906" t="inlineStr">
@@ -31286,7 +31983,7 @@
       <c r="I59" s="902" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="980" t="inlineStr">
+      <c r="A60" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -31296,13 +31993,13 @@
           <t>Smoke Screen and Orb of Regret EXHAUST but ready each Awaken. Use them EVERY turn. Combined with Ahri legend = 3 free -1M effects per turn before you spend any runes.</t>
         </is>
       </c>
-      <c r="C60" s="981" t="inlineStr"/>
-      <c r="D60" s="981" t="inlineStr"/>
-      <c r="E60" s="981" t="inlineStr"/>
-      <c r="F60" s="981" t="inlineStr"/>
-      <c r="G60" s="981" t="inlineStr"/>
-      <c r="H60" s="981" t="inlineStr"/>
-      <c r="I60" s="981" t="inlineStr"/>
+      <c r="C60" s="1010" t="inlineStr"/>
+      <c r="D60" s="1010" t="inlineStr"/>
+      <c r="E60" s="1010" t="inlineStr"/>
+      <c r="F60" s="1010" t="inlineStr"/>
+      <c r="G60" s="1010" t="inlineStr"/>
+      <c r="H60" s="1010" t="inlineStr"/>
+      <c r="I60" s="1010" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="982" t="inlineStr">
@@ -31324,7 +32021,7 @@
       <c r="I61" s="983" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="980" t="inlineStr">
+      <c r="A62" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -31334,13 +32031,13 @@
           <t>Frigid Touch REPEAT 2 = pay 2 more runes to repeat the -2M effect. Total cost 4 runes for -4M. With Eager Apprentice at field: -4M for 3 runes. Their 9M dragon attacks as 5M. Your 5M body holds.</t>
         </is>
       </c>
-      <c r="C62" s="981" t="inlineStr"/>
-      <c r="D62" s="981" t="inlineStr"/>
-      <c r="E62" s="981" t="inlineStr"/>
-      <c r="F62" s="981" t="inlineStr"/>
-      <c r="G62" s="981" t="inlineStr"/>
-      <c r="H62" s="981" t="inlineStr"/>
-      <c r="I62" s="981" t="inlineStr"/>
+      <c r="C62" s="1010" t="inlineStr"/>
+      <c r="D62" s="1010" t="inlineStr"/>
+      <c r="E62" s="1010" t="inlineStr"/>
+      <c r="F62" s="1010" t="inlineStr"/>
+      <c r="G62" s="1010" t="inlineStr"/>
+      <c r="H62" s="1010" t="inlineStr"/>
+      <c r="I62" s="1010" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
       <c r="A63" s="982" t="inlineStr">
@@ -31362,7 +32059,7 @@
       <c r="I63" s="983" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="980" t="inlineStr">
+      <c r="A64" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -31372,13 +32069,13 @@
           <t>Consult the Past: hide it as a HIDDEN card (pay 1 rune). Later, react for free = draw 2 at any time. Hide all 3 copies. Any time opponent taps out or leaves a field open: react = draw 6 total.</t>
         </is>
       </c>
-      <c r="C64" s="981" t="inlineStr"/>
-      <c r="D64" s="981" t="inlineStr"/>
-      <c r="E64" s="981" t="inlineStr"/>
-      <c r="F64" s="981" t="inlineStr"/>
-      <c r="G64" s="981" t="inlineStr"/>
-      <c r="H64" s="981" t="inlineStr"/>
-      <c r="I64" s="981" t="inlineStr"/>
+      <c r="C64" s="1010" t="inlineStr"/>
+      <c r="D64" s="1010" t="inlineStr"/>
+      <c r="E64" s="1010" t="inlineStr"/>
+      <c r="F64" s="1010" t="inlineStr"/>
+      <c r="G64" s="1010" t="inlineStr"/>
+      <c r="H64" s="1010" t="inlineStr"/>
+      <c r="I64" s="1010" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="982" t="inlineStr">
@@ -31400,7 +32097,7 @@
       <c r="I65" s="983" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="980" t="inlineStr">
+      <c r="A66" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -31410,13 +32107,13 @@
           <t>Breakneck Mech needs another Mech to enter ready. Breakneck itself counts as a Mech. Play Production Surge (Mind, SFD-076) from SB: play a 3M Mech token. Then play Breakneck = other Mech exists = enters ready. Hits both fields immediately.</t>
         </is>
       </c>
-      <c r="C66" s="981" t="inlineStr"/>
-      <c r="D66" s="981" t="inlineStr"/>
-      <c r="E66" s="981" t="inlineStr"/>
-      <c r="F66" s="981" t="inlineStr"/>
-      <c r="G66" s="981" t="inlineStr"/>
-      <c r="H66" s="981" t="inlineStr"/>
-      <c r="I66" s="981" t="inlineStr"/>
+      <c r="C66" s="1010" t="inlineStr"/>
+      <c r="D66" s="1010" t="inlineStr"/>
+      <c r="E66" s="1010" t="inlineStr"/>
+      <c r="F66" s="1010" t="inlineStr"/>
+      <c r="G66" s="1010" t="inlineStr"/>
+      <c r="H66" s="1010" t="inlineStr"/>
+      <c r="I66" s="1010" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="982" t="inlineStr">
@@ -31437,6 +32134,22 @@
       <c r="H67" s="983" t="inlineStr"/>
       <c r="I67" s="983" t="inlineStr"/>
     </row>
+    <row r="68" ht="4" customHeight="1">
+      <c r="A68" s="1017" t="inlineStr"/>
+      <c r="B68" s="1017" t="inlineStr"/>
+      <c r="C68" s="1017" t="inlineStr"/>
+      <c r="D68" s="1017" t="inlineStr"/>
+      <c r="E68" s="1017" t="inlineStr"/>
+      <c r="F68" s="1017" t="inlineStr"/>
+      <c r="G68" s="1017" t="inlineStr"/>
+      <c r="H68" s="1017" t="inlineStr"/>
+      <c r="I68" s="1017" t="inlineStr"/>
+    </row>
+    <row r="69" ht="15" customHeight="1"/>
+    <row r="70" ht="18" customHeight="1"/>
+    <row r="71" ht="32" customHeight="1"/>
+    <row r="72" ht="32" customHeight="1"/>
+    <row r="73" ht="32" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31448,7 +32161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31493,15 +32206,15 @@
       <c r="I2" s="950" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
-      <c r="I3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
+      <c r="I3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="952" t="inlineStr">
@@ -31531,15 +32244,15 @@
       </c>
     </row>
     <row r="5" ht="4" customHeight="1">
-      <c r="A5" s="951" t="inlineStr"/>
-      <c r="B5" s="951" t="inlineStr"/>
-      <c r="C5" s="951" t="inlineStr"/>
-      <c r="D5" s="951" t="inlineStr"/>
-      <c r="E5" s="951" t="inlineStr"/>
-      <c r="F5" s="951" t="inlineStr"/>
-      <c r="G5" s="951" t="inlineStr"/>
-      <c r="H5" s="951" t="inlineStr"/>
-      <c r="I5" s="951" t="inlineStr"/>
+      <c r="A5" s="1017" t="inlineStr"/>
+      <c r="B5" s="1017" t="inlineStr"/>
+      <c r="C5" s="1017" t="inlineStr"/>
+      <c r="D5" s="1017" t="inlineStr"/>
+      <c r="E5" s="1017" t="inlineStr"/>
+      <c r="F5" s="1017" t="inlineStr"/>
+      <c r="G5" s="1017" t="inlineStr"/>
+      <c r="H5" s="1017" t="inlineStr"/>
+      <c r="I5" s="1017" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="954" t="inlineStr">
@@ -31582,20 +32295,24 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="958" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>OGN-278</t>
         </is>
       </c>
       <c r="B8" s="959" t="inlineStr">
         <is>
-          <t>BEGINNING</t>
+          <t>Bandle Tree</t>
         </is>
       </c>
       <c r="C8" s="685" t="inlineStr">
         <is>
-          <t>Score held fields. Check opponent's board — identify their biggest threat. That's your Switcheroo target.</t>
-        </is>
-      </c>
-      <c r="D8" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D8" s="957" t="inlineStr">
+        <is>
+          <t>You may hide an additional card here.</t>
+        </is>
+      </c>
       <c r="E8" s="957" t="inlineStr"/>
       <c r="F8" s="957" t="inlineStr"/>
       <c r="G8" s="957" t="inlineStr"/>
@@ -31605,20 +32322,24 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="960" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OGN-284</t>
         </is>
       </c>
       <c r="B9" s="961" t="inlineStr">
         <is>
-          <t>CHANNEL</t>
+          <t>Obelisk of Power</t>
         </is>
       </c>
       <c r="C9" s="685" t="inlineStr">
         <is>
-          <t>Draw Mind+Chaos runes. Hold Gust and Switcheroo as reactions. Do NOT play them proactively — their value is surprise.</t>
-        </is>
-      </c>
-      <c r="D9" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D9" s="957" t="inlineStr">
+        <is>
+          <t>Players channel one additional rune during their first Runic Phase this game.</t>
+        </is>
+      </c>
       <c r="E9" s="957" t="inlineStr"/>
       <c r="F9" s="957" t="inlineStr"/>
       <c r="G9" s="957" t="inlineStr"/>
@@ -31628,20 +32349,24 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="962" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>SFD-220</t>
         </is>
       </c>
       <c r="B10" s="963" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>Treasure Hoard</t>
         </is>
       </c>
       <c r="C10" s="685" t="inlineStr">
         <is>
-          <t>Draw 1. Stacked Deck: look top 3 draw 1. Undercover Agent DEATHKNELL draws 2. Always be drawing.</t>
-        </is>
-      </c>
-      <c r="D10" s="957" t="inlineStr"/>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D10" s="957" t="inlineStr">
+        <is>
+          <t>When you conquer here, you may pay 1 to play a Gold gear token exhausted.</t>
+        </is>
+      </c>
       <c r="E10" s="957" t="inlineStr"/>
       <c r="F10" s="957" t="inlineStr"/>
       <c r="G10" s="957" t="inlineStr"/>
@@ -31718,15 +32443,15 @@
       <c r="I13" s="957" t="inlineStr"/>
     </row>
     <row r="14" ht="4" customHeight="1">
-      <c r="A14" s="951" t="inlineStr"/>
-      <c r="B14" s="951" t="inlineStr"/>
-      <c r="C14" s="951" t="inlineStr"/>
-      <c r="D14" s="951" t="inlineStr"/>
-      <c r="E14" s="951" t="inlineStr"/>
-      <c r="F14" s="951" t="inlineStr"/>
-      <c r="G14" s="951" t="inlineStr"/>
-      <c r="H14" s="951" t="inlineStr"/>
-      <c r="I14" s="951" t="inlineStr"/>
+      <c r="A14" s="1017" t="inlineStr"/>
+      <c r="B14" s="1017" t="inlineStr"/>
+      <c r="C14" s="1017" t="inlineStr"/>
+      <c r="D14" s="1017" t="inlineStr"/>
+      <c r="E14" s="1017" t="inlineStr"/>
+      <c r="F14" s="1017" t="inlineStr"/>
+      <c r="G14" s="1017" t="inlineStr"/>
+      <c r="H14" s="1017" t="inlineStr"/>
+      <c r="I14" s="1017" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="954" t="inlineStr">
@@ -31885,15 +32610,15 @@
       </c>
     </row>
     <row r="19" ht="4" customHeight="1">
-      <c r="A19" s="951" t="inlineStr"/>
-      <c r="B19" s="951" t="inlineStr"/>
-      <c r="C19" s="951" t="inlineStr"/>
-      <c r="D19" s="951" t="inlineStr"/>
-      <c r="E19" s="951" t="inlineStr"/>
-      <c r="F19" s="951" t="inlineStr"/>
-      <c r="G19" s="951" t="inlineStr"/>
-      <c r="H19" s="951" t="inlineStr"/>
-      <c r="I19" s="951" t="inlineStr"/>
+      <c r="A19" s="1017" t="inlineStr"/>
+      <c r="B19" s="1017" t="inlineStr"/>
+      <c r="C19" s="1017" t="inlineStr"/>
+      <c r="D19" s="1017" t="inlineStr"/>
+      <c r="E19" s="1017" t="inlineStr"/>
+      <c r="F19" s="1017" t="inlineStr"/>
+      <c r="G19" s="1017" t="inlineStr"/>
+      <c r="H19" s="1017" t="inlineStr"/>
+      <c r="I19" s="1017" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="954" t="inlineStr">
@@ -32732,15 +33457,15 @@
       <c r="I39" s="948" t="inlineStr"/>
     </row>
     <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="951" t="inlineStr"/>
-      <c r="B40" s="951" t="inlineStr"/>
-      <c r="C40" s="951" t="inlineStr"/>
-      <c r="D40" s="951" t="inlineStr"/>
-      <c r="E40" s="951" t="inlineStr"/>
-      <c r="F40" s="951" t="inlineStr"/>
-      <c r="G40" s="951" t="inlineStr"/>
-      <c r="H40" s="951" t="inlineStr"/>
-      <c r="I40" s="951" t="inlineStr"/>
+      <c r="A40" s="1017" t="inlineStr"/>
+      <c r="B40" s="1017" t="inlineStr"/>
+      <c r="C40" s="1017" t="inlineStr"/>
+      <c r="D40" s="1017" t="inlineStr"/>
+      <c r="E40" s="1017" t="inlineStr"/>
+      <c r="F40" s="1017" t="inlineStr"/>
+      <c r="G40" s="1017" t="inlineStr"/>
+      <c r="H40" s="1017" t="inlineStr"/>
+      <c r="I40" s="1017" t="inlineStr"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="954" t="inlineStr">
@@ -33116,15 +33841,15 @@
       </c>
     </row>
     <row r="50" ht="4" customHeight="1">
-      <c r="A50" s="951" t="inlineStr"/>
-      <c r="B50" s="951" t="inlineStr"/>
-      <c r="C50" s="951" t="inlineStr"/>
-      <c r="D50" s="951" t="inlineStr"/>
-      <c r="E50" s="951" t="inlineStr"/>
-      <c r="F50" s="951" t="inlineStr"/>
-      <c r="G50" s="951" t="inlineStr"/>
-      <c r="H50" s="951" t="inlineStr"/>
-      <c r="I50" s="951" t="inlineStr"/>
+      <c r="A50" s="1017" t="inlineStr"/>
+      <c r="B50" s="1017" t="inlineStr"/>
+      <c r="C50" s="1017" t="inlineStr"/>
+      <c r="D50" s="1017" t="inlineStr"/>
+      <c r="E50" s="1017" t="inlineStr"/>
+      <c r="F50" s="1017" t="inlineStr"/>
+      <c r="G50" s="1017" t="inlineStr"/>
+      <c r="H50" s="1017" t="inlineStr"/>
+      <c r="I50" s="1017" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="954" t="inlineStr">
@@ -33142,7 +33867,7 @@
       <c r="I51" s="948" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="980" t="inlineStr">
+      <c r="A52" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -33152,13 +33877,13 @@
           <t>Switcheroo is a REACTION played from hidden. When their unit attacks and they think they've won — react. Swap their 9M with your 2M. Combat resolves. Their unit dies. Yours survives.</t>
         </is>
       </c>
-      <c r="C52" s="981" t="inlineStr"/>
-      <c r="D52" s="981" t="inlineStr"/>
-      <c r="E52" s="981" t="inlineStr"/>
-      <c r="F52" s="981" t="inlineStr"/>
-      <c r="G52" s="981" t="inlineStr"/>
-      <c r="H52" s="981" t="inlineStr"/>
-      <c r="I52" s="981" t="inlineStr"/>
+      <c r="C52" s="1010" t="inlineStr"/>
+      <c r="D52" s="1010" t="inlineStr"/>
+      <c r="E52" s="1010" t="inlineStr"/>
+      <c r="F52" s="1010" t="inlineStr"/>
+      <c r="G52" s="1010" t="inlineStr"/>
+      <c r="H52" s="1010" t="inlineStr"/>
+      <c r="I52" s="1010" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="982" t="inlineStr">
@@ -33180,7 +33905,7 @@
       <c r="I53" s="983" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="980" t="inlineStr">
+      <c r="A54" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -33190,13 +33915,13 @@
           <t>Mushroom Pouch draws 1 every turn you have a hidden card at a battlefield. Always have at least one facedown card. Stacked Deck + Mushroom Pouch = draw 2-3 per turn cycle.</t>
         </is>
       </c>
-      <c r="C54" s="981" t="inlineStr"/>
-      <c r="D54" s="981" t="inlineStr"/>
-      <c r="E54" s="981" t="inlineStr"/>
-      <c r="F54" s="981" t="inlineStr"/>
-      <c r="G54" s="981" t="inlineStr"/>
-      <c r="H54" s="981" t="inlineStr"/>
-      <c r="I54" s="981" t="inlineStr"/>
+      <c r="C54" s="1010" t="inlineStr"/>
+      <c r="D54" s="1010" t="inlineStr"/>
+      <c r="E54" s="1010" t="inlineStr"/>
+      <c r="F54" s="1010" t="inlineStr"/>
+      <c r="G54" s="1010" t="inlineStr"/>
+      <c r="H54" s="1010" t="inlineStr"/>
+      <c r="I54" s="1010" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="982" t="inlineStr">
@@ -33218,7 +33943,7 @@
       <c r="I55" s="983" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="980" t="inlineStr">
+      <c r="A56" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -33228,13 +33953,13 @@
           <t>Possession targeting: take their LEGEND-SYNERGY unit. Their Yone with 5 gears attached. Their Wildclaw Shaman with 3 buffs. The unit that's been growing all game. Now it's yours.</t>
         </is>
       </c>
-      <c r="C56" s="981" t="inlineStr"/>
-      <c r="D56" s="981" t="inlineStr"/>
-      <c r="E56" s="981" t="inlineStr"/>
-      <c r="F56" s="981" t="inlineStr"/>
-      <c r="G56" s="981" t="inlineStr"/>
-      <c r="H56" s="981" t="inlineStr"/>
-      <c r="I56" s="981" t="inlineStr"/>
+      <c r="C56" s="1010" t="inlineStr"/>
+      <c r="D56" s="1010" t="inlineStr"/>
+      <c r="E56" s="1010" t="inlineStr"/>
+      <c r="F56" s="1010" t="inlineStr"/>
+      <c r="G56" s="1010" t="inlineStr"/>
+      <c r="H56" s="1010" t="inlineStr"/>
+      <c r="I56" s="1010" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="982" t="inlineStr">
@@ -33256,7 +33981,7 @@
       <c r="I57" s="983" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="980" t="inlineStr">
+      <c r="A58" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -33266,13 +33991,13 @@
           <t>Rhasa the Sunderer watch your trash count. By turn 6-7 you've played 8-10 cards. Rhasa costs 2-3. A 10/6 for 2 runes ends games. Don't discard him early — wait for the big turn.</t>
         </is>
       </c>
-      <c r="C58" s="981" t="inlineStr"/>
-      <c r="D58" s="981" t="inlineStr"/>
-      <c r="E58" s="981" t="inlineStr"/>
-      <c r="F58" s="981" t="inlineStr"/>
-      <c r="G58" s="981" t="inlineStr"/>
-      <c r="H58" s="981" t="inlineStr"/>
-      <c r="I58" s="981" t="inlineStr"/>
+      <c r="C58" s="1010" t="inlineStr"/>
+      <c r="D58" s="1010" t="inlineStr"/>
+      <c r="E58" s="1010" t="inlineStr"/>
+      <c r="F58" s="1010" t="inlineStr"/>
+      <c r="G58" s="1010" t="inlineStr"/>
+      <c r="H58" s="1010" t="inlineStr"/>
+      <c r="I58" s="1010" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="982" t="inlineStr">
@@ -33293,6 +34018,22 @@
       <c r="H59" s="983" t="inlineStr"/>
       <c r="I59" s="983" t="inlineStr"/>
     </row>
+    <row r="60" ht="4" customHeight="1">
+      <c r="A60" s="1017" t="inlineStr"/>
+      <c r="B60" s="1017" t="inlineStr"/>
+      <c r="C60" s="1017" t="inlineStr"/>
+      <c r="D60" s="1017" t="inlineStr"/>
+      <c r="E60" s="1017" t="inlineStr"/>
+      <c r="F60" s="1017" t="inlineStr"/>
+      <c r="G60" s="1017" t="inlineStr"/>
+      <c r="H60" s="1017" t="inlineStr"/>
+      <c r="I60" s="1017" t="inlineStr"/>
+    </row>
+    <row r="61" ht="15" customHeight="1"/>
+    <row r="62" ht="18" customHeight="1"/>
+    <row r="63" ht="32" customHeight="1"/>
+    <row r="64" ht="32" customHeight="1"/>
+    <row r="65" ht="32" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45661,37 +46402,37 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="999" t="inlineStr">
+      <c r="A9" s="1008" t="inlineStr">
         <is>
           <t>Teemo</t>
         </is>
       </c>
-      <c r="B9" s="1000" t="inlineStr">
+      <c r="B9" s="1010" t="inlineStr">
         <is>
           <t>Mind+Chaos</t>
         </is>
       </c>
-      <c r="C9" s="1000" t="inlineStr">
+      <c r="C9" s="1010" t="inlineStr">
         <is>
           <t>The Thief — Bounce Steal Swap</t>
         </is>
       </c>
-      <c r="D9" s="1000" t="inlineStr">
+      <c r="D9" s="1010" t="inlineStr">
         <is>
           <t>Teemo - Swift Scout</t>
         </is>
       </c>
-      <c r="E9" s="1001" t="inlineStr">
+      <c r="E9" s="1007" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F9" s="1001" t="inlineStr">
+      <c r="F9" s="1007" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="1002" t="inlineStr">
+      <c r="G9" s="1009" t="inlineStr">
         <is>
           <t>Small buy</t>
         </is>
@@ -71563,7 +72304,7 @@
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="911" t="inlineStr">
+      <c r="A5" s="995" t="inlineStr">
         <is>
           <t>vs Draven</t>
         </is>
@@ -71573,22 +72314,22 @@
           <t>71.2%</t>
         </is>
       </c>
-      <c r="C5" s="912" t="inlineStr">
+      <c r="C5" s="997" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="D5" s="912" t="inlineStr">
+      <c r="D5" s="997" t="inlineStr">
         <is>
           <t>+17.9%</t>
         </is>
       </c>
-      <c r="E5" s="912" t="inlineStr">
+      <c r="E5" s="997" t="inlineStr">
         <is>
           <t>T5.0</t>
         </is>
       </c>
-      <c r="F5" s="360" t="inlineStr">
+      <c r="F5" s="1009" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -71598,7 +72339,7 @@
           <t>✓ PASS</t>
         </is>
       </c>
-      <c r="H5" s="913" t="inlineStr"/>
+      <c r="H5" s="996" t="inlineStr"/>
       <c r="I5" s="112" t="inlineStr">
         <is>
           <t>Brutalizer gives +2M on attach → board crosses 6M by T2-3. Soldiers on field before he scores 5pts.</t>
@@ -71606,7 +72347,7 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="911" t="inlineStr">
+      <c r="A6" s="995" t="inlineStr">
         <is>
           <t>vs Irelia</t>
         </is>
@@ -71616,22 +72357,22 @@
           <t>86.2%</t>
         </is>
       </c>
-      <c r="C6" s="912" t="inlineStr">
+      <c r="C6" s="997" t="inlineStr">
         <is>
           <t>98.3%</t>
         </is>
       </c>
-      <c r="D6" s="912" t="inlineStr">
+      <c r="D6" s="997" t="inlineStr">
         <is>
           <t>+12.1%</t>
         </is>
       </c>
-      <c r="E6" s="912" t="inlineStr">
+      <c r="E6" s="997" t="inlineStr">
         <is>
           <t>T4.1</t>
         </is>
       </c>
-      <c r="F6" s="360" t="inlineStr">
+      <c r="F6" s="1009" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -71641,7 +72382,7 @@
           <t>✓ PASS</t>
         </is>
       </c>
-      <c r="H6" s="913" t="inlineStr"/>
+      <c r="H6" s="996" t="inlineStr"/>
       <c r="I6" s="112" t="inlineStr">
         <is>
           <t>Already passing. Brutalizer makes soldiers Mighty faster → Sovereign attack more devastating.</t>
@@ -71649,7 +72390,7 @@
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="911" t="inlineStr">
+      <c r="A7" s="995" t="inlineStr">
         <is>
           <t>vs Ezreal</t>
         </is>
@@ -71659,22 +72400,22 @@
           <t>85.0%</t>
         </is>
       </c>
-      <c r="C7" s="912" t="inlineStr">
+      <c r="C7" s="997" t="inlineStr">
         <is>
           <t>98.3%</t>
         </is>
       </c>
-      <c r="D7" s="912" t="inlineStr">
+      <c r="D7" s="997" t="inlineStr">
         <is>
           <t>+13.3%</t>
         </is>
       </c>
-      <c r="E7" s="912" t="inlineStr">
+      <c r="E7" s="997" t="inlineStr">
         <is>
           <t>T3.5</t>
         </is>
       </c>
-      <c r="F7" s="360" t="inlineStr">
+      <c r="F7" s="1009" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -71684,7 +72425,7 @@
           <t>✓ PASS</t>
         </is>
       </c>
-      <c r="H7" s="913" t="inlineStr"/>
+      <c r="H7" s="996" t="inlineStr"/>
       <c r="I7" s="112" t="inlineStr">
         <is>
           <t>Already passing. Faster board = scoring starts T2 not T3. Lead insurmountable before T6 combo.</t>
@@ -71749,7 +72490,7 @@
           <t>1.9</t>
         </is>
       </c>
-      <c r="C10" s="980" t="inlineStr">
+      <c r="C10" s="1007" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
@@ -71764,29 +72505,29 @@
           <t>0.50</t>
         </is>
       </c>
-      <c r="F10" s="912" t="inlineStr">
+      <c r="F10" s="997" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="G10" s="936" t="inlineStr">
+      <c r="G10" s="998" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H10" s="912" t="inlineStr">
+      <c r="H10" s="997" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="I10" s="936" t="inlineStr">
+      <c r="I10" s="998" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="980" t="inlineStr">
+      <c r="A11" s="1007" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -71811,22 +72552,22 @@
           <t>1.50</t>
         </is>
       </c>
-      <c r="F11" s="912" t="inlineStr">
+      <c r="F11" s="997" t="inlineStr">
         <is>
           <t>4.70</t>
         </is>
       </c>
-      <c r="G11" s="936" t="inlineStr">
+      <c r="G11" s="998" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H11" s="912" t="inlineStr">
+      <c r="H11" s="997" t="inlineStr">
         <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="I11" s="936" t="inlineStr">
+      <c r="I11" s="998" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
@@ -71838,7 +72579,7 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="B12" s="912" t="inlineStr">
+      <c r="B12" s="997" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -71848,44 +72589,44 @@
           <t>1.9</t>
         </is>
       </c>
-      <c r="D12" s="912" t="inlineStr">
+      <c r="D12" s="997" t="inlineStr">
         <is>
           <t>3.38</t>
         </is>
       </c>
-      <c r="E12" s="936" t="inlineStr">
+      <c r="E12" s="998" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="F12" s="912" t="inlineStr">
+      <c r="F12" s="997" t="inlineStr">
         <is>
           <t>6.47</t>
         </is>
       </c>
-      <c r="G12" s="936" t="inlineStr">
+      <c r="G12" s="998" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="H12" s="912" t="inlineStr">
+      <c r="H12" s="997" t="inlineStr">
         <is>
           <t>7.07</t>
         </is>
       </c>
-      <c r="I12" s="936" t="inlineStr">
+      <c r="I12" s="998" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="980" t="inlineStr">
+      <c r="A13" s="1007" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B13" s="912" t="inlineStr">
+      <c r="B13" s="997" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
@@ -71895,32 +72636,32 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="D13" s="912" t="inlineStr">
+      <c r="D13" s="997" t="inlineStr">
         <is>
           <t>6.06</t>
         </is>
       </c>
-      <c r="E13" s="936" t="inlineStr">
+      <c r="E13" s="998" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="F13" s="912" t="inlineStr">
+      <c r="F13" s="997" t="inlineStr">
         <is>
           <t>8.11</t>
         </is>
       </c>
-      <c r="G13" s="936" t="inlineStr">
+      <c r="G13" s="998" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="H13" s="912" t="inlineStr">
+      <c r="H13" s="997" t="inlineStr">
         <is>
           <t>7.82</t>
         </is>
       </c>
-      <c r="I13" s="936" t="inlineStr">
+      <c r="I13" s="998" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
@@ -71932,59 +72673,59 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="B14" s="912" t="inlineStr">
+      <c r="B14" s="997" t="inlineStr">
         <is>
           <t>24.4</t>
         </is>
       </c>
-      <c r="C14" s="912" t="inlineStr">
+      <c r="C14" s="997" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="D14" s="912" t="inlineStr">
+      <c r="D14" s="997" t="inlineStr">
         <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="E14" s="936" t="inlineStr">
+      <c r="E14" s="998" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="F14" s="912" t="inlineStr">
+      <c r="F14" s="997" t="inlineStr">
         <is>
           <t>6.83</t>
         </is>
       </c>
-      <c r="G14" s="936" t="inlineStr">
+      <c r="G14" s="998" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="H14" s="912" t="inlineStr">
+      <c r="H14" s="997" t="inlineStr">
         <is>
           <t>7.51</t>
         </is>
       </c>
-      <c r="I14" s="936" t="inlineStr">
+      <c r="I14" s="998" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="980" t="inlineStr">
+      <c r="A15" s="1007" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B15" s="912" t="inlineStr">
+      <c r="B15" s="997" t="inlineStr">
         <is>
           <t>28.0</t>
         </is>
       </c>
-      <c r="C15" s="912" t="inlineStr">
+      <c r="C15" s="997" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -71999,22 +72740,22 @@
           <t>9.50</t>
         </is>
       </c>
-      <c r="F15" s="912" t="inlineStr">
+      <c r="F15" s="997" t="inlineStr">
         <is>
           <t>8.06</t>
         </is>
       </c>
-      <c r="G15" s="936" t="inlineStr">
+      <c r="G15" s="998" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="H15" s="912" t="inlineStr">
+      <c r="H15" s="997" t="inlineStr">
         <is>
           <t>6.54</t>
         </is>
       </c>
-      <c r="I15" s="936" t="inlineStr">
+      <c r="I15" s="998" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
@@ -72031,7 +72772,7 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="C16" s="980" t="inlineStr">
+      <c r="C16" s="1007" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -72041,7 +72782,7 @@
           <t>0.00</t>
         </is>
       </c>
-      <c r="E16" s="936" t="inlineStr">
+      <c r="E16" s="998" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
@@ -72092,14 +72833,14 @@
 Unleashed (May 8) likely adds more equipment and token support — this archetype only gets better.</t>
         </is>
       </c>
-      <c r="B18" s="913" t="inlineStr"/>
-      <c r="C18" s="913" t="inlineStr"/>
-      <c r="D18" s="913" t="inlineStr"/>
-      <c r="E18" s="913" t="inlineStr"/>
-      <c r="F18" s="913" t="inlineStr"/>
-      <c r="G18" s="913" t="inlineStr"/>
-      <c r="H18" s="913" t="inlineStr"/>
-      <c r="I18" s="913" t="inlineStr"/>
+      <c r="B18" s="996" t="inlineStr"/>
+      <c r="C18" s="996" t="inlineStr"/>
+      <c r="D18" s="996" t="inlineStr"/>
+      <c r="E18" s="996" t="inlineStr"/>
+      <c r="F18" s="996" t="inlineStr"/>
+      <c r="G18" s="996" t="inlineStr"/>
+      <c r="H18" s="996" t="inlineStr"/>
+      <c r="I18" s="996" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -72165,12 +72906,12 @@
           <t>ENGINE STATUS</t>
         </is>
       </c>
-      <c r="B3" s="912" t="inlineStr">
+      <c r="B3" s="997" t="inlineStr">
         <is>
           <t>Draven AI</t>
         </is>
       </c>
-      <c r="C3" s="915" t="inlineStr">
+      <c r="C3" s="988" t="inlineStr">
         <is>
           <t>Azir AI</t>
         </is>
@@ -72192,7 +72933,7 @@
       <c r="J3" s="833" t="inlineStr"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="834" t="inlineStr">
+      <c r="A4" s="1008" t="inlineStr">
         <is>
           <t>AI Calibration</t>
         </is>
@@ -72217,11 +72958,11 @@
           <t>✗ NEEDS WORK — multi-turn ramp plan not modeled</t>
         </is>
       </c>
-      <c r="F4" s="981" t="inlineStr"/>
-      <c r="G4" s="981" t="inlineStr"/>
-      <c r="H4" s="981" t="inlineStr"/>
-      <c r="I4" s="981" t="inlineStr"/>
-      <c r="J4" s="981" t="inlineStr"/>
+      <c r="F4" s="1010" t="inlineStr"/>
+      <c r="G4" s="1010" t="inlineStr"/>
+      <c r="H4" s="1010" t="inlineStr"/>
+      <c r="I4" s="1010" t="inlineStr"/>
+      <c r="J4" s="1010" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="836" t="inlineStr">
@@ -72280,7 +73021,7 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="834" t="inlineStr">
+      <c r="A8" s="1008" t="inlineStr">
         <is>
           <t>vs Azir</t>
         </is>
@@ -72300,7 +73041,7 @@
           <t>32.6%</t>
         </is>
       </c>
-      <c r="E8" s="912" t="inlineStr">
+      <c r="E8" s="997" t="inlineStr">
         <is>
           <t>67.8%</t>
         </is>
@@ -72310,9 +73051,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="981" t="inlineStr"/>
-      <c r="H8" s="981" t="inlineStr"/>
-      <c r="I8" s="981" t="inlineStr"/>
+      <c r="G8" s="1010" t="inlineStr"/>
+      <c r="H8" s="1010" t="inlineStr"/>
+      <c r="I8" s="1010" t="inlineStr"/>
       <c r="J8" s="97" t="inlineStr">
         <is>
           <t>Our Azir deck. Token flood + Grand Strategem.</t>
@@ -72320,7 +73061,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="834" t="inlineStr">
+      <c r="A9" s="1008" t="inlineStr">
         <is>
           <t>vs Draven</t>
         </is>
@@ -72350,9 +73091,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="981" t="inlineStr"/>
-      <c r="H9" s="981" t="inlineStr"/>
-      <c r="I9" s="981" t="inlineStr"/>
+      <c r="G9" s="1010" t="inlineStr"/>
+      <c r="H9" s="1010" t="inlineStr"/>
+      <c r="I9" s="1010" t="inlineStr"/>
       <c r="J9" s="97" t="inlineStr">
         <is>
           <t>Our Draven deck. Resource domination engine.</t>
@@ -72360,12 +73101,12 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="834" t="inlineStr">
+      <c r="A10" s="1008" t="inlineStr">
         <is>
           <t>vs MF</t>
         </is>
       </c>
-      <c r="B10" s="912" t="inlineStr">
+      <c r="B10" s="997" t="inlineStr">
         <is>
           <t>74.9%</t>
         </is>
@@ -72380,7 +73121,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="912" t="inlineStr">
+      <c r="E10" s="997" t="inlineStr">
         <is>
           <t>87.6%</t>
         </is>
@@ -72390,9 +73131,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="981" t="inlineStr"/>
-      <c r="H10" s="981" t="inlineStr"/>
-      <c r="I10" s="981" t="inlineStr"/>
+      <c r="G10" s="1010" t="inlineStr"/>
+      <c r="H10" s="1010" t="inlineStr"/>
+      <c r="I10" s="1010" t="inlineStr"/>
       <c r="J10" s="97" t="inlineStr">
         <is>
           <t>Our MF deck. AI underrepresents — real MF plays faster.</t>
@@ -72400,12 +73141,12 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="834" t="inlineStr">
+      <c r="A11" s="1008" t="inlineStr">
         <is>
           <t>vs Draven</t>
         </is>
       </c>
-      <c r="B11" s="915" t="inlineStr">
+      <c r="B11" s="988" t="inlineStr">
         <is>
           <t>50.9%</t>
         </is>
@@ -72420,7 +73161,7 @@
           <t>19.6%</t>
         </is>
       </c>
-      <c r="E11" s="912" t="inlineStr">
+      <c r="E11" s="997" t="inlineStr">
         <is>
           <t>68.2%</t>
         </is>
@@ -72430,9 +73171,9 @@
           <t>64.3%</t>
         </is>
       </c>
-      <c r="G11" s="981" t="inlineStr"/>
-      <c r="H11" s="981" t="inlineStr"/>
-      <c r="I11" s="981" t="inlineStr"/>
+      <c r="G11" s="1010" t="inlineStr"/>
+      <c r="H11" s="1010" t="inlineStr"/>
+      <c r="I11" s="1010" t="inlineStr"/>
       <c r="J11" s="97" t="inlineStr">
         <is>
           <t>Real WR: Draven 64.3% (Vegas). Our Draven at 67.6% avg is close.</t>
@@ -72440,12 +73181,12 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="834" t="inlineStr">
+      <c r="A12" s="1008" t="inlineStr">
         <is>
           <t>vs Ezreal</t>
         </is>
       </c>
-      <c r="B12" s="912" t="inlineStr">
+      <c r="B12" s="997" t="inlineStr">
         <is>
           <t>62.1%</t>
         </is>
@@ -72460,7 +73201,7 @@
           <t>3.9%</t>
         </is>
       </c>
-      <c r="E12" s="912" t="inlineStr">
+      <c r="E12" s="997" t="inlineStr">
         <is>
           <t>66.2%</t>
         </is>
@@ -72470,9 +73211,9 @@
           <t>~61%</t>
         </is>
       </c>
-      <c r="G12" s="981" t="inlineStr"/>
-      <c r="H12" s="981" t="inlineStr"/>
-      <c r="I12" s="981" t="inlineStr"/>
+      <c r="G12" s="1010" t="inlineStr"/>
+      <c r="H12" s="1010" t="inlineStr"/>
+      <c r="I12" s="1010" t="inlineStr"/>
       <c r="J12" s="97" t="inlineStr">
         <is>
           <t>Real WR: Ezreal ~61%. Won Bologna. Rising each event.</t>
@@ -72480,12 +73221,12 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="834" t="inlineStr">
+      <c r="A13" s="1008" t="inlineStr">
         <is>
           <t>vs Irelia</t>
         </is>
       </c>
-      <c r="B13" s="915" t="inlineStr">
+      <c r="B13" s="988" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
@@ -72495,12 +73236,12 @@
           <t>1.0%</t>
         </is>
       </c>
-      <c r="D13" s="915" t="inlineStr">
+      <c r="D13" s="988" t="inlineStr">
         <is>
           <t>45.5%</t>
         </is>
       </c>
-      <c r="E13" s="912" t="inlineStr">
+      <c r="E13" s="997" t="inlineStr">
         <is>
           <t>68.4%</t>
         </is>
@@ -72510,9 +73251,9 @@
           <t>~58%</t>
         </is>
       </c>
-      <c r="G13" s="981" t="inlineStr"/>
-      <c r="H13" s="981" t="inlineStr"/>
-      <c r="I13" s="981" t="inlineStr"/>
+      <c r="G13" s="1010" t="inlineStr"/>
+      <c r="H13" s="1010" t="inlineStr"/>
+      <c r="I13" s="1010" t="inlineStr"/>
       <c r="J13" s="97" t="inlineStr">
         <is>
           <t>Real WR: Irelia ~58%. S-tier but never won a regional final.</t>
@@ -72520,12 +73261,12 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="834" t="inlineStr">
+      <c r="A14" s="1008" t="inlineStr">
         <is>
           <t>vs Voli</t>
         </is>
       </c>
-      <c r="B14" s="912" t="inlineStr">
+      <c r="B14" s="997" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -72535,12 +73276,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="912" t="inlineStr">
+      <c r="D14" s="997" t="inlineStr">
         <is>
           <t>99.9%</t>
         </is>
       </c>
-      <c r="E14" s="912" t="inlineStr">
+      <c r="E14" s="997" t="inlineStr">
         <is>
           <t>99.9%</t>
         </is>
@@ -72550,9 +73291,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="981" t="inlineStr"/>
-      <c r="H14" s="981" t="inlineStr"/>
-      <c r="I14" s="981" t="inlineStr"/>
+      <c r="G14" s="1010" t="inlineStr"/>
+      <c r="H14" s="1010" t="inlineStr"/>
+      <c r="I14" s="1010" t="inlineStr"/>
       <c r="J14" s="97" t="inlineStr">
         <is>
           <t>Our Voli deck. AI underrepresents — real Voli ~38-58% vs meta.</t>
@@ -73840,46 +74581,46 @@
       <c r="H23" s="910" t="inlineStr"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="916" t="inlineStr"/>
-      <c r="B24" s="916" t="inlineStr">
+      <c r="A24" s="987" t="inlineStr"/>
+      <c r="B24" s="987" t="inlineStr">
         <is>
           <t>YELLOW = MED — wait for deals</t>
         </is>
       </c>
-      <c r="C24" s="916" t="inlineStr"/>
-      <c r="D24" s="916" t="inlineStr"/>
-      <c r="E24" s="916" t="inlineStr"/>
-      <c r="F24" s="916" t="inlineStr"/>
-      <c r="G24" s="916" t="inlineStr"/>
-      <c r="H24" s="916" t="inlineStr"/>
+      <c r="C24" s="987" t="inlineStr"/>
+      <c r="D24" s="987" t="inlineStr"/>
+      <c r="E24" s="987" t="inlineStr"/>
+      <c r="F24" s="987" t="inlineStr"/>
+      <c r="G24" s="987" t="inlineStr"/>
+      <c r="H24" s="987" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="981" t="inlineStr"/>
-      <c r="B25" s="981" t="inlineStr">
+      <c r="A25" s="1010" t="inlineStr"/>
+      <c r="B25" s="1010" t="inlineStr">
         <is>
           <t>WHITE = LOW — future builds</t>
         </is>
       </c>
-      <c r="C25" s="981" t="inlineStr"/>
-      <c r="D25" s="981" t="inlineStr"/>
-      <c r="E25" s="981" t="inlineStr"/>
-      <c r="F25" s="981" t="inlineStr"/>
-      <c r="G25" s="981" t="inlineStr"/>
-      <c r="H25" s="981" t="inlineStr"/>
+      <c r="C25" s="1010" t="inlineStr"/>
+      <c r="D25" s="1010" t="inlineStr"/>
+      <c r="E25" s="1010" t="inlineStr"/>
+      <c r="F25" s="1010" t="inlineStr"/>
+      <c r="G25" s="1010" t="inlineStr"/>
+      <c r="H25" s="1010" t="inlineStr"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="913" t="inlineStr"/>
-      <c r="B26" s="913" t="inlineStr">
+      <c r="A26" s="996" t="inlineStr"/>
+      <c r="B26" s="996" t="inlineStr">
         <is>
           <t>GREEN = HAVE or BULK buys</t>
         </is>
       </c>
-      <c r="C26" s="913" t="inlineStr"/>
-      <c r="D26" s="913" t="inlineStr"/>
-      <c r="E26" s="913" t="inlineStr"/>
-      <c r="F26" s="913" t="inlineStr"/>
-      <c r="G26" s="913" t="inlineStr"/>
-      <c r="H26" s="913" t="inlineStr"/>
+      <c r="C26" s="996" t="inlineStr"/>
+      <c r="D26" s="996" t="inlineStr"/>
+      <c r="E26" s="996" t="inlineStr"/>
+      <c r="F26" s="996" t="inlineStr"/>
+      <c r="G26" s="996" t="inlineStr"/>
+      <c r="H26" s="996" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -73941,18 +74682,18 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="980" t="n">
+      <c r="A5" s="1007" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="360" t="n">
+      <c r="B5" s="1009" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="834" t="inlineStr">
+      <c r="C5" s="1008" t="inlineStr">
         <is>
           <t>Traveling Merchant / Scrapheap</t>
         </is>
       </c>
-      <c r="D5" s="980" t="inlineStr">
+      <c r="D5" s="1007" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -73987,18 +74728,18 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="980" t="n">
+      <c r="A7" s="1007" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="360" t="n">
+      <c r="B7" s="1009" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="834" t="inlineStr">
+      <c r="C7" s="1008" t="inlineStr">
         <is>
           <t>Draven Vanquisher attacking</t>
         </is>
       </c>
-      <c r="D7" s="980" t="inlineStr">
+      <c r="D7" s="1007" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -74033,18 +74774,18 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="980" t="n">
+      <c r="A9" s="1007" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="360" t="n">
+      <c r="B9" s="1009" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="834" t="inlineStr">
+      <c r="C9" s="1008" t="inlineStr">
         <is>
           <t>Battering Ram (4 cards played)</t>
         </is>
       </c>
-      <c r="D9" s="980" t="inlineStr">
+      <c r="D9" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -74079,18 +74820,18 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="980" t="n">
+      <c r="A11" s="1007" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="360" t="n">
+      <c r="B11" s="1009" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="834" t="inlineStr">
+      <c r="C11" s="1008" t="inlineStr">
         <is>
           <t>COMBO: Ram x3 + Rhasa at 0-3</t>
         </is>
       </c>
-      <c r="D11" s="980" t="inlineStr">
+      <c r="D11" s="1007" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -74140,18 +74881,18 @@
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="980" t="n">
+      <c r="A15" s="1007" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="360" t="n">
+      <c r="B15" s="1009" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="834" t="inlineStr">
+      <c r="C15" s="1008" t="inlineStr">
         <is>
           <t>Guardian Angel (hidden/played)</t>
         </is>
       </c>
-      <c r="D15" s="980" t="inlineStr">
+      <c r="D15" s="1007" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -74186,18 +74927,18 @@
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="980" t="n">
+      <c r="A17" s="1007" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="360" t="n">
+      <c r="B17" s="1009" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="834" t="inlineStr">
+      <c r="C17" s="1008" t="inlineStr">
         <is>
           <t>Irelia - Fervent enters</t>
         </is>
       </c>
-      <c r="D17" s="980" t="inlineStr">
+      <c r="D17" s="1007" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -74232,18 +74973,18 @@
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="980" t="n">
+      <c r="A19" s="1007" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="360" t="n">
+      <c r="B19" s="1009" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="834" t="inlineStr">
+      <c r="C19" s="1008" t="inlineStr">
         <is>
           <t>Irelia + En Garde + Defiant</t>
         </is>
       </c>
-      <c r="D19" s="980" t="inlineStr">
+      <c r="D19" s="1007" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -74278,18 +75019,18 @@
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="980" t="n">
+      <c r="A21" s="1007" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="360" t="n">
+      <c r="B21" s="1009" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="834" t="inlineStr">
+      <c r="C21" s="1008" t="inlineStr">
         <is>
           <t>Draven Audacious enters</t>
         </is>
       </c>
-      <c r="D21" s="980" t="inlineStr">
+      <c r="D21" s="1007" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -74339,18 +75080,18 @@
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="980" t="n">
+      <c r="A25" s="1007" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="360" t="n">
+      <c r="B25" s="1009" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="834" t="inlineStr">
+      <c r="C25" s="1008" t="inlineStr">
         <is>
           <t>Scrapheap / Stacked Deck</t>
         </is>
       </c>
-      <c r="D25" s="980" t="inlineStr">
+      <c r="D25" s="1007" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -74385,18 +75126,18 @@
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="980" t="n">
+      <c r="A27" s="1007" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="360" t="n">
+      <c r="B27" s="1009" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="834" t="inlineStr">
+      <c r="C27" s="1008" t="inlineStr">
         <is>
           <t>Ezreal - Prodigy enters</t>
         </is>
       </c>
-      <c r="D27" s="980" t="inlineStr">
+      <c r="D27" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -74431,18 +75172,18 @@
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="980" t="n">
+      <c r="A29" s="1007" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="360" t="n">
+      <c r="B29" s="1009" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="834" t="inlineStr">
+      <c r="C29" s="1008" t="inlineStr">
         <is>
           <t>Ravenbloom Student + spells</t>
         </is>
       </c>
-      <c r="D29" s="980" t="inlineStr">
+      <c r="D29" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -74477,18 +75218,18 @@
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="980" t="n">
+      <c r="A31" s="1007" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="360" t="n">
+      <c r="B31" s="1009" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="834" t="inlineStr">
+      <c r="C31" s="1008" t="inlineStr">
         <is>
           <t>COMBO flood turn</t>
         </is>
       </c>
-      <c r="D31" s="980" t="inlineStr">
+      <c r="D31" s="1007" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -74510,7 +75251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -74552,14 +75293,14 @@
       <c r="H2" s="671" t="inlineStr"/>
     </row>
     <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="951" t="inlineStr"/>
-      <c r="B3" s="951" t="inlineStr"/>
-      <c r="C3" s="951" t="inlineStr"/>
-      <c r="D3" s="951" t="inlineStr"/>
-      <c r="E3" s="951" t="inlineStr"/>
-      <c r="F3" s="951" t="inlineStr"/>
-      <c r="G3" s="951" t="inlineStr"/>
-      <c r="H3" s="951" t="inlineStr"/>
+      <c r="A3" s="1017" t="inlineStr"/>
+      <c r="B3" s="1017" t="inlineStr"/>
+      <c r="C3" s="1017" t="inlineStr"/>
+      <c r="D3" s="1017" t="inlineStr"/>
+      <c r="E3" s="1017" t="inlineStr"/>
+      <c r="F3" s="1017" t="inlineStr"/>
+      <c r="G3" s="1017" t="inlineStr"/>
+      <c r="H3" s="1017" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="954" t="inlineStr">
@@ -74628,25 +75369,25 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="911" t="inlineStr">
+      <c r="A7" s="995" t="inlineStr">
         <is>
           <t>vs Irelia (meta)</t>
         </is>
       </c>
-      <c r="B7" s="912" t="inlineStr">
+      <c r="B7" s="997" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="C7" s="912" t="inlineStr">
+      <c r="C7" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D7" s="913" t="inlineStr"/>
-      <c r="E7" s="913" t="inlineStr"/>
-      <c r="F7" s="913" t="inlineStr"/>
-      <c r="G7" s="913" t="inlineStr"/>
+      <c r="D7" s="996" t="inlineStr"/>
+      <c r="E7" s="996" t="inlineStr"/>
+      <c r="F7" s="996" t="inlineStr"/>
+      <c r="G7" s="996" t="inlineStr"/>
       <c r="H7" s="112" t="inlineStr">
         <is>
           <t>She protects one unit and double-conquers. Your deck floods 2+ units at fields she can only cover one of. She can't be everywhere.</t>
@@ -74654,25 +75395,25 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="911" t="inlineStr">
+      <c r="A8" s="995" t="inlineStr">
         <is>
           <t>vs Ezreal (meta)</t>
         </is>
       </c>
-      <c r="B8" s="912" t="inlineStr">
+      <c r="B8" s="997" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="C8" s="912" t="inlineStr">
+      <c r="C8" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D8" s="913" t="inlineStr"/>
-      <c r="E8" s="913" t="inlineStr"/>
-      <c r="F8" s="913" t="inlineStr"/>
-      <c r="G8" s="913" t="inlineStr"/>
+      <c r="D8" s="996" t="inlineStr"/>
+      <c r="E8" s="996" t="inlineStr"/>
+      <c r="F8" s="996" t="inlineStr"/>
+      <c r="G8" s="996" t="inlineStr"/>
       <c r="H8" s="112" t="inlineStr">
         <is>
           <t>Reactive draw engine. He needs to target your units twice per turn to draw. Play proactively, he can't keep up with your board pressure.</t>
@@ -74706,25 +75447,25 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="911" t="inlineStr">
+      <c r="A10" s="995" t="inlineStr">
         <is>
           <t>vs Volibear (ours)</t>
         </is>
       </c>
-      <c r="B10" s="912" t="inlineStr">
+      <c r="B10" s="997" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="C10" s="912" t="inlineStr">
+      <c r="C10" s="997" t="inlineStr">
         <is>
           <t>✓ STRONG</t>
         </is>
       </c>
-      <c r="D10" s="913" t="inlineStr"/>
-      <c r="E10" s="913" t="inlineStr"/>
-      <c r="F10" s="913" t="inlineStr"/>
-      <c r="G10" s="913" t="inlineStr"/>
+      <c r="D10" s="996" t="inlineStr"/>
+      <c r="E10" s="996" t="inlineStr"/>
+      <c r="F10" s="996" t="inlineStr"/>
+      <c r="G10" s="996" t="inlineStr"/>
       <c r="H10" s="112" t="inlineStr">
         <is>
           <t>Dragon is 9M. Arrives turn 6. Fast decks score 4-5pts before it lands. Slow decks fall behind waiting for ramp. G2 SB answers the dragon directly.</t>
@@ -74784,14 +75525,14 @@
       </c>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="951" t="inlineStr"/>
-      <c r="B13" s="951" t="inlineStr"/>
-      <c r="C13" s="951" t="inlineStr"/>
-      <c r="D13" s="951" t="inlineStr"/>
-      <c r="E13" s="951" t="inlineStr"/>
-      <c r="F13" s="951" t="inlineStr"/>
-      <c r="G13" s="951" t="inlineStr"/>
-      <c r="H13" s="951" t="inlineStr"/>
+      <c r="A13" s="1017" t="inlineStr"/>
+      <c r="B13" s="1017" t="inlineStr"/>
+      <c r="C13" s="1017" t="inlineStr"/>
+      <c r="D13" s="1017" t="inlineStr"/>
+      <c r="E13" s="1017" t="inlineStr"/>
+      <c r="F13" s="1017" t="inlineStr"/>
+      <c r="G13" s="1017" t="inlineStr"/>
+      <c r="H13" s="1017" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="954" t="inlineStr">
@@ -74962,14 +75703,14 @@
       <c r="H21" s="957" t="inlineStr"/>
     </row>
     <row r="22" ht="4" customHeight="1">
-      <c r="A22" s="951" t="inlineStr"/>
-      <c r="B22" s="951" t="inlineStr"/>
-      <c r="C22" s="951" t="inlineStr"/>
-      <c r="D22" s="951" t="inlineStr"/>
-      <c r="E22" s="951" t="inlineStr"/>
-      <c r="F22" s="951" t="inlineStr"/>
-      <c r="G22" s="951" t="inlineStr"/>
-      <c r="H22" s="951" t="inlineStr"/>
+      <c r="A22" s="1017" t="inlineStr"/>
+      <c r="B22" s="1017" t="inlineStr"/>
+      <c r="C22" s="1017" t="inlineStr"/>
+      <c r="D22" s="1017" t="inlineStr"/>
+      <c r="E22" s="1017" t="inlineStr"/>
+      <c r="F22" s="1017" t="inlineStr"/>
+      <c r="G22" s="1017" t="inlineStr"/>
+      <c r="H22" s="1017" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="954" t="inlineStr">
@@ -75028,37 +75769,37 @@
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="912" t="inlineStr">
+      <c r="A25" s="997" t="inlineStr">
         <is>
           <t>SFD-197</t>
         </is>
       </c>
-      <c r="B25" s="912" t="inlineStr">
+      <c r="B25" s="997" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="C25" s="911" t="inlineStr">
+      <c r="C25" s="995" t="inlineStr">
         <is>
           <t>Legend Zone</t>
         </is>
       </c>
-      <c r="D25" s="911" t="inlineStr">
+      <c r="D25" s="995" t="inlineStr">
         <is>
           <t>Azir - Emperor of the Sands</t>
         </is>
       </c>
-      <c r="E25" s="913" t="inlineStr">
+      <c r="E25" s="996" t="inlineStr">
         <is>
           <t>Calm;Order</t>
         </is>
       </c>
-      <c r="F25" s="936" t="inlineStr">
+      <c r="F25" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G25" s="936" t="inlineStr">
+      <c r="G25" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75070,37 +75811,37 @@
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="915" t="inlineStr">
+      <c r="A26" s="988" t="inlineStr">
         <is>
           <t>SFD-177</t>
         </is>
       </c>
-      <c r="B26" s="915" t="inlineStr">
+      <c r="B26" s="988" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="C26" s="914" t="inlineStr">
+      <c r="C26" s="986" t="inlineStr">
         <is>
           <t>Champion Zone</t>
         </is>
       </c>
-      <c r="D26" s="914" t="inlineStr">
+      <c r="D26" s="986" t="inlineStr">
         <is>
           <t>Azir - Sovereign</t>
         </is>
       </c>
-      <c r="E26" s="916" t="inlineStr">
+      <c r="E26" s="987" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F26" s="897" t="inlineStr">
+      <c r="F26" s="989" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G26" s="897" t="inlineStr">
+      <c r="G26" s="989" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -75112,14 +75853,14 @@
       </c>
     </row>
     <row r="27" ht="4" customHeight="1">
-      <c r="A27" s="951" t="inlineStr"/>
-      <c r="B27" s="951" t="inlineStr"/>
-      <c r="C27" s="951" t="inlineStr"/>
-      <c r="D27" s="951" t="inlineStr"/>
-      <c r="E27" s="951" t="inlineStr"/>
-      <c r="F27" s="951" t="inlineStr"/>
-      <c r="G27" s="951" t="inlineStr"/>
-      <c r="H27" s="951" t="inlineStr"/>
+      <c r="A27" s="1017" t="inlineStr"/>
+      <c r="B27" s="1017" t="inlineStr"/>
+      <c r="C27" s="1017" t="inlineStr"/>
+      <c r="D27" s="1017" t="inlineStr"/>
+      <c r="E27" s="1017" t="inlineStr"/>
+      <c r="F27" s="1017" t="inlineStr"/>
+      <c r="G27" s="1017" t="inlineStr"/>
+      <c r="H27" s="1017" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="954" t="inlineStr">
@@ -75178,35 +75919,35 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="912" t="inlineStr">
+      <c r="A30" s="997" t="inlineStr">
         <is>
           <t>OGN-058</t>
         </is>
       </c>
-      <c r="B30" s="912" t="n">
+      <c r="B30" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="913" t="inlineStr">
+      <c r="C30" s="996" t="inlineStr">
         <is>
           <t>Reaction</t>
         </is>
       </c>
-      <c r="D30" s="911" t="inlineStr">
+      <c r="D30" s="995" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="E30" s="936" t="inlineStr">
+      <c r="E30" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F30" s="936" t="inlineStr">
+      <c r="F30" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G30" s="936" t="inlineStr">
+      <c r="G30" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75218,35 +75959,35 @@
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="915" t="inlineStr">
+      <c r="A31" s="988" t="inlineStr">
         <is>
           <t>OGN-209</t>
         </is>
       </c>
-      <c r="B31" s="915" t="n">
+      <c r="B31" s="988" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="916" t="inlineStr">
+      <c r="C31" s="987" t="inlineStr">
         <is>
           <t>Removal</t>
         </is>
       </c>
-      <c r="D31" s="914" t="inlineStr">
+      <c r="D31" s="986" t="inlineStr">
         <is>
           <t>Cull the Weak</t>
         </is>
       </c>
-      <c r="E31" s="897" t="inlineStr">
+      <c r="E31" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F31" s="897" t="inlineStr">
+      <c r="F31" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G31" s="897" t="inlineStr">
+      <c r="G31" s="989" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75258,35 +75999,35 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="915" t="inlineStr">
+      <c r="A32" s="988" t="inlineStr">
         <is>
           <t>OGN-213</t>
         </is>
       </c>
-      <c r="B32" s="915" t="n">
+      <c r="B32" s="988" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="916" t="inlineStr">
+      <c r="C32" s="987" t="inlineStr">
         <is>
           <t>Body</t>
         </is>
       </c>
-      <c r="D32" s="914" t="inlineStr">
+      <c r="D32" s="986" t="inlineStr">
         <is>
           <t>Hidden Blade</t>
         </is>
       </c>
-      <c r="E32" s="897" t="inlineStr">
+      <c r="E32" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F32" s="897" t="inlineStr">
+      <c r="F32" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G32" s="897" t="inlineStr">
+      <c r="G32" s="989" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75298,35 +76039,35 @@
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="912" t="inlineStr">
+      <c r="A33" s="997" t="inlineStr">
         <is>
           <t>SFD-031</t>
         </is>
       </c>
-      <c r="B33" s="912" t="n">
+      <c r="B33" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="913" t="inlineStr">
+      <c r="C33" s="996" t="inlineStr">
         <is>
           <t>Body</t>
         </is>
       </c>
-      <c r="D33" s="911" t="inlineStr">
+      <c r="D33" s="995" t="inlineStr">
         <is>
           <t>Desert's Call</t>
         </is>
       </c>
-      <c r="E33" s="936" t="inlineStr">
+      <c r="E33" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F33" s="936" t="inlineStr">
+      <c r="F33" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G33" s="936" t="inlineStr"/>
+      <c r="G33" s="998" t="inlineStr"/>
       <c r="H33" s="112" t="inlineStr">
         <is>
           <t>Royal Guard. Play = play a 2M Sand Soldier here. Instant two bodies for one card.</t>
@@ -75334,35 +76075,35 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="912" t="inlineStr">
+      <c r="A34" s="997" t="inlineStr">
         <is>
           <t>SFD-033</t>
         </is>
       </c>
-      <c r="B34" s="912" t="n">
+      <c r="B34" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="913" t="inlineStr">
+      <c r="C34" s="996" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D34" s="911" t="inlineStr">
+      <c r="D34" s="995" t="inlineStr">
         <is>
           <t>Doran's Shield</t>
         </is>
       </c>
-      <c r="E34" s="936" t="inlineStr">
+      <c r="E34" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F34" s="936" t="inlineStr">
+      <c r="F34" s="998" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G34" s="936" t="inlineStr">
+      <c r="G34" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75374,35 +76115,35 @@
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="912" t="inlineStr">
+      <c r="A35" s="997" t="inlineStr">
         <is>
           <t>SFD-034</t>
         </is>
       </c>
-      <c r="B35" s="912" t="n">
+      <c r="B35" s="997" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="913" t="inlineStr">
+      <c r="C35" s="996" t="inlineStr">
         <is>
           <t>Pump</t>
         </is>
       </c>
-      <c r="D35" s="911" t="inlineStr">
+      <c r="D35" s="995" t="inlineStr">
         <is>
           <t>Feral Strength</t>
         </is>
       </c>
-      <c r="E35" s="936" t="inlineStr">
+      <c r="E35" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F35" s="936" t="inlineStr">
+      <c r="F35" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G35" s="936" t="inlineStr">
+      <c r="G35" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75414,35 +76155,35 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="912" t="inlineStr">
+      <c r="A36" s="997" t="inlineStr">
         <is>
           <t>SFD-038</t>
         </is>
       </c>
-      <c r="B36" s="912" t="n">
+      <c r="B36" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="913" t="inlineStr">
+      <c r="C36" s="996" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D36" s="911" t="inlineStr">
+      <c r="D36" s="995" t="inlineStr">
         <is>
           <t>Ribbon Dancer</t>
         </is>
       </c>
-      <c r="E36" s="936" t="inlineStr">
+      <c r="E36" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F36" s="936" t="inlineStr">
+      <c r="F36" s="998" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G36" s="936" t="inlineStr">
+      <c r="G36" s="998" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -75454,35 +76195,35 @@
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="912" t="inlineStr">
+      <c r="A37" s="997" t="inlineStr">
         <is>
           <t>SFD-039</t>
         </is>
       </c>
-      <c r="B37" s="912" t="n">
+      <c r="B37" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="913" t="inlineStr">
+      <c r="C37" s="996" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D37" s="911" t="inlineStr">
+      <c r="D37" s="995" t="inlineStr">
         <is>
           <t>Royal Entourage</t>
         </is>
       </c>
-      <c r="E37" s="936" t="inlineStr">
+      <c r="E37" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F37" s="936" t="inlineStr">
+      <c r="F37" s="998" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G37" s="936" t="inlineStr">
+      <c r="G37" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -75494,35 +76235,35 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="912" t="inlineStr">
+      <c r="A38" s="997" t="inlineStr">
         <is>
           <t>SFD-042</t>
         </is>
       </c>
-      <c r="B38" s="912" t="n">
+      <c r="B38" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="913" t="inlineStr">
+      <c r="C38" s="996" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D38" s="911" t="inlineStr">
+      <c r="D38" s="995" t="inlineStr">
         <is>
           <t>Brutalizer</t>
         </is>
       </c>
-      <c r="E38" s="936" t="inlineStr">
+      <c r="E38" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F38" s="936" t="inlineStr">
+      <c r="F38" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G38" s="936" t="inlineStr"/>
+      <c r="G38" s="998" t="inlineStr"/>
       <c r="H38" s="112" t="inlineStr">
         <is>
           <t>Brutalizer. Equip Calm. +1M base, +2M if attached this turn. Combo with Azir legend trigger.</t>
@@ -75530,35 +76271,35 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="912" t="inlineStr">
+      <c r="A39" s="997" t="inlineStr">
         <is>
           <t>SFD-043</t>
         </is>
       </c>
-      <c r="B39" s="912" t="n">
+      <c r="B39" s="997" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="913" t="inlineStr">
+      <c r="C39" s="996" t="inlineStr">
         <is>
           <t>Body</t>
         </is>
       </c>
-      <c r="D39" s="911" t="inlineStr">
+      <c r="D39" s="995" t="inlineStr">
         <is>
           <t>Emperor's Divide</t>
         </is>
       </c>
-      <c r="E39" s="936" t="inlineStr">
+      <c r="E39" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F39" s="936" t="inlineStr">
+      <c r="F39" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G39" s="936" t="inlineStr"/>
+      <c r="G39" s="998" t="inlineStr"/>
       <c r="H39" s="112" t="inlineStr">
         <is>
           <t>Laurent Duelist. 4/3. ASSAULT 2 = attacks as 5M. Synergizes with Azir equipment flow.</t>
@@ -75566,35 +76307,35 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="912" t="inlineStr">
+      <c r="A40" s="997" t="inlineStr">
         <is>
           <t>SFD-051</t>
         </is>
       </c>
-      <c r="B40" s="912" t="n">
+      <c r="B40" s="997" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="913" t="inlineStr">
+      <c r="C40" s="996" t="inlineStr">
         <is>
           <t>Finisher</t>
         </is>
       </c>
-      <c r="D40" s="911" t="inlineStr">
+      <c r="D40" s="995" t="inlineStr">
         <is>
           <t>Guardian Angel</t>
         </is>
       </c>
-      <c r="E40" s="936" t="inlineStr">
+      <c r="E40" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F40" s="936" t="inlineStr">
+      <c r="F40" s="998" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G40" s="936" t="inlineStr">
+      <c r="G40" s="998" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75606,35 +76347,35 @@
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="915" t="inlineStr">
+      <c r="A41" s="988" t="inlineStr">
         <is>
           <t>SFD-153</t>
         </is>
       </c>
-      <c r="B41" s="915" t="n">
+      <c r="B41" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C41" s="916" t="inlineStr">
+      <c r="C41" s="987" t="inlineStr">
         <is>
           <t>Soldier</t>
         </is>
       </c>
-      <c r="D41" s="914" t="inlineStr">
+      <c r="D41" s="986" t="inlineStr">
         <is>
           <t>Eye of the Herald</t>
         </is>
       </c>
-      <c r="E41" s="897" t="inlineStr">
+      <c r="E41" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F41" s="897" t="inlineStr">
+      <c r="F41" s="989" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G41" s="897" t="inlineStr"/>
+      <c r="G41" s="989" t="inlineStr"/>
       <c r="H41" s="217" t="inlineStr">
         <is>
           <t>Sand Soldier unit token. 2M. Plays from Azir legend free. The core of the strategy.</t>
@@ -75642,35 +76383,35 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="915" t="inlineStr">
+      <c r="A42" s="988" t="inlineStr">
         <is>
           <t>SFD-154</t>
         </is>
       </c>
-      <c r="B42" s="915" t="n">
+      <c r="B42" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="916" t="inlineStr">
+      <c r="C42" s="987" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D42" s="914" t="inlineStr">
+      <c r="D42" s="986" t="inlineStr">
         <is>
           <t>Guards!</t>
         </is>
       </c>
-      <c r="E42" s="897" t="inlineStr">
+      <c r="E42" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F42" s="897" t="inlineStr">
+      <c r="F42" s="989" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G42" s="897" t="inlineStr"/>
+      <c r="G42" s="989" t="inlineStr"/>
       <c r="H42" s="217" t="inlineStr">
         <is>
           <t>B.F. Sword. Equip Order. +3M. Turns any unit into a serious threat.</t>
@@ -75678,35 +76419,35 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="915" t="inlineStr">
+      <c r="A43" s="988" t="inlineStr">
         <is>
           <t>SFD-161</t>
         </is>
       </c>
-      <c r="B43" s="915" t="n">
+      <c r="B43" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="916" t="inlineStr">
+      <c r="C43" s="987" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D43" s="914" t="inlineStr">
+      <c r="D43" s="986" t="inlineStr">
         <is>
           <t>B.F. Sword</t>
         </is>
       </c>
-      <c r="E43" s="897" t="inlineStr">
+      <c r="E43" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F43" s="897" t="inlineStr">
+      <c r="F43" s="989" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G43" s="897" t="inlineStr">
+      <c r="G43" s="989" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -75718,35 +76459,35 @@
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="915" t="inlineStr">
+      <c r="A44" s="988" t="inlineStr">
         <is>
           <t>SFD-163</t>
         </is>
       </c>
-      <c r="B44" s="915" t="n">
+      <c r="B44" s="988" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="916" t="inlineStr">
+      <c r="C44" s="987" t="inlineStr">
         <is>
           <t>Body</t>
         </is>
       </c>
-      <c r="D44" s="914" t="inlineStr">
+      <c r="D44" s="986" t="inlineStr">
         <is>
           <t>Deathgrip</t>
         </is>
       </c>
-      <c r="E44" s="897" t="inlineStr">
+      <c r="E44" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F44" s="897" t="inlineStr">
+      <c r="F44" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G44" s="897" t="inlineStr"/>
+      <c r="G44" s="989" t="inlineStr"/>
       <c r="H44" s="217" t="inlineStr">
         <is>
           <t>Unsung Hero. 2/2. DEATHKNELL if MIGHTY: draw 2. Buff it once, it dies drawing 2 cards.</t>
@@ -75754,35 +76495,35 @@
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="915" t="inlineStr">
+      <c r="A45" s="988" t="inlineStr">
         <is>
           <t>SFD-172</t>
         </is>
       </c>
-      <c r="B45" s="915" t="n">
+      <c r="B45" s="988" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="916" t="inlineStr">
+      <c r="C45" s="987" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D45" s="914" t="inlineStr">
+      <c r="D45" s="986" t="inlineStr">
         <is>
           <t>Sacred Shears</t>
         </is>
       </c>
-      <c r="E45" s="897" t="inlineStr">
+      <c r="E45" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F45" s="897" t="inlineStr">
+      <c r="F45" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G45" s="897" t="inlineStr"/>
+      <c r="G45" s="989" t="inlineStr"/>
       <c r="H45" s="217" t="inlineStr">
         <is>
           <t>Assembly Rig. Equipment + Fury. Recycle + spawn Mech token. Gear engine.</t>
@@ -75790,35 +76531,35 @@
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="912" t="inlineStr">
+      <c r="A46" s="997" t="inlineStr">
         <is>
           <t>SFD-198</t>
         </is>
       </c>
-      <c r="B46" s="912" t="n">
+      <c r="B46" s="997" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="913" t="inlineStr">
+      <c r="C46" s="996" t="inlineStr">
         <is>
           <t>Finisher</t>
         </is>
       </c>
-      <c r="D46" s="911" t="inlineStr">
+      <c r="D46" s="995" t="inlineStr">
         <is>
           <t>Arise!</t>
         </is>
       </c>
-      <c r="E46" s="936" t="inlineStr">
+      <c r="E46" s="998" t="inlineStr">
         <is>
           <t>Calm;Order</t>
         </is>
       </c>
-      <c r="F46" s="936" t="inlineStr">
+      <c r="F46" s="998" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G46" s="936" t="inlineStr"/>
+      <c r="G46" s="998" t="inlineStr"/>
       <c r="H46" s="112" t="inlineStr">
         <is>
           <t>Arise! Epic signature. Play a 2M Sand Soldier for every equipment you control. One card = 3-4 soldiers.</t>
@@ -75842,14 +76583,14 @@
       <c r="H47" s="948" t="inlineStr"/>
     </row>
     <row r="48" ht="4" customHeight="1">
-      <c r="A48" s="951" t="inlineStr"/>
-      <c r="B48" s="951" t="inlineStr"/>
-      <c r="C48" s="951" t="inlineStr"/>
-      <c r="D48" s="951" t="inlineStr"/>
-      <c r="E48" s="951" t="inlineStr"/>
-      <c r="F48" s="951" t="inlineStr"/>
-      <c r="G48" s="951" t="inlineStr"/>
-      <c r="H48" s="951" t="inlineStr"/>
+      <c r="A48" s="1017" t="inlineStr"/>
+      <c r="B48" s="1017" t="inlineStr"/>
+      <c r="C48" s="1017" t="inlineStr"/>
+      <c r="D48" s="1017" t="inlineStr"/>
+      <c r="E48" s="1017" t="inlineStr"/>
+      <c r="F48" s="1017" t="inlineStr"/>
+      <c r="G48" s="1017" t="inlineStr"/>
+      <c r="H48" s="1017" t="inlineStr"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="899" t="inlineStr">
@@ -75870,14 +76611,14 @@
       <c r="H49" s="900" t="inlineStr"/>
     </row>
     <row r="50" ht="4" customHeight="1">
-      <c r="A50" s="951" t="inlineStr"/>
-      <c r="B50" s="951" t="inlineStr"/>
-      <c r="C50" s="951" t="inlineStr"/>
-      <c r="D50" s="951" t="inlineStr"/>
-      <c r="E50" s="951" t="inlineStr"/>
-      <c r="F50" s="951" t="inlineStr"/>
-      <c r="G50" s="951" t="inlineStr"/>
-      <c r="H50" s="951" t="inlineStr"/>
+      <c r="A50" s="1017" t="inlineStr"/>
+      <c r="B50" s="1017" t="inlineStr"/>
+      <c r="C50" s="1017" t="inlineStr"/>
+      <c r="D50" s="1017" t="inlineStr"/>
+      <c r="E50" s="1017" t="inlineStr"/>
+      <c r="F50" s="1017" t="inlineStr"/>
+      <c r="G50" s="1017" t="inlineStr"/>
+      <c r="H50" s="1017" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="954" t="inlineStr">
@@ -75936,35 +76677,35 @@
       </c>
     </row>
     <row r="53" ht="50" customHeight="1">
-      <c r="A53" s="915" t="inlineStr">
+      <c r="A53" s="988" t="inlineStr">
         <is>
           <t>SFD-157</t>
         </is>
       </c>
-      <c r="B53" s="915" t="n">
+      <c r="B53" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="914" t="inlineStr">
+      <c r="C53" s="986" t="inlineStr">
         <is>
           <t>vs Fast Aggro</t>
         </is>
       </c>
-      <c r="D53" s="914" t="inlineStr">
+      <c r="D53" s="986" t="inlineStr">
         <is>
           <t>Royal Guard</t>
         </is>
       </c>
-      <c r="E53" s="897" t="inlineStr">
+      <c r="E53" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F53" s="897" t="inlineStr">
+      <c r="F53" s="989" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G53" s="897" t="inlineStr">
+      <c r="G53" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -75976,35 +76717,35 @@
       </c>
     </row>
     <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="915" t="inlineStr">
+      <c r="A54" s="988" t="inlineStr">
         <is>
           <t>SFD-159</t>
         </is>
       </c>
-      <c r="B54" s="915" t="n">
+      <c r="B54" s="988" t="n">
         <v>3</v>
       </c>
-      <c r="C54" s="914" t="inlineStr">
+      <c r="C54" s="986" t="inlineStr">
         <is>
           <t>vs Control</t>
         </is>
       </c>
-      <c r="D54" s="914" t="inlineStr">
+      <c r="D54" s="986" t="inlineStr">
         <is>
           <t>Trusty Ramhound</t>
         </is>
       </c>
-      <c r="E54" s="897" t="inlineStr">
+      <c r="E54" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F54" s="897" t="inlineStr">
+      <c r="F54" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G54" s="897" t="inlineStr">
+      <c r="G54" s="989" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -76016,35 +76757,35 @@
       </c>
     </row>
     <row r="55" ht="50" customHeight="1">
-      <c r="A55" s="915" t="inlineStr">
+      <c r="A55" s="988" t="inlineStr">
         <is>
           <t>SFD-158</t>
         </is>
       </c>
-      <c r="B55" s="915" t="n">
+      <c r="B55" s="988" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="914" t="inlineStr">
+      <c r="C55" s="986" t="inlineStr">
         <is>
           <t>vs Big Units</t>
         </is>
       </c>
-      <c r="D55" s="914" t="inlineStr">
+      <c r="D55" s="986" t="inlineStr">
         <is>
           <t>Sandshifter</t>
         </is>
       </c>
-      <c r="E55" s="897" t="inlineStr">
+      <c r="E55" s="989" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="F55" s="897" t="inlineStr">
+      <c r="F55" s="989" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G55" s="897" t="inlineStr">
+      <c r="G55" s="989" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -76056,35 +76797,35 @@
       </c>
     </row>
     <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="912" t="inlineStr">
+      <c r="A56" s="997" t="inlineStr">
         <is>
           <t>OGN-065</t>
         </is>
       </c>
-      <c r="B56" s="912" t="n">
+      <c r="B56" s="997" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="911" t="inlineStr">
+      <c r="C56" s="995" t="inlineStr">
         <is>
           <t>vs Reactive Decks</t>
         </is>
       </c>
-      <c r="D56" s="911" t="inlineStr">
+      <c r="D56" s="995" t="inlineStr">
         <is>
           <t>Wizened Elder</t>
         </is>
       </c>
-      <c r="E56" s="936" t="inlineStr">
+      <c r="E56" s="998" t="inlineStr">
         <is>
           <t>Calm</t>
         </is>
       </c>
-      <c r="F56" s="936" t="inlineStr">
+      <c r="F56" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G56" s="936" t="inlineStr">
+      <c r="G56" s="998" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -76096,14 +76837,14 @@
       </c>
     </row>
     <row r="57" ht="4" customHeight="1">
-      <c r="A57" s="951" t="inlineStr"/>
-      <c r="B57" s="951" t="inlineStr"/>
-      <c r="C57" s="951" t="inlineStr"/>
-      <c r="D57" s="951" t="inlineStr"/>
-      <c r="E57" s="951" t="inlineStr"/>
-      <c r="F57" s="951" t="inlineStr"/>
-      <c r="G57" s="951" t="inlineStr"/>
-      <c r="H57" s="951" t="inlineStr"/>
+      <c r="A57" s="1017" t="inlineStr"/>
+      <c r="B57" s="1017" t="inlineStr"/>
+      <c r="C57" s="1017" t="inlineStr"/>
+      <c r="D57" s="1017" t="inlineStr"/>
+      <c r="E57" s="1017" t="inlineStr"/>
+      <c r="F57" s="1017" t="inlineStr"/>
+      <c r="G57" s="1017" t="inlineStr"/>
+      <c r="H57" s="1017" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="954" t="inlineStr">
@@ -76120,7 +76861,7 @@
       <c r="H58" s="948" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="980" t="inlineStr">
+      <c r="A59" s="1007" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -76130,12 +76871,12 @@
           <t>Play equipment every turn to trigger Azir legend. Even cheap 1-cost equipment activates the free soldier. Never skip equipment.</t>
         </is>
       </c>
-      <c r="C59" s="981" t="inlineStr"/>
-      <c r="D59" s="981" t="inlineStr"/>
-      <c r="E59" s="981" t="inlineStr"/>
-      <c r="F59" s="981" t="inlineStr"/>
-      <c r="G59" s="981" t="inlineStr"/>
-      <c r="H59" s="981" t="inlineStr"/>
+      <c r="C59" s="1010" t="inlineStr"/>
+      <c r="D59" s="1010" t="inlineStr"/>
+      <c r="E59" s="1010" t="inlineStr"/>
+      <c r="F59" s="1010" t="inlineStr"/>
+      <c r="G59" s="1010" t="inlineStr"/>
+      <c r="H59" s="1010" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1">
       <c r="A60" s="982" t="inlineStr">
@@ -76156,7 +76897,7 @@
       <c r="H60" s="983" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="980" t="inlineStr">
+      <c r="A61" s="1007" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -76166,12 +76907,12 @@
           <t>Arise! is your biggest turn. Wait until you have 3+ equipment in play. One card makes 3-4 soldiers instantly. Play it when opponent is tapped out.</t>
         </is>
       </c>
-      <c r="C61" s="981" t="inlineStr"/>
-      <c r="D61" s="981" t="inlineStr"/>
-      <c r="E61" s="981" t="inlineStr"/>
-      <c r="F61" s="981" t="inlineStr"/>
-      <c r="G61" s="981" t="inlineStr"/>
-      <c r="H61" s="981" t="inlineStr"/>
+      <c r="C61" s="1010" t="inlineStr"/>
+      <c r="D61" s="1010" t="inlineStr"/>
+      <c r="E61" s="1010" t="inlineStr"/>
+      <c r="F61" s="1010" t="inlineStr"/>
+      <c r="G61" s="1010" t="inlineStr"/>
+      <c r="H61" s="1010" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="982" t="inlineStr">
@@ -76192,7 +76933,7 @@
       <c r="H62" s="983" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="980" t="inlineStr">
+      <c r="A63" s="1007" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -76202,12 +76943,12 @@
           <t>Azir Sovereign moves and swaps with another unit. Move him to a contested field mid-attack. Bring equipment with him. Surprise attacker.</t>
         </is>
       </c>
-      <c r="C63" s="981" t="inlineStr"/>
-      <c r="D63" s="981" t="inlineStr"/>
-      <c r="E63" s="981" t="inlineStr"/>
-      <c r="F63" s="981" t="inlineStr"/>
-      <c r="G63" s="981" t="inlineStr"/>
-      <c r="H63" s="981" t="inlineStr"/>
+      <c r="C63" s="1010" t="inlineStr"/>
+      <c r="D63" s="1010" t="inlineStr"/>
+      <c r="E63" s="1010" t="inlineStr"/>
+      <c r="F63" s="1010" t="inlineStr"/>
+      <c r="G63" s="1010" t="inlineStr"/>
+      <c r="H63" s="1010" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="982" t="inlineStr">
@@ -76228,7 +76969,7 @@
       <c r="H64" s="983" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="980" t="inlineStr">
+      <c r="A65" s="1007" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -76238,12 +76979,12 @@
           <t>Unsung Hero: buff it first with Feral Strength or B.F. Sword. Then let it die in combat. Drawing 2 cards from a unit death is massive.</t>
         </is>
       </c>
-      <c r="C65" s="981" t="inlineStr"/>
-      <c r="D65" s="981" t="inlineStr"/>
-      <c r="E65" s="981" t="inlineStr"/>
-      <c r="F65" s="981" t="inlineStr"/>
-      <c r="G65" s="981" t="inlineStr"/>
-      <c r="H65" s="981" t="inlineStr"/>
+      <c r="C65" s="1010" t="inlineStr"/>
+      <c r="D65" s="1010" t="inlineStr"/>
+      <c r="E65" s="1010" t="inlineStr"/>
+      <c r="F65" s="1010" t="inlineStr"/>
+      <c r="G65" s="1010" t="inlineStr"/>
+      <c r="H65" s="1010" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="982" t="inlineStr">
@@ -76263,6 +77004,140 @@
       <c r="G66" s="983" t="inlineStr"/>
       <c r="H66" s="983" t="inlineStr"/>
     </row>
+    <row r="67" ht="4" customHeight="1">
+      <c r="A67" s="1017" t="inlineStr"/>
+      <c r="B67" s="1017" t="inlineStr"/>
+      <c r="C67" s="1017" t="inlineStr"/>
+      <c r="D67" s="1017" t="inlineStr"/>
+      <c r="E67" s="1017" t="inlineStr"/>
+      <c r="F67" s="1017" t="inlineStr"/>
+      <c r="G67" s="1017" t="inlineStr"/>
+      <c r="H67" s="1017" t="inlineStr"/>
+      <c r="I67" s="1017" t="inlineStr"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="1004" t="inlineStr">
+        <is>
+          <t>BATTLEFIELDS — Choose 2 of These 3 Each Game</t>
+        </is>
+      </c>
+      <c r="B68" s="1005" t="inlineStr"/>
+      <c r="C68" s="1005" t="inlineStr"/>
+      <c r="D68" s="1005" t="inlineStr"/>
+      <c r="E68" s="1005" t="inlineStr"/>
+      <c r="F68" s="1005" t="inlineStr"/>
+      <c r="G68" s="1005" t="inlineStr"/>
+      <c r="H68" s="1005" t="inlineStr"/>
+      <c r="I68" s="1005" t="inlineStr"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="1006" t="inlineStr">
+        <is>
+          <t>Card ID</t>
+        </is>
+      </c>
+      <c r="B69" s="1006" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C69" s="1006" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D69" s="1006" t="inlineStr"/>
+      <c r="E69" s="1006" t="inlineStr"/>
+      <c r="F69" s="1006" t="inlineStr"/>
+      <c r="G69" s="1006" t="inlineStr"/>
+      <c r="H69" s="1006" t="inlineStr"/>
+      <c r="I69" s="1006" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="1007" t="inlineStr">
+        <is>
+          <t>SFD-207</t>
+        </is>
+      </c>
+      <c r="B70" s="1008" t="inlineStr">
+        <is>
+          <t>Emperor's Dais</t>
+        </is>
+      </c>
+      <c r="C70" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D70" s="1010" t="inlineStr"/>
+      <c r="E70" s="1010" t="inlineStr"/>
+      <c r="F70" s="1010" t="inlineStr"/>
+      <c r="G70" s="1010" t="inlineStr"/>
+      <c r="H70" s="1010" t="inlineStr"/>
+      <c r="I70" s="97" t="inlineStr">
+        <is>
+          <t>When you conquer here, you may pay 1 and return a unit you control here to its owner's hand. If you do, play a 2 Might Sand Soldier unit token here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="1007" t="inlineStr">
+        <is>
+          <t>SFD-210</t>
+        </is>
+      </c>
+      <c r="B71" s="1008" t="inlineStr">
+        <is>
+          <t>Hall of Legends</t>
+        </is>
+      </c>
+      <c r="C71" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D71" s="1010" t="inlineStr"/>
+      <c r="E71" s="1010" t="inlineStr"/>
+      <c r="F71" s="1010" t="inlineStr"/>
+      <c r="G71" s="1010" t="inlineStr"/>
+      <c r="H71" s="1010" t="inlineStr"/>
+      <c r="I71" s="97" t="inlineStr">
+        <is>
+          <t>When you conquer here, you may pay 1 to ready your legend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="1007" t="inlineStr">
+        <is>
+          <t>OGN-293</t>
+        </is>
+      </c>
+      <c r="B72" s="1008" t="inlineStr">
+        <is>
+          <t>The Grand Plaza</t>
+        </is>
+      </c>
+      <c r="C72" s="1009" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="D72" s="1010" t="inlineStr"/>
+      <c r="E72" s="1010" t="inlineStr"/>
+      <c r="F72" s="1010" t="inlineStr"/>
+      <c r="G72" s="1010" t="inlineStr"/>
+      <c r="H72" s="1010" t="inlineStr"/>
+      <c r="I72" s="97" t="inlineStr">
+        <is>
+          <t>When you hold here, if you have 7+ units here, you win the game.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
